--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>24759</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>34.1500015258789</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>33.9500007629395</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>25164</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>34.7999992370605</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>33.4500007629395</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>34.2999992370605</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>34.4500007629395</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>14696</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>34.8499984741211</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>35</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -62940,7 +62940,7 @@
         <v>14696</v>
       </c>
       <c r="C2721" t="n">
-        <v>34.8499984741211</v>
+        <v>35</v>
       </c>
       <c r="D2721" t="n">
         <v>34</v>
@@ -62952,6 +62952,29 @@
         <v>35</v>
       </c>
       <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>72828</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>35.4000015258789</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>99351</v>
+        <v>34055</v>
       </c>
       <c r="C2715" t="n">
-        <v>36.1500015258789</v>
+        <v>35.8499984741211</v>
       </c>
       <c r="D2715" t="n">
-        <v>34.1500015258789</v>
+        <v>34.6500015258789</v>
       </c>
       <c r="E2715" t="n">
+        <v>35.8499984741211</v>
+      </c>
+      <c r="F2715" t="n">
         <v>35.2000007629395</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>35.7000007629395</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>158306</v>
+        <v>99351</v>
       </c>
       <c r="C2716" t="n">
-        <v>36.25</v>
+        <v>36.1500015258789</v>
       </c>
       <c r="D2716" t="n">
-        <v>33.4000015258789</v>
+        <v>34.1500015258789</v>
       </c>
       <c r="E2716" t="n">
-        <v>35.9000015258789</v>
+        <v>35.2000007629395</v>
       </c>
       <c r="F2716" t="n">
-        <v>35.75</v>
+        <v>35.7000007629395</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>83284</v>
+        <v>158306</v>
       </c>
       <c r="C2717" t="n">
-        <v>36.75</v>
+        <v>36.25</v>
       </c>
       <c r="D2717" t="n">
-        <v>35.5</v>
+        <v>33.4000015258789</v>
       </c>
       <c r="E2717" t="n">
-        <v>35.5</v>
+        <v>35.9000015258789</v>
       </c>
       <c r="F2717" t="n">
-        <v>36.4500007629395</v>
+        <v>35.75</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>51718</v>
+        <v>83284</v>
       </c>
       <c r="C2718" t="n">
-        <v>36.3499984741211</v>
+        <v>36.75</v>
       </c>
       <c r="D2718" t="n">
-        <v>33.8499984741211</v>
+        <v>35.5</v>
       </c>
       <c r="E2718" t="n">
-        <v>36.3499984741211</v>
+        <v>35.5</v>
       </c>
       <c r="F2718" t="n">
-        <v>33.8499984741211</v>
+        <v>36.4500007629395</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>24759</v>
+        <v>51718</v>
       </c>
       <c r="C2719" t="n">
-        <v>34.5</v>
+        <v>36.3499984741211</v>
       </c>
       <c r="D2719" t="n">
-        <v>33.5</v>
+        <v>33.8499984741211</v>
       </c>
       <c r="E2719" t="n">
-        <v>34.1500015258789</v>
+        <v>36.3499984741211</v>
       </c>
       <c r="F2719" t="n">
-        <v>33.9500007629395</v>
+        <v>33.8499984741211</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>25164</v>
+        <v>24759</v>
       </c>
       <c r="C2720" t="n">
-        <v>34.7999992370605</v>
+        <v>34.5</v>
       </c>
       <c r="D2720" t="n">
-        <v>33.4500007629395</v>
+        <v>33.5</v>
       </c>
       <c r="E2720" t="n">
-        <v>34.2999992370605</v>
+        <v>34.1500015258789</v>
       </c>
       <c r="F2720" t="n">
-        <v>34.4500007629395</v>
+        <v>33.9500007629395</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>14696</v>
+        <v>25164</v>
       </c>
       <c r="C2721" t="n">
-        <v>35</v>
+        <v>34.7999992370605</v>
       </c>
       <c r="D2721" t="n">
-        <v>34</v>
+        <v>33.4500007629395</v>
       </c>
       <c r="E2721" t="n">
-        <v>34</v>
+        <v>34.2999992370605</v>
       </c>
       <c r="F2721" t="n">
-        <v>35</v>
+        <v>34.4500007629395</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>72828</v>
+        <v>14696</v>
       </c>
       <c r="C2722" t="n">
-        <v>36.0999984741211</v>
+        <v>35</v>
       </c>
       <c r="D2722" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2722" t="n">
         <v>35</v>
       </c>
-      <c r="E2722" t="n">
-        <v>35.4000015258789</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>35.7000007629395</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>54673</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>36.2999992370605</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>35.4500007629395</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>35.6500015258789</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>35.5499992370605</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82393503189087</v>
+        <v>6.82393550872803</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G3" t="n">
-        <v>6.73136425018311</v>
+        <v>6.73136377334595</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>6.74458789825439</v>
+        <v>6.74458742141724</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>6.74458789825439</v>
+        <v>6.74458742141724</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G8" t="n">
-        <v>6.70050573348999</v>
+        <v>6.70050525665283</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>6.78867053985596</v>
+        <v>6.7886700630188</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>6.29494857788086</v>
+        <v>6.2949481010437</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>6.07453727722168</v>
+        <v>6.07453632354736</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>6.32580661773682</v>
+        <v>6.3258056640625</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>6.21560144424438</v>
+        <v>6.21560096740723</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>6.53299236297607</v>
+        <v>6.53299331665039</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>6.43601179122925</v>
+        <v>6.43601226806641</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G17" t="n">
-        <v>5.87175941467285</v>
+        <v>5.87175893783569</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>6.62997436523438</v>
+        <v>6.62997388839722</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>6.70050573348999</v>
+        <v>6.70050525665283</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>6.65642404556274</v>
+        <v>6.65642356872559</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>6.21560144424438</v>
+        <v>6.21560096740723</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G26" t="n">
-        <v>5.87175941467285</v>
+        <v>5.87175893783569</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G27" t="n">
-        <v>5.99518918991089</v>
+        <v>5.99519014358521</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87616682052612</v>
+        <v>5.87616777420044</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>6.25968265533447</v>
+        <v>6.25968313217163</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>6.22882461547852</v>
+        <v>6.22882509231567</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G33" t="n">
-        <v>6.3169903755188</v>
+        <v>6.31698942184448</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>6.48450183868408</v>
+        <v>6.4845027923584</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G37" t="n">
-        <v>6.40074634552002</v>
+        <v>6.40074586868286</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>6.36548042297363</v>
+        <v>6.36548089981079</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.125</v>
       </c>
       <c r="G40" t="n">
-        <v>6.28172492980957</v>
+        <v>6.28172397613525</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>6.38311338424683</v>
+        <v>6.38311290740967</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>6.33021402359009</v>
+        <v>6.33021450042725</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>6.43601179122925</v>
+        <v>6.43601226806641</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>6.60793256759644</v>
+        <v>6.60793304443359</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>6.4095630645752</v>
+        <v>6.40956211090088</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>6.4095630645752</v>
+        <v>6.40956211090088</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.2023754119873</v>
+        <v>6.20237636566162</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G48" t="n">
-        <v>6.22000885009766</v>
+        <v>6.2200083732605</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>6.2508659362793</v>
+        <v>6.25086688995361</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>6.25968265533447</v>
+        <v>6.25968313217163</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G51" t="n">
-        <v>6.24205017089844</v>
+        <v>6.2420506477356</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>6.43601179122925</v>
+        <v>6.43601226806641</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>6.41397047042847</v>
+        <v>6.41397094726562</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>6.43601179122925</v>
+        <v>6.43601226806641</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G56" t="n">
-        <v>6.38752031326294</v>
+        <v>6.3875207901001</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G57" t="n">
-        <v>6.42719554901123</v>
+        <v>6.42719602584839</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>6.43160390853882</v>
+        <v>6.43160438537598</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="n">
-        <v>6.17151784896851</v>
+        <v>6.17151927947998</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>6.04367971420288</v>
+        <v>6.04367923736572</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7</v>
       </c>
       <c r="G63" t="n">
-        <v>6.17151784896851</v>
+        <v>6.17151927947998</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.38752031326294</v>
+        <v>6.3875207901001</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>6.26849985122681</v>
+        <v>6.26849937438965</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G68" t="n">
-        <v>6.22441673278809</v>
+        <v>6.22441625595093</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G69" t="n">
-        <v>6.19796848297119</v>
+        <v>6.19796752929688</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G70" t="n">
-        <v>6.2332329750061</v>
+        <v>6.23323392868042</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.125</v>
       </c>
       <c r="G73" t="n">
-        <v>6.28172492980957</v>
+        <v>6.28172397613525</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>6.25968265533447</v>
+        <v>6.25968313217163</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G75" t="n">
-        <v>6.40074634552002</v>
+        <v>6.40074586868286</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42719554901123</v>
+        <v>6.42719602584839</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>6.56384992599487</v>
+        <v>6.56385040283203</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G80" t="n">
-        <v>6.56384992599487</v>
+        <v>6.56385040283203</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G81" t="n">
-        <v>6.45364475250244</v>
+        <v>6.4536452293396</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>6.47127866744995</v>
+        <v>6.47127819061279</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>6.39633846282959</v>
+        <v>6.39633798599243</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>6.4095630645752</v>
+        <v>6.40956211090088</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>6.60761165618896</v>
+        <v>6.60761117935181</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>6.42756700515747</v>
+        <v>6.42756652832031</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>6.51758813858032</v>
+        <v>6.51758861541748</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>6.41856575012207</v>
+        <v>6.41856527328491</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>6.48158025741577</v>
+        <v>6.48157978057861</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>6.34204578399658</v>
+        <v>6.3420467376709</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>6.59410667419434</v>
+        <v>6.59410762786865</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>6.66612529754639</v>
+        <v>6.66612482070923</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G94" t="n">
-        <v>6.57160234451294</v>
+        <v>6.5716028213501</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>6.48158025741577</v>
+        <v>6.48157978057861</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>6.59410667419434</v>
+        <v>6.59410762786865</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G98" t="n">
-        <v>6.67962789535522</v>
+        <v>6.67962884902954</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G99" t="n">
-        <v>6.72463846206665</v>
+        <v>6.72463941574097</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G101" t="n">
-        <v>6.9181866645813</v>
+        <v>6.91818618774414</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.95869636535645</v>
+        <v>6.95869541168213</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>7.29177808761597</v>
+        <v>7.29177856445312</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>8.25</v>
       </c>
       <c r="G106" t="n">
-        <v>7.42681121826172</v>
+        <v>7.42681169509888</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G107" t="n">
-        <v>7.27377271652222</v>
+        <v>7.27377367019653</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G109" t="n">
-        <v>7.22876214981079</v>
+        <v>7.22876167297363</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>7.20175504684448</v>
+        <v>7.20175647735596</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.27377271652222</v>
+        <v>7.27377367019653</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.1972541809082</v>
+        <v>7.19725513458252</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G113" t="n">
-        <v>7.17024803161621</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>7.06672239303589</v>
+        <v>7.06672286987305</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>7.11173439025879</v>
+        <v>7.11173343658447</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.75</v>
       </c>
       <c r="G116" t="n">
-        <v>6.97669982910156</v>
+        <v>6.97670125961304</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>6.93169069290161</v>
+        <v>6.93168973922729</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>6.81466102600098</v>
+        <v>6.81466150283813</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.875</v>
       </c>
       <c r="G120" t="n">
-        <v>7.08922863006592</v>
+        <v>7.08922815322876</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>7.28277587890625</v>
+        <v>7.28277635574341</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>6.97219944000244</v>
+        <v>6.9721999168396</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>6.70663547515869</v>
+        <v>6.70663452148438</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.95869636535645</v>
+        <v>6.95869541168213</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.93169069290161</v>
+        <v>6.93168973922729</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>7.1567440032959</v>
+        <v>7.15674448013306</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>6.83266544342041</v>
+        <v>6.83266592025757</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>6.65262222290039</v>
+        <v>6.65262126922607</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>6.54459619522095</v>
+        <v>6.54459524154663</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>6.60761165618896</v>
+        <v>6.60761117935181</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.57160234451294</v>
+        <v>6.5716028213501</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>6.41856575012207</v>
+        <v>6.41856527328491</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>6.39155769348145</v>
+        <v>6.3915581703186</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>6.72013854980469</v>
+        <v>6.72013807296753</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G141" t="n">
-        <v>6.62561559677124</v>
+        <v>6.62561511993408</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.25</v>
       </c>
       <c r="G142" t="n">
-        <v>6.5265908241272</v>
+        <v>6.52659130096436</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>6.43656921386719</v>
+        <v>6.43656969070435</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>6.40956258773804</v>
+        <v>6.4095630645752</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>6.7291407585144</v>
+        <v>6.72913980484009</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>6.54459619522095</v>
+        <v>6.54459524154663</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.5</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.5</v>
       </c>
       <c r="G149" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G150" t="n">
-        <v>6.68412923812866</v>
+        <v>6.68413019180298</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G152" t="n">
-        <v>6.46357488632202</v>
+        <v>6.46357583999634</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>6.63461637496948</v>
+        <v>6.6346173286438</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>6.81466102600098</v>
+        <v>6.81466150283813</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>6.70663547515869</v>
+        <v>6.70663452148438</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>6.73364162445068</v>
+        <v>6.73364114761353</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G160" t="n">
-        <v>6.85067081451416</v>
+        <v>6.850670337677</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>6.67512798309326</v>
+        <v>6.67512655258179</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>6.72013854980469</v>
+        <v>6.72013807296753</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G164" t="n">
-        <v>6.76064920425415</v>
+        <v>6.76064872741699</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>6.70663547515869</v>
+        <v>6.70663452148438</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G170" t="n">
-        <v>6.77865314483643</v>
+        <v>6.77865266799927</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>6.87767744064331</v>
+        <v>6.87767696380615</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>6.84166812896729</v>
+        <v>6.84166765213013</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>6.95419502258301</v>
+        <v>6.95419549942017</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G177" t="n">
-        <v>7.1567440032959</v>
+        <v>7.15674448013306</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20175504684448</v>
+        <v>7.20175647735596</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>7.1567440032959</v>
+        <v>7.15674448013306</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G180" t="n">
-        <v>7.17024803161621</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G183" t="n">
-        <v>6.98570251464844</v>
+        <v>6.98570394515991</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G184" t="n">
-        <v>6.94969367980957</v>
+        <v>6.94969320297241</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G185" t="n">
-        <v>6.94969367980957</v>
+        <v>6.94969320297241</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>6.94969367980957</v>
+        <v>6.94969320297241</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>6.93169069290161</v>
+        <v>6.93168973922729</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G188" t="n">
-        <v>6.87767744064331</v>
+        <v>6.87767696380615</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G190" t="n">
-        <v>6.60761165618896</v>
+        <v>6.60761117935181</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>6.62561559677124</v>
+        <v>6.62561511993408</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.5</v>
       </c>
       <c r="G194" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G198" t="n">
-        <v>6.96319770812988</v>
+        <v>6.96319723129272</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G199" t="n">
-        <v>7.16574764251709</v>
+        <v>7.16574716567993</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8</v>
       </c>
       <c r="G200" t="n">
-        <v>7.20175504684448</v>
+        <v>7.20175647735596</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>7.12973785400391</v>
+        <v>7.12973833084106</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>7.18375158309937</v>
+        <v>7.18375110626221</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>7.20175504684448</v>
+        <v>7.20175647735596</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>7.27377271652222</v>
+        <v>7.27377367019653</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>7.35479259490967</v>
+        <v>7.35479354858398</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G216" t="n">
-        <v>7.19275283813477</v>
+        <v>7.19275379180908</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G217" t="n">
-        <v>7.21976089477539</v>
+        <v>7.21975994110107</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G218" t="n">
-        <v>7.1567440032959</v>
+        <v>7.15674448013306</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>7.16124582290649</v>
+        <v>7.16124629974365</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G220" t="n">
-        <v>7.17024803161621</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G222" t="n">
-        <v>7.34128999710083</v>
+        <v>7.34128952026367</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>7.06672239303589</v>
+        <v>7.06672286987305</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G225" t="n">
-        <v>6.85517072677612</v>
+        <v>6.85517120361328</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.5</v>
       </c>
       <c r="G226" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G228" t="n">
-        <v>7.15224409103394</v>
+        <v>7.15224361419678</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>6.88667964935303</v>
+        <v>6.88667869567871</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>6.87767744064331</v>
+        <v>6.87767696380615</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>7.11173439025879</v>
+        <v>7.11173343658447</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>7.11173439025879</v>
+        <v>7.11173343658447</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>7.20175504684448</v>
+        <v>7.20175647735596</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8</v>
       </c>
       <c r="G234" t="n">
-        <v>7.20175504684448</v>
+        <v>7.20175647735596</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G235" t="n">
-        <v>7.1567440032959</v>
+        <v>7.15674448013306</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G236" t="n">
-        <v>6.94969367980957</v>
+        <v>6.94969320297241</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G237" t="n">
-        <v>7.21976089477539</v>
+        <v>7.21975994110107</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8</v>
       </c>
       <c r="G238" t="n">
-        <v>7.20175504684448</v>
+        <v>7.20175647735596</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G239" t="n">
-        <v>7.15224409103394</v>
+        <v>7.15224361419678</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G240" t="n">
-        <v>7.1567440032959</v>
+        <v>7.15674448013306</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G241" t="n">
-        <v>7.4898247718811</v>
+        <v>7.48982572555542</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G242" t="n">
-        <v>7.44931507110596</v>
+        <v>7.44931602478027</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>7.17024803161621</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76064920425415</v>
+        <v>6.76064872741699</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G246" t="n">
-        <v>7.15224409103394</v>
+        <v>7.15224361419678</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>7.38179874420166</v>
+        <v>7.38179922103882</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G248" t="n">
-        <v>7.38179874420166</v>
+        <v>7.38179922103882</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>7.24676704406738</v>
+        <v>7.24676656723022</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>7.38179874420166</v>
+        <v>7.38179922103882</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>7.57984781265259</v>
+        <v>7.57984828948975</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G252" t="n">
-        <v>7.63386154174805</v>
+        <v>7.63386011123657</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>7.69687700271606</v>
+        <v>7.69687604904175</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>7.69687700271606</v>
+        <v>7.69687604904175</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.5</v>
       </c>
       <c r="G255" t="n">
-        <v>7.65186643600464</v>
+        <v>7.65186548233032</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>7.64736413955688</v>
+        <v>7.64736461639404</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G257" t="n">
-        <v>7.60685443878174</v>
+        <v>7.60685396194458</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G258" t="n">
-        <v>7.74188756942749</v>
+        <v>7.74188709259033</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G259" t="n">
-        <v>7.9399356842041</v>
+        <v>7.93993616104126</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G260" t="n">
-        <v>8.30902481079102</v>
+        <v>8.30902576446533</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G261" t="n">
-        <v>8.38104248046875</v>
+        <v>8.38104438781738</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G262" t="n">
-        <v>8.41705226898193</v>
+        <v>8.41705417633057</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G264" t="n">
-        <v>8.3450345993042</v>
+        <v>8.34503269195557</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G265" t="n">
-        <v>8.37654113769531</v>
+        <v>8.37654209136963</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>8.21000194549561</v>
+        <v>8.21000003814697</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G270" t="n">
-        <v>8.30452442169189</v>
+        <v>8.30452632904053</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G272" t="n">
-        <v>8.29552364349365</v>
+        <v>8.29552173614502</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>8.33153247833252</v>
+        <v>8.33153057098389</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.34053516387939</v>
+        <v>8.34053421020508</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.43505573272705</v>
+        <v>8.43505668640137</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>8.26851654052734</v>
+        <v>8.26851558685303</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.30452442169189</v>
+        <v>8.30452632904053</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.23700714111328</v>
+        <v>8.2370080947876</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>8.17399215698242</v>
+        <v>8.17399311065674</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G285" t="n">
-        <v>8.04346084594727</v>
+        <v>8.04346179962158</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>8.37203979492188</v>
+        <v>8.37204074859619</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G290" t="n">
-        <v>8.44855880737305</v>
+        <v>8.44855976104736</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G291" t="n">
-        <v>8.37203979492188</v>
+        <v>8.37204074859619</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G292" t="n">
-        <v>8.39004516601562</v>
+        <v>8.39004707336426</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.37203979492188</v>
+        <v>8.37204074859619</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G295" t="n">
-        <v>8.19649696350098</v>
+        <v>8.19649791717529</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G296" t="n">
-        <v>8.24150943756104</v>
+        <v>8.24151039123535</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G297" t="n">
-        <v>7.99844884872437</v>
+        <v>7.99844980239868</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9</v>
       </c>
       <c r="G298" t="n">
-        <v>8.10197639465332</v>
+        <v>8.101975440979</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>8.17399215698242</v>
+        <v>8.17399311065674</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G303" t="n">
-        <v>8.37203979492188</v>
+        <v>8.37204074859619</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.38104248046875</v>
+        <v>8.38104438781738</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.37203979492188</v>
+        <v>8.37204074859619</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>8.3990478515625</v>
+        <v>8.39904880523682</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>8.37203979492188</v>
+        <v>8.37204074859619</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>9.18223762512207</v>
+        <v>9.18223857879639</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G313" t="n">
-        <v>9.12822723388672</v>
+        <v>9.12822532653809</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>9.17323589324951</v>
+        <v>9.1732349395752</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G317" t="n">
-        <v>9.19124031066895</v>
+        <v>9.19123935699463</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10</v>
       </c>
       <c r="G321" t="n">
-        <v>9.00219440460205</v>
+        <v>9.00219535827637</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10</v>
       </c>
       <c r="G322" t="n">
-        <v>9.00219440460205</v>
+        <v>9.00219535827637</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G323" t="n">
-        <v>9.18223762512207</v>
+        <v>9.18223857879639</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>9.0922155380249</v>
+        <v>9.09221744537354</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>9.18223762512207</v>
+        <v>9.18223857879639</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>9.18223762512207</v>
+        <v>9.18223857879639</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G327" t="n">
-        <v>9.19124031066895</v>
+        <v>9.19123935699463</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>9.31727313995361</v>
+        <v>9.3172721862793</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G330" t="n">
-        <v>9.51531887054443</v>
+        <v>9.51532077789307</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>9.43429851531982</v>
+        <v>9.43430042266846</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G334" t="n">
-        <v>10.1724815368652</v>
+        <v>10.1724796295166</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>10.1724815368652</v>
+        <v>10.1724796295166</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>12</v>
       </c>
       <c r="G338" t="n">
-        <v>10.8026342391968</v>
+        <v>10.8026332855225</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G339" t="n">
-        <v>10.7666244506836</v>
+        <v>10.7666254043579</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G340" t="n">
-        <v>10.8656492233276</v>
+        <v>10.8656482696533</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>10.8926553726196</v>
+        <v>10.8926572799683</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G342" t="n">
-        <v>10.6946077346802</v>
+        <v>10.6946058273315</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>10.6675996780396</v>
+        <v>10.6676006317139</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>10.7126092910767</v>
+        <v>10.7126111984253</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>9.97381114959717</v>
+        <v>9.97381019592285</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G356" t="n">
-        <v>10.4725008010864</v>
+        <v>10.4724998474121</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G357" t="n">
-        <v>10.4725008010864</v>
+        <v>10.4724998474121</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>10.7033777236938</v>
+        <v>10.7033767700195</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>11.0358362197876</v>
+        <v>11.0358371734619</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.5</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5437622070312</v>
+        <v>11.5437631607056</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G370" t="n">
-        <v>11.1004838943481</v>
+        <v>11.1004829406738</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G371" t="n">
-        <v>10.9896602630615</v>
+        <v>10.9896612167358</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>10.7126092910767</v>
+        <v>10.7126121520996</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>10.9434862136841</v>
+        <v>10.9434881210327</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>10.9434862136841</v>
+        <v>10.9434881210327</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>10.9434862136841</v>
+        <v>10.9434881210327</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>10.5279102325439</v>
+        <v>10.5279111862183</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12</v>
       </c>
       <c r="G381" t="n">
-        <v>11.0820121765137</v>
+        <v>11.082010269165</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>11.0173683166504</v>
+        <v>11.0173664093018</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G383" t="n">
-        <v>11.4421758651733</v>
+        <v>11.442177772522</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G384" t="n">
-        <v>11.0266008377075</v>
+        <v>11.0266017913818</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>10.8973112106323</v>
+        <v>10.8973121643066</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G386" t="n">
-        <v>11.405237197876</v>
+        <v>11.4052381515503</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>11.3590631484985</v>
+        <v>11.3590621948242</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>12.0516872406006</v>
+        <v>12.0516881942749</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G393" t="n">
-        <v>12.4764986038208</v>
+        <v>12.4764995574951</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G394" t="n">
-        <v>12.6242599487305</v>
+        <v>12.6242580413818</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.75</v>
       </c>
       <c r="G395" t="n">
-        <v>12.6981382369995</v>
+        <v>12.6981391906738</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7443151473999</v>
+        <v>12.7443141937256</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G398" t="n">
-        <v>12.6796684265137</v>
+        <v>12.6796674728394</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>12.494969367981</v>
+        <v>12.4949684143066</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G400" t="n">
-        <v>12.5319089889526</v>
+        <v>12.5319080352783</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.5134401321411</v>
+        <v>12.5134382247925</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>12.4210872650146</v>
+        <v>12.4210891723633</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G403" t="n">
-        <v>12.4487934112549</v>
+        <v>12.4487953186035</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G405" t="n">
-        <v>12.494969367981</v>
+        <v>12.4949684143066</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6334934234619</v>
+        <v>12.6334943771362</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G408" t="n">
-        <v>12.5042028427124</v>
+        <v>12.5042037963867</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G409" t="n">
-        <v>12.1348028182983</v>
+        <v>12.1348037719727</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>12.3749122619629</v>
+        <v>12.3749132156372</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G413" t="n">
-        <v>12.3195018768311</v>
+        <v>12.3195037841797</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>11.839282989502</v>
+        <v>11.8392848968506</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13</v>
       </c>
       <c r="G417" t="n">
-        <v>12.0055122375488</v>
+        <v>12.0055131912231</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2640943527222</v>
+        <v>12.2640924453735</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>11.9131622314453</v>
+        <v>11.9131631851196</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="n">
-        <v>11.839282989502</v>
+        <v>11.8392848968506</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>13</v>
       </c>
       <c r="G426" t="n">
-        <v>12.0055122375488</v>
+        <v>12.0055131912231</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>12.3749122619629</v>
+        <v>12.3749132156372</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>12.3749122619629</v>
+        <v>12.3749132156372</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G430" t="n">
-        <v>12.3933839797974</v>
+        <v>12.3933849334717</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G431" t="n">
-        <v>12.3010339736938</v>
+        <v>12.3010320663452</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3287391662598</v>
+        <v>12.3287382125854</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13</v>
       </c>
       <c r="G438" t="n">
-        <v>12.0055122375488</v>
+        <v>12.0055131912231</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G441" t="n">
-        <v>12.4026193618774</v>
+        <v>12.4026184082031</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G446" t="n">
-        <v>12.2548599243164</v>
+        <v>12.2548589706421</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G448" t="n">
-        <v>12.2548599243164</v>
+        <v>12.2548589706421</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>12.3287391662598</v>
+        <v>12.3287382125854</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G451" t="n">
-        <v>12.0147485733032</v>
+        <v>12.0147476196289</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G452" t="n">
-        <v>11.9778089523315</v>
+        <v>11.9778079986572</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G453" t="n">
-        <v>11.3960027694702</v>
+        <v>11.3960018157959</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.5899381637573</v>
+        <v>11.5899391174316</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7469339370728</v>
+        <v>11.7469320297241</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G456" t="n">
-        <v>11.5899381637573</v>
+        <v>11.5899391174316</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G457" t="n">
-        <v>11.6176433563232</v>
+        <v>11.6176424026489</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G459" t="n">
-        <v>11.700756072998</v>
+        <v>11.700758934021</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G460" t="n">
-        <v>11.8762216567993</v>
+        <v>11.8762226104736</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G461" t="n">
-        <v>11.5899381637573</v>
+        <v>11.5899391174316</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9131622314453</v>
+        <v>11.9131631851196</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>11.8208141326904</v>
+        <v>11.8208131790161</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G469" t="n">
-        <v>11.839282989502</v>
+        <v>11.8392848968506</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>12.1440372467041</v>
+        <v>12.1440382003784</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>11.8208141326904</v>
+        <v>11.8208131790161</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7469339370728</v>
+        <v>11.7469320297241</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G476" t="n">
-        <v>11.7469339370728</v>
+        <v>11.7469320297241</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G477" t="n">
-        <v>11.7192277908325</v>
+        <v>11.7192268371582</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G478" t="n">
-        <v>11.7469339370728</v>
+        <v>11.7469320297241</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G479" t="n">
-        <v>11.6730527877808</v>
+        <v>11.6730518341064</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>11.5899381637573</v>
+        <v>11.5899391174316</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G481" t="n">
-        <v>11.146656036377</v>
+        <v>11.1466579437256</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G482" t="n">
-        <v>11.2482433319092</v>
+        <v>11.2482423782349</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G483" t="n">
-        <v>11.146656036377</v>
+        <v>11.1466579437256</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G484" t="n">
-        <v>11.118953704834</v>
+        <v>11.1189517974854</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>11.5437622070312</v>
+        <v>11.5437631607056</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G487" t="n">
-        <v>11.4237060546875</v>
+        <v>11.4237070083618</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>11.405237197876</v>
+        <v>11.4052381515503</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>11.4421758651733</v>
+        <v>11.442177772522</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>11.405237197876</v>
+        <v>11.4052381515503</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G492" t="n">
-        <v>11.5345268249512</v>
+        <v>11.5345287322998</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G497" t="n">
-        <v>11.8115768432617</v>
+        <v>11.8115787506104</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.8208141326904</v>
+        <v>11.8208131790161</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.097864151001</v>
+        <v>12.0978631973267</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.9593362808228</v>
+        <v>11.9593372344971</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>11.8669881820679</v>
+        <v>11.8669891357422</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G503" t="n">
-        <v>11.6730527877808</v>
+        <v>11.6730518341064</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>13</v>
       </c>
       <c r="G504" t="n">
-        <v>12.0055122375488</v>
+        <v>12.0055131912231</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>12.097864151001</v>
+        <v>12.0978631973267</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>12.1440372467041</v>
+        <v>12.1440382003784</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G507" t="n">
-        <v>12.3195018768311</v>
+        <v>12.3195037841797</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>12.3749122619629</v>
+        <v>12.3749132156372</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G510" t="n">
-        <v>12.3933839797974</v>
+        <v>12.3933849334717</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G512" t="n">
-        <v>12.4210872650146</v>
+        <v>12.4210891723633</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G513" t="n">
-        <v>12.3933839797974</v>
+        <v>12.3933849334717</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>12.3749122619629</v>
+        <v>12.3749132156372</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G515" t="n">
-        <v>12.3933839797974</v>
+        <v>12.3933849334717</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G516" t="n">
-        <v>12.4487934112549</v>
+        <v>12.4487953186035</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G517" t="n">
-        <v>12.8736019134521</v>
+        <v>12.8736038208008</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G518" t="n">
-        <v>13.8709859848022</v>
+        <v>13.8709850311279</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G519" t="n">
-        <v>14.0556859970093</v>
+        <v>14.0556840896606</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>13.9448661804199</v>
+        <v>13.9448652267456</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G523" t="n">
-        <v>14.5728464126587</v>
+        <v>14.5728454589844</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>15</v>
       </c>
       <c r="G524" t="n">
-        <v>13.8525142669678</v>
+        <v>13.8525161743164</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>13.5754652023315</v>
+        <v>13.5754642486572</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G526" t="n">
-        <v>14.1480340957642</v>
+        <v>14.1480350494385</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9633369445801</v>
+        <v>13.9633359909058</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G528" t="n">
-        <v>13.6493463516235</v>
+        <v>13.6493434906006</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>13.9448661804199</v>
+        <v>13.9448652267456</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G530" t="n">
-        <v>14.3327360153198</v>
+        <v>14.3327379226685</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G531" t="n">
-        <v>14.462025642395</v>
+        <v>14.4620265960693</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G534" t="n">
-        <v>14.1295652389526</v>
+        <v>14.1295642852783</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G536" t="n">
-        <v>12.9474840164185</v>
+        <v>12.9474830627441</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G537" t="n">
-        <v>12.7258434295654</v>
+        <v>12.7258443832397</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G538" t="n">
-        <v>13.5754652023315</v>
+        <v>13.5754642486572</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G539" t="n">
-        <v>13.3168840408325</v>
+        <v>13.3168849945068</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>12.6889028549194</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G543" t="n">
-        <v>12.5042028427124</v>
+        <v>12.5042037963867</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>14</v>
       </c>
       <c r="G544" t="n">
-        <v>12.9290142059326</v>
+        <v>12.9290151596069</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G545" t="n">
-        <v>13.4646463394165</v>
+        <v>13.4646444320679</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G547" t="n">
-        <v>12.6889028549194</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>12.6889028549194</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G549" t="n">
-        <v>12.6150236129761</v>
+        <v>12.6150245666504</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>12.3749122619629</v>
+        <v>12.3749132156372</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>11.9685735702515</v>
+        <v>11.9685726165771</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>12.3749122619629</v>
+        <v>12.3749132156372</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G558" t="n">
-        <v>12.5042028427124</v>
+        <v>12.5042037963867</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>12.5411434173584</v>
+        <v>12.5411443710327</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G560" t="n">
-        <v>12.6704349517822</v>
+        <v>12.6704330444336</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>12.5596132278442</v>
+        <v>12.5596141815186</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G562" t="n">
-        <v>12.1163339614868</v>
+        <v>12.1163330078125</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>12.097864151001</v>
+        <v>12.0978631973267</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>12.1163339614868</v>
+        <v>12.1163330078125</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>11.987042427063</v>
+        <v>11.9870433807373</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G568" t="n">
-        <v>12.023983001709</v>
+        <v>12.0239839553833</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G569" t="n">
-        <v>11.8762216567993</v>
+        <v>11.8762226104736</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G570" t="n">
-        <v>11.5622329711914</v>
+        <v>11.5622320175171</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G571" t="n">
-        <v>11.9685735702515</v>
+        <v>11.9685726165771</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>12.7443151473999</v>
+        <v>12.7443141937256</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>13</v>
       </c>
       <c r="G575" t="n">
-        <v>12.0055122375488</v>
+        <v>12.0055131912231</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G576" t="n">
-        <v>11.9685735702515</v>
+        <v>11.9685726165771</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G578" t="n">
-        <v>11.9685735702515</v>
+        <v>11.9685726165771</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G579" t="n">
-        <v>11.8023433685303</v>
+        <v>11.802342414856</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>12.1902122497559</v>
+        <v>12.1902132034302</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>12.1902122497559</v>
+        <v>12.1902132034302</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G589" t="n">
-        <v>14.2034482955933</v>
+        <v>14.2034463882446</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>14.6836652755737</v>
+        <v>14.6836643218994</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G593" t="n">
-        <v>14.7390756607056</v>
+        <v>14.7390747070312</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>15.6237955093384</v>
+        <v>15.6237964630127</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>15.3414373397827</v>
+        <v>15.3414392471313</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G597" t="n">
-        <v>15.1720266342163</v>
+        <v>15.1720237731934</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G598" t="n">
-        <v>15.0214319229126</v>
+        <v>15.0214328765869</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>16</v>
       </c>
       <c r="G599" t="n">
-        <v>15.0590810775757</v>
+        <v>15.05908203125</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G600" t="n">
-        <v>15.1155519485474</v>
+        <v>15.1155529022217</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>15.2473201751709</v>
+        <v>15.2473211288452</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G602" t="n">
-        <v>15.0214319229126</v>
+        <v>15.0214328765869</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G605" t="n">
-        <v>13.2143449783325</v>
+        <v>13.2143440246582</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G607" t="n">
-        <v>13.6284675598145</v>
+        <v>13.6284685134888</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>13.0261068344116</v>
+        <v>13.026104927063</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>13.2143449783325</v>
+        <v>13.2143440246582</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.0637521743774</v>
+        <v>13.0637531280518</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>13.0261068344116</v>
+        <v>13.026104927063</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G613" t="n">
-        <v>12.8378686904907</v>
+        <v>12.8378677368164</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>12.0472660064697</v>
+        <v>12.0472650527954</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G617" t="n">
-        <v>12.9508104324341</v>
+        <v>12.9508113861084</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G619" t="n">
-        <v>12.6496276855469</v>
+        <v>12.6496286392212</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>13.5</v>
       </c>
       <c r="G620" t="n">
-        <v>12.7061004638672</v>
+        <v>12.7060995101929</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G624" t="n">
-        <v>12.6684513092041</v>
+        <v>12.6684532165527</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6496276855469</v>
+        <v>12.6496286392212</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G630" t="n">
-        <v>13.9108266830444</v>
+        <v>13.9108257293701</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G635" t="n">
-        <v>13.5343494415283</v>
+        <v>13.5343503952026</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>13.364933013916</v>
+        <v>13.3649349212646</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G639" t="n">
-        <v>13.1955213546753</v>
+        <v>13.1955223083496</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>13.082576751709</v>
+        <v>13.0825786590576</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>13.2708158493042</v>
+        <v>13.2708139419556</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>13.2708158493042</v>
+        <v>13.2708139419556</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G645" t="n">
-        <v>12.6684513092041</v>
+        <v>12.6684532165527</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8378686904907</v>
+        <v>12.8378677368164</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G647" t="n">
-        <v>13.1578712463379</v>
+        <v>13.1578702926636</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>13.3084630966187</v>
+        <v>13.308464050293</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G649" t="n">
-        <v>13.1578712463379</v>
+        <v>13.1578702926636</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G651" t="n">
-        <v>12.6684513092041</v>
+        <v>12.6684532165527</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G652" t="n">
-        <v>13.0261068344116</v>
+        <v>13.026104927063</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G653" t="n">
-        <v>12.5178623199463</v>
+        <v>12.517861366272</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G654" t="n">
-        <v>12.4613885879517</v>
+        <v>12.461389541626</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G656" t="n">
-        <v>12.6496276855469</v>
+        <v>12.6496286392212</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9319868087769</v>
+        <v>12.9319858551025</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>13.082576751709</v>
+        <v>13.0825786590576</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G662" t="n">
-        <v>12.7625722885132</v>
+        <v>12.7625713348389</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G663" t="n">
-        <v>12.9508104324341</v>
+        <v>12.9508113861084</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G665" t="n">
-        <v>12.913161277771</v>
+        <v>12.9131622314453</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G672" t="n">
-        <v>12.9319868087769</v>
+        <v>12.9319858551025</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G673" t="n">
-        <v>13.5343494415283</v>
+        <v>13.5343503952026</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G675" t="n">
-        <v>14.0614156723022</v>
+        <v>14.0614166259766</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>14.2120094299316</v>
+        <v>14.2120084762573</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G677" t="n">
-        <v>14.2496547698975</v>
+        <v>14.2496576309204</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G678" t="n">
-        <v>14.0049467086792</v>
+        <v>14.0049457550049</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G680" t="n">
-        <v>13.6284675598145</v>
+        <v>13.6284685134888</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G681" t="n">
-        <v>13.4402313232422</v>
+        <v>13.4402294158936</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G684" t="n">
-        <v>13.1955213546753</v>
+        <v>13.1955223083496</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G685" t="n">
-        <v>13.1955213546753</v>
+        <v>13.1955223083496</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>15</v>
       </c>
       <c r="G686" t="n">
-        <v>14.1178874969482</v>
+        <v>14.1178884506226</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G687" t="n">
-        <v>14.2120094299316</v>
+        <v>14.2120084762573</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>14.2120094299316</v>
+        <v>14.2120084762573</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>14.8708438873291</v>
+        <v>14.8708429336548</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>15.4355583190918</v>
+        <v>15.4355564117432</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G692" t="n">
-        <v>15.0967292785645</v>
+        <v>15.0967302322388</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>15.3414373397827</v>
+        <v>15.3414392471313</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>17.5</v>
       </c>
       <c r="G694" t="n">
-        <v>16.4708709716797</v>
+        <v>16.4708671569824</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>16.8473453521729</v>
+        <v>16.8473472595215</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>17.5</v>
       </c>
       <c r="G698" t="n">
-        <v>16.4708709716797</v>
+        <v>16.4708671569824</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>17.5</v>
       </c>
       <c r="G699" t="n">
-        <v>16.4708709716797</v>
+        <v>16.4708671569824</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G700" t="n">
-        <v>16.1696910858154</v>
+        <v>16.1696872711182</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G701" t="n">
-        <v>15.8496837615967</v>
+        <v>15.849681854248</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>16.5</v>
       </c>
       <c r="G702" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296792984009</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G704" t="n">
-        <v>15.1720266342163</v>
+        <v>15.1720237731934</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>16.5</v>
       </c>
       <c r="G705" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296792984009</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>16</v>
       </c>
       <c r="G708" t="n">
-        <v>15.0590810775757</v>
+        <v>15.05908203125</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G710" t="n">
-        <v>14.3249521255493</v>
+        <v>14.324951171875</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G712" t="n">
-        <v>14.3814220428467</v>
+        <v>14.381422996521</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>15.5</v>
       </c>
       <c r="G713" t="n">
-        <v>14.5884857177734</v>
+        <v>14.5884847640991</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>14.2496547698975</v>
+        <v>14.2496576309204</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G715" t="n">
-        <v>14.1931848526001</v>
+        <v>14.1931838989258</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G716" t="n">
-        <v>14.1367130279541</v>
+        <v>14.1367139816284</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G717" t="n">
-        <v>14.1367130279541</v>
+        <v>14.1367139816284</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G718" t="n">
-        <v>13.8355321884155</v>
+        <v>13.8355312347412</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G720" t="n">
-        <v>13.4402313232422</v>
+        <v>13.4402294158936</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G722" t="n">
-        <v>13.7978820800781</v>
+        <v>13.7978830337524</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>13.9672975540161</v>
+        <v>13.9672985076904</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>14.3625993728638</v>
+        <v>14.3626003265381</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>16.5</v>
       </c>
       <c r="G729" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296792984009</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>15.3414373397827</v>
+        <v>15.3414392471313</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>16</v>
       </c>
       <c r="G732" t="n">
-        <v>15.0590810775757</v>
+        <v>15.05908203125</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>14.9084920883179</v>
+        <v>14.9084901809692</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G734" t="n">
-        <v>16.0190982818604</v>
+        <v>16.019100189209</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>17</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0002765655518</v>
+        <v>16.0002746582031</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>15.8120346069336</v>
+        <v>15.8120355606079</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>15.6237955093384</v>
+        <v>15.6237964630127</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G742" t="n">
-        <v>16.2826309204102</v>
+        <v>16.2826290130615</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>16.0379238128662</v>
+        <v>16.0379219055176</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G744" t="n">
-        <v>16.2638092041016</v>
+        <v>16.2638111114502</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G745" t="n">
-        <v>15.5861482620239</v>
+        <v>15.5861492156982</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G747" t="n">
-        <v>16.0379238128662</v>
+        <v>16.0379219055176</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G752" t="n">
-        <v>15.0214319229126</v>
+        <v>15.0214328765869</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>15.3414373397827</v>
+        <v>15.3414392471313</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G755" t="n">
-        <v>15.7932147979736</v>
+        <v>15.7932119369507</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>14.6826057434082</v>
+        <v>14.6826047897339</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G759" t="n">
-        <v>14.8520202636719</v>
+        <v>14.8520174026489</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>14.494366645813</v>
+        <v>14.4943647384644</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G761" t="n">
-        <v>14.7578983306885</v>
+        <v>14.7579011917114</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G763" t="n">
-        <v>14.9273138046265</v>
+        <v>14.9273147583008</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G764" t="n">
-        <v>15.4732055664062</v>
+        <v>15.4732093811035</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G766" t="n">
-        <v>15.8496837615967</v>
+        <v>15.849681854248</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G769" t="n">
-        <v>15.6802673339844</v>
+        <v>15.6802682876587</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.5</v>
       </c>
       <c r="G770" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296792984009</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G771" t="n">
-        <v>15.5861482620239</v>
+        <v>15.5861492156982</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G773" t="n">
-        <v>14.9837865829468</v>
+        <v>14.9837846755981</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G778" t="n">
-        <v>15.4732055664062</v>
+        <v>15.4732093811035</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G779" t="n">
-        <v>15.8308591842651</v>
+        <v>15.8308582305908</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>15.9061555862427</v>
+        <v>15.9061546325684</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>15.9061555862427</v>
+        <v>15.9061546325684</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="n">
-        <v>16.0002765655518</v>
+        <v>16.0002746582031</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9438028335571</v>
+        <v>15.9438009262085</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>15.9061555862427</v>
+        <v>15.9061546325684</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>15.9061555862427</v>
+        <v>15.9061546325684</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G787" t="n">
-        <v>15.9249811172485</v>
+        <v>15.924976348877</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G788" t="n">
-        <v>15.9438028335571</v>
+        <v>15.9438009262085</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>15.5485019683838</v>
+        <v>15.5485010147095</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>16.5</v>
       </c>
       <c r="G790" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296792984009</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G791" t="n">
-        <v>14.6261339187622</v>
+        <v>14.6261329650879</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G792" t="n">
-        <v>14.8520202636719</v>
+        <v>14.8520174026489</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G794" t="n">
-        <v>14.7955465316772</v>
+        <v>14.7955474853516</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>15.4355583190918</v>
+        <v>15.4355564117432</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G798" t="n">
-        <v>15.0402574539185</v>
+        <v>15.0402565002441</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G799" t="n">
-        <v>15.1155519485474</v>
+        <v>15.1155529022217</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G801" t="n">
-        <v>15.1155519485474</v>
+        <v>15.1155529022217</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>16</v>
       </c>
       <c r="G803" t="n">
-        <v>15.0590810775757</v>
+        <v>15.05908203125</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G805" t="n">
-        <v>15.2284965515137</v>
+        <v>15.228497505188</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6802673339844</v>
+        <v>15.6802682876587</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G808" t="n">
-        <v>16.1320381164551</v>
+        <v>16.1320400238037</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>17.2238235473633</v>
+        <v>17.2238216400146</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>17.0355834960938</v>
+        <v>17.035587310791</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G814" t="n">
-        <v>16.9979381561279</v>
+        <v>16.9979362487793</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G815" t="n">
-        <v>16.9979381561279</v>
+        <v>16.9979362487793</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>17.9767780303955</v>
+        <v>17.9767799377441</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G817" t="n">
-        <v>17.3367671966553</v>
+        <v>17.3367652893066</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2991180419922</v>
+        <v>17.2991218566895</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G821" t="n">
-        <v>16.9791164398193</v>
+        <v>16.9791145324707</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G824" t="n">
-        <v>17.2991180419922</v>
+        <v>17.2991218566895</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>17.0355834960938</v>
+        <v>17.035587310791</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>17.7885417938232</v>
+        <v>17.7885398864746</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>17.2238235473633</v>
+        <v>17.2238216400146</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G834" t="n">
-        <v>17.2614727020264</v>
+        <v>17.2614707946777</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>17.0355834960938</v>
+        <v>17.035587310791</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>16.8473453521729</v>
+        <v>16.8473472595215</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>16.2826309204102</v>
+        <v>16.2826290130615</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>16.7908744812012</v>
+        <v>16.7908725738525</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G850" t="n">
-        <v>16.3243141174316</v>
+        <v>16.324312210083</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>16.3817939758301</v>
+        <v>16.3817920684814</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G854" t="n">
-        <v>15.9219522476196</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G855" t="n">
-        <v>16.6117115020752</v>
+        <v>16.6117134094238</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G856" t="n">
-        <v>16.7458343505859</v>
+        <v>16.7458324432373</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G857" t="n">
-        <v>16.6117115020752</v>
+        <v>16.6117134094238</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>17.5</v>
       </c>
       <c r="G858" t="n">
-        <v>16.7649955749512</v>
+        <v>16.7649917602539</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G859" t="n">
-        <v>16.6883525848389</v>
+        <v>16.6883544921875</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G863" t="n">
-        <v>16.4584350585938</v>
+        <v>16.4584331512451</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>15.8836307525635</v>
+        <v>15.8836317062378</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>16.3817939758301</v>
+        <v>16.3817920684814</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G868" t="n">
-        <v>16.400951385498</v>
+        <v>16.4009532928467</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G870" t="n">
-        <v>15.9602718353271</v>
+        <v>15.9602737426758</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.5</v>
       </c>
       <c r="G872" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G875" t="n">
-        <v>15.9219522476196</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G877" t="n">
-        <v>15.3088331222534</v>
+        <v>15.3088321685791</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G878" t="n">
-        <v>15.2513542175293</v>
+        <v>15.251353263855</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>15.0405921936035</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G886" t="n">
-        <v>15.0597524642944</v>
+        <v>15.0597534179688</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>15.002272605896</v>
+        <v>15.0022745132446</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G889" t="n">
-        <v>14.8106737136841</v>
+        <v>14.8106746673584</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.7915143966675</v>
+        <v>14.7915134429932</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G891" t="n">
-        <v>14.6573944091797</v>
+        <v>14.6573934555054</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G893" t="n">
-        <v>15.1172342300415</v>
+        <v>15.1172332763672</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>15.0405921936035</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G898" t="n">
-        <v>15.0214319229126</v>
+        <v>15.0214338302612</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G899" t="n">
-        <v>14.9064741134644</v>
+        <v>14.90647315979</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>15.0980739593506</v>
+        <v>15.0980730056763</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>14.6573944091797</v>
+        <v>14.6573934555054</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>15.5</v>
       </c>
       <c r="G905" t="n">
-        <v>14.8489942550659</v>
+        <v>14.8489933013916</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>15.5</v>
       </c>
       <c r="G907" t="n">
-        <v>14.8489942550659</v>
+        <v>14.8489933013916</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>14.7531938552856</v>
+        <v>14.753191947937</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G911" t="n">
-        <v>14.8106737136841</v>
+        <v>14.8106746673584</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G912" t="n">
-        <v>15.0597524642944</v>
+        <v>15.0597534179688</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G915" t="n">
-        <v>14.8298330307007</v>
+        <v>14.8298320770264</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G916" t="n">
-        <v>14.4849538803101</v>
+        <v>14.4849548339844</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G918" t="n">
-        <v>14.5424337387085</v>
+        <v>14.5424327850342</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G921" t="n">
-        <v>14.5807542800903</v>
+        <v>14.580753326416</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G924" t="n">
-        <v>14.408314704895</v>
+        <v>14.4083137512207</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G925" t="n">
-        <v>14.4849538803101</v>
+        <v>14.4849548339844</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G926" t="n">
-        <v>14.5807542800903</v>
+        <v>14.580753326416</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G927" t="n">
-        <v>14.3891534805298</v>
+        <v>14.3891544342041</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G928" t="n">
-        <v>14.5999135971069</v>
+        <v>14.5999126434326</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G930" t="n">
-        <v>14.8681545257568</v>
+        <v>14.8681554794312</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G931" t="n">
-        <v>14.8106737136841</v>
+        <v>14.8106746673584</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G933" t="n">
-        <v>14.8106737136841</v>
+        <v>14.8106746673584</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G934" t="n">
-        <v>14.5424337387085</v>
+        <v>14.5424327850342</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G935" t="n">
-        <v>14.8298330307007</v>
+        <v>14.8298320770264</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G936" t="n">
-        <v>15.2896738052368</v>
+        <v>15.2896728515625</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G938" t="n">
-        <v>15.6153917312622</v>
+        <v>15.6153926849365</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G939" t="n">
-        <v>15.4621143341064</v>
+        <v>15.4621152877808</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G940" t="n">
-        <v>15.6537132263184</v>
+        <v>15.653712272644</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G941" t="n">
-        <v>15.730354309082</v>
+        <v>15.7303524017334</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>15.7111930847168</v>
+        <v>15.7111902236938</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G945" t="n">
-        <v>15.7495126724243</v>
+        <v>15.7495155334473</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.5</v>
       </c>
       <c r="G951" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>15.7878322601318</v>
+        <v>15.7878313064575</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>16.5</v>
       </c>
       <c r="G953" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>16.5</v>
       </c>
       <c r="G954" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G955" t="n">
-        <v>15.5195941925049</v>
+        <v>15.5195960998535</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G956" t="n">
-        <v>15.4429550170898</v>
+        <v>15.4429531097412</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>15.7111930847168</v>
+        <v>15.7111902236938</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G962" t="n">
-        <v>15.6537132263184</v>
+        <v>15.653712272644</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G963" t="n">
-        <v>15.8644714355469</v>
+        <v>15.8644723892212</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>16.5</v>
       </c>
       <c r="G964" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G965" t="n">
-        <v>15.9219522476196</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G966" t="n">
-        <v>16.0560741424561</v>
+        <v>16.0560722351074</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>16.3817939758301</v>
+        <v>16.3817920684814</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G969" t="n">
-        <v>17.0907135009766</v>
+        <v>17.0907115936279</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G970" t="n">
-        <v>16.9374313354492</v>
+        <v>16.9374332427979</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G971" t="n">
-        <v>16.8799533843994</v>
+        <v>16.8799514770508</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>17.5</v>
       </c>
       <c r="G972" t="n">
-        <v>16.7649955749512</v>
+        <v>16.7649917602539</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G973" t="n">
-        <v>16.8224697113037</v>
+        <v>16.8224716186523</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G974" t="n">
-        <v>16.9374313354492</v>
+        <v>16.9374332427979</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>17.0523891448975</v>
+        <v>17.0523929595947</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G977" t="n">
-        <v>16.7458343505859</v>
+        <v>16.7458324432373</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G978" t="n">
-        <v>16.8224697113037</v>
+        <v>16.8224716186523</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G979" t="n">
-        <v>17.2056732177734</v>
+        <v>17.2056713104248</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>17.5313930511475</v>
+        <v>17.5313892364502</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>17.9145927429199</v>
+        <v>17.9145946502686</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>18.0487117767334</v>
+        <v>18.048713684082</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G987" t="n">
-        <v>17.8954315185547</v>
+        <v>17.8954334259033</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G990" t="n">
-        <v>17.8954315185547</v>
+        <v>17.8954334259033</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G991" t="n">
-        <v>17.9145927429199</v>
+        <v>17.9145946502686</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G992" t="n">
-        <v>17.8571090698242</v>
+        <v>17.8571128845215</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>19.5</v>
       </c>
       <c r="G994" t="n">
-        <v>18.6809902191162</v>
+        <v>18.6809921264648</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G996" t="n">
-        <v>18.9492340087891</v>
+        <v>18.9492359161377</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G997" t="n">
-        <v>18.4702301025391</v>
+        <v>18.4702339172363</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>19.5</v>
       </c>
       <c r="G998" t="n">
-        <v>18.6809902191162</v>
+        <v>18.6809921264648</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G999" t="n">
-        <v>18.8917503356934</v>
+        <v>18.8917541503906</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>19.3515911102295</v>
+        <v>19.3515930175781</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>19.7347927093506</v>
+        <v>19.734790802002</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.4473934173584</v>
+        <v>19.4473915100098</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>19.5910930633545</v>
+        <v>19.5910911560059</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.2078914642334</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.2078914642334</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>18.7767906188965</v>
+        <v>18.7767925262451</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>19.5431900024414</v>
+        <v>19.5431938171387</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>20.5</v>
       </c>
       <c r="G1009" t="n">
-        <v>19.6389923095703</v>
+        <v>19.6389904022217</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1011" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>19.4473934173584</v>
+        <v>19.4473915100098</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>19.2078914642334</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>19.5431900024414</v>
+        <v>19.5431938171387</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1017" t="n">
-        <v>19.5910930633545</v>
+        <v>19.5910911560059</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>21</v>
       </c>
       <c r="G1019" t="n">
-        <v>20.117992401123</v>
+        <v>20.1179904937744</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>22.129789352417</v>
+        <v>22.1297912597656</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>20.7406883239746</v>
+        <v>20.7406902313232</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>20.54909324646</v>
+        <v>20.5490913391113</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322929382324</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322929382324</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1029" t="n">
-        <v>20.644889831543</v>
+        <v>20.6448917388916</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>21.5</v>
       </c>
       <c r="G1030" t="n">
-        <v>20.5969905853271</v>
+        <v>20.5969924926758</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>20.644889831543</v>
+        <v>20.6448917388916</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>21.5</v>
       </c>
       <c r="G1032" t="n">
-        <v>20.5969905853271</v>
+        <v>20.5969924926758</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>20.75</v>
       </c>
       <c r="G1033" t="n">
-        <v>19.8784885406494</v>
+        <v>19.8784923553467</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>20.2137928009033</v>
+        <v>20.2137889862061</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>19.9263896942139</v>
+        <v>19.9263916015625</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1036" t="n">
-        <v>19.7826919555664</v>
+        <v>19.7826900482178</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>20.75</v>
       </c>
       <c r="G1039" t="n">
-        <v>19.8784885406494</v>
+        <v>19.8784923553467</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>21.75</v>
       </c>
       <c r="G1041" t="n">
-        <v>20.8364906311035</v>
+        <v>20.8364887237549</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>20.644889831543</v>
+        <v>20.6448917388916</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1043" t="n">
-        <v>20.5011920928955</v>
+        <v>20.5011901855469</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322929382324</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>21.1717948913574</v>
+        <v>21.1717929840088</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>22.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>21.3154926300049</v>
+        <v>21.3154907226562</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1047" t="n">
-        <v>21.1238899230957</v>
+        <v>21.1238918304443</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>22.25</v>
       </c>
       <c r="G1051" t="n">
-        <v>21.3154926300049</v>
+        <v>21.3154907226562</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1054" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>19.5431900024414</v>
+        <v>19.5431938171387</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>20.5</v>
       </c>
       <c r="G1057" t="n">
-        <v>19.6389923095703</v>
+        <v>19.6389904022217</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1058" t="n">
-        <v>18.6618347167969</v>
+        <v>18.6618328094482</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>19.5</v>
       </c>
       <c r="G1059" t="n">
-        <v>18.6809902191162</v>
+        <v>18.6809921264648</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>18.7767906188965</v>
+        <v>18.7767925262451</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1063" t="n">
-        <v>16.7458343505859</v>
+        <v>16.7458324432373</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>15</v>
       </c>
       <c r="G1067" t="n">
-        <v>14.3699932098389</v>
+        <v>14.3699941635132</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.4156742095947</v>
+        <v>12.415675163269</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>12.5</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9749946594238</v>
+        <v>11.9749965667725</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.2587146759033</v>
+        <v>13.2587127685547</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>13.507794380188</v>
+        <v>13.5077924728394</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.2358732223511</v>
+        <v>14.2358722686768</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5999135971069</v>
+        <v>14.5999126434326</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>14.6573944091797</v>
+        <v>14.6573934555054</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>15</v>
       </c>
       <c r="G1084" t="n">
-        <v>14.3699932098389</v>
+        <v>14.3699941635132</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1086" t="n">
-        <v>14.6765537261963</v>
+        <v>14.6765546798706</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1087" t="n">
-        <v>14.7915143966675</v>
+        <v>14.7915134429932</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1088" t="n">
-        <v>14.2358732223511</v>
+        <v>14.2358722686768</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>15</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.3699932098389</v>
+        <v>14.3699941635132</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.3471536636353</v>
+        <v>15.3471527099609</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1092" t="n">
-        <v>15.0980739593506</v>
+        <v>15.0980730056763</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.9219522476196</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1094" t="n">
-        <v>16.803316116333</v>
+        <v>16.8033142089844</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1095" t="n">
-        <v>16.1135520935059</v>
+        <v>16.1135540008545</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.9219522476196</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.6537132263184</v>
+        <v>15.653712272644</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.8681545257568</v>
+        <v>14.8681554794312</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.0405921936035</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.7111930847168</v>
+        <v>15.7111902236938</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.3471536636353</v>
+        <v>15.3471527099609</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.7531938552856</v>
+        <v>14.753191947937</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.6153917312622</v>
+        <v>15.6153926849365</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>15.998592376709</v>
+        <v>15.9985942840576</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1115" t="n">
-        <v>15.4621143341064</v>
+        <v>15.4621152877808</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1117" t="n">
-        <v>15.9602718353271</v>
+        <v>15.9602737426758</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1118" t="n">
-        <v>16.5350723266602</v>
+        <v>16.5350742340088</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1121" t="n">
-        <v>16.8607921600342</v>
+        <v>16.8607940673828</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1122" t="n">
-        <v>16.9949111938477</v>
+        <v>16.9949131011963</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1123" t="n">
-        <v>18.1828327178955</v>
+        <v>18.1828346252441</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1124" t="n">
-        <v>18.5660305023193</v>
+        <v>18.5660285949707</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1125" t="n">
-        <v>18.0069313049316</v>
+        <v>18.006929397583</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3899917602539</v>
+        <v>17.3899936676025</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1129" t="n">
-        <v>17.1393585205078</v>
+        <v>17.1393604278564</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1133" t="n">
-        <v>17.1007995605469</v>
+        <v>17.1008014678955</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1134" t="n">
-        <v>17.5827827453613</v>
+        <v>17.58278465271</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1135" t="n">
-        <v>17.4285488128662</v>
+        <v>17.4285507202148</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>18.5081939697266</v>
+        <v>18.5081958770752</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1146" t="n">
-        <v>18.3732357025146</v>
+        <v>18.3732376098633</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1150" t="n">
-        <v>17.9683723449707</v>
+        <v>17.9683704376221</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1151" t="n">
-        <v>18.3732357025146</v>
+        <v>18.3732376098633</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1152" t="n">
-        <v>18.758825302124</v>
+        <v>18.7588214874268</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>18.6045913696289</v>
+        <v>18.6045894622803</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1159" t="n">
-        <v>18.8745021820068</v>
+        <v>18.8745002746582</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1164" t="n">
-        <v>19.4239635467529</v>
+        <v>19.4239654541016</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1165" t="n">
-        <v>19.5685596466064</v>
+        <v>19.5685615539551</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>20.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>20.0023460388184</v>
+        <v>20.0023441314697</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>21</v>
       </c>
       <c r="G1167" t="n">
-        <v>20.2433376312256</v>
+        <v>20.243335723877</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1168" t="n">
-        <v>20.5325241088867</v>
+        <v>20.5325260162354</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>21.25</v>
       </c>
       <c r="G1169" t="n">
-        <v>20.4843311309814</v>
+        <v>20.4843292236328</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>22</v>
       </c>
       <c r="G1171" t="n">
-        <v>21.2073078155518</v>
+        <v>21.2073059082031</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22</v>
       </c>
       <c r="G1172" t="n">
-        <v>21.2073078155518</v>
+        <v>21.2073059082031</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.2073078155518</v>
+        <v>21.2073059082031</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22</v>
       </c>
       <c r="G1174" t="n">
-        <v>21.2073078155518</v>
+        <v>21.2073059082031</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>21.1109066009521</v>
+        <v>21.1109085083008</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>21.1109066009521</v>
+        <v>21.1109085083008</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.4964942932129</v>
+        <v>21.4964962005615</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.7856884002686</v>
+        <v>21.7856864929199</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.7856884002686</v>
+        <v>21.7856864929199</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.255500793457</v>
+        <v>21.2555046081543</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>22.5</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.6892910003662</v>
+        <v>21.6892890930176</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>22.364070892334</v>
+        <v>22.3640689849854</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>22.5</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.6892910003662</v>
+        <v>21.6892890930176</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>22.7014560699463</v>
+        <v>22.7014541625977</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.2316398620605</v>
+        <v>23.2316417694092</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>22.7014560699463</v>
+        <v>22.7014541625977</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>23.3280372619629</v>
+        <v>23.3280353546143</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>24.3884029388428</v>
+        <v>24.3883991241455</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>23.9546165466309</v>
+        <v>23.9546184539795</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>23.5690288543701</v>
+        <v>23.5690307617188</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>23.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>22.6532611846924</v>
+        <v>22.6532592773438</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>22.7978553771973</v>
+        <v>22.7978534698486</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1205" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1206" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1207" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>22.4604644775391</v>
+        <v>22.4604625701904</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1210" t="n">
-        <v>21.7374858856201</v>
+        <v>21.7374877929688</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>22.5</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.6892910003662</v>
+        <v>21.6892890930176</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>21.4964942932129</v>
+        <v>21.4964962005615</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>21.5446968078613</v>
+        <v>21.5446949005127</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1219" t="n">
-        <v>21.3037052154541</v>
+        <v>21.3037033081055</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1220" t="n">
-        <v>21.0145111083984</v>
+        <v>21.0145130157471</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1221" t="n">
-        <v>21.4000988006592</v>
+        <v>21.4001007080078</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1222" t="n">
-        <v>21.4964942932129</v>
+        <v>21.4964962005615</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>21.7374858856201</v>
+        <v>21.7374877929688</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>22.5</v>
       </c>
       <c r="G1225" t="n">
-        <v>21.6892910003662</v>
+        <v>21.6892890930176</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>21.8820838928223</v>
+        <v>21.8820858001709</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>21.1109066009521</v>
+        <v>21.1109085083008</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1230" t="n">
-        <v>21.4964942932129</v>
+        <v>21.4964962005615</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>22.0266799926758</v>
+        <v>22.0266780853271</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>22.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>21.6892910003662</v>
+        <v>21.6892890930176</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1241" t="n">
-        <v>24.2438087463379</v>
+        <v>24.2438068389893</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>26.8947200775146</v>
+        <v>26.8947219848633</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>26.5573310852051</v>
+        <v>26.5573291778564</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>27.5694961547852</v>
+        <v>27.5694980621338</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>30.75</v>
       </c>
       <c r="G1254" t="n">
-        <v>29.6420269012451</v>
+        <v>29.6420307159424</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>30.2686080932617</v>
+        <v>30.2686100006104</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>31.6181640625</v>
+        <v>31.6181678771973</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1258" t="n">
-        <v>31.9073543548584</v>
+        <v>31.9073581695557</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G1260" t="n">
-        <v>31.9555587768555</v>
+        <v>31.9555549621582</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>33.25</v>
       </c>
       <c r="G1263" t="n">
-        <v>32.0519485473633</v>
+        <v>32.0519523620605</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1265" t="n">
-        <v>31.9073543548584</v>
+        <v>31.9073581695557</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>33.0641174316406</v>
+        <v>33.0641136169434</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G1270" t="n">
-        <v>33.5943031311035</v>
+        <v>33.594295501709</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>35.25</v>
       </c>
       <c r="G1271" t="n">
-        <v>33.9798851013184</v>
+        <v>33.9798927307129</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>34.6064682006836</v>
+        <v>34.6064720153809</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G1274" t="n">
-        <v>35.2330436706543</v>
+        <v>35.2330474853516</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1275" t="n">
-        <v>35.3294486999512</v>
+        <v>35.3294448852539</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1276" t="n">
-        <v>36.6789970397949</v>
+        <v>36.6790008544922</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1277" t="n">
-        <v>37.0163879394531</v>
+        <v>37.0163917541504</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>36.0524215698242</v>
+        <v>36.0524253845215</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G1279" t="n">
-        <v>34.1726875305176</v>
+        <v>34.1726837158203</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>33.25</v>
       </c>
       <c r="G1280" t="n">
-        <v>32.0519485473633</v>
+        <v>32.0519523620605</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>33.75</v>
       </c>
       <c r="G1282" t="n">
-        <v>32.5339317321777</v>
+        <v>32.533935546875</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1283" t="n">
-        <v>32.6303291320801</v>
+        <v>32.6303253173828</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1284" t="n">
-        <v>32.5821380615234</v>
+        <v>32.5821342468262</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>33</v>
       </c>
       <c r="G1285" t="n">
-        <v>31.8109588623047</v>
+        <v>31.810962677002</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.2204132080078</v>
+        <v>30.2204113006592</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.7023963928223</v>
+        <v>30.7023944854736</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1288" t="n">
-        <v>30.4614067077637</v>
+        <v>30.4614009857178</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>31.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>30.3650054931641</v>
+        <v>30.3650074005127</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>32.5821380615234</v>
+        <v>32.5821342468262</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>33.75</v>
       </c>
       <c r="G1292" t="n">
-        <v>32.5339317321777</v>
+        <v>32.533935546875</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>33.3051071166992</v>
+        <v>33.3051109313965</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>35.25</v>
       </c>
       <c r="G1295" t="n">
-        <v>33.9798851013184</v>
+        <v>33.9798927307129</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>36.4500007629395</v>
       </c>
       <c r="G1296" t="n">
-        <v>35.1366539001465</v>
+        <v>35.1366500854492</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>36.8235969543457</v>
+        <v>36.8235931396484</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G1302" t="n">
-        <v>35.8114318847656</v>
+        <v>35.8114280700684</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1303" t="n">
-        <v>36.2934150695801</v>
+        <v>36.2934074401855</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>36.25</v>
       </c>
       <c r="G1304" t="n">
-        <v>34.9438552856445</v>
+        <v>34.9438514709473</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1305" t="n">
-        <v>34.8474655151367</v>
+        <v>34.8474578857422</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1306" t="n">
-        <v>36.5344047546387</v>
+        <v>36.5344085693359</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>36.919994354248</v>
+        <v>36.9199905395508</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>38.9000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>37.4983749389648</v>
+        <v>37.4983711242676</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1310" t="n">
-        <v>37.8839569091797</v>
+        <v>37.883960723877</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G1311" t="n">
-        <v>38.4623413085938</v>
+        <v>38.462345123291</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1313" t="n">
-        <v>39.6673011779785</v>
+        <v>39.6673049926758</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>41</v>
       </c>
       <c r="G1314" t="n">
-        <v>39.5227088928223</v>
+        <v>39.522705078125</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1315" t="n">
-        <v>38.4141426086426</v>
+        <v>38.4141464233398</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1317" t="n">
-        <v>39.6673011779785</v>
+        <v>39.6673049926758</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>41.5</v>
       </c>
       <c r="G1320" t="n">
-        <v>40.0046920776367</v>
+        <v>40.0046882629395</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>40.75</v>
       </c>
       <c r="G1321" t="n">
-        <v>39.2817153930664</v>
+        <v>39.2817115783691</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>45.5499992370605</v>
       </c>
       <c r="G1323" t="n">
-        <v>43.908763885498</v>
+        <v>43.9087600708008</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>41.0168571472168</v>
+        <v>41.0168609619141</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>43.25</v>
       </c>
       <c r="G1327" t="n">
-        <v>41.6916351318359</v>
+        <v>41.6916389465332</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>43.75</v>
       </c>
       <c r="G1328" t="n">
-        <v>42.1736221313477</v>
+        <v>42.1736145019531</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>42.2218132019043</v>
+        <v>42.2218170166016</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>43.3303833007812</v>
+        <v>43.3303871154785</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>46.25</v>
       </c>
       <c r="G1336" t="n">
-        <v>44.5835456848145</v>
+        <v>44.5835380554199</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>45.8367004394531</v>
+        <v>45.8367042541504</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>47</v>
       </c>
       <c r="G1341" t="n">
-        <v>45.3065223693848</v>
+        <v>45.3065185546875</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G1342" t="n">
-        <v>44.7763328552246</v>
+        <v>44.7763366699219</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G1343" t="n">
-        <v>46.077693939209</v>
+        <v>46.0776901245117</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>46.25</v>
       </c>
       <c r="G1345" t="n">
-        <v>44.5835456848145</v>
+        <v>44.5835380554199</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>46.0999984741211</v>
       </c>
       <c r="G1346" t="n">
-        <v>44.4389495849609</v>
+        <v>44.4389457702637</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>45.75</v>
       </c>
       <c r="G1350" t="n">
-        <v>44.1015586853027</v>
+        <v>44.1015548706055</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G1352" t="n">
-        <v>42.9929885864258</v>
+        <v>42.992992401123</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>44.75</v>
       </c>
       <c r="G1353" t="n">
-        <v>43.1375923156738</v>
+        <v>43.1375885009766</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>43.0893936157227</v>
+        <v>43.0893898010254</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>44.8499984741211</v>
       </c>
       <c r="G1359" t="n">
-        <v>43.2339859008789</v>
+        <v>43.2339820861816</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G1360" t="n">
-        <v>42.2700157165527</v>
+        <v>42.2700119018555</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1362" t="n">
-        <v>42.2218132019043</v>
+        <v>42.2218170166016</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>43.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>42.1736221313477</v>
+        <v>42.1736145019531</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>40.75</v>
       </c>
       <c r="G1366" t="n">
-        <v>39.644172668457</v>
+        <v>39.6441764831543</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1367" t="n">
-        <v>39.3036766052246</v>
+        <v>39.3036804199219</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>40.75</v>
       </c>
       <c r="G1368" t="n">
-        <v>39.644172668457</v>
+        <v>39.6441764831543</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1371" t="n">
-        <v>39.8387451171875</v>
+        <v>39.8387489318848</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>41.75</v>
       </c>
       <c r="G1373" t="n">
-        <v>40.6170387268066</v>
+        <v>40.6170349121094</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>40.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>39.644172668457</v>
+        <v>39.6441764831543</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1382" t="n">
-        <v>39.3036766052246</v>
+        <v>39.3036804199219</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1383" t="n">
-        <v>39.3036766052246</v>
+        <v>39.3036804199219</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1386" t="n">
-        <v>39.7901077270508</v>
+        <v>39.7901039123535</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1389" t="n">
-        <v>36.5796546936035</v>
+        <v>36.5796585083008</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>39</v>
       </c>
       <c r="G1393" t="n">
-        <v>37.9416656494141</v>
+        <v>37.9416618347168</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1402" t="n">
-        <v>40.2278938293457</v>
+        <v>40.2278900146484</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1405" t="n">
-        <v>42.0276908874512</v>
+        <v>42.0276947021484</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1407" t="n">
-        <v>42.0276908874512</v>
+        <v>42.0276947021484</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1408" t="n">
-        <v>41.7844734191895</v>
+        <v>41.7844772338867</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>43.75</v>
       </c>
       <c r="G1410" t="n">
-        <v>42.5627670288086</v>
+        <v>42.5627708435059</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>46.5</v>
       </c>
       <c r="G1412" t="n">
-        <v>45.2381401062012</v>
+        <v>45.2381362915039</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>48.3513031005859</v>
+        <v>48.3512992858887</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>49.75</v>
       </c>
       <c r="G1418" t="n">
-        <v>48.3999481201172</v>
+        <v>48.3999443054199</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>50</v>
       </c>
       <c r="G1419" t="n">
-        <v>48.6431579589844</v>
+        <v>48.6431617736816</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1426" t="n">
-        <v>51.1726036071777</v>
+        <v>51.1725997924805</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>51.5</v>
       </c>
       <c r="G1429" t="n">
-        <v>50.1024551391602</v>
+        <v>50.1024513244629</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>52</v>
       </c>
       <c r="G1438" t="n">
-        <v>50.5888862609863</v>
+        <v>50.5888900756836</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1441" t="n">
-        <v>51.6590385437012</v>
+        <v>51.6590347290039</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>51.7563247680664</v>
+        <v>51.7563285827637</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>50</v>
       </c>
       <c r="G1445" t="n">
-        <v>48.6431579589844</v>
+        <v>48.6431617736816</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1449" t="n">
-        <v>43.3410606384277</v>
+        <v>43.3410530090332</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G1451" t="n">
-        <v>44.1193504333496</v>
+        <v>44.1193466186523</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G1454" t="n">
-        <v>43.8761291503906</v>
+        <v>43.8761253356934</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>41.0548324584961</v>
+        <v>41.0548286437988</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1461" t="n">
-        <v>40.8116111755371</v>
+        <v>40.8116149902344</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>42.75</v>
       </c>
       <c r="G1462" t="n">
-        <v>41.589900970459</v>
+        <v>41.5899047851562</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>43.75</v>
       </c>
       <c r="G1463" t="n">
-        <v>42.5627670288086</v>
+        <v>42.5627708435059</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>43.3410606384277</v>
+        <v>43.3410530090332</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>42.903263092041</v>
+        <v>42.9032669067383</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>44.75</v>
       </c>
       <c r="G1471" t="n">
-        <v>43.5356254577637</v>
+        <v>43.5356292724609</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1472" t="n">
-        <v>44.1679916381836</v>
+        <v>44.1679954528809</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>46.5</v>
       </c>
       <c r="G1480" t="n">
-        <v>45.2381401062012</v>
+        <v>45.2381362915039</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>42.25</v>
       </c>
       <c r="G1482" t="n">
-        <v>41.1034736633301</v>
+        <v>41.1034660339355</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>42.25</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.1034736633301</v>
+        <v>41.1034660339355</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G1484" t="n">
-        <v>42.5141258239746</v>
+        <v>42.5141220092773</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>43.3499984741211</v>
       </c>
       <c r="G1488" t="n">
-        <v>42.1736221313477</v>
+        <v>42.1736145019531</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>41.7844734191895</v>
+        <v>41.7844772338867</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>38.7199554443359</v>
+        <v>38.7199516296387</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G1497" t="n">
-        <v>38.0875930786133</v>
+        <v>38.0875968933105</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>41.75</v>
       </c>
       <c r="G1502" t="n">
-        <v>40.6170387268066</v>
+        <v>40.6170349121094</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>39.692813873291</v>
+        <v>39.6928176879883</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>41.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>40.3738212585449</v>
+        <v>40.3738250732422</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>41.5</v>
       </c>
       <c r="G1509" t="n">
-        <v>40.3738212585449</v>
+        <v>40.3738250732422</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1510" t="n">
-        <v>41.6871910095215</v>
+        <v>41.6871871948242</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1513" t="n">
-        <v>40.9575386047363</v>
+        <v>40.9575424194336</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>41.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>40.6170387268066</v>
+        <v>40.6170349121094</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1518" t="n">
-        <v>41.4926147460938</v>
+        <v>41.492618560791</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>39.8387451171875</v>
+        <v>39.8387489318848</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1520" t="n">
-        <v>40.2278938293457</v>
+        <v>40.2278900146484</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>43.5</v>
       </c>
       <c r="G1523" t="n">
-        <v>42.3195533752441</v>
+        <v>42.3195495605469</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>44</v>
       </c>
       <c r="G1525" t="n">
-        <v>42.805980682373</v>
+        <v>42.8059768676758</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1528" t="n">
-        <v>41.4926147460938</v>
+        <v>41.492618560791</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>41.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>40.3738212585449</v>
+        <v>40.3738250732422</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1531" t="n">
-        <v>40.0819664001465</v>
+        <v>40.0819625854492</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1534" t="n">
-        <v>40.4711074829102</v>
+        <v>40.4711112976074</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1537" t="n">
-        <v>42.7086982727051</v>
+        <v>42.7086944580078</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>44.5</v>
       </c>
       <c r="G1539" t="n">
-        <v>43.2924118041992</v>
+        <v>43.2924156188965</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1546" t="n">
-        <v>38.9631690979004</v>
+        <v>38.9631729125977</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1547" t="n">
-        <v>40.9575386047363</v>
+        <v>40.9575424194336</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>42.4168319702148</v>
+        <v>42.4168395996094</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>41.75</v>
       </c>
       <c r="G1551" t="n">
-        <v>40.6170387268066</v>
+        <v>40.6170349121094</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>39.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>38.4280967712402</v>
+        <v>38.4281005859375</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1553" t="n">
-        <v>36.2877998352051</v>
+        <v>36.2877960205078</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1556" t="n">
-        <v>35.6554412841797</v>
+        <v>35.6554374694824</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G1557" t="n">
-        <v>34.5852813720703</v>
+        <v>34.5852851867676</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>36.4500007629395</v>
       </c>
       <c r="G1558" t="n">
-        <v>35.460865020752</v>
+        <v>35.4608612060547</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>36.5796546936035</v>
+        <v>36.5796585083008</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>37.5</v>
       </c>
       <c r="G1561" t="n">
-        <v>36.482364654541</v>
+        <v>36.4823684692383</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G1562" t="n">
-        <v>35.9472999572754</v>
+        <v>35.9472961425781</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>37</v>
       </c>
       <c r="G1563" t="n">
-        <v>35.9959449768066</v>
+        <v>35.9959373474121</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>35.3149337768555</v>
+        <v>35.3149375915527</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G1565" t="n">
-        <v>34.3907165527344</v>
+        <v>34.3907089233398</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>35.3149337768555</v>
+        <v>35.3149375915527</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>37.25</v>
       </c>
       <c r="G1567" t="n">
-        <v>36.2391510009766</v>
+        <v>36.2391548156738</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>37</v>
       </c>
       <c r="G1569" t="n">
-        <v>35.9959449768066</v>
+        <v>35.9959373474121</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1571" t="n">
-        <v>32.0072059631348</v>
+        <v>32.0071983337402</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1573" t="n">
-        <v>31.5207691192627</v>
+        <v>31.52077293396</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G1575" t="n">
-        <v>32.250415802002</v>
+        <v>32.2504196166992</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>34.25</v>
       </c>
       <c r="G1576" t="n">
-        <v>33.3205680847168</v>
+        <v>33.3205642700195</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1578" t="n">
-        <v>34.4393577575684</v>
+        <v>34.4393615722656</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>31.909912109375</v>
+        <v>31.9099159240723</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1582" t="n">
-        <v>33.4664916992188</v>
+        <v>33.466495513916</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G1588" t="n">
-        <v>32.5422782897949</v>
+        <v>32.5422744750977</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1590" t="n">
-        <v>31.5207691192627</v>
+        <v>31.52077293396</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>31.9599990844727</v>
       </c>
       <c r="G1591" t="n">
-        <v>31.0927085876465</v>
+        <v>31.0927104949951</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>31.7600002288818</v>
       </c>
       <c r="G1592" t="n">
-        <v>30.898136138916</v>
+        <v>30.8981342315674</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>30.3533344268799</v>
+        <v>30.3533325195312</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>33</v>
       </c>
       <c r="G1596" t="n">
-        <v>32.1044883728027</v>
+        <v>32.1044845581055</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1599" t="n">
-        <v>31.2094535827637</v>
+        <v>31.2094554901123</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>31.7600002288818</v>
       </c>
       <c r="G1603" t="n">
-        <v>30.898136138916</v>
+        <v>30.8981342315674</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1604" t="n">
-        <v>29.7696132659912</v>
+        <v>29.7696151733398</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1610" t="n">
-        <v>28.7578372955322</v>
+        <v>28.7578392028809</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>29.6200008392334</v>
       </c>
       <c r="G1611" t="n">
-        <v>28.8162078857422</v>
+        <v>28.8162097930908</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1613" t="n">
-        <v>28.1935749053955</v>
+        <v>28.1935787200928</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>28.3103199005127</v>
+        <v>28.3103218078613</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1615" t="n">
-        <v>26.9093952178955</v>
+        <v>26.9093971252441</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>28.1157474517822</v>
+        <v>28.1157455444336</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1619" t="n">
-        <v>28.4465179443359</v>
+        <v>28.4465198516846</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>34.75</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>284617</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>34.8499984741211</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>30.4500007629395</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>34.7999992370605</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>30.6000003814697</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>30.6000003814697</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82393550872803</v>
+        <v>6.82393598556519</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>6.63438177108765</v>
+        <v>6.6343822479248</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>6.74458742141724</v>
+        <v>6.74458789825439</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>6.74458742141724</v>
+        <v>6.74458789825439</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.61234092712402</v>
+        <v>6.61234140396118</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>6.7886700630188</v>
+        <v>6.78867053985596</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>6.52417659759521</v>
+        <v>6.52417612075806</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>6.07453632354736</v>
+        <v>6.07453727722168</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>6.3258056640625</v>
+        <v>6.32580661773682</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>6.53299331665039</v>
+        <v>6.53299283981323</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>6.62997388839722</v>
+        <v>6.62997341156006</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G22" t="n">
-        <v>6.63879060745239</v>
+        <v>6.63879108428955</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6652398109436</v>
+        <v>6.66524028778076</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>6.65642356872559</v>
+        <v>6.65642261505127</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G27" t="n">
-        <v>5.99519014358521</v>
+        <v>5.99518918991089</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87616777420044</v>
+        <v>5.87616729736328</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>6.25968313217163</v>
+        <v>6.25968265533447</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G30" t="n">
-        <v>6.03927087783813</v>
+        <v>6.03927230834961</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>6.37429618835449</v>
+        <v>6.37429571151733</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G33" t="n">
-        <v>6.31698942184448</v>
+        <v>6.31698989868164</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>6.52417659759521</v>
+        <v>6.52417612075806</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>6.30817317962646</v>
+        <v>6.30817365646362</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G37" t="n">
-        <v>6.40074586868286</v>
+        <v>6.40074634552002</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>6.36548089981079</v>
+        <v>6.36548042297363</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>6.37429618835449</v>
+        <v>6.37429571151733</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.125</v>
       </c>
       <c r="G40" t="n">
-        <v>6.28172397613525</v>
+        <v>6.28172492980957</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>6.33021450042725</v>
+        <v>6.3302149772644</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>6.60793304443359</v>
+        <v>6.60793256759644</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>6.40956211090088</v>
+        <v>6.4095630645752</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>6.40956211090088</v>
+        <v>6.4095630645752</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.20237636566162</v>
+        <v>6.20237588882446</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>6.25086688995361</v>
+        <v>6.25086641311646</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>6.25968313217163</v>
+        <v>6.25968265533447</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G51" t="n">
-        <v>6.2420506477356</v>
+        <v>6.24204969406128</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G52" t="n">
-        <v>6.60352420806885</v>
+        <v>6.60352373123169</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>6.41397094726562</v>
+        <v>6.41397047042847</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G56" t="n">
-        <v>6.3875207901001</v>
+        <v>6.38752126693726</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G57" t="n">
-        <v>6.42719602584839</v>
+        <v>6.42719507217407</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.5</v>
       </c>
       <c r="G58" t="n">
-        <v>6.61234092712402</v>
+        <v>6.61234140396118</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>6.43160438537598</v>
+        <v>6.43160486221313</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G60" t="n">
-        <v>6.34343910217285</v>
+        <v>6.34343957901001</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="n">
-        <v>6.17151927947998</v>
+        <v>6.17151737213135</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>6.04367923736572</v>
+        <v>6.04368019104004</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7</v>
       </c>
       <c r="G63" t="n">
-        <v>6.17151927947998</v>
+        <v>6.17151737213135</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>6.2640905380249</v>
+        <v>6.26409101486206</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.3875207901001</v>
+        <v>6.38752126693726</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>6.26849937438965</v>
+        <v>6.26849985122681</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G68" t="n">
-        <v>6.22441625595093</v>
+        <v>6.22441673278809</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G69" t="n">
-        <v>6.19796752929688</v>
+        <v>6.19796800613403</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>6.16710948944092</v>
+        <v>6.16711044311523</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.125</v>
       </c>
       <c r="G73" t="n">
-        <v>6.28172397613525</v>
+        <v>6.28172492980957</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>6.25968313217163</v>
+        <v>6.25968265533447</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G75" t="n">
-        <v>6.40074586868286</v>
+        <v>6.40074634552002</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G76" t="n">
-        <v>6.30817317962646</v>
+        <v>6.30817365646362</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42719602584839</v>
+        <v>6.42719507217407</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>6.60352420806885</v>
+        <v>6.60352373123169</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G81" t="n">
-        <v>6.4536452293396</v>
+        <v>6.45364475250244</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>6.47127819061279</v>
+        <v>6.47127771377563</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>6.39633798599243</v>
+        <v>6.39633846282959</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>6.40956211090088</v>
+        <v>6.4095630645752</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>6.42756652832031</v>
+        <v>6.42756748199463</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>6.51758861541748</v>
+        <v>6.51758813858032</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>6.41856527328491</v>
+        <v>6.41856479644775</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>6.48157978057861</v>
+        <v>6.48158025741577</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G94" t="n">
-        <v>6.5716028213501</v>
+        <v>6.57160234451294</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>6.65712261199951</v>
+        <v>6.65712308883667</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>6.48157978057861</v>
+        <v>6.48158025741577</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G98" t="n">
-        <v>6.67962884902954</v>
+        <v>6.67962837219238</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>6.82366371154785</v>
+        <v>6.82366275787354</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G101" t="n">
-        <v>6.91818618774414</v>
+        <v>6.9181866645813</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.95869541168213</v>
+        <v>6.9586968421936</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G103" t="n">
-        <v>7.07572507858276</v>
+        <v>7.07572460174561</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>7.29177856445312</v>
+        <v>7.29177808761597</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>8.25</v>
       </c>
       <c r="G106" t="n">
-        <v>7.42681169509888</v>
+        <v>7.42681121826172</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G107" t="n">
-        <v>7.27377367019653</v>
+        <v>7.27377319335938</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>7.35029220581055</v>
+        <v>7.35029268264771</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G109" t="n">
-        <v>7.22876167297363</v>
+        <v>7.22876214981079</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>7.20175647735596</v>
+        <v>7.20175552368164</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.27377367019653</v>
+        <v>7.27377319335938</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.19725513458252</v>
+        <v>7.1972541809082</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>7.11173343658447</v>
+        <v>7.11173391342163</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.75</v>
       </c>
       <c r="G116" t="n">
-        <v>6.97670125961304</v>
+        <v>6.97669982910156</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>7.05321979522705</v>
+        <v>7.05321931838989</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>6.93168973922729</v>
+        <v>6.93169021606445</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>6.81466150283813</v>
+        <v>6.81466197967529</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.875</v>
       </c>
       <c r="G120" t="n">
-        <v>7.08922815322876</v>
+        <v>7.08922910690308</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>7.28277635574341</v>
+        <v>7.28277587890625</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G123" t="n">
-        <v>7.29627847671509</v>
+        <v>7.29627895355225</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>6.9721999168396</v>
+        <v>6.97219944000244</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>6.70663452148438</v>
+        <v>6.70663499832153</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.95869541168213</v>
+        <v>6.9586968421936</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.93168973922729</v>
+        <v>6.93169021606445</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G128" t="n">
-        <v>7.06222152709961</v>
+        <v>7.06222200393677</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>6.83266592025757</v>
+        <v>6.83266496658325</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>6.65262126922607</v>
+        <v>6.65262174606323</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G132" t="n">
-        <v>6.4725775718689</v>
+        <v>6.47257804870605</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>6.54459524154663</v>
+        <v>6.54459619522095</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.5716028213501</v>
+        <v>6.57160234451294</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G137" t="n">
-        <v>6.4725775718689</v>
+        <v>6.47257804870605</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>6.41856527328491</v>
+        <v>6.41856479644775</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>6.3915581703186</v>
+        <v>6.39155721664429</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>6.72013807296753</v>
+        <v>6.72013902664185</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.25</v>
       </c>
       <c r="G142" t="n">
-        <v>6.52659130096436</v>
+        <v>6.52659177780151</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>6.43656969070435</v>
+        <v>6.43656921386719</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>6.4095630645752</v>
+        <v>6.40956258773804</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>6.72913980484009</v>
+        <v>6.7291407585144</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>6.54009437561035</v>
+        <v>6.54009389877319</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>6.54459524154663</v>
+        <v>6.54459619522095</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.5</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164651870728</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.5</v>
       </c>
       <c r="G149" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164651870728</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G150" t="n">
-        <v>6.68413019180298</v>
+        <v>6.68412971496582</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G151" t="n">
-        <v>6.54009437561035</v>
+        <v>6.54009389877319</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G152" t="n">
-        <v>6.46357583999634</v>
+        <v>6.4635763168335</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>6.6346173286438</v>
+        <v>6.63461780548096</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164651870728</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>6.81466150283813</v>
+        <v>6.81466197967529</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>6.70663452148438</v>
+        <v>6.70663499832153</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>6.66162395477295</v>
+        <v>6.66162347793579</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>6.73364114761353</v>
+        <v>6.73364210128784</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G160" t="n">
-        <v>6.850670337677</v>
+        <v>6.85067081451416</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>6.67512655258179</v>
+        <v>6.6751275062561</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>6.72013807296753</v>
+        <v>6.72013902664185</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66162395477295</v>
+        <v>6.66162347793579</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>6.70663452148438</v>
+        <v>6.70663499832153</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>6.76965045928955</v>
+        <v>6.76964950561523</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>6.78765535354614</v>
+        <v>6.78765487670898</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>6.7966570854187</v>
+        <v>6.79665660858154</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G170" t="n">
-        <v>6.77865266799927</v>
+        <v>6.77865314483643</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>6.84166765213013</v>
+        <v>6.84166812896729</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>6.95419549942017</v>
+        <v>6.95419502258301</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G175" t="n">
-        <v>7.07572507858276</v>
+        <v>7.07572460174561</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G176" t="n">
-        <v>7.14774227142334</v>
+        <v>7.14774322509766</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20175647735596</v>
+        <v>7.20175552368164</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.05321979522705</v>
+        <v>7.05321931838989</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>7.05321979522705</v>
+        <v>7.05321931838989</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G184" t="n">
-        <v>6.94969320297241</v>
+        <v>6.94969367980957</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G185" t="n">
-        <v>6.94969320297241</v>
+        <v>6.94969367980957</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>6.94969320297241</v>
+        <v>6.94969367980957</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>6.93168973922729</v>
+        <v>6.93169021606445</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.7966570854187</v>
+        <v>6.79665660858154</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.5</v>
       </c>
       <c r="G194" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164651870728</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G195" t="n">
-        <v>6.85967206954956</v>
+        <v>6.85967254638672</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.90468311309814</v>
+        <v>6.90468406677246</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>6.99470567703247</v>
+        <v>6.99470520019531</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G198" t="n">
-        <v>6.96319723129272</v>
+        <v>6.96319770812988</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G199" t="n">
-        <v>7.16574716567993</v>
+        <v>7.16574764251709</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8</v>
       </c>
       <c r="G200" t="n">
-        <v>7.20175647735596</v>
+        <v>7.20175552368164</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G201" t="n">
-        <v>7.14774227142334</v>
+        <v>7.14774322509766</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>6.99470567703247</v>
+        <v>6.99470520019531</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G204" t="n">
-        <v>7.07572507858276</v>
+        <v>7.07572460174561</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G205" t="n">
-        <v>7.02171230316162</v>
+        <v>7.02171182632446</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G209" t="n">
-        <v>7.05772113800049</v>
+        <v>7.05772066116333</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>7.20175647735596</v>
+        <v>7.20175552368164</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>7.27377367019653</v>
+        <v>7.27377319335938</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G216" t="n">
-        <v>7.19275379180908</v>
+        <v>7.19275426864624</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G217" t="n">
-        <v>7.21975994110107</v>
+        <v>7.21976089477539</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>7.16124629974365</v>
+        <v>7.16124534606934</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G221" t="n">
-        <v>7.32778644561768</v>
+        <v>7.32778692245483</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>6.78765535354614</v>
+        <v>6.78765487670898</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.5</v>
       </c>
       <c r="G226" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164651870728</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G227" t="n">
-        <v>7.00820875167847</v>
+        <v>7.00820922851562</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G228" t="n">
-        <v>7.15224361419678</v>
+        <v>7.15224409103394</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>7.11173343658447</v>
+        <v>7.11173391342163</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>7.11173343658447</v>
+        <v>7.11173391342163</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>7.20175647735596</v>
+        <v>7.20175552368164</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8</v>
       </c>
       <c r="G234" t="n">
-        <v>7.20175647735596</v>
+        <v>7.20175552368164</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G236" t="n">
-        <v>6.94969320297241</v>
+        <v>6.94969367980957</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G237" t="n">
-        <v>7.21975994110107</v>
+        <v>7.21976089477539</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8</v>
       </c>
       <c r="G238" t="n">
-        <v>7.20175647735596</v>
+        <v>7.20175552368164</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G239" t="n">
-        <v>7.15224361419678</v>
+        <v>7.15224409103394</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G241" t="n">
-        <v>7.48982572555542</v>
+        <v>7.48982524871826</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>7.47182178497314</v>
+        <v>7.47182130813599</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G246" t="n">
-        <v>7.15224361419678</v>
+        <v>7.15224409103394</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>7.24676656723022</v>
+        <v>7.24676704406738</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>7.69687604904175</v>
+        <v>7.69687509536743</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>7.69687604904175</v>
+        <v>7.69687509536743</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.5</v>
       </c>
       <c r="G255" t="n">
-        <v>7.65186548233032</v>
+        <v>7.65186643600464</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>7.64736461639404</v>
+        <v>7.64736413955688</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G259" t="n">
-        <v>7.93993616104126</v>
+        <v>7.93993473052979</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G260" t="n">
-        <v>8.30902576446533</v>
+        <v>8.30902481079102</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G261" t="n">
-        <v>8.38104438781738</v>
+        <v>8.38104248046875</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G262" t="n">
-        <v>8.41705417633057</v>
+        <v>8.41705322265625</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G263" t="n">
-        <v>8.54308319091797</v>
+        <v>8.54308223724365</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G264" t="n">
-        <v>8.34503269195557</v>
+        <v>8.34503555297852</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>8.21000003814697</v>
+        <v>8.21000194549561</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G270" t="n">
-        <v>8.30452632904053</v>
+        <v>8.30452537536621</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G272" t="n">
-        <v>8.29552173614502</v>
+        <v>8.29552268981934</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>8.29102230072021</v>
+        <v>8.2910213470459</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>8.33153057098389</v>
+        <v>8.3315315246582</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27301692962646</v>
+        <v>8.27301597595215</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>8.26851558685303</v>
+        <v>8.26851654052734</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.30452632904053</v>
+        <v>8.30452537536621</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G281" t="n">
-        <v>8.27301692962646</v>
+        <v>8.27301597595215</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.2370080947876</v>
+        <v>8.23700904846191</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G285" t="n">
-        <v>8.04346179962158</v>
+        <v>8.04346084594727</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G289" t="n">
-        <v>8.37204074859619</v>
+        <v>8.37203979492188</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G291" t="n">
-        <v>8.37204074859619</v>
+        <v>8.37203979492188</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G292" t="n">
-        <v>8.39004707336426</v>
+        <v>8.39004516601562</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.37204074859619</v>
+        <v>8.37203979492188</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>8.29102230072021</v>
+        <v>8.2910213470459</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G295" t="n">
-        <v>8.19649791717529</v>
+        <v>8.19649696350098</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G296" t="n">
-        <v>8.24151039123535</v>
+        <v>8.24150943756104</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G303" t="n">
-        <v>8.37204074859619</v>
+        <v>8.37203979492188</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.38104438781738</v>
+        <v>8.38104248046875</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.37204074859619</v>
+        <v>8.37203979492188</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>8.39904880523682</v>
+        <v>8.3990478515625</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>8.37204074859619</v>
+        <v>8.37203979492188</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>9.18223857879639</v>
+        <v>9.18223762512207</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G314" t="n">
-        <v>9.16423416137695</v>
+        <v>9.16423606872559</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>9.1732349395752</v>
+        <v>9.17323589324951</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G316" t="n">
-        <v>9.16423416137695</v>
+        <v>9.16423606872559</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G317" t="n">
-        <v>9.19123935699463</v>
+        <v>9.19124126434326</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G318" t="n">
-        <v>9.16423416137695</v>
+        <v>9.16423606872559</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G319" t="n">
-        <v>9.16423416137695</v>
+        <v>9.16423606872559</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10</v>
       </c>
       <c r="G321" t="n">
-        <v>9.00219535827637</v>
+        <v>9.00219345092773</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10</v>
       </c>
       <c r="G322" t="n">
-        <v>9.00219535827637</v>
+        <v>9.00219345092773</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G323" t="n">
-        <v>9.18223857879639</v>
+        <v>9.18223762512207</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>9.09221744537354</v>
+        <v>9.09221649169922</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>9.18223857879639</v>
+        <v>9.18223762512207</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>9.18223857879639</v>
+        <v>9.18223762512207</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G327" t="n">
-        <v>9.19123935699463</v>
+        <v>9.19124126434326</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>9.3172721862793</v>
+        <v>9.31727313995361</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G330" t="n">
-        <v>9.51532077789307</v>
+        <v>9.51531791687012</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>9.43430042266846</v>
+        <v>9.43429851531982</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>9.76738166809082</v>
+        <v>9.7673807144165</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>9.85740184783936</v>
+        <v>9.8574047088623</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G334" t="n">
-        <v>10.1724796295166</v>
+        <v>10.1724815368652</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>10.1724796295166</v>
+        <v>10.1724815368652</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>11</v>
       </c>
       <c r="G336" t="n">
-        <v>9.90241432189941</v>
+        <v>9.90241527557373</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>10.4065370559692</v>
+        <v>10.4065380096436</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G339" t="n">
-        <v>10.7666254043579</v>
+        <v>10.7666244506836</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>10.8926572799683</v>
+        <v>10.8926563262939</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G342" t="n">
-        <v>10.6946058273315</v>
+        <v>10.6946067810059</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>10.7126111984253</v>
+        <v>10.7126092910767</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G345" t="n">
-        <v>10.4355611801147</v>
+        <v>10.4355621337891</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G346" t="n">
-        <v>10.1862163543701</v>
+        <v>10.1862173080444</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G348" t="n">
-        <v>10.3432102203369</v>
+        <v>10.3432111740112</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>11.25</v>
       </c>
       <c r="G349" t="n">
-        <v>10.3893880844116</v>
+        <v>10.3893871307373</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>10.4355611801147</v>
+        <v>10.4355621337891</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>10.4355611801147</v>
+        <v>10.4355621337891</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G353" t="n">
-        <v>10.1862163543701</v>
+        <v>10.1862173080444</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G355" t="n">
-        <v>10.3432102203369</v>
+        <v>10.3432111740112</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G356" t="n">
-        <v>10.4724998474121</v>
+        <v>10.4725017547607</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G357" t="n">
-        <v>10.4724998474121</v>
+        <v>10.4725017547607</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G358" t="n">
-        <v>10.4540309906006</v>
+        <v>10.4540319442749</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>11.25</v>
       </c>
       <c r="G359" t="n">
-        <v>10.3893880844116</v>
+        <v>10.3893871307373</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>10.3432102203369</v>
+        <v>10.3432111740112</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G361" t="n">
-        <v>10.4355611801147</v>
+        <v>10.4355621337891</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>11.0358371734619</v>
+        <v>11.0358362197876</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>11.7284622192383</v>
+        <v>11.7284631729126</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>11.1743621826172</v>
+        <v>11.1743612289429</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G369" t="n">
-        <v>11.0543079376221</v>
+        <v>11.0543060302734</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G370" t="n">
-        <v>11.1004829406738</v>
+        <v>11.1004838943481</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G372" t="n">
-        <v>10.7864923477173</v>
+        <v>10.7864933013916</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>10.7126121520996</v>
+        <v>10.712610244751</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G374" t="n">
-        <v>10.6941413879395</v>
+        <v>10.6941404342651</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434862136841</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434862136841</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434862136841</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>10.5279111862183</v>
+        <v>10.5279102325439</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G380" t="n">
-        <v>10.6941413879395</v>
+        <v>10.6941404342651</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12</v>
       </c>
       <c r="G381" t="n">
-        <v>11.082010269165</v>
+        <v>11.0820121765137</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>11.0173664093018</v>
+        <v>11.0173683166504</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G383" t="n">
-        <v>11.442177772522</v>
+        <v>11.4421768188477</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G384" t="n">
-        <v>11.0266017913818</v>
+        <v>11.0266008377075</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>10.8973121643066</v>
+        <v>10.897310256958</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>11.3590621948242</v>
+        <v>11.3590631484985</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G388" t="n">
-        <v>11.6638174057007</v>
+        <v>11.663818359375</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>13.5</v>
       </c>
       <c r="G392" t="n">
-        <v>12.4672632217407</v>
+        <v>12.4672651290894</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G393" t="n">
-        <v>12.4764995574951</v>
+        <v>12.4764986038208</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G394" t="n">
-        <v>12.6242580413818</v>
+        <v>12.6242589950562</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.75</v>
       </c>
       <c r="G395" t="n">
-        <v>12.6981391906738</v>
+        <v>12.6981382369995</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G396" t="n">
-        <v>12.4857349395752</v>
+        <v>12.4857330322266</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7443141937256</v>
+        <v>12.7443151473999</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G398" t="n">
-        <v>12.6796674728394</v>
+        <v>12.679669380188</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>12.4949684143066</v>
+        <v>12.494969367981</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G400" t="n">
-        <v>12.5319080352783</v>
+        <v>12.5319089889526</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.5134382247925</v>
+        <v>12.5134401321411</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>12.4210891723633</v>
+        <v>12.421088218689</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G403" t="n">
-        <v>12.4487953186035</v>
+        <v>12.4487924575806</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G405" t="n">
-        <v>12.4949684143066</v>
+        <v>12.494969367981</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G409" t="n">
-        <v>12.1348037719727</v>
+        <v>12.134804725647</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G410" t="n">
-        <v>12.3472089767456</v>
+        <v>12.3472080230713</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749141693115</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G413" t="n">
-        <v>12.3195037841797</v>
+        <v>12.3195028305054</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>11.8392848968506</v>
+        <v>11.8392820358276</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>13.25</v>
       </c>
       <c r="G415" t="n">
-        <v>12.2363891601562</v>
+        <v>12.2363901138306</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G416" t="n">
-        <v>12.1255674362183</v>
+        <v>12.1255693435669</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13</v>
       </c>
       <c r="G417" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055141448975</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2640924453735</v>
+        <v>12.2640943527222</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2179193496704</v>
+        <v>12.2179183959961</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="n">
-        <v>11.8392848968506</v>
+        <v>11.8392820358276</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>13</v>
       </c>
       <c r="G426" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055141448975</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749141693115</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749141693115</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.2825622558594</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G430" t="n">
-        <v>12.3933849334717</v>
+        <v>12.393383026123</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G431" t="n">
-        <v>12.3010320663452</v>
+        <v>12.3010330200195</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3287382125854</v>
+        <v>12.3287391662598</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.25</v>
       </c>
       <c r="G433" t="n">
-        <v>12.2363891601562</v>
+        <v>12.2363901138306</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G434" t="n">
-        <v>12.1070985794067</v>
+        <v>12.1070976257324</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>12.2179193496704</v>
+        <v>12.2179183959961</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G436" t="n">
-        <v>12.1255674362183</v>
+        <v>12.1255693435669</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G437" t="n">
-        <v>12.1070985794067</v>
+        <v>12.1070976257324</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13</v>
       </c>
       <c r="G438" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055141448975</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G441" t="n">
-        <v>12.4026184082031</v>
+        <v>12.4026193618774</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G442" t="n">
-        <v>12.1532726287842</v>
+        <v>12.1532735824585</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G444" t="n">
-        <v>12.2825622558594</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G446" t="n">
-        <v>12.2548589706421</v>
+        <v>12.2548580169678</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G447" t="n">
-        <v>12.208683013916</v>
+        <v>12.2086820602417</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G448" t="n">
-        <v>12.2548589706421</v>
+        <v>12.2548580169678</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>12.3287382125854</v>
+        <v>12.3287391662598</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>13.25</v>
       </c>
       <c r="G450" t="n">
-        <v>12.2363891601562</v>
+        <v>12.2363901138306</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G451" t="n">
-        <v>12.0147476196289</v>
+        <v>12.0147485733032</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G453" t="n">
-        <v>11.3960018157959</v>
+        <v>11.3960027694702</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7469320297241</v>
+        <v>11.7469339370728</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G457" t="n">
-        <v>11.6176424026489</v>
+        <v>11.6176433563232</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G459" t="n">
-        <v>11.700758934021</v>
+        <v>11.700756072998</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>11.6638174057007</v>
+        <v>11.663818359375</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G463" t="n">
-        <v>11.7284622192383</v>
+        <v>11.7284631729126</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>11.7284622192383</v>
+        <v>11.7284631729126</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>12.75</v>
       </c>
       <c r="G466" t="n">
-        <v>11.77463722229</v>
+        <v>11.7746381759644</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G469" t="n">
-        <v>11.8392848968506</v>
+        <v>11.8392820358276</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>12.1809778213501</v>
+        <v>12.1809768676758</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G472" t="n">
-        <v>12.1809778213501</v>
+        <v>12.1809768676758</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>11.7284622192383</v>
+        <v>11.7284631729126</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7469320297241</v>
+        <v>11.7469339370728</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G476" t="n">
-        <v>11.7469320297241</v>
+        <v>11.7469339370728</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G477" t="n">
-        <v>11.7192268371582</v>
+        <v>11.7192277908325</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G478" t="n">
-        <v>11.7469320297241</v>
+        <v>11.7469339370728</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G479" t="n">
-        <v>11.6730518341064</v>
+        <v>11.6730527877808</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G481" t="n">
-        <v>11.1466579437256</v>
+        <v>11.146656036377</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G482" t="n">
-        <v>11.2482423782349</v>
+        <v>11.2482433319092</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G483" t="n">
-        <v>11.1466579437256</v>
+        <v>11.146656036377</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G484" t="n">
-        <v>11.1189517974854</v>
+        <v>11.1189527511597</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>11.4975881576538</v>
+        <v>11.4975891113281</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G487" t="n">
-        <v>11.4237070083618</v>
+        <v>11.4237060546875</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G488" t="n">
-        <v>11.5529985427856</v>
+        <v>11.552996635437</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>11.442177772522</v>
+        <v>11.4421768188477</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G492" t="n">
-        <v>11.5345287322998</v>
+        <v>11.5345268249512</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>11.4514122009277</v>
+        <v>11.4514102935791</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>11.4514122009277</v>
+        <v>11.4514102935791</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G497" t="n">
-        <v>11.8115787506104</v>
+        <v>11.8115768432617</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>12.75</v>
       </c>
       <c r="G498" t="n">
-        <v>11.77463722229</v>
+        <v>11.7746381759644</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.0978631973267</v>
+        <v>12.097864151001</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G503" t="n">
-        <v>11.6730518341064</v>
+        <v>11.6730527877808</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>13</v>
       </c>
       <c r="G504" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055141448975</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>12.0978631973267</v>
+        <v>12.097864151001</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G507" t="n">
-        <v>12.3195037841797</v>
+        <v>12.3195028305054</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G508" t="n">
-        <v>12.208683013916</v>
+        <v>12.2086820602417</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749141693115</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G510" t="n">
-        <v>12.3933849334717</v>
+        <v>12.393383026123</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G512" t="n">
-        <v>12.4210891723633</v>
+        <v>12.421088218689</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G513" t="n">
-        <v>12.3933849334717</v>
+        <v>12.393383026123</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749141693115</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G515" t="n">
-        <v>12.3933849334717</v>
+        <v>12.393383026123</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G516" t="n">
-        <v>12.4487953186035</v>
+        <v>12.4487924575806</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G517" t="n">
-        <v>12.8736038208008</v>
+        <v>12.8736028671265</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G519" t="n">
-        <v>14.0556840896606</v>
+        <v>14.0556859970093</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>14.0372152328491</v>
+        <v>14.0372142791748</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>13.9448652267456</v>
+        <v>13.9448661804199</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G523" t="n">
-        <v>14.5728454589844</v>
+        <v>14.5728464126587</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>15</v>
       </c>
       <c r="G524" t="n">
-        <v>13.8525161743164</v>
+        <v>13.8525142669678</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>13.5754642486572</v>
+        <v>13.5754652023315</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G526" t="n">
-        <v>14.1480350494385</v>
+        <v>14.1480340957642</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G528" t="n">
-        <v>13.6493434906006</v>
+        <v>13.6493444442749</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>13.9448652267456</v>
+        <v>13.9448661804199</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G530" t="n">
-        <v>14.3327379226685</v>
+        <v>14.3327369689941</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G531" t="n">
-        <v>14.4620265960693</v>
+        <v>14.462025642395</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G532" t="n">
-        <v>14.5174360275269</v>
+        <v>14.5174350738525</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G533" t="n">
-        <v>14.4250860214233</v>
+        <v>14.425085067749</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G534" t="n">
-        <v>14.1295642852783</v>
+        <v>14.1295652389526</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G536" t="n">
-        <v>12.9474830627441</v>
+        <v>12.9474849700928</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G538" t="n">
-        <v>13.5754642486572</v>
+        <v>13.5754652023315</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>12.6889038085938</v>
+        <v>12.6889028549194</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>14</v>
       </c>
       <c r="G544" t="n">
-        <v>12.9290151596069</v>
+        <v>12.9290142059326</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G545" t="n">
-        <v>13.4646444320679</v>
+        <v>13.4646463394165</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G546" t="n">
-        <v>13.2614736557007</v>
+        <v>13.261474609375</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G547" t="n">
-        <v>12.6889038085938</v>
+        <v>12.6889028549194</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>12.6889038085938</v>
+        <v>12.6889028549194</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G550" t="n">
-        <v>12.0609226226807</v>
+        <v>12.060923576355</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749141693115</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G552" t="n">
-        <v>12.0609226226807</v>
+        <v>12.060923576355</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>11.7284622192383</v>
+        <v>11.7284631729126</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G555" t="n">
-        <v>11.7838735580444</v>
+        <v>11.7838726043701</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>12.0609226226807</v>
+        <v>12.060923576355</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749141693115</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G560" t="n">
-        <v>12.6704330444336</v>
+        <v>12.6704339981079</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>12.5596141815186</v>
+        <v>12.5596132278442</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>12.0978631973267</v>
+        <v>12.097864151001</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>12.2825622558594</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G567" t="n">
-        <v>12.1532726287842</v>
+        <v>12.1532735824585</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G568" t="n">
-        <v>12.0239839553833</v>
+        <v>12.023983001709</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>12.7443141937256</v>
+        <v>12.7443151473999</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>12.4118518829346</v>
+        <v>12.4118528366089</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>13</v>
       </c>
       <c r="G575" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055141448975</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>11.7654027938843</v>
+        <v>11.76540184021</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G580" t="n">
-        <v>12.2825622558594</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G582" t="n">
-        <v>12.208683013916</v>
+        <v>12.2086820602417</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G584" t="n">
-        <v>12.208683013916</v>
+        <v>12.2086820602417</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>13.2984142303467</v>
+        <v>13.298415184021</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G590" t="n">
-        <v>14.8498954772949</v>
+        <v>14.8498964309692</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G593" t="n">
-        <v>14.7390747070312</v>
+        <v>14.7390766143799</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649600982666</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>15.3414392471313</v>
+        <v>15.3414373397827</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G597" t="n">
-        <v>15.1720237731934</v>
+        <v>15.1720266342163</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G598" t="n">
-        <v>15.0214328765869</v>
+        <v>15.0214347839355</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>16</v>
       </c>
       <c r="G599" t="n">
-        <v>15.05908203125</v>
+        <v>15.0590810775757</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G600" t="n">
-        <v>15.1155529022217</v>
+        <v>15.1155519485474</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>15.2473211288452</v>
+        <v>15.2473201751709</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G602" t="n">
-        <v>15.0214328765869</v>
+        <v>15.0214347839355</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>13.5531721115112</v>
+        <v>13.5531740188599</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G607" t="n">
-        <v>13.6284685134888</v>
+        <v>13.6284675598145</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>13.026104927063</v>
+        <v>13.0261068344116</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.0637531280518</v>
+        <v>13.0637540817261</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>13.026104927063</v>
+        <v>13.0261068344116</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G617" t="n">
-        <v>12.9508113861084</v>
+        <v>12.9508094787598</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G618" t="n">
-        <v>12.5743322372437</v>
+        <v>12.574333190918</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>13.5</v>
       </c>
       <c r="G620" t="n">
-        <v>12.7060995101929</v>
+        <v>12.7061004638672</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G622" t="n">
-        <v>12.2919750213623</v>
+        <v>12.2919759750366</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G624" t="n">
-        <v>12.6684532165527</v>
+        <v>12.6684522628784</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G628" t="n">
-        <v>13.6849403381348</v>
+        <v>13.6849412918091</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G629" t="n">
-        <v>13.7225875854492</v>
+        <v>13.7225885391235</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G633" t="n">
-        <v>13.6849403381348</v>
+        <v>13.6849412918091</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>13.3649349212646</v>
+        <v>13.3649339675903</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G637" t="n">
-        <v>13.4025821685791</v>
+        <v>13.4025831222534</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G638" t="n">
-        <v>13.3837585449219</v>
+        <v>13.3837594985962</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G639" t="n">
-        <v>13.1955223083496</v>
+        <v>13.1955213546753</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>13.0825786590576</v>
+        <v>13.082576751709</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>13.2708139419556</v>
+        <v>13.2708168029785</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G642" t="n">
-        <v>13.4214057922363</v>
+        <v>13.4214067459106</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G643" t="n">
-        <v>13.4025821685791</v>
+        <v>13.4025831222534</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>13.2708139419556</v>
+        <v>13.2708168029785</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G645" t="n">
-        <v>12.6684532165527</v>
+        <v>12.6684522628784</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G647" t="n">
-        <v>13.1578702926636</v>
+        <v>13.1578722000122</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>13.308464050293</v>
+        <v>13.3084650039673</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G649" t="n">
-        <v>13.1578702926636</v>
+        <v>13.1578722000122</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G651" t="n">
-        <v>12.6684532165527</v>
+        <v>12.6684522628784</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G652" t="n">
-        <v>13.026104927063</v>
+        <v>13.0261068344116</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G653" t="n">
-        <v>12.517861366272</v>
+        <v>12.5178623199463</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>13.0825786590576</v>
+        <v>13.082576751709</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G662" t="n">
-        <v>12.7625713348389</v>
+        <v>12.7625722885132</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G663" t="n">
-        <v>12.9508113861084</v>
+        <v>12.9508094787598</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G665" t="n">
-        <v>12.9131622314453</v>
+        <v>12.9131631851196</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G675" t="n">
-        <v>14.0614166259766</v>
+        <v>14.0614175796509</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G677" t="n">
-        <v>14.2496576309204</v>
+        <v>14.2496547698975</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>14.5</v>
       </c>
       <c r="G679" t="n">
-        <v>13.6472930908203</v>
+        <v>13.6472940444946</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G680" t="n">
-        <v>13.6284685134888</v>
+        <v>13.6284675598145</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G683" t="n">
-        <v>13.4967021942139</v>
+        <v>13.4967012405396</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G684" t="n">
-        <v>13.1955223083496</v>
+        <v>13.1955213546753</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G685" t="n">
-        <v>13.1955223083496</v>
+        <v>13.1955213546753</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>15</v>
       </c>
       <c r="G686" t="n">
-        <v>14.1178884506226</v>
+        <v>14.1178874969482</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>15.4355564117432</v>
+        <v>15.4355583190918</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G691" t="n">
-        <v>15.2096719741821</v>
+        <v>15.2096700668335</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G692" t="n">
-        <v>15.0967302322388</v>
+        <v>15.0967292785645</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>15.3414392471313</v>
+        <v>15.3414373397827</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G695" t="n">
-        <v>16.640287399292</v>
+        <v>16.6402854919434</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>16.5649890899658</v>
+        <v>16.5649909973145</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G700" t="n">
-        <v>16.1696872711182</v>
+        <v>16.1696891784668</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G701" t="n">
-        <v>15.849681854248</v>
+        <v>15.8496809005737</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>16.5</v>
       </c>
       <c r="G702" t="n">
-        <v>15.5296792984009</v>
+        <v>15.5296773910522</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G703" t="n">
-        <v>15.2096719741821</v>
+        <v>15.2096700668335</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G704" t="n">
-        <v>15.1720237731934</v>
+        <v>15.1720266342163</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>16.5</v>
       </c>
       <c r="G705" t="n">
-        <v>15.5296792984009</v>
+        <v>15.5296773910522</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G706" t="n">
-        <v>15.4543828964233</v>
+        <v>15.454381942749</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9461393356323</v>
+        <v>14.946138381958</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>16</v>
       </c>
       <c r="G708" t="n">
-        <v>15.05908203125</v>
+        <v>15.0590810775757</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G709" t="n">
-        <v>15.1532001495361</v>
+        <v>15.1532020568848</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G710" t="n">
-        <v>14.324951171875</v>
+        <v>14.3249521255493</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G712" t="n">
-        <v>14.381422996521</v>
+        <v>14.3814220428467</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>15.5</v>
       </c>
       <c r="G713" t="n">
-        <v>14.5884847640991</v>
+        <v>14.5884838104248</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>14.2496576309204</v>
+        <v>14.2496547698975</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G715" t="n">
-        <v>14.1931838989258</v>
+        <v>14.1931848526001</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G716" t="n">
-        <v>14.1367139816284</v>
+        <v>14.1367130279541</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G717" t="n">
-        <v>14.1367139816284</v>
+        <v>14.1367130279541</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G721" t="n">
-        <v>13.4025821685791</v>
+        <v>13.4025831222534</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>13.9672985076904</v>
+        <v>13.9672966003418</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G725" t="n">
-        <v>14.4190702438354</v>
+        <v>14.4190692901611</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>14.3626003265381</v>
+        <v>14.3625993728638</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649600982666</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649600982666</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>16.5</v>
       </c>
       <c r="G729" t="n">
-        <v>15.5296792984009</v>
+        <v>15.5296773910522</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>15.3414392471313</v>
+        <v>15.3414373397827</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G731" t="n">
-        <v>15.4920301437378</v>
+        <v>15.4920282363892</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>16</v>
       </c>
       <c r="G732" t="n">
-        <v>15.05908203125</v>
+        <v>15.0590810775757</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G734" t="n">
-        <v>16.019100189209</v>
+        <v>16.0190982818604</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>16.188512802124</v>
+        <v>16.1885108947754</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G737" t="n">
-        <v>15.9814500808716</v>
+        <v>15.9814481735229</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>15.8120355606079</v>
+        <v>15.8120346069336</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G741" t="n">
-        <v>15.96262550354</v>
+        <v>15.9626235961914</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G742" t="n">
-        <v>16.2826290130615</v>
+        <v>16.2826309204102</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>16.0379219055176</v>
+        <v>16.0379199981689</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G744" t="n">
-        <v>16.2638111114502</v>
+        <v>16.2638072967529</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G746" t="n">
-        <v>15.7367391586304</v>
+        <v>15.7367401123047</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G747" t="n">
-        <v>16.0379219055176</v>
+        <v>16.0379199981689</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G748" t="n">
-        <v>15.9814500808716</v>
+        <v>15.9814481735229</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649600982666</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G751" t="n">
-        <v>15.002610206604</v>
+        <v>15.0026092529297</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G752" t="n">
-        <v>15.0214328765869</v>
+        <v>15.0214347839355</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649600982666</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>15.3414392471313</v>
+        <v>15.3414373397827</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G756" t="n">
-        <v>15.4167346954346</v>
+        <v>15.4167366027832</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G757" t="n">
-        <v>15.002610206604</v>
+        <v>15.0026092529297</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>14.6826047897339</v>
+        <v>14.6826057434082</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G759" t="n">
-        <v>14.8520174026489</v>
+        <v>14.8520193099976</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>14.4943647384644</v>
+        <v>14.4943656921387</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G761" t="n">
-        <v>14.7579011917114</v>
+        <v>14.7579002380371</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G763" t="n">
-        <v>14.9273147583008</v>
+        <v>14.9273138046265</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G764" t="n">
-        <v>15.4732093811035</v>
+        <v>15.4732065200806</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>15.1532001495361</v>
+        <v>15.1532020568848</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G766" t="n">
-        <v>15.849681854248</v>
+        <v>15.8496809005737</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G767" t="n">
-        <v>15.9814500808716</v>
+        <v>15.9814481735229</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G768" t="n">
-        <v>15.9814500808716</v>
+        <v>15.9814481735229</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G769" t="n">
-        <v>15.6802682876587</v>
+        <v>15.6802673339844</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.5</v>
       </c>
       <c r="G770" t="n">
-        <v>15.5296792984009</v>
+        <v>15.5296773910522</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G772" t="n">
-        <v>15.2096719741821</v>
+        <v>15.2096700668335</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G773" t="n">
-        <v>14.9837846755981</v>
+        <v>14.9837865829468</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G774" t="n">
-        <v>15.3602638244629</v>
+        <v>15.3602628707886</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G775" t="n">
-        <v>15.6990928649902</v>
+        <v>15.699089050293</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G778" t="n">
-        <v>15.4732093811035</v>
+        <v>15.4732065200806</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G779" t="n">
-        <v>15.8308582305908</v>
+        <v>15.8308563232422</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>15.9061546325684</v>
+        <v>15.9061527252197</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>15.9061546325684</v>
+        <v>15.9061527252197</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>15.9061546325684</v>
+        <v>15.9061527252197</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>15.9061546325684</v>
+        <v>15.9061527252197</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G786" t="n">
-        <v>15.9814500808716</v>
+        <v>15.9814481735229</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G787" t="n">
-        <v>15.924976348877</v>
+        <v>15.9249773025513</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>15.5485010147095</v>
+        <v>15.5485019683838</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>16.5</v>
       </c>
       <c r="G790" t="n">
-        <v>15.5296792984009</v>
+        <v>15.5296773910522</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G791" t="n">
-        <v>14.6261329650879</v>
+        <v>14.6261320114136</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G792" t="n">
-        <v>14.8520174026489</v>
+        <v>14.8520193099976</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G794" t="n">
-        <v>14.7955474853516</v>
+        <v>14.7955465316772</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G795" t="n">
-        <v>14.9461393356323</v>
+        <v>14.946138381958</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G796" t="n">
-        <v>15.1343765258789</v>
+        <v>15.1343774795532</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>15.4355564117432</v>
+        <v>15.4355583190918</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G798" t="n">
-        <v>15.0402565002441</v>
+        <v>15.0402574539185</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G799" t="n">
-        <v>15.1155529022217</v>
+        <v>15.1155519485474</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649600982666</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G801" t="n">
-        <v>15.1155529022217</v>
+        <v>15.1155519485474</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>15.1532001495361</v>
+        <v>15.1532020568848</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>16</v>
       </c>
       <c r="G803" t="n">
-        <v>15.05908203125</v>
+        <v>15.0590810775757</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G804" t="n">
-        <v>15.002610206604</v>
+        <v>15.0026092529297</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G805" t="n">
-        <v>15.228497505188</v>
+        <v>15.2284955978394</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6802682876587</v>
+        <v>15.6802673339844</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G807" t="n">
-        <v>15.96262550354</v>
+        <v>15.9626235961914</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>18</v>
       </c>
       <c r="G809" t="n">
-        <v>16.9414672851562</v>
+        <v>16.9414653778076</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G810" t="n">
-        <v>17.1673526763916</v>
+        <v>17.167350769043</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G811" t="n">
-        <v>17.1861801147461</v>
+        <v>17.1861763000488</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>17.2238216400146</v>
+        <v>17.2238235473633</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>17.035587310791</v>
+        <v>17.0355854034424</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>17.9767799377441</v>
+        <v>17.9767780303955</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G817" t="n">
-        <v>17.3367652893066</v>
+        <v>17.3367671966553</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G818" t="n">
-        <v>17.2802963256836</v>
+        <v>17.280294418335</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2991218566895</v>
+        <v>17.2991180419922</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>18</v>
       </c>
       <c r="G822" t="n">
-        <v>16.9414672851562</v>
+        <v>16.9414653778076</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18</v>
       </c>
       <c r="G823" t="n">
-        <v>16.9414672851562</v>
+        <v>16.9414653778076</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G824" t="n">
-        <v>17.2991218566895</v>
+        <v>17.2991180419922</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>17.035587310791</v>
+        <v>17.0355854034424</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>17.7885398864746</v>
+        <v>17.788537979126</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G830" t="n">
-        <v>17.7508926391602</v>
+        <v>17.7508907318115</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>17.2238216400146</v>
+        <v>17.2238235473633</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>17.035587310791</v>
+        <v>17.0355854034424</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="n">
-        <v>16.9414672851562</v>
+        <v>16.9414653778076</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.5649890899658</v>
+        <v>16.5649909973145</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G841" t="n">
-        <v>16.5649890899658</v>
+        <v>16.5649909973145</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>16.2826290130615</v>
+        <v>16.2826309204102</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>16.7908725738525</v>
+        <v>16.7908744812012</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G853" t="n">
-        <v>15.9411125183105</v>
+        <v>15.9411115646362</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G854" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219522476196</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G855" t="n">
-        <v>16.6117134094238</v>
+        <v>16.6117115020752</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G857" t="n">
-        <v>16.6117134094238</v>
+        <v>16.6117115020752</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G859" t="n">
-        <v>16.6883544921875</v>
+        <v>16.6883506774902</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>15.8836317062378</v>
+        <v>15.8836336135864</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G868" t="n">
-        <v>16.4009532928467</v>
+        <v>16.400951385498</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G870" t="n">
-        <v>15.9602737426758</v>
+        <v>15.9602718353271</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.5</v>
       </c>
       <c r="G872" t="n">
-        <v>15.8069934844971</v>
+        <v>15.8069925308228</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G875" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219522476196</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G877" t="n">
-        <v>15.3088321685791</v>
+        <v>15.3088331222534</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G878" t="n">
-        <v>15.251353263855</v>
+        <v>15.2513542175293</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G879" t="n">
-        <v>14.9256343841553</v>
+        <v>14.925633430481</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G881" t="n">
-        <v>15.1747140884399</v>
+        <v>15.1747131347656</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>15.0789127349854</v>
+        <v>15.0789136886597</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G886" t="n">
-        <v>15.0597534179688</v>
+        <v>15.0597524642944</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G887" t="n">
-        <v>15.1938734054565</v>
+        <v>15.1938724517822</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>15.0022745132446</v>
+        <v>15.0022735595703</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G889" t="n">
-        <v>14.8106746673584</v>
+        <v>14.8106737136841</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.7915134429932</v>
+        <v>14.7915143966675</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G893" t="n">
-        <v>15.1172332763672</v>
+        <v>15.1172342300415</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G894" t="n">
-        <v>15.0789127349854</v>
+        <v>15.0789136886597</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G896" t="n">
-        <v>15.0789127349854</v>
+        <v>15.0789136886597</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G898" t="n">
-        <v>15.0214338302612</v>
+        <v>15.0214328765869</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G899" t="n">
-        <v>14.90647315979</v>
+        <v>14.9064741134644</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>15.0980730056763</v>
+        <v>15.0980739593506</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G902" t="n">
-        <v>14.7340354919434</v>
+        <v>14.734034538269</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G904" t="n">
-        <v>14.6957130432129</v>
+        <v>14.6957120895386</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G909" t="n">
-        <v>15.1938734054565</v>
+        <v>15.1938724517822</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>14.753191947937</v>
+        <v>14.7531938552856</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G911" t="n">
-        <v>14.8106746673584</v>
+        <v>14.8106737136841</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G912" t="n">
-        <v>15.0597534179688</v>
+        <v>15.0597524642944</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G916" t="n">
-        <v>14.4849548339844</v>
+        <v>14.4849538803101</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G917" t="n">
-        <v>14.5232734680176</v>
+        <v>14.5232725143433</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G919" t="n">
-        <v>14.6957130432129</v>
+        <v>14.6957120895386</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G920" t="n">
-        <v>14.4466333389282</v>
+        <v>14.4466342926025</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G921" t="n">
-        <v>14.580753326416</v>
+        <v>14.5807542800903</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G922" t="n">
-        <v>14.5232734680176</v>
+        <v>14.5232725143433</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>14.5615940093994</v>
+        <v>14.5615930557251</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G925" t="n">
-        <v>14.4849548339844</v>
+        <v>14.4849538803101</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G926" t="n">
-        <v>14.580753326416</v>
+        <v>14.5807542800903</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G927" t="n">
-        <v>14.3891544342041</v>
+        <v>14.3891534805298</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G928" t="n">
-        <v>14.5999126434326</v>
+        <v>14.5999135971069</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G929" t="n">
-        <v>15.1938734054565</v>
+        <v>15.1938724517822</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G930" t="n">
-        <v>14.8681554794312</v>
+        <v>14.8681545257568</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G931" t="n">
-        <v>14.8106746673584</v>
+        <v>14.8106737136841</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G932" t="n">
-        <v>14.504114151001</v>
+        <v>14.5041131973267</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G933" t="n">
-        <v>14.8106746673584</v>
+        <v>14.8106737136841</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G936" t="n">
-        <v>15.2896728515625</v>
+        <v>15.2896747589111</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>16</v>
       </c>
       <c r="G937" t="n">
-        <v>15.3279933929443</v>
+        <v>15.32799243927</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G938" t="n">
-        <v>15.6153926849365</v>
+        <v>15.6153917312622</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G939" t="n">
-        <v>15.4621152877808</v>
+        <v>15.4621133804321</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G940" t="n">
-        <v>15.653712272644</v>
+        <v>15.6537132263184</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G941" t="n">
-        <v>15.7303524017334</v>
+        <v>15.7303533554077</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>16.0943946838379</v>
+        <v>16.0943927764893</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>15.7111902236938</v>
+        <v>15.7111930847168</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G945" t="n">
-        <v>15.7495155334473</v>
+        <v>15.7495136260986</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G946" t="n">
-        <v>15.9411125183105</v>
+        <v>15.9411115646362</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G947" t="n">
-        <v>15.8453121185303</v>
+        <v>15.8453130722046</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G949" t="n">
-        <v>15.5579128265381</v>
+        <v>15.5579137802124</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.5</v>
       </c>
       <c r="G951" t="n">
-        <v>15.8069934844971</v>
+        <v>15.8069925308228</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>15.7878313064575</v>
+        <v>15.7878332138062</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>16.5</v>
       </c>
       <c r="G953" t="n">
-        <v>15.8069934844971</v>
+        <v>15.8069925308228</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>16.5</v>
       </c>
       <c r="G954" t="n">
-        <v>15.8069934844971</v>
+        <v>15.8069925308228</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G955" t="n">
-        <v>15.5195960998535</v>
+        <v>15.5195941925049</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G956" t="n">
-        <v>15.4429531097412</v>
+        <v>15.4429550170898</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>16</v>
       </c>
       <c r="G957" t="n">
-        <v>15.3279933929443</v>
+        <v>15.32799243927</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G959" t="n">
-        <v>15.7686729431152</v>
+        <v>15.7686719894409</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>15.7111902236938</v>
+        <v>15.7111930847168</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G962" t="n">
-        <v>15.653712272644</v>
+        <v>15.6537132263184</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G963" t="n">
-        <v>15.8644723892212</v>
+        <v>15.8644733428955</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>16.5</v>
       </c>
       <c r="G964" t="n">
-        <v>15.8069934844971</v>
+        <v>15.8069925308228</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G965" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219522476196</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>16.0943946838379</v>
+        <v>16.0943927764893</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G969" t="n">
-        <v>17.0907115936279</v>
+        <v>17.0907135009766</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G970" t="n">
-        <v>16.9374332427979</v>
+        <v>16.9374313354492</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G971" t="n">
-        <v>16.8799514770508</v>
+        <v>16.8799533843994</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G974" t="n">
-        <v>16.9374332427979</v>
+        <v>16.9374313354492</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>17.0523929595947</v>
+        <v>17.0523891448975</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>19</v>
       </c>
       <c r="G980" t="n">
-        <v>18.2019920349121</v>
+        <v>18.2019901275635</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G981" t="n">
-        <v>18.1061935424805</v>
+        <v>18.1061916351318</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>17.5313892364502</v>
+        <v>17.5313930511475</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>17.5888748168945</v>
+        <v>17.5888729095459</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G984" t="n">
-        <v>18.0295524597168</v>
+        <v>18.0295505523682</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>17.9145946502686</v>
+        <v>17.9145927429199</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>18.048713684082</v>
+        <v>18.0487117767334</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G987" t="n">
-        <v>17.8954334259033</v>
+        <v>17.8954315185547</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="n">
-        <v>17.991231918335</v>
+        <v>17.9912338256836</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G990" t="n">
-        <v>17.8954334259033</v>
+        <v>17.8954315185547</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G991" t="n">
-        <v>17.9145946502686</v>
+        <v>17.9145927429199</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G992" t="n">
-        <v>17.8571128845215</v>
+        <v>17.8571090698242</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>19.5</v>
       </c>
       <c r="G994" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809902191162</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G997" t="n">
-        <v>18.4702339172363</v>
+        <v>18.4702320098877</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>19.5</v>
       </c>
       <c r="G998" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809902191162</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G999" t="n">
-        <v>18.8917541503906</v>
+        <v>18.8917503356934</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.2078895568848</v>
+        <v>19.2078914642334</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.2078895568848</v>
+        <v>19.2078914642334</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>18.7767925262451</v>
+        <v>18.7767944335938</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>19.5431938171387</v>
+        <v>19.5431900024414</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>20.5</v>
       </c>
       <c r="G1009" t="n">
-        <v>19.6389904022217</v>
+        <v>19.6389923095703</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>19.2557907104492</v>
+        <v>19.2557926177979</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>19.2557907104492</v>
+        <v>19.2557926177979</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>19.2078895568848</v>
+        <v>19.2078914642334</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>19.5431938171387</v>
+        <v>19.5431900024414</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>21</v>
       </c>
       <c r="G1019" t="n">
-        <v>20.1179904937744</v>
+        <v>20.117992401123</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>22.1297912597656</v>
+        <v>22.129789352417</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>20.9322929382324</v>
+        <v>20.9322910308838</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>20.9322929382324</v>
+        <v>20.9322910308838</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1029" t="n">
-        <v>20.6448917388916</v>
+        <v>20.6448879241943</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>21.5</v>
       </c>
       <c r="G1030" t="n">
-        <v>20.5969924926758</v>
+        <v>20.5969944000244</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>20.6448917388916</v>
+        <v>20.6448879241943</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>21.5</v>
       </c>
       <c r="G1032" t="n">
-        <v>20.5969924926758</v>
+        <v>20.5969944000244</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>20.75</v>
       </c>
       <c r="G1033" t="n">
-        <v>19.8784923553467</v>
+        <v>19.878490447998</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>20.2137889862061</v>
+        <v>20.2137928009033</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1037" t="n">
-        <v>19.2557907104492</v>
+        <v>19.2557926177979</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>20.75</v>
       </c>
       <c r="G1039" t="n">
-        <v>19.8784923553467</v>
+        <v>19.878490447998</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>21.75</v>
       </c>
       <c r="G1041" t="n">
-        <v>20.8364887237549</v>
+        <v>20.8364906311035</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>20.6448917388916</v>
+        <v>20.6448879241943</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>20.9322929382324</v>
+        <v>20.9322910308838</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>21.1717929840088</v>
+        <v>21.1717948913574</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>22.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>21.3154907226562</v>
+        <v>21.3154926300049</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1047" t="n">
-        <v>21.1238918304443</v>
+        <v>21.1238880157471</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>22.5</v>
       </c>
       <c r="G1048" t="n">
-        <v>21.5549907684326</v>
+        <v>21.5549926757812</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>21.3633880615234</v>
+        <v>21.3633899688721</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1050" t="n">
-        <v>21.7465915679932</v>
+        <v>21.7465934753418</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>22.25</v>
       </c>
       <c r="G1051" t="n">
-        <v>21.3154907226562</v>
+        <v>21.3154926300049</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>20.0221900939941</v>
+        <v>20.0221920013428</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>19.5431938171387</v>
+        <v>19.5431900024414</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>20.5</v>
       </c>
       <c r="G1057" t="n">
-        <v>19.6389904022217</v>
+        <v>19.6389923095703</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>19.5</v>
       </c>
       <c r="G1059" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809902191162</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>18.7767925262451</v>
+        <v>18.7767944335938</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1064" t="n">
-        <v>16.2476749420166</v>
+        <v>16.2476711273193</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1065" t="n">
-        <v>16.1327133178711</v>
+        <v>16.1327114105225</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1066" t="n">
-        <v>14.4274749755859</v>
+        <v>14.4274740219116</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>15</v>
       </c>
       <c r="G1067" t="n">
-        <v>14.3699941635132</v>
+        <v>14.3699932098389</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.415675163269</v>
+        <v>12.4156732559204</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>12.5</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9749965667725</v>
+        <v>11.9749946594238</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1070" t="n">
-        <v>12.0899534225464</v>
+        <v>12.0899543762207</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1072" t="n">
-        <v>12.8563537597656</v>
+        <v>12.8563547134399</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1073" t="n">
-        <v>11.9366760253906</v>
+        <v>11.9366750717163</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.2587127685547</v>
+        <v>13.2587146759033</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>13.5077924728394</v>
+        <v>13.507794380188</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1076" t="n">
-        <v>13.9676342010498</v>
+        <v>13.9676351547241</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1077" t="n">
-        <v>14.1400747299194</v>
+        <v>14.1400737762451</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5999126434326</v>
+        <v>14.5999135971069</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1081" t="n">
-        <v>14.5232734680176</v>
+        <v>14.5232725143433</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1082" t="n">
-        <v>13.9676342010498</v>
+        <v>13.9676351547241</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>15</v>
       </c>
       <c r="G1084" t="n">
-        <v>14.3699941635132</v>
+        <v>14.3699932098389</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1085" t="n">
-        <v>14.4274749755859</v>
+        <v>14.4274740219116</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1086" t="n">
-        <v>14.6765546798706</v>
+        <v>14.676552772522</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1087" t="n">
-        <v>14.7915134429932</v>
+        <v>14.7915143966675</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>15</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.3699941635132</v>
+        <v>14.3699932098389</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.3471527099609</v>
+        <v>15.3471536636353</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1092" t="n">
-        <v>15.0980730056763</v>
+        <v>15.0980739593506</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219522476196</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1095" t="n">
-        <v>16.1135540008545</v>
+        <v>16.1135501861572</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219522476196</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.653712272644</v>
+        <v>15.6537132263184</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.8453121185303</v>
+        <v>15.8453130722046</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.8681554794312</v>
+        <v>14.8681545257568</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>15.0789127349854</v>
+        <v>15.0789136886597</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.7111902236938</v>
+        <v>15.7111930847168</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.3471527099609</v>
+        <v>15.3471536636353</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>16</v>
       </c>
       <c r="G1107" t="n">
-        <v>15.3279933929443</v>
+        <v>15.32799243927</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.753191947937</v>
+        <v>14.7531938552856</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.6153926849365</v>
+        <v>15.6153917312622</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>16</v>
       </c>
       <c r="G1111" t="n">
-        <v>15.3279933929443</v>
+        <v>15.32799243927</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>15.9985942840576</v>
+        <v>15.998592376709</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1113" t="n">
-        <v>16.0752353668213</v>
+        <v>16.0752334594727</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1114" t="n">
-        <v>15.9794340133667</v>
+        <v>15.9794301986694</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1115" t="n">
-        <v>15.4621152877808</v>
+        <v>15.4621133804321</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1117" t="n">
-        <v>15.9602737426758</v>
+        <v>15.9602718353271</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1118" t="n">
-        <v>16.5350742340088</v>
+        <v>16.5350723266602</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1122" t="n">
-        <v>16.9949131011963</v>
+        <v>16.9949111938477</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1123" t="n">
-        <v>18.1828346252441</v>
+        <v>18.1828308105469</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1124" t="n">
-        <v>18.5660285949707</v>
+        <v>18.5660305023193</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1125" t="n">
-        <v>18.006929397583</v>
+        <v>18.0069313049316</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3899936676025</v>
+        <v>17.3899917602539</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.3707103729248</v>
+        <v>17.3707122802734</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1129" t="n">
-        <v>17.1393604278564</v>
+        <v>17.1393585205078</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1130" t="n">
-        <v>16.8887271881104</v>
+        <v>16.8887252807617</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1133" t="n">
-        <v>17.1008014678955</v>
+        <v>17.1007995605469</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1134" t="n">
-        <v>17.58278465271</v>
+        <v>17.5827827453613</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1135" t="n">
-        <v>17.4285507202148</v>
+        <v>17.4285488128662</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>19</v>
       </c>
       <c r="G1140" t="n">
-        <v>18.3154010772705</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1144" t="n">
-        <v>18.1804466247559</v>
+        <v>18.1804447174072</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>18.5081958770752</v>
+        <v>18.5081939697266</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1147" t="n">
-        <v>18.1804466247559</v>
+        <v>18.1804447174072</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1152" t="n">
-        <v>18.7588214874268</v>
+        <v>18.758825302124</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1156" t="n">
-        <v>18.9708995819092</v>
+        <v>18.9708976745605</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>20</v>
       </c>
       <c r="G1158" t="n">
-        <v>19.279369354248</v>
+        <v>19.2793674468994</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1159" t="n">
-        <v>18.8745002746582</v>
+        <v>18.8745021820068</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1164" t="n">
-        <v>19.4239654541016</v>
+        <v>19.4239616394043</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1165" t="n">
-        <v>19.5685615539551</v>
+        <v>19.5685577392578</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>20.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>20.0023441314697</v>
+        <v>20.0023460388184</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>21</v>
       </c>
       <c r="G1167" t="n">
-        <v>20.243335723877</v>
+        <v>20.2433376312256</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1168" t="n">
-        <v>20.5325260162354</v>
+        <v>20.5325241088867</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>21.1109085083008</v>
+        <v>21.1109066009521</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>21.1109085083008</v>
+        <v>21.1109066009521</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.4964962005615</v>
+        <v>21.4964942932129</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.7856864929199</v>
+        <v>21.7856884002686</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.7856864929199</v>
+        <v>21.7856884002686</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.2555046081543</v>
+        <v>21.255500793457</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>22.5</v>
       </c>
       <c r="G1184" t="n">
-        <v>21.6892890930176</v>
+        <v>21.6892910003662</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>22.5</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.6892890930176</v>
+        <v>21.6892910003662</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>22.7014541625977</v>
+        <v>22.7014560699463</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.2316417694092</v>
+        <v>23.2316398620605</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>22.7014541625977</v>
+        <v>22.7014560699463</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.62939453125</v>
+        <v>24.6293964385986</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>24.3883991241455</v>
+        <v>24.3884010314941</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>23.9546184539795</v>
+        <v>23.9546165466309</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>23.5690307617188</v>
+        <v>23.5690288543701</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.9906463623047</v>
+        <v>22.9906482696533</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>22.7978534698486</v>
+        <v>22.7978553771973</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>22.4604625701904</v>
+        <v>22.4604644775391</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1210" t="n">
-        <v>21.7374877929688</v>
+        <v>21.7374858856201</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>22.5</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.6892890930176</v>
+        <v>21.6892910003662</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>21.4964962005615</v>
+        <v>21.4964942932129</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>21.5446949005127</v>
+        <v>21.5446968078613</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1219" t="n">
-        <v>21.3037033081055</v>
+        <v>21.3037052154541</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1220" t="n">
-        <v>21.0145130157471</v>
+        <v>21.0145111083984</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1221" t="n">
-        <v>21.4001007080078</v>
+        <v>21.4000988006592</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1222" t="n">
-        <v>21.4964962005615</v>
+        <v>21.4964942932129</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>21.7374877929688</v>
+        <v>21.7374858856201</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>22.5</v>
       </c>
       <c r="G1225" t="n">
-        <v>21.6892890930176</v>
+        <v>21.6892910003662</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>21.8820858001709</v>
+        <v>21.8820838928223</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>21.1109085083008</v>
+        <v>21.1109066009521</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1230" t="n">
-        <v>21.4964962005615</v>
+        <v>21.4964942932129</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>22.0266780853271</v>
+        <v>22.0266799926758</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>22.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>21.6892890930176</v>
+        <v>21.6892910003662</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>25.25</v>
       </c>
       <c r="G1240" t="n">
-        <v>24.340202331543</v>
+        <v>24.3402042388916</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>27.5694980621338</v>
+        <v>27.5694961547852</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>28.5334663391113</v>
+        <v>28.53346824646</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.8226566314697</v>
+        <v>28.8226585388184</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>30.75</v>
       </c>
       <c r="G1254" t="n">
-        <v>29.6420307159424</v>
+        <v>29.6420288085938</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>30.2686100006104</v>
+        <v>30.2686080932617</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>31.6181678771973</v>
+        <v>31.6181640625</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1258" t="n">
-        <v>31.9073581695557</v>
+        <v>31.9073543548584</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1259" t="n">
-        <v>31.4253711700439</v>
+        <v>31.4253692626953</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G1260" t="n">
-        <v>31.9555549621582</v>
+        <v>31.9555587768555</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>31.4253711700439</v>
+        <v>31.4253692626953</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1262" t="n">
-        <v>31.1361789703369</v>
+        <v>31.1361770629883</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>33.25</v>
       </c>
       <c r="G1263" t="n">
-        <v>32.0519523620605</v>
+        <v>32.0519485473633</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1265" t="n">
-        <v>31.9073581695557</v>
+        <v>31.9073543548584</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>33.1605186462402</v>
+        <v>33.160514831543</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>33.0641136169434</v>
+        <v>33.0641212463379</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1269" t="n">
-        <v>33.3533058166504</v>
+        <v>33.3533096313477</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G1270" t="n">
-        <v>33.594295501709</v>
+        <v>33.5942993164062</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>35.25</v>
       </c>
       <c r="G1271" t="n">
-        <v>33.9798927307129</v>
+        <v>33.9798889160156</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>34.6064720153809</v>
+        <v>34.6064682006836</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G1274" t="n">
-        <v>35.2330474853516</v>
+        <v>35.233039855957</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1275" t="n">
-        <v>35.3294448852539</v>
+        <v>35.3294486999512</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1277" t="n">
-        <v>37.0163917541504</v>
+        <v>37.0163879394531</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>36.0524253845215</v>
+        <v>36.0524215698242</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G1279" t="n">
-        <v>34.1726837158203</v>
+        <v>34.1726875305176</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>33.25</v>
       </c>
       <c r="G1280" t="n">
-        <v>32.0519523620605</v>
+        <v>32.0519485473633</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>33.75</v>
       </c>
       <c r="G1282" t="n">
-        <v>32.533935546875</v>
+        <v>32.5339317321777</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1283" t="n">
-        <v>32.6303253173828</v>
+        <v>32.6303291320801</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>33</v>
       </c>
       <c r="G1285" t="n">
-        <v>31.810962677002</v>
+        <v>31.8109588623047</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.2204113006592</v>
+        <v>30.2204132080078</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.7023944854736</v>
+        <v>30.7023963928223</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1288" t="n">
-        <v>30.4614009857178</v>
+        <v>30.461404800415</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>31.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>30.3650074005127</v>
+        <v>30.3650054931641</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>33.75</v>
       </c>
       <c r="G1292" t="n">
-        <v>32.533935546875</v>
+        <v>32.5339317321777</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>33.3051109313965</v>
+        <v>33.305103302002</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>35</v>
       </c>
       <c r="G1294" t="n">
-        <v>33.738899230957</v>
+        <v>33.7388954162598</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>35.25</v>
       </c>
       <c r="G1295" t="n">
-        <v>33.9798927307129</v>
+        <v>33.9798889160156</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>36.4500007629395</v>
       </c>
       <c r="G1296" t="n">
-        <v>35.1366500854492</v>
+        <v>35.1366539001465</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1297" t="n">
-        <v>35.5222358703613</v>
+        <v>35.5222320556641</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>36.8235931396484</v>
+        <v>36.8235969543457</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G1302" t="n">
-        <v>35.8114280700684</v>
+        <v>35.8114318847656</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1303" t="n">
-        <v>36.2934074401855</v>
+        <v>36.2934150695801</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1305" t="n">
-        <v>34.8474578857422</v>
+        <v>34.8474655151367</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1306" t="n">
-        <v>36.5344085693359</v>
+        <v>36.5344047546387</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1313" t="n">
-        <v>39.6673049926758</v>
+        <v>39.6673011779785</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>41</v>
       </c>
       <c r="G1314" t="n">
-        <v>39.522705078125</v>
+        <v>39.5227088928223</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1315" t="n">
-        <v>38.4141464233398</v>
+        <v>38.4141426086426</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>40</v>
       </c>
       <c r="G1316" t="n">
-        <v>38.5587387084961</v>
+        <v>38.5587348937988</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1317" t="n">
-        <v>39.6673049926758</v>
+        <v>39.6673011779785</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>40.2938766479492</v>
+        <v>40.2938804626465</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>41.5</v>
       </c>
       <c r="G1320" t="n">
-        <v>40.0046882629395</v>
+        <v>40.0046920776367</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>40.75</v>
       </c>
       <c r="G1321" t="n">
-        <v>39.2817115783691</v>
+        <v>39.2817153930664</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>41.0168609619141</v>
+        <v>41.0168571472168</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>43.25</v>
       </c>
       <c r="G1327" t="n">
-        <v>41.6916389465332</v>
+        <v>41.6916351318359</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>43.75</v>
       </c>
       <c r="G1328" t="n">
-        <v>42.1736145019531</v>
+        <v>42.1736183166504</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G1329" t="n">
-        <v>41.8844299316406</v>
+        <v>41.8844261169434</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>44.0499992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>42.4628105163574</v>
+        <v>42.4628067016602</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>43</v>
       </c>
       <c r="G1331" t="n">
-        <v>41.4506454467773</v>
+        <v>41.4506492614746</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>42.2218170166016</v>
+        <v>42.2218132019043</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>43.3303871154785</v>
+        <v>43.330379486084</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>46.25</v>
       </c>
       <c r="G1336" t="n">
-        <v>44.5835380554199</v>
+        <v>44.5835418701172</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G1340" t="n">
-        <v>45.8367042541504</v>
+        <v>45.8367004394531</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>46.25</v>
       </c>
       <c r="G1345" t="n">
-        <v>44.5835380554199</v>
+        <v>44.5835418701172</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>45.75</v>
       </c>
       <c r="G1350" t="n">
-        <v>44.1015548706055</v>
+        <v>44.1015586853027</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G1352" t="n">
-        <v>42.992992401123</v>
+        <v>42.9929885864258</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>44.75</v>
       </c>
       <c r="G1353" t="n">
-        <v>43.1375885009766</v>
+        <v>43.1375923156738</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>43.0893898010254</v>
+        <v>43.0893936157227</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>44.8499984741211</v>
       </c>
       <c r="G1359" t="n">
-        <v>43.2339820861816</v>
+        <v>43.2339859008789</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G1360" t="n">
-        <v>42.2700119018555</v>
+        <v>42.2700157165527</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G1361" t="n">
-        <v>41.8844299316406</v>
+        <v>41.8844261169434</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1362" t="n">
-        <v>42.2218170166016</v>
+        <v>42.2218132019043</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>43.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>42.1736145019531</v>
+        <v>42.1736183166504</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>40.75</v>
       </c>
       <c r="G1366" t="n">
-        <v>39.6441764831543</v>
+        <v>39.644172668457</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1367" t="n">
-        <v>39.3036804199219</v>
+        <v>39.3036766052246</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>40.75</v>
       </c>
       <c r="G1368" t="n">
-        <v>39.6441764831543</v>
+        <v>39.644172668457</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1369" t="n">
-        <v>39.9360389709473</v>
+        <v>39.93603515625</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G1370" t="n">
-        <v>40.7143287658691</v>
+        <v>40.7143249511719</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1371" t="n">
-        <v>39.8387489318848</v>
+        <v>39.8387451171875</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>41.75</v>
       </c>
       <c r="G1373" t="n">
-        <v>40.6170349121094</v>
+        <v>40.6170387268066</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>40.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>39.6441764831543</v>
+        <v>39.644172668457</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G1381" t="n">
-        <v>39.1091041564941</v>
+        <v>39.1091003417969</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1382" t="n">
-        <v>39.3036804199219</v>
+        <v>39.3036766052246</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1383" t="n">
-        <v>39.3036804199219</v>
+        <v>39.3036766052246</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1386" t="n">
-        <v>39.7901039123535</v>
+        <v>39.7901077270508</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1387" t="n">
-        <v>39.9360389709473</v>
+        <v>39.93603515625</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1388" t="n">
-        <v>37.7470932006836</v>
+        <v>37.7470893859863</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1389" t="n">
-        <v>36.5796585083008</v>
+        <v>36.5796546936035</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G1396" t="n">
-        <v>39.1091041564941</v>
+        <v>39.1091003417969</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>41.5412635803223</v>
+        <v>41.541259765625</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1402" t="n">
-        <v>40.2278900146484</v>
+        <v>40.2278938293457</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1403" t="n">
-        <v>40.276538848877</v>
+        <v>40.2765350341797</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1405" t="n">
-        <v>42.0276947021484</v>
+        <v>42.0276908874512</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1407" t="n">
-        <v>42.0276947021484</v>
+        <v>42.0276908874512</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1409" t="n">
-        <v>41.2494010925293</v>
+        <v>41.2494049072266</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>43.75</v>
       </c>
       <c r="G1410" t="n">
-        <v>42.5627708435059</v>
+        <v>42.5627670288086</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>46.5</v>
       </c>
       <c r="G1412" t="n">
-        <v>45.2381362915039</v>
+        <v>45.2381401062012</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>46.016429901123</v>
+        <v>46.0164337158203</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>48.3512992858887</v>
+        <v>48.3513069152832</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>49.75</v>
       </c>
       <c r="G1418" t="n">
-        <v>48.3999443054199</v>
+        <v>48.3999481201172</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>50</v>
       </c>
       <c r="G1419" t="n">
-        <v>48.6431617736816</v>
+        <v>48.6431579589844</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1421" t="n">
-        <v>49.5187377929688</v>
+        <v>49.518741607666</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>49.7133102416992</v>
+        <v>49.713306427002</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1430" t="n">
-        <v>49.5187377929688</v>
+        <v>49.518741607666</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1433" t="n">
-        <v>49.5187377929688</v>
+        <v>49.518741607666</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1435" t="n">
-        <v>49.7133102416992</v>
+        <v>49.713306427002</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1440" t="n">
-        <v>49.7133102416992</v>
+        <v>49.713306427002</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>50</v>
       </c>
       <c r="G1445" t="n">
-        <v>48.6431617736816</v>
+        <v>48.6431579589844</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>46.3499984741211</v>
       </c>
       <c r="G1446" t="n">
-        <v>45.0922088623047</v>
+        <v>45.092212677002</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>46.3499984741211</v>
       </c>
       <c r="G1447" t="n">
-        <v>45.0922088623047</v>
+        <v>45.092212677002</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1449" t="n">
-        <v>43.3410530090332</v>
+        <v>43.3410568237305</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G1451" t="n">
-        <v>44.1193466186523</v>
+        <v>44.1193504333496</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>46.3499984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>45.0922088623047</v>
+        <v>45.092212677002</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>46</v>
       </c>
       <c r="G1453" t="n">
-        <v>44.7517051696777</v>
+        <v>44.751708984375</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>41.0548286437988</v>
+        <v>41.0548324584961</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1461" t="n">
-        <v>40.8116149902344</v>
+        <v>40.8116111755371</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>43.75</v>
       </c>
       <c r="G1463" t="n">
-        <v>42.5627708435059</v>
+        <v>42.5627670288086</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>43.3410530090332</v>
+        <v>43.3410568237305</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>43.2999992370605</v>
       </c>
       <c r="G1466" t="n">
-        <v>42.1249732971191</v>
+        <v>42.1249771118164</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>43.2999992370605</v>
       </c>
       <c r="G1467" t="n">
-        <v>42.1249732971191</v>
+        <v>42.1249771118164</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1468" t="n">
-        <v>42.9032669067383</v>
+        <v>42.903263092041</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>44.75</v>
       </c>
       <c r="G1471" t="n">
-        <v>43.5356292724609</v>
+        <v>43.5356254577637</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1472" t="n">
-        <v>44.1679954528809</v>
+        <v>44.1679878234863</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>46.3499984741211</v>
       </c>
       <c r="G1474" t="n">
-        <v>45.0922088623047</v>
+        <v>45.092212677002</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>46.75</v>
       </c>
       <c r="G1476" t="n">
-        <v>45.4813537597656</v>
+        <v>45.4813575744629</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>46.75</v>
       </c>
       <c r="G1477" t="n">
-        <v>45.4813537597656</v>
+        <v>45.4813575744629</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>46.5</v>
       </c>
       <c r="G1480" t="n">
-        <v>45.2381362915039</v>
+        <v>45.2381401062012</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>42.25</v>
       </c>
       <c r="G1482" t="n">
-        <v>41.1034660339355</v>
+        <v>41.1034736633301</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>42.25</v>
       </c>
       <c r="G1483" t="n">
-        <v>41.1034660339355</v>
+        <v>41.1034736633301</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>44.1500015258789</v>
       </c>
       <c r="G1487" t="n">
-        <v>42.9519119262695</v>
+        <v>42.9519157409668</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>43.3499984741211</v>
       </c>
       <c r="G1488" t="n">
-        <v>42.1736145019531</v>
+        <v>42.1736183166504</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>42.5</v>
       </c>
       <c r="G1491" t="n">
-        <v>41.3466873168945</v>
+        <v>41.3466835021973</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>42.5</v>
       </c>
       <c r="G1492" t="n">
-        <v>41.3466873168945</v>
+        <v>41.3466835021973</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>38.7199516296387</v>
+        <v>38.7199554443359</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G1497" t="n">
-        <v>38.0875968933105</v>
+        <v>38.0875930786133</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>40</v>
       </c>
       <c r="G1498" t="n">
-        <v>38.9145278930664</v>
+        <v>38.9145240783691</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>41.75</v>
       </c>
       <c r="G1502" t="n">
-        <v>40.6170349121094</v>
+        <v>40.6170387268066</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>41.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>40.3738250732422</v>
+        <v>40.3738212585449</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1506" t="n">
-        <v>40.276538848877</v>
+        <v>40.2765350341797</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>41.5</v>
       </c>
       <c r="G1509" t="n">
-        <v>40.3738250732422</v>
+        <v>40.3738212585449</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1510" t="n">
-        <v>41.6871871948242</v>
+        <v>41.6871910095215</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1513" t="n">
-        <v>40.9575424194336</v>
+        <v>40.9575386047363</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>41.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>40.6170349121094</v>
+        <v>40.6170387268066</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1518" t="n">
-        <v>41.492618560791</v>
+        <v>41.4926147460938</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>39.8387489318848</v>
+        <v>39.8387451171875</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1520" t="n">
-        <v>40.2278900146484</v>
+        <v>40.2278938293457</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>44</v>
       </c>
       <c r="G1525" t="n">
-        <v>42.8059768676758</v>
+        <v>42.8059844970703</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1528" t="n">
-        <v>41.492618560791</v>
+        <v>41.4926147460938</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>41.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>40.3738250732422</v>
+        <v>40.3738212585449</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1531" t="n">
-        <v>40.0819625854492</v>
+        <v>40.0819702148438</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1534" t="n">
-        <v>40.4711112976074</v>
+        <v>40.4711074829102</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>44.1500015258789</v>
       </c>
       <c r="G1538" t="n">
-        <v>42.9519119262695</v>
+        <v>42.9519157409668</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>43.8274879455566</v>
+        <v>43.8274841308594</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>44.1500015258789</v>
       </c>
       <c r="G1541" t="n">
-        <v>42.9519119262695</v>
+        <v>42.9519157409668</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1542" t="n">
-        <v>41.2494010925293</v>
+        <v>41.2494049072266</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>40</v>
       </c>
       <c r="G1543" t="n">
-        <v>38.9145278930664</v>
+        <v>38.9145240783691</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1545" t="n">
-        <v>40.7629699707031</v>
+        <v>40.7629737854004</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1546" t="n">
-        <v>38.9631729125977</v>
+        <v>38.9631690979004</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1547" t="n">
-        <v>40.9575424194336</v>
+        <v>40.9575386047363</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>42.4168395996094</v>
+        <v>42.4168357849121</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>43.6500015258789</v>
       </c>
       <c r="G1549" t="n">
-        <v>42.4654808044434</v>
+        <v>42.4654846191406</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>41.75</v>
       </c>
       <c r="G1551" t="n">
-        <v>40.6170349121094</v>
+        <v>40.6170387268066</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>39.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>38.4281005859375</v>
+        <v>38.4280967712402</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1553" t="n">
-        <v>36.2877960205078</v>
+        <v>36.2877998352051</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1556" t="n">
-        <v>35.6554374694824</v>
+        <v>35.6554412841797</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>36.4500007629395</v>
       </c>
       <c r="G1558" t="n">
-        <v>35.4608612060547</v>
+        <v>35.460865020752</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>36.5796585083008</v>
+        <v>36.5796546936035</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>37</v>
       </c>
       <c r="G1563" t="n">
-        <v>35.9959373474121</v>
+        <v>35.9959449768066</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>35.3149375915527</v>
+        <v>35.3149337768555</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G1565" t="n">
-        <v>34.3907089233398</v>
+        <v>34.3907165527344</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>35.3149375915527</v>
+        <v>35.3149337768555</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>37.25</v>
       </c>
       <c r="G1567" t="n">
-        <v>36.2391548156738</v>
+        <v>36.2391510009766</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>37</v>
       </c>
       <c r="G1569" t="n">
-        <v>35.9959373474121</v>
+        <v>35.9959449768066</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1571" t="n">
-        <v>32.0071983337402</v>
+        <v>32.0072021484375</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>32.25</v>
       </c>
       <c r="G1572" t="n">
-        <v>31.3748378753662</v>
+        <v>31.3748397827148</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1573" t="n">
-        <v>31.52077293396</v>
+        <v>31.5207691192627</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1578" t="n">
-        <v>34.4393615722656</v>
+        <v>34.4393577575684</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>31.9099159240723</v>
+        <v>31.909912109375</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>33.75</v>
       </c>
       <c r="G1583" t="n">
-        <v>32.8341331481934</v>
+        <v>32.8341293334961</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1590" t="n">
-        <v>31.52077293396</v>
+        <v>31.5207691192627</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>31.9599990844727</v>
       </c>
       <c r="G1591" t="n">
-        <v>31.0927104949951</v>
+        <v>31.0927066802979</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>31.7600002288818</v>
       </c>
       <c r="G1592" t="n">
-        <v>30.8981342315674</v>
+        <v>30.898136138916</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>30.3533325195312</v>
+        <v>30.3533344268799</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>33</v>
       </c>
       <c r="G1596" t="n">
-        <v>32.1044845581055</v>
+        <v>32.1044883728027</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1599" t="n">
-        <v>31.2094554901123</v>
+        <v>31.2094535827637</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G1601" t="n">
-        <v>31.2678241729736</v>
+        <v>31.267822265625</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>31.7600002288818</v>
       </c>
       <c r="G1603" t="n">
-        <v>30.8981342315674</v>
+        <v>30.898136138916</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1604" t="n">
-        <v>29.7696151733398</v>
+        <v>29.7696132659912</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>29.0599994659424</v>
       </c>
       <c r="G1606" t="n">
-        <v>28.2714042663574</v>
+        <v>28.2714023590088</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>29.1800003051758</v>
       </c>
       <c r="G1607" t="n">
-        <v>28.388147354126</v>
+        <v>28.3881492614746</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>29.1800003051758</v>
       </c>
       <c r="G1609" t="n">
-        <v>28.388147354126</v>
+        <v>28.3881492614746</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1610" t="n">
-        <v>28.7578392028809</v>
+        <v>28.7578353881836</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1613" t="n">
-        <v>28.1935787200928</v>
+        <v>28.1935749053955</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>28.3103218078613</v>
+        <v>28.3103199005127</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1615" t="n">
-        <v>26.9093971252441</v>
+        <v>26.9093952178955</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1619" t="n">
-        <v>28.4465198516846</v>
+        <v>28.4465179443359</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G1620" t="n">
-        <v>28.071704864502</v>
+        <v>28.0717029571533</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>27</v>
       </c>
       <c r="G1627" t="n">
-        <v>26.6316223144531</v>
+        <v>26.6316242218018</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>28.3400001525879</v>
       </c>
       <c r="G1629" t="n">
-        <v>27.9533424377441</v>
+        <v>27.9533405303955</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1630" t="n">
-        <v>28.2887020111084</v>
+        <v>28.288703918457</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G1632" t="n">
-        <v>27.6574325561523</v>
+        <v>27.657434463501</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>28.2199993133545</v>
       </c>
       <c r="G1633" t="n">
-        <v>27.8349781036377</v>
+        <v>27.8349800109863</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>29.4200000762939</v>
       </c>
       <c r="G1638" t="n">
-        <v>29.0186061859131</v>
+        <v>29.0186080932617</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1641" t="n">
-        <v>24.9153652191162</v>
+        <v>24.9153633117676</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1642" t="n">
-        <v>25.5466327667236</v>
+        <v>25.546630859375</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G1657" t="n">
-        <v>23.4555549621582</v>
+        <v>23.4555568695068</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1658" t="n">
-        <v>24.1065521240234</v>
+        <v>24.1065540313721</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1659" t="n">
-        <v>23.5147380828857</v>
+        <v>23.5147361755371</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G1661" t="n">
-        <v>22.8242874145508</v>
+        <v>22.8242893218994</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1662" t="n">
-        <v>22.3311080932617</v>
+        <v>22.3311100006104</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1663" t="n">
-        <v>21.4828453063965</v>
+        <v>21.4828433990479</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G1665" t="n">
-        <v>22.8637447357178</v>
+        <v>22.8637428283691</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1670" t="n">
-        <v>24.6391849517822</v>
+        <v>24.6391830444336</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1671" t="n">
-        <v>24.5010929107666</v>
+        <v>24.5010948181152</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G1673" t="n">
-        <v>25.0929088592529</v>
+        <v>25.0929069519043</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G1676" t="n">
-        <v>25.0929088592529</v>
+        <v>25.0929069519043</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G1677" t="n">
-        <v>25.9806289672852</v>
+        <v>25.9806308746338</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1681" t="n">
-        <v>24.5010929107666</v>
+        <v>24.5010948181152</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1684" t="n">
-        <v>26.0398082733154</v>
+        <v>26.0398101806641</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G1689" t="n">
-        <v>23.9290065765381</v>
+        <v>23.9290084838867</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G1690" t="n">
-        <v>23.9290065765381</v>
+        <v>23.9290084838867</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1694" t="n">
-        <v>24.2249145507812</v>
+        <v>24.2249126434326</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>24.5</v>
       </c>
       <c r="G1695" t="n">
-        <v>24.1657314300537</v>
+        <v>24.1657333374023</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G1697" t="n">
-        <v>23.5344638824463</v>
+        <v>23.5344657897949</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1699" t="n">
-        <v>23.7711906433105</v>
+        <v>23.7711887359619</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G1708" t="n">
-        <v>23.5344638824463</v>
+        <v>23.5344657897949</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>23.0599994659424</v>
       </c>
       <c r="G1709" t="n">
-        <v>22.7453804016113</v>
+        <v>22.7453784942627</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G1714" t="n">
-        <v>20.0427627563477</v>
+        <v>20.042760848999</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1715" t="n">
-        <v>19.7863101959229</v>
+        <v>19.7863082885742</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G1719" t="n">
-        <v>20.1611270904541</v>
+        <v>20.1611251831055</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1720" t="n">
-        <v>21.36448097229</v>
+        <v>21.3644790649414</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1725" t="n">
-        <v>21.4828453063965</v>
+        <v>21.4828433990479</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1726" t="n">
-        <v>20.7726650238037</v>
+        <v>20.7726669311523</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1727" t="n">
-        <v>21.3053016662598</v>
+        <v>21.3052997589111</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1729" t="n">
-        <v>21.9168376922607</v>
+        <v>21.9168395996094</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1733" t="n">
-        <v>21.4828453063965</v>
+        <v>21.4828433990479</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1735" t="n">
-        <v>22.3311080932617</v>
+        <v>22.3311100006104</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>22</v>
       </c>
       <c r="G1741" t="n">
-        <v>21.6998405456543</v>
+        <v>21.6998424530029</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G1742" t="n">
-        <v>21.9760208129883</v>
+        <v>21.9760227203369</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G1746" t="n">
-        <v>24.0473670959473</v>
+        <v>24.0473690032959</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1748" t="n">
-        <v>26.9275302886963</v>
+        <v>26.9275283813477</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G1752" t="n">
-        <v>23.9290065765381</v>
+        <v>23.9290084838867</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G1754" t="n">
-        <v>23.8895530700684</v>
+        <v>23.8895511627197</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1756" t="n">
-        <v>24.9548168182373</v>
+        <v>24.9548187255859</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1763" t="n">
-        <v>26.5921688079834</v>
+        <v>26.5921669006348</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G1764" t="n">
-        <v>26.6118946075439</v>
+        <v>26.6118965148926</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1768" t="n">
-        <v>24.6194553375244</v>
+        <v>24.619457244873</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1780" t="n">
-        <v>25.5466327667236</v>
+        <v>25.546630859375</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G1781" t="n">
-        <v>26.0200843811035</v>
+        <v>26.0200824737549</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G1784" t="n">
-        <v>26.1581726074219</v>
+        <v>26.1581745147705</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1786" t="n">
-        <v>26.5921688079834</v>
+        <v>26.5921669006348</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1791" t="n">
-        <v>28.5846118927002</v>
+        <v>28.5846099853516</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>28.5</v>
       </c>
       <c r="G1794" t="n">
-        <v>28.1111583709717</v>
+        <v>28.1111602783203</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1797" t="n">
-        <v>28.702974319458</v>
+        <v>28.7029724121094</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1802" t="n">
-        <v>28.7424259185791</v>
+        <v>28.7424278259277</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1804" t="n">
-        <v>28.8607902526855</v>
+        <v>28.8607921600342</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1805" t="n">
-        <v>28.6832427978516</v>
+        <v>28.6832447052002</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>30</v>
       </c>
       <c r="G1809" t="n">
-        <v>29.5906925201416</v>
+        <v>29.5906944274902</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>30</v>
       </c>
       <c r="G1810" t="n">
-        <v>29.5906925201416</v>
+        <v>29.5906944274902</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>29.4200000762939</v>
       </c>
       <c r="G1812" t="n">
-        <v>29.0186061859131</v>
+        <v>29.0186080932617</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1817" t="n">
-        <v>29.1369686126709</v>
+        <v>29.1369705200195</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>29.2199993133545</v>
       </c>
       <c r="G1818" t="n">
-        <v>28.8213367462158</v>
+        <v>28.8213348388672</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1820" t="n">
-        <v>28.15061378479</v>
+        <v>28.1506118774414</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1822" t="n">
-        <v>27.6968879699707</v>
+        <v>27.6968860626221</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G1828" t="n">
-        <v>27.5390720367432</v>
+        <v>27.5390739440918</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G1832" t="n">
-        <v>26.6710796356201</v>
+        <v>26.6710777282715</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>25.9200000762939</v>
       </c>
       <c r="G1834" t="n">
-        <v>25.5663585662842</v>
+        <v>25.5663566589355</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1835" t="n">
-        <v>24.3827304840088</v>
+        <v>24.3827323913574</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1837" t="n">
-        <v>22.2916564941406</v>
+        <v>22.291654586792</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>24.5</v>
       </c>
       <c r="G1840" t="n">
-        <v>24.1657314300537</v>
+        <v>24.1657333374023</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1842" t="n">
-        <v>24.3827304840088</v>
+        <v>24.3827323913574</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G1844" t="n">
-        <v>24.9942722320557</v>
+        <v>24.994270324707</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G1848" t="n">
-        <v>26.2863998413086</v>
+        <v>26.2864017486572</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>27</v>
       </c>
       <c r="G1850" t="n">
-        <v>26.6316223144531</v>
+        <v>26.6316242218018</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>27.75</v>
       </c>
       <c r="G1853" t="n">
-        <v>27.3713912963867</v>
+        <v>27.3713893890381</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1854" t="n">
-        <v>27.9632053375244</v>
+        <v>27.963207244873</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G1855" t="n">
-        <v>27.6672954559326</v>
+        <v>27.6672973632812</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1856" t="n">
-        <v>27.5686645507812</v>
+        <v>27.5686626434326</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>27.75</v>
       </c>
       <c r="G1860" t="n">
-        <v>27.3713912963867</v>
+        <v>27.3713893890381</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>27.75</v>
       </c>
       <c r="G1861" t="n">
-        <v>27.3713912963867</v>
+        <v>27.3713893890381</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>27.75</v>
       </c>
       <c r="G1862" t="n">
-        <v>27.3713912963867</v>
+        <v>27.3713893890381</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1868" t="n">
-        <v>26.7795791625977</v>
+        <v>26.779577255249</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>27.25</v>
       </c>
       <c r="G1872" t="n">
-        <v>26.8782119750977</v>
+        <v>26.8782138824463</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1879" t="n">
-        <v>27.9632053375244</v>
+        <v>27.963207244873</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1881" t="n">
-        <v>27.9632053375244</v>
+        <v>27.963207244873</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1884" t="n">
-        <v>27.9632053375244</v>
+        <v>27.963207244873</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1886" t="n">
-        <v>27.9632053375244</v>
+        <v>27.963207244873</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>31.25</v>
       </c>
       <c r="G1891" t="n">
-        <v>30.823637008667</v>
+        <v>30.8236389160156</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1892" t="n">
-        <v>31.9579524993896</v>
+        <v>31.9579486846924</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>33.25</v>
       </c>
       <c r="G1895" t="n">
-        <v>32.7963523864746</v>
+        <v>32.7963485717773</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>31.8593101501465</v>
+        <v>31.8593139648438</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1903" t="n">
-        <v>30.5277328491211</v>
+        <v>30.5277309417725</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>30.75</v>
       </c>
       <c r="G1908" t="n">
-        <v>30.3304615020752</v>
+        <v>30.3304595947266</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>30.6000003814697</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>176986</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>28.7999992370605</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>30.6000003814697</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>28.7999992370605</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>28.7999992370605</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>31.1499996185303</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>31.25</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>49796</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>31.8999996185303</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>30.3999996185303</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>31.6499996185303</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>31.6499996185303</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>30.5499992370605</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>49597</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -63308,7 +63308,7 @@
         <v>49597</v>
       </c>
       <c r="C2737" t="n">
-        <v>31.75</v>
+        <v>31.7999992370605</v>
       </c>
       <c r="D2737" t="n">
         <v>30.5</v>
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>30.5</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>31.7999992370605</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>53577</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>31.8999996185303</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>31.1000003814697</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>31.7000007629395</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>31.7000007629395</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>31.6499996185303</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>32697</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>32.4500007629395</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>31.2000007629395</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>31.2000007629395</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>45967</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>33.2000007629395</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>32.2999992370605</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>33</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82393646240234</v>
+        <v>6.82393598556519</v>
       </c>
       <c r="H2" t="n">
         <v>27799</v>
@@ -456,7 +456,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G3" t="n">
-        <v>6.73136377334595</v>
+        <v>6.73136281967163</v>
       </c>
       <c r="H3" t="n">
         <v>30952</v>
@@ -485,7 +485,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6343822479248</v>
+        <v>6.63438272476196</v>
       </c>
       <c r="H4" t="n">
         <v>6498</v>
@@ -514,7 +514,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>6.74458742141724</v>
+        <v>6.74458837509155</v>
       </c>
       <c r="H5" t="n">
         <v>87223</v>
@@ -543,7 +543,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>6.74458742141724</v>
+        <v>6.74458837509155</v>
       </c>
       <c r="H6" t="n">
         <v>33933</v>
@@ -572,7 +572,7 @@
         <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.61234140396118</v>
+        <v>6.61234045028687</v>
       </c>
       <c r="H7" t="n">
         <v>14765</v>
@@ -630,7 +630,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>6.7886700630188</v>
+        <v>6.78866910934448</v>
       </c>
       <c r="H9" t="n">
         <v>11646</v>
@@ -659,7 +659,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>6.52417612075806</v>
+        <v>6.52417659759521</v>
       </c>
       <c r="H10" t="n">
         <v>35744</v>
@@ -688,7 +688,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2949481010437</v>
+        <v>6.29494762420654</v>
       </c>
       <c r="H11" t="n">
         <v>36818</v>
@@ -717,7 +717,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>6.07453727722168</v>
+        <v>6.07453632354736</v>
       </c>
       <c r="H12" t="n">
         <v>100254</v>
@@ -746,7 +746,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>6.32580614089966</v>
+        <v>6.32580709457397</v>
       </c>
       <c r="H13" t="n">
         <v>18590</v>
@@ -804,7 +804,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>6.53299140930176</v>
+        <v>6.53299283981323</v>
       </c>
       <c r="H15" t="n">
         <v>54538</v>
@@ -833,7 +833,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>6.43601083755493</v>
+        <v>6.43601131439209</v>
       </c>
       <c r="H16" t="n">
         <v>98737</v>
@@ -891,7 +891,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>6.497727394104</v>
+        <v>6.49772644042969</v>
       </c>
       <c r="H18" t="n">
         <v>45693</v>
@@ -920,7 +920,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>6.62997388839722</v>
+        <v>6.62997436523438</v>
       </c>
       <c r="H19" t="n">
         <v>19134</v>
@@ -949,7 +949,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G20" t="n">
-        <v>6.73577070236206</v>
+        <v>6.73577117919922</v>
       </c>
       <c r="H20" t="n">
         <v>8655</v>
@@ -1007,7 +1007,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G22" t="n">
-        <v>6.63878965377808</v>
+        <v>6.63879013061523</v>
       </c>
       <c r="H22" t="n">
         <v>4038</v>
@@ -1181,7 +1181,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87616634368896</v>
+        <v>5.87616682052612</v>
       </c>
       <c r="H28" t="n">
         <v>32757</v>
@@ -1210,7 +1210,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>6.25968217849731</v>
+        <v>6.25968265533447</v>
       </c>
       <c r="H29" t="n">
         <v>30386</v>
@@ -1268,7 +1268,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>6.22882604598999</v>
+        <v>6.22882556915283</v>
       </c>
       <c r="H31" t="n">
         <v>13397</v>
@@ -1326,7 +1326,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G33" t="n">
-        <v>6.31698989868164</v>
+        <v>6.31698894500732</v>
       </c>
       <c r="H33" t="n">
         <v>2348</v>
@@ -1355,7 +1355,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>6.48450231552124</v>
+        <v>6.48450183868408</v>
       </c>
       <c r="H34" t="n">
         <v>9218</v>
@@ -1384,7 +1384,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>6.52417612075806</v>
+        <v>6.52417659759521</v>
       </c>
       <c r="H35" t="n">
         <v>11539</v>
@@ -1471,7 +1471,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>6.36548042297363</v>
+        <v>6.36547946929932</v>
       </c>
       <c r="H38" t="n">
         <v>930</v>
@@ -1616,7 +1616,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>6.43601083755493</v>
+        <v>6.43601131439209</v>
       </c>
       <c r="H43" t="n">
         <v>8528</v>
@@ -1674,7 +1674,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>6.40956354141235</v>
+        <v>6.40956258773804</v>
       </c>
       <c r="H45" t="n">
         <v>25241</v>
@@ -1703,7 +1703,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>6.40956354141235</v>
+        <v>6.40956258773804</v>
       </c>
       <c r="H46" t="n">
         <v>1765</v>
@@ -1732,7 +1732,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.2023754119873</v>
+        <v>6.20237493515015</v>
       </c>
       <c r="H47" t="n">
         <v>9433</v>
@@ -1761,7 +1761,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G48" t="n">
-        <v>6.22000932693481</v>
+        <v>6.2200083732605</v>
       </c>
       <c r="H48" t="n">
         <v>8976</v>
@@ -1790,7 +1790,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>6.2508659362793</v>
+        <v>6.25086641311646</v>
       </c>
       <c r="H49" t="n">
         <v>44447</v>
@@ -1819,7 +1819,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>6.25968217849731</v>
+        <v>6.25968265533447</v>
       </c>
       <c r="H50" t="n">
         <v>5680</v>
@@ -1877,7 +1877,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G52" t="n">
-        <v>6.60352468490601</v>
+        <v>6.60352420806885</v>
       </c>
       <c r="H52" t="n">
         <v>32408</v>
@@ -1906,7 +1906,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>6.43601083755493</v>
+        <v>6.43601131439209</v>
       </c>
       <c r="H53" t="n">
         <v>34534</v>
@@ -1935,7 +1935,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>6.41397047042847</v>
+        <v>6.41397142410278</v>
       </c>
       <c r="H54" t="n">
         <v>22911</v>
@@ -1964,7 +1964,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>6.43601083755493</v>
+        <v>6.43601131439209</v>
       </c>
       <c r="H55" t="n">
         <v>41740</v>
@@ -2022,7 +2022,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G57" t="n">
-        <v>6.42719554901123</v>
+        <v>6.42719507217407</v>
       </c>
       <c r="H57" t="n">
         <v>56192</v>
@@ -2051,7 +2051,7 @@
         <v>7.5</v>
       </c>
       <c r="G58" t="n">
-        <v>6.61234140396118</v>
+        <v>6.61234045028687</v>
       </c>
       <c r="H58" t="n">
         <v>51559</v>
@@ -2080,7 +2080,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>6.4316029548645</v>
+        <v>6.43160390853882</v>
       </c>
       <c r="H59" t="n">
         <v>14204</v>
@@ -2138,7 +2138,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="n">
-        <v>6.17151784896851</v>
+        <v>6.17151832580566</v>
       </c>
       <c r="H61" t="n">
         <v>13993</v>
@@ -2196,7 +2196,7 @@
         <v>7</v>
       </c>
       <c r="G63" t="n">
-        <v>6.17151784896851</v>
+        <v>6.17151832580566</v>
       </c>
       <c r="H63" t="n">
         <v>22234</v>
@@ -2225,7 +2225,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>6.2640905380249</v>
+        <v>6.26409149169922</v>
       </c>
       <c r="H64" t="n">
         <v>26313</v>
@@ -2312,7 +2312,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>6.26849937438965</v>
+        <v>6.26849985122681</v>
       </c>
       <c r="H67" t="n">
         <v>68623</v>
@@ -2341,7 +2341,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G68" t="n">
-        <v>6.22441720962524</v>
+        <v>6.2244176864624</v>
       </c>
       <c r="H68" t="n">
         <v>16070</v>
@@ -2370,7 +2370,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G69" t="n">
-        <v>6.19796848297119</v>
+        <v>6.19796800613403</v>
       </c>
       <c r="H69" t="n">
         <v>64201</v>
@@ -2399,7 +2399,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G70" t="n">
-        <v>6.23323345184326</v>
+        <v>6.23323440551758</v>
       </c>
       <c r="H70" t="n">
         <v>45475</v>
@@ -2428,7 +2428,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>6.13184452056885</v>
+        <v>6.13184404373169</v>
       </c>
       <c r="H71" t="n">
         <v>17623</v>
@@ -2457,7 +2457,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>6.16710948944092</v>
+        <v>6.16710901260376</v>
       </c>
       <c r="H72" t="n">
         <v>104245</v>
@@ -2515,7 +2515,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>6.25968217849731</v>
+        <v>6.25968265533447</v>
       </c>
       <c r="H74" t="n">
         <v>2836</v>
@@ -2602,7 +2602,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42719554901123</v>
+        <v>6.42719507217407</v>
       </c>
       <c r="H77" t="n">
         <v>4802</v>
@@ -2631,7 +2631,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>6.60352468490601</v>
+        <v>6.60352420806885</v>
       </c>
       <c r="H78" t="n">
         <v>55158</v>
@@ -2660,7 +2660,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>6.56385040283203</v>
+        <v>6.56385087966919</v>
       </c>
       <c r="H79" t="n">
         <v>13140</v>
@@ -2689,7 +2689,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G80" t="n">
-        <v>6.56385040283203</v>
+        <v>6.56385087966919</v>
       </c>
       <c r="H80" t="n">
         <v>12413</v>
@@ -2718,7 +2718,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G81" t="n">
-        <v>6.4536452293396</v>
+        <v>6.45364570617676</v>
       </c>
       <c r="H81" t="n">
         <v>18134</v>
@@ -2747,7 +2747,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>6.47127723693848</v>
+        <v>6.47127771377563</v>
       </c>
       <c r="H82" t="n">
         <v>74460</v>
@@ -2805,7 +2805,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>6.40956354141235</v>
+        <v>6.40956258773804</v>
       </c>
       <c r="H84" t="n">
         <v>1248</v>
@@ -2834,7 +2834,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>6.60761117935181</v>
+        <v>6.60761165618896</v>
       </c>
       <c r="H85" t="n">
         <v>14179</v>
@@ -2863,7 +2863,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>6.42756652832031</v>
+        <v>6.42756605148315</v>
       </c>
       <c r="H86" t="n">
         <v>17484</v>
@@ -2921,7 +2921,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>6.4185643196106</v>
+        <v>6.41856527328491</v>
       </c>
       <c r="H88" t="n">
         <v>8092</v>
@@ -2950,7 +2950,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>6.48157978057861</v>
+        <v>6.48158025741577</v>
       </c>
       <c r="H89" t="n">
         <v>3750</v>
@@ -3066,7 +3066,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>6.66612529754639</v>
+        <v>6.66612577438354</v>
       </c>
       <c r="H93" t="n">
         <v>11596</v>
@@ -3095,7 +3095,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G94" t="n">
-        <v>6.57160186767578</v>
+        <v>6.57160234451294</v>
       </c>
       <c r="H94" t="n">
         <v>45313</v>
@@ -3124,7 +3124,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>6.65712308883667</v>
+        <v>6.65712261199951</v>
       </c>
       <c r="H95" t="n">
         <v>34946</v>
@@ -3153,7 +3153,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>6.48157978057861</v>
+        <v>6.48158025741577</v>
       </c>
       <c r="H96" t="n">
         <v>17792</v>
@@ -3298,7 +3298,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G101" t="n">
-        <v>6.91818714141846</v>
+        <v>6.91818618774414</v>
       </c>
       <c r="H101" t="n">
         <v>23319</v>
@@ -3356,7 +3356,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G103" t="n">
-        <v>7.07572460174561</v>
+        <v>7.07572555541992</v>
       </c>
       <c r="H103" t="n">
         <v>33454</v>
@@ -3414,7 +3414,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>7.29177761077881</v>
+        <v>7.29177856445312</v>
       </c>
       <c r="H105" t="n">
         <v>25887</v>
@@ -3472,7 +3472,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G107" t="n">
-        <v>7.27377319335938</v>
+        <v>7.27377367019653</v>
       </c>
       <c r="H107" t="n">
         <v>8356</v>
@@ -3530,7 +3530,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G109" t="n">
-        <v>7.22876119613647</v>
+        <v>7.22876167297363</v>
       </c>
       <c r="H109" t="n">
         <v>17502</v>
@@ -3559,7 +3559,7 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>7.20175552368164</v>
+        <v>7.2017560005188</v>
       </c>
       <c r="H110" t="n">
         <v>20674</v>
@@ -3588,7 +3588,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.27377319335938</v>
+        <v>7.27377367019653</v>
       </c>
       <c r="H111" t="n">
         <v>10639</v>
@@ -3617,7 +3617,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.1972541809082</v>
+        <v>7.19725465774536</v>
       </c>
       <c r="H112" t="n">
         <v>4314</v>
@@ -3646,7 +3646,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G113" t="n">
-        <v>7.17024755477905</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H113" t="n">
         <v>15482</v>
@@ -3704,7 +3704,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>7.11173343658447</v>
+        <v>7.11173439025879</v>
       </c>
       <c r="H115" t="n">
         <v>25325</v>
@@ -3733,7 +3733,7 @@
         <v>7.75</v>
       </c>
       <c r="G116" t="n">
-        <v>6.9767017364502</v>
+        <v>6.97670030593872</v>
       </c>
       <c r="H116" t="n">
         <v>36916</v>
@@ -3762,7 +3762,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>7.05322027206421</v>
+        <v>7.05321979522705</v>
       </c>
       <c r="H117" t="n">
         <v>13746</v>
@@ -3791,7 +3791,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>6.93169021606445</v>
+        <v>6.93168878555298</v>
       </c>
       <c r="H118" t="n">
         <v>32849</v>
@@ -3820,7 +3820,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>6.81466245651245</v>
+        <v>6.81466197967529</v>
       </c>
       <c r="H119" t="n">
         <v>32283</v>
@@ -3849,7 +3849,7 @@
         <v>7.875</v>
       </c>
       <c r="G120" t="n">
-        <v>7.08922815322876</v>
+        <v>7.08922863006592</v>
       </c>
       <c r="H120" t="n">
         <v>11937</v>
@@ -3878,7 +3878,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G121" t="n">
-        <v>7.13873958587646</v>
+        <v>7.13874006271362</v>
       </c>
       <c r="H121" t="n">
         <v>15972</v>
@@ -3907,7 +3907,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>7.28277635574341</v>
+        <v>7.28277540206909</v>
       </c>
       <c r="H122" t="n">
         <v>34317</v>
@@ -3936,7 +3936,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G123" t="n">
-        <v>7.29627799987793</v>
+        <v>7.29627895355225</v>
       </c>
       <c r="H123" t="n">
         <v>7525</v>
@@ -3965,7 +3965,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>6.97219944000244</v>
+        <v>6.9721999168396</v>
       </c>
       <c r="H124" t="n">
         <v>18527</v>
@@ -4052,7 +4052,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>6.93169021606445</v>
+        <v>6.93168878555298</v>
       </c>
       <c r="H127" t="n">
         <v>26380</v>
@@ -4110,7 +4110,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H129" t="n">
         <v>30647</v>
@@ -4139,7 +4139,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>6.83266592025757</v>
+        <v>6.83266544342041</v>
       </c>
       <c r="H130" t="n">
         <v>18898</v>
@@ -4168,7 +4168,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>6.65262222290039</v>
+        <v>6.65262174606323</v>
       </c>
       <c r="H131" t="n">
         <v>10765</v>
@@ -4197,7 +4197,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G132" t="n">
-        <v>6.47257804870605</v>
+        <v>6.4725775718689</v>
       </c>
       <c r="H132" t="n">
         <v>8491</v>
@@ -4226,7 +4226,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>6.54459619522095</v>
+        <v>6.54459571838379</v>
       </c>
       <c r="H133" t="n">
         <v>6391</v>
@@ -4255,7 +4255,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>6.60761117935181</v>
+        <v>6.60761165618896</v>
       </c>
       <c r="H134" t="n">
         <v>11755</v>
@@ -4313,7 +4313,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.57160186767578</v>
+        <v>6.57160234451294</v>
       </c>
       <c r="H136" t="n">
         <v>11466</v>
@@ -4342,7 +4342,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G137" t="n">
-        <v>6.47257804870605</v>
+        <v>6.4725775718689</v>
       </c>
       <c r="H137" t="n">
         <v>23478</v>
@@ -4371,7 +4371,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>6.4185643196106</v>
+        <v>6.41856527328491</v>
       </c>
       <c r="H138" t="n">
         <v>7018</v>
@@ -4400,7 +4400,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>6.39155769348145</v>
+        <v>6.3915581703186</v>
       </c>
       <c r="H139" t="n">
         <v>14786</v>
@@ -4487,7 +4487,7 @@
         <v>7.25</v>
       </c>
       <c r="G142" t="n">
-        <v>6.5265908241272</v>
+        <v>6.52659130096436</v>
       </c>
       <c r="H142" t="n">
         <v>6347</v>
@@ -4516,7 +4516,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>6.43656921386719</v>
+        <v>6.43656969070435</v>
       </c>
       <c r="H143" t="n">
         <v>14044</v>
@@ -4603,7 +4603,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>6.54009389877319</v>
+        <v>6.54009437561035</v>
       </c>
       <c r="H146" t="n">
         <v>3693</v>
@@ -4632,7 +4632,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>6.54459619522095</v>
+        <v>6.54459571838379</v>
       </c>
       <c r="H147" t="n">
         <v>5328</v>
@@ -4661,7 +4661,7 @@
         <v>7.5</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164556503296</v>
       </c>
       <c r="H148" t="n">
         <v>13911</v>
@@ -4690,7 +4690,7 @@
         <v>7.5</v>
       </c>
       <c r="G149" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164556503296</v>
       </c>
       <c r="H149" t="n">
         <v>16812</v>
@@ -4719,7 +4719,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G150" t="n">
-        <v>6.68413019180298</v>
+        <v>6.68413066864014</v>
       </c>
       <c r="H150" t="n">
         <v>1322</v>
@@ -4748,7 +4748,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G151" t="n">
-        <v>6.54009389877319</v>
+        <v>6.54009437561035</v>
       </c>
       <c r="H151" t="n">
         <v>2590</v>
@@ -4777,7 +4777,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G152" t="n">
-        <v>6.46357583999634</v>
+        <v>6.46357536315918</v>
       </c>
       <c r="H152" t="n">
         <v>32309</v>
@@ -4806,7 +4806,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G153" t="n">
-        <v>6.51308870315552</v>
+        <v>6.5130877494812</v>
       </c>
       <c r="H153" t="n">
         <v>3696</v>
@@ -4835,7 +4835,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>6.6346173286438</v>
+        <v>6.63461780548096</v>
       </c>
       <c r="H154" t="n">
         <v>3535</v>
@@ -4864,7 +4864,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164556503296</v>
       </c>
       <c r="H155" t="n">
         <v>38855</v>
@@ -4893,7 +4893,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>6.81466245651245</v>
+        <v>6.81466197967529</v>
       </c>
       <c r="H156" t="n">
         <v>19365</v>
@@ -4980,7 +4980,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>6.73364162445068</v>
+        <v>6.73364114761353</v>
       </c>
       <c r="H159" t="n">
         <v>45305</v>
@@ -5009,7 +5009,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G160" t="n">
-        <v>6.85067129135132</v>
+        <v>6.85067081451416</v>
       </c>
       <c r="H160" t="n">
         <v>21418</v>
@@ -5125,7 +5125,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G164" t="n">
-        <v>6.76064825057983</v>
+        <v>6.76064872741699</v>
       </c>
       <c r="H164" t="n">
         <v>44354</v>
@@ -5241,7 +5241,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G168" t="n">
-        <v>6.79215574264526</v>
+        <v>6.79215621948242</v>
       </c>
       <c r="H168" t="n">
         <v>73891</v>
@@ -5270,7 +5270,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>6.7966570854187</v>
+        <v>6.79665660858154</v>
       </c>
       <c r="H169" t="n">
         <v>14815</v>
@@ -5299,7 +5299,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G170" t="n">
-        <v>6.77865266799927</v>
+        <v>6.77865219116211</v>
       </c>
       <c r="H170" t="n">
         <v>8152</v>
@@ -5386,7 +5386,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>6.84166812896729</v>
+        <v>6.84166765213013</v>
       </c>
       <c r="H173" t="n">
         <v>4472</v>
@@ -5444,7 +5444,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G175" t="n">
-        <v>7.07572460174561</v>
+        <v>7.07572555541992</v>
       </c>
       <c r="H175" t="n">
         <v>50017</v>
@@ -5502,7 +5502,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G177" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H177" t="n">
         <v>109990</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20175552368164</v>
+        <v>7.2017560005188</v>
       </c>
       <c r="H178" t="n">
         <v>55216</v>
@@ -5560,7 +5560,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H179" t="n">
         <v>14514</v>
@@ -5589,7 +5589,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G180" t="n">
-        <v>7.17024755477905</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H180" t="n">
         <v>5632</v>
@@ -5618,7 +5618,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.05322027206421</v>
+        <v>7.05321979522705</v>
       </c>
       <c r="H181" t="n">
         <v>17322</v>
@@ -5647,7 +5647,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>7.05322027206421</v>
+        <v>7.05321979522705</v>
       </c>
       <c r="H182" t="n">
         <v>12460</v>
@@ -5705,7 +5705,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G184" t="n">
-        <v>6.94969415664673</v>
+        <v>6.94969367980957</v>
       </c>
       <c r="H184" t="n">
         <v>57488</v>
@@ -5734,7 +5734,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G185" t="n">
-        <v>6.94969415664673</v>
+        <v>6.94969367980957</v>
       </c>
       <c r="H185" t="n">
         <v>10419</v>
@@ -5763,7 +5763,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>6.94969415664673</v>
+        <v>6.94969367980957</v>
       </c>
       <c r="H186" t="n">
         <v>27635</v>
@@ -5792,7 +5792,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>6.93169021606445</v>
+        <v>6.93168878555298</v>
       </c>
       <c r="H187" t="n">
         <v>14831</v>
@@ -5850,7 +5850,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.7966570854187</v>
+        <v>6.79665660858154</v>
       </c>
       <c r="H189" t="n">
         <v>17762</v>
@@ -5879,7 +5879,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G190" t="n">
-        <v>6.60761117935181</v>
+        <v>6.60761165618896</v>
       </c>
       <c r="H190" t="n">
         <v>16505</v>
@@ -5966,7 +5966,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G193" t="n">
-        <v>6.67062520980835</v>
+        <v>6.67062616348267</v>
       </c>
       <c r="H193" t="n">
         <v>23088</v>
@@ -5995,7 +5995,7 @@
         <v>7.5</v>
       </c>
       <c r="G194" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164556503296</v>
       </c>
       <c r="H194" t="n">
         <v>25240</v>
@@ -6053,7 +6053,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.90468406677246</v>
+        <v>6.9046835899353</v>
       </c>
       <c r="H196" t="n">
         <v>8970</v>
@@ -6082,7 +6082,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>6.99470520019531</v>
+        <v>6.99470567703247</v>
       </c>
       <c r="H197" t="n">
         <v>5061</v>
@@ -6111,7 +6111,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G198" t="n">
-        <v>6.96319770812988</v>
+        <v>6.96319723129272</v>
       </c>
       <c r="H198" t="n">
         <v>16556</v>
@@ -6140,7 +6140,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G199" t="n">
-        <v>7.16574621200562</v>
+        <v>7.16574668884277</v>
       </c>
       <c r="H199" t="n">
         <v>15275</v>
@@ -6169,7 +6169,7 @@
         <v>8</v>
       </c>
       <c r="G200" t="n">
-        <v>7.20175552368164</v>
+        <v>7.2017560005188</v>
       </c>
       <c r="H200" t="n">
         <v>17845</v>
@@ -6227,7 +6227,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>6.99470520019531</v>
+        <v>6.99470567703247</v>
       </c>
       <c r="H202" t="n">
         <v>8408</v>
@@ -6256,7 +6256,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G203" t="n">
-        <v>7.03071451187134</v>
+        <v>7.03071403503418</v>
       </c>
       <c r="H203" t="n">
         <v>1632</v>
@@ -6285,7 +6285,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G204" t="n">
-        <v>7.07572460174561</v>
+        <v>7.07572555541992</v>
       </c>
       <c r="H204" t="n">
         <v>10951</v>
@@ -6401,7 +6401,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>7.12073516845703</v>
+        <v>7.12073564529419</v>
       </c>
       <c r="H208" t="n">
         <v>8822</v>
@@ -6430,7 +6430,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G209" t="n">
-        <v>7.05772113800049</v>
+        <v>7.05772066116333</v>
       </c>
       <c r="H209" t="n">
         <v>37159</v>
@@ -6459,7 +6459,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G210" t="n">
-        <v>7.03521585464478</v>
+        <v>7.03521537780762</v>
       </c>
       <c r="H210" t="n">
         <v>10188</v>
@@ -6517,7 +6517,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>7.18375062942505</v>
+        <v>7.18375158309937</v>
       </c>
       <c r="H212" t="n">
         <v>2652</v>
@@ -6546,7 +6546,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>7.20175552368164</v>
+        <v>7.2017560005188</v>
       </c>
       <c r="H213" t="n">
         <v>12600</v>
@@ -6575,7 +6575,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>7.27377319335938</v>
+        <v>7.27377367019653</v>
       </c>
       <c r="H214" t="n">
         <v>16829</v>
@@ -6604,7 +6604,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>7.35479259490967</v>
+        <v>7.35479307174683</v>
       </c>
       <c r="H215" t="n">
         <v>10432</v>
@@ -6633,7 +6633,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G216" t="n">
-        <v>7.19275283813477</v>
+        <v>7.19275331497192</v>
       </c>
       <c r="H216" t="n">
         <v>12650</v>
@@ -6662,7 +6662,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G217" t="n">
-        <v>7.21976041793823</v>
+        <v>7.21976137161255</v>
       </c>
       <c r="H217" t="n">
         <v>14711</v>
@@ -6691,7 +6691,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G218" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H218" t="n">
         <v>5931</v>
@@ -6720,7 +6720,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>7.16124582290649</v>
+        <v>7.16124534606934</v>
       </c>
       <c r="H219" t="n">
         <v>3644</v>
@@ -6749,7 +6749,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G220" t="n">
-        <v>7.17024755477905</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H220" t="n">
         <v>11070</v>
@@ -6894,7 +6894,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G225" t="n">
-        <v>6.85517024993896</v>
+        <v>6.85517072677612</v>
       </c>
       <c r="H225" t="n">
         <v>3694</v>
@@ -6923,7 +6923,7 @@
         <v>7.5</v>
       </c>
       <c r="G226" t="n">
-        <v>6.75164604187012</v>
+        <v>6.75164556503296</v>
       </c>
       <c r="H226" t="n">
         <v>30587</v>
@@ -6981,7 +6981,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G228" t="n">
-        <v>7.15224361419678</v>
+        <v>7.15224313735962</v>
       </c>
       <c r="H228" t="n">
         <v>13253</v>
@@ -7010,7 +7010,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>6.88667917251587</v>
+        <v>6.88667869567871</v>
       </c>
       <c r="H229" t="n">
         <v>32778</v>
@@ -7068,7 +7068,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>7.11173343658447</v>
+        <v>7.11173439025879</v>
       </c>
       <c r="H231" t="n">
         <v>25042</v>
@@ -7097,7 +7097,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>7.11173343658447</v>
+        <v>7.11173439025879</v>
       </c>
       <c r="H232" t="n">
         <v>21015</v>
@@ -7126,7 +7126,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>7.20175552368164</v>
+        <v>7.2017560005188</v>
       </c>
       <c r="H233" t="n">
         <v>8031</v>
@@ -7155,7 +7155,7 @@
         <v>8</v>
       </c>
       <c r="G234" t="n">
-        <v>7.20175552368164</v>
+        <v>7.2017560005188</v>
       </c>
       <c r="H234" t="n">
         <v>31114</v>
@@ -7184,7 +7184,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G235" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H235" t="n">
         <v>6049</v>
@@ -7213,7 +7213,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G236" t="n">
-        <v>6.94969415664673</v>
+        <v>6.94969367980957</v>
       </c>
       <c r="H236" t="n">
         <v>10021</v>
@@ -7242,7 +7242,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G237" t="n">
-        <v>7.21976041793823</v>
+        <v>7.21976137161255</v>
       </c>
       <c r="H237" t="n">
         <v>36844</v>
@@ -7271,7 +7271,7 @@
         <v>8</v>
       </c>
       <c r="G238" t="n">
-        <v>7.20175552368164</v>
+        <v>7.2017560005188</v>
       </c>
       <c r="H238" t="n">
         <v>25207</v>
@@ -7300,7 +7300,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G239" t="n">
-        <v>7.15224361419678</v>
+        <v>7.15224313735962</v>
       </c>
       <c r="H239" t="n">
         <v>103907</v>
@@ -7329,7 +7329,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G240" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H240" t="n">
         <v>9254</v>
@@ -7358,7 +7358,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G241" t="n">
-        <v>7.48982572555542</v>
+        <v>7.48982524871826</v>
       </c>
       <c r="H241" t="n">
         <v>99151</v>
@@ -7387,7 +7387,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G242" t="n">
-        <v>7.44931554794312</v>
+        <v>7.44931602478027</v>
       </c>
       <c r="H242" t="n">
         <v>12622</v>
@@ -7416,7 +7416,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>7.4718222618103</v>
+        <v>7.47182178497314</v>
       </c>
       <c r="H243" t="n">
         <v>2167</v>
@@ -7445,7 +7445,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>7.17024755477905</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H244" t="n">
         <v>14353</v>
@@ -7474,7 +7474,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76064825057983</v>
+        <v>6.76064872741699</v>
       </c>
       <c r="H245" t="n">
         <v>205811</v>
@@ -7503,7 +7503,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G246" t="n">
-        <v>7.15224361419678</v>
+        <v>7.15224313735962</v>
       </c>
       <c r="H246" t="n">
         <v>60307</v>
@@ -7532,7 +7532,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>7.38179922103882</v>
+        <v>7.38179874420166</v>
       </c>
       <c r="H247" t="n">
         <v>12031</v>
@@ -7561,7 +7561,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G248" t="n">
-        <v>7.38179922103882</v>
+        <v>7.38179874420166</v>
       </c>
       <c r="H248" t="n">
         <v>5183</v>
@@ -7619,7 +7619,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>7.38179922103882</v>
+        <v>7.38179874420166</v>
       </c>
       <c r="H250" t="n">
         <v>7849</v>
@@ -7648,7 +7648,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>7.57984685897827</v>
+        <v>7.57984781265259</v>
       </c>
       <c r="H251" t="n">
         <v>10255</v>
@@ -7677,7 +7677,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G252" t="n">
-        <v>7.63386011123657</v>
+        <v>7.63386058807373</v>
       </c>
       <c r="H252" t="n">
         <v>12877</v>
@@ -7706,7 +7706,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>7.69687652587891</v>
+        <v>7.69687747955322</v>
       </c>
       <c r="H253" t="n">
         <v>15824</v>
@@ -7735,7 +7735,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>7.69687652587891</v>
+        <v>7.69687747955322</v>
       </c>
       <c r="H254" t="n">
         <v>4269</v>
@@ -7764,7 +7764,7 @@
         <v>8.5</v>
       </c>
       <c r="G255" t="n">
-        <v>7.65186595916748</v>
+        <v>7.65186548233032</v>
       </c>
       <c r="H255" t="n">
         <v>9504</v>
@@ -7793,7 +7793,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>7.64736366271973</v>
+        <v>7.64736413955688</v>
       </c>
       <c r="H256" t="n">
         <v>6072</v>
@@ -7851,7 +7851,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G258" t="n">
-        <v>7.74188852310181</v>
+        <v>7.74188756942749</v>
       </c>
       <c r="H258" t="n">
         <v>16688</v>
@@ -7880,7 +7880,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G259" t="n">
-        <v>7.93993425369263</v>
+        <v>7.93993616104126</v>
       </c>
       <c r="H259" t="n">
         <v>22787</v>
@@ -7909,7 +7909,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G260" t="n">
-        <v>8.30902576446533</v>
+        <v>8.30902481079102</v>
       </c>
       <c r="H260" t="n">
         <v>53287</v>
@@ -7938,7 +7938,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G261" t="n">
-        <v>8.38104248046875</v>
+        <v>8.38104343414307</v>
       </c>
       <c r="H261" t="n">
         <v>17570</v>
@@ -7967,7 +7967,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G262" t="n">
-        <v>8.41705322265625</v>
+        <v>8.41705226898193</v>
       </c>
       <c r="H262" t="n">
         <v>14117</v>
@@ -8025,7 +8025,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G264" t="n">
-        <v>8.3450345993042</v>
+        <v>8.34503650665283</v>
       </c>
       <c r="H264" t="n">
         <v>15973</v>
@@ -8083,7 +8083,7 @@
         <v>9.25</v>
       </c>
       <c r="G266" t="n">
-        <v>8.32702922821045</v>
+        <v>8.32703018188477</v>
       </c>
       <c r="H266" t="n">
         <v>11327</v>
@@ -8112,7 +8112,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G267" t="n">
-        <v>8.19199848175049</v>
+        <v>8.19199752807617</v>
       </c>
       <c r="H267" t="n">
         <v>22967</v>
@@ -8141,7 +8141,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>8.21000289916992</v>
+        <v>8.21000099182129</v>
       </c>
       <c r="H268" t="n">
         <v>19678</v>
@@ -8170,7 +8170,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.19199848175049</v>
+        <v>8.19199752807617</v>
       </c>
       <c r="H269" t="n">
         <v>14531</v>
@@ -8199,7 +8199,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G270" t="n">
-        <v>8.30452442169189</v>
+        <v>8.30452632904053</v>
       </c>
       <c r="H270" t="n">
         <v>20634</v>
@@ -8228,7 +8228,7 @@
         <v>9.25</v>
       </c>
       <c r="G271" t="n">
-        <v>8.32702922821045</v>
+        <v>8.32703018188477</v>
       </c>
       <c r="H271" t="n">
         <v>4940</v>
@@ -8286,7 +8286,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>8.2910213470459</v>
+        <v>8.29102325439453</v>
       </c>
       <c r="H273" t="n">
         <v>8840</v>
@@ -8315,7 +8315,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>8.33152961730957</v>
+        <v>8.33153247833252</v>
       </c>
       <c r="H274" t="n">
         <v>6261</v>
@@ -8344,7 +8344,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.34053325653076</v>
+        <v>8.34053230285645</v>
       </c>
       <c r="H275" t="n">
         <v>9669</v>
@@ -8373,7 +8373,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.43505668640137</v>
+        <v>8.43505573272705</v>
       </c>
       <c r="H276" t="n">
         <v>15308</v>
@@ -8460,7 +8460,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>8.06596755981445</v>
+        <v>8.06596660614014</v>
       </c>
       <c r="H279" t="n">
         <v>8370</v>
@@ -8489,7 +8489,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.30452442169189</v>
+        <v>8.30452632904053</v>
       </c>
       <c r="H280" t="n">
         <v>12394</v>
@@ -8576,7 +8576,7 @@
         <v>9.25</v>
       </c>
       <c r="G283" t="n">
-        <v>8.32702922821045</v>
+        <v>8.32703018188477</v>
       </c>
       <c r="H283" t="n">
         <v>12954</v>
@@ -8634,7 +8634,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G285" t="n">
-        <v>8.04346084594727</v>
+        <v>8.04346179962158</v>
       </c>
       <c r="H285" t="n">
         <v>7927</v>
@@ -8663,7 +8663,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G286" t="n">
-        <v>8.07946872711182</v>
+        <v>8.07946968078613</v>
       </c>
       <c r="H286" t="n">
         <v>6600</v>
@@ -8692,7 +8692,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>8.25051116943359</v>
+        <v>8.25051021575928</v>
       </c>
       <c r="H287" t="n">
         <v>7786</v>
@@ -8721,7 +8721,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G288" t="n">
-        <v>8.26401519775391</v>
+        <v>8.26401615142822</v>
       </c>
       <c r="H288" t="n">
         <v>14301</v>
@@ -8779,7 +8779,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G290" t="n">
-        <v>8.44855785369873</v>
+        <v>8.44855976104736</v>
       </c>
       <c r="H290" t="n">
         <v>15210</v>
@@ -8837,7 +8837,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G292" t="n">
-        <v>8.39004611968994</v>
+        <v>8.39004516601562</v>
       </c>
       <c r="H292" t="n">
         <v>8874</v>
@@ -8895,7 +8895,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>8.2910213470459</v>
+        <v>8.29102325439453</v>
       </c>
       <c r="H294" t="n">
         <v>1198</v>
@@ -8924,7 +8924,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G295" t="n">
-        <v>8.19649982452393</v>
+        <v>8.19649696350098</v>
       </c>
       <c r="H295" t="n">
         <v>6432</v>
@@ -8982,7 +8982,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G297" t="n">
-        <v>7.99844884872437</v>
+        <v>7.99844980239868</v>
       </c>
       <c r="H297" t="n">
         <v>21782</v>
@@ -9069,7 +9069,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G300" t="n">
-        <v>8.19199848175049</v>
+        <v>8.19199752807617</v>
       </c>
       <c r="H300" t="n">
         <v>4018</v>
@@ -9098,7 +9098,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G301" t="n">
-        <v>8.24600982666016</v>
+        <v>8.24601078033447</v>
       </c>
       <c r="H301" t="n">
         <v>3221</v>
@@ -9127,7 +9127,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G302" t="n">
-        <v>8.26401519775391</v>
+        <v>8.26401615142822</v>
       </c>
       <c r="H302" t="n">
         <v>4416</v>
@@ -9185,7 +9185,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.38104248046875</v>
+        <v>8.38104343414307</v>
       </c>
       <c r="H304" t="n">
         <v>8463</v>
@@ -9301,7 +9301,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>8.66011142730713</v>
+        <v>8.66011047363281</v>
       </c>
       <c r="H308" t="n">
         <v>35883</v>
@@ -9330,7 +9330,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>9.54232597351074</v>
+        <v>9.54232788085938</v>
       </c>
       <c r="H309" t="n">
         <v>74268</v>
@@ -9359,7 +9359,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G310" t="n">
-        <v>9.21824550628662</v>
+        <v>9.21824741363525</v>
       </c>
       <c r="H310" t="n">
         <v>329180</v>
@@ -9388,7 +9388,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>9.18223857879639</v>
+        <v>9.1822395324707</v>
       </c>
       <c r="H311" t="n">
         <v>148251</v>
@@ -9417,7 +9417,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G312" t="n">
-        <v>8.9841890335083</v>
+        <v>8.98419094085693</v>
       </c>
       <c r="H312" t="n">
         <v>187205</v>
@@ -9446,7 +9446,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G313" t="n">
-        <v>9.12822532653809</v>
+        <v>9.12822723388672</v>
       </c>
       <c r="H313" t="n">
         <v>92730</v>
@@ -9475,7 +9475,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G314" t="n">
-        <v>9.16423511505127</v>
+        <v>9.16423416137695</v>
       </c>
       <c r="H314" t="n">
         <v>80975</v>
@@ -9533,7 +9533,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G316" t="n">
-        <v>9.16423511505127</v>
+        <v>9.16423416137695</v>
       </c>
       <c r="H316" t="n">
         <v>66929</v>
@@ -9562,7 +9562,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G317" t="n">
-        <v>9.19124126434326</v>
+        <v>9.19124031066895</v>
       </c>
       <c r="H317" t="n">
         <v>89765</v>
@@ -9591,7 +9591,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G318" t="n">
-        <v>9.16423511505127</v>
+        <v>9.16423416137695</v>
       </c>
       <c r="H318" t="n">
         <v>26437</v>
@@ -9620,7 +9620,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G319" t="n">
-        <v>9.16423511505127</v>
+        <v>9.16423416137695</v>
       </c>
       <c r="H319" t="n">
         <v>40041</v>
@@ -9649,7 +9649,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>8.91217422485352</v>
+        <v>8.91217136383057</v>
       </c>
       <c r="H320" t="n">
         <v>33661</v>
@@ -9678,7 +9678,7 @@
         <v>10</v>
       </c>
       <c r="G321" t="n">
-        <v>9.00219440460205</v>
+        <v>9.00219535827637</v>
       </c>
       <c r="H321" t="n">
         <v>86078</v>
@@ -9707,7 +9707,7 @@
         <v>10</v>
       </c>
       <c r="G322" t="n">
-        <v>9.00219440460205</v>
+        <v>9.00219535827637</v>
       </c>
       <c r="H322" t="n">
         <v>62887</v>
@@ -9736,7 +9736,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G323" t="n">
-        <v>9.18223857879639</v>
+        <v>9.1822395324707</v>
       </c>
       <c r="H323" t="n">
         <v>28608</v>
@@ -9794,7 +9794,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>9.18223857879639</v>
+        <v>9.1822395324707</v>
       </c>
       <c r="H325" t="n">
         <v>31199</v>
@@ -9823,7 +9823,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>9.18223857879639</v>
+        <v>9.1822395324707</v>
       </c>
       <c r="H326" t="n">
         <v>9038</v>
@@ -9852,7 +9852,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G327" t="n">
-        <v>9.19124126434326</v>
+        <v>9.19124031066895</v>
       </c>
       <c r="H327" t="n">
         <v>18130</v>
@@ -9881,7 +9881,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>9.21824550628662</v>
+        <v>9.21824741363525</v>
       </c>
       <c r="H328" t="n">
         <v>33831</v>
@@ -9910,7 +9910,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>9.3172721862793</v>
+        <v>9.31727123260498</v>
       </c>
       <c r="H329" t="n">
         <v>53113</v>
@@ -9968,7 +9968,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>9.43429851531982</v>
+        <v>9.43429946899414</v>
       </c>
       <c r="H331" t="n">
         <v>20952</v>
@@ -10055,7 +10055,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G334" t="n">
-        <v>10.1724796295166</v>
+        <v>10.1724805831909</v>
       </c>
       <c r="H334" t="n">
         <v>69722</v>
@@ -10084,7 +10084,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>10.1724796295166</v>
+        <v>10.1724805831909</v>
       </c>
       <c r="H335" t="n">
         <v>42397</v>
@@ -10113,7 +10113,7 @@
         <v>11</v>
       </c>
       <c r="G336" t="n">
-        <v>9.90241432189941</v>
+        <v>9.9024133682251</v>
       </c>
       <c r="H336" t="n">
         <v>76445</v>
@@ -10171,7 +10171,7 @@
         <v>12</v>
       </c>
       <c r="G338" t="n">
-        <v>10.8026332855225</v>
+        <v>10.8026323318481</v>
       </c>
       <c r="H338" t="n">
         <v>30759</v>
@@ -10229,7 +10229,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G340" t="n">
-        <v>10.8656482696533</v>
+        <v>10.8656492233276</v>
       </c>
       <c r="H340" t="n">
         <v>22947</v>
@@ -10287,7 +10287,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G342" t="n">
-        <v>10.6946086883545</v>
+        <v>10.6946067810059</v>
       </c>
       <c r="H342" t="n">
         <v>25809</v>
@@ -10432,7 +10432,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>9.97381019592285</v>
+        <v>9.97381114959717</v>
       </c>
       <c r="H347" t="n">
         <v>68068</v>
@@ -10490,7 +10490,7 @@
         <v>11.25</v>
       </c>
       <c r="G349" t="n">
-        <v>10.3893852233887</v>
+        <v>10.3893871307373</v>
       </c>
       <c r="H349" t="n">
         <v>56227</v>
@@ -10635,7 +10635,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G354" t="n">
-        <v>10.3616809844971</v>
+        <v>10.3616819381714</v>
       </c>
       <c r="H354" t="n">
         <v>31434</v>
@@ -10693,7 +10693,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G356" t="n">
-        <v>10.4725017547607</v>
+        <v>10.4725008010864</v>
       </c>
       <c r="H356" t="n">
         <v>48558</v>
@@ -10722,7 +10722,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G357" t="n">
-        <v>10.4725017547607</v>
+        <v>10.4725008010864</v>
       </c>
       <c r="H357" t="n">
         <v>24284</v>
@@ -10751,7 +10751,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G358" t="n">
-        <v>10.4540328979492</v>
+        <v>10.4540319442749</v>
       </c>
       <c r="H358" t="n">
         <v>13229</v>
@@ -10780,7 +10780,7 @@
         <v>11.25</v>
       </c>
       <c r="G359" t="n">
-        <v>10.3893852233887</v>
+        <v>10.3893871307373</v>
       </c>
       <c r="H359" t="n">
         <v>34591</v>
@@ -10867,7 +10867,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G362" t="n">
-        <v>10.5002059936523</v>
+        <v>10.5002069473267</v>
       </c>
       <c r="H362" t="n">
         <v>218070</v>
@@ -10925,7 +10925,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>11.0358362197876</v>
+        <v>11.0358371734619</v>
       </c>
       <c r="H364" t="n">
         <v>26623</v>
@@ -10954,7 +10954,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>11.7284631729126</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H365" t="n">
         <v>70727</v>
@@ -10983,7 +10983,7 @@
         <v>12.5</v>
       </c>
       <c r="G366" t="n">
-        <v>11.5437631607056</v>
+        <v>11.5437622070312</v>
       </c>
       <c r="H366" t="n">
         <v>34569</v>
@@ -11012,7 +11012,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>11.1743612289429</v>
+        <v>11.1743621826172</v>
       </c>
       <c r="H367" t="n">
         <v>25812</v>
@@ -11070,7 +11070,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G369" t="n">
-        <v>11.0543069839478</v>
+        <v>11.0543088912964</v>
       </c>
       <c r="H369" t="n">
         <v>23293</v>
@@ -11099,7 +11099,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G370" t="n">
-        <v>11.1004829406738</v>
+        <v>11.1004819869995</v>
       </c>
       <c r="H370" t="n">
         <v>24644</v>
@@ -11128,7 +11128,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G371" t="n">
-        <v>10.9896612167358</v>
+        <v>10.9896621704102</v>
       </c>
       <c r="H371" t="n">
         <v>8663</v>
@@ -11157,7 +11157,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G372" t="n">
-        <v>10.7864933013916</v>
+        <v>10.786491394043</v>
       </c>
       <c r="H372" t="n">
         <v>5170</v>
@@ -11186,7 +11186,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>10.7126121520996</v>
+        <v>10.7126111984253</v>
       </c>
       <c r="H373" t="n">
         <v>10682</v>
@@ -11215,7 +11215,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G374" t="n">
-        <v>10.6941423416138</v>
+        <v>10.6941404342651</v>
       </c>
       <c r="H374" t="n">
         <v>15214</v>
@@ -11244,7 +11244,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434871673584</v>
       </c>
       <c r="H375" t="n">
         <v>7306</v>
@@ -11273,7 +11273,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434871673584</v>
       </c>
       <c r="H376" t="n">
         <v>16228</v>
@@ -11331,7 +11331,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434871673584</v>
       </c>
       <c r="H378" t="n">
         <v>19573</v>
@@ -11360,7 +11360,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>10.5279111862183</v>
+        <v>10.5279121398926</v>
       </c>
       <c r="H379" t="n">
         <v>10435</v>
@@ -11389,7 +11389,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G380" t="n">
-        <v>10.6941423416138</v>
+        <v>10.6941404342651</v>
       </c>
       <c r="H380" t="n">
         <v>9143</v>
@@ -11418,7 +11418,7 @@
         <v>12</v>
       </c>
       <c r="G381" t="n">
-        <v>11.082013130188</v>
+        <v>11.0820121765137</v>
       </c>
       <c r="H381" t="n">
         <v>23532</v>
@@ -11447,7 +11447,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>11.0173673629761</v>
+        <v>11.0173664093018</v>
       </c>
       <c r="H382" t="n">
         <v>68936</v>
@@ -11476,7 +11476,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G383" t="n">
-        <v>11.442177772522</v>
+        <v>11.4421787261963</v>
       </c>
       <c r="H383" t="n">
         <v>36094</v>
@@ -11505,7 +11505,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G384" t="n">
-        <v>11.0266008377075</v>
+        <v>11.0266017913818</v>
       </c>
       <c r="H384" t="n">
         <v>32520</v>
@@ -11534,7 +11534,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>10.897310256958</v>
+        <v>10.8973121643066</v>
       </c>
       <c r="H385" t="n">
         <v>17643</v>
@@ -11563,7 +11563,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G386" t="n">
-        <v>11.4052381515503</v>
+        <v>11.405237197876</v>
       </c>
       <c r="H386" t="n">
         <v>24629</v>
@@ -11592,7 +11592,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>11.3590631484985</v>
+        <v>11.3590621948242</v>
       </c>
       <c r="H387" t="n">
         <v>23382</v>
@@ -11621,7 +11621,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G388" t="n">
-        <v>11.6638164520264</v>
+        <v>11.6638174057007</v>
       </c>
       <c r="H388" t="n">
         <v>26892</v>
@@ -11650,7 +11650,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>12.0516881942749</v>
+        <v>12.0516872406006</v>
       </c>
       <c r="H389" t="n">
         <v>23206</v>
@@ -11679,7 +11679,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>12.2733268737793</v>
+        <v>12.2733287811279</v>
       </c>
       <c r="H390" t="n">
         <v>35825</v>
@@ -11708,7 +11708,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G391" t="n">
-        <v>11.848518371582</v>
+        <v>11.8485174179077</v>
       </c>
       <c r="H391" t="n">
         <v>56028</v>
@@ -11737,7 +11737,7 @@
         <v>13.5</v>
       </c>
       <c r="G392" t="n">
-        <v>12.4672632217407</v>
+        <v>12.467264175415</v>
       </c>
       <c r="H392" t="n">
         <v>55837</v>
@@ -11766,7 +11766,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G393" t="n">
-        <v>12.4765005111694</v>
+        <v>12.4764986038208</v>
       </c>
       <c r="H393" t="n">
         <v>15976</v>
@@ -11824,7 +11824,7 @@
         <v>13.75</v>
       </c>
       <c r="G395" t="n">
-        <v>12.6981401443481</v>
+        <v>12.6981391906738</v>
       </c>
       <c r="H395" t="n">
         <v>26338</v>
@@ -11882,7 +11882,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7443141937256</v>
+        <v>12.7443132400513</v>
       </c>
       <c r="H397" t="n">
         <v>74045</v>
@@ -11911,7 +11911,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G398" t="n">
-        <v>12.6796674728394</v>
+        <v>12.6796684265137</v>
       </c>
       <c r="H398" t="n">
         <v>50702</v>
@@ -11969,7 +11969,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G400" t="n">
-        <v>12.531907081604</v>
+        <v>12.5319080352783</v>
       </c>
       <c r="H400" t="n">
         <v>70356</v>
@@ -11998,7 +11998,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.5134382247925</v>
+        <v>12.5134391784668</v>
       </c>
       <c r="H401" t="n">
         <v>7478</v>
@@ -12056,7 +12056,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G403" t="n">
-        <v>12.4487934112549</v>
+        <v>12.4487924575806</v>
       </c>
       <c r="H403" t="n">
         <v>14247</v>
@@ -12085,7 +12085,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G404" t="n">
-        <v>12.4395580291748</v>
+        <v>12.4395589828491</v>
       </c>
       <c r="H404" t="n">
         <v>11075</v>
@@ -12143,7 +12143,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6334953308105</v>
+        <v>12.6334924697876</v>
       </c>
       <c r="H406" t="n">
         <v>44462</v>
@@ -12259,7 +12259,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G410" t="n">
-        <v>12.3472080230713</v>
+        <v>12.347207069397</v>
       </c>
       <c r="H410" t="n">
         <v>16035</v>
@@ -12288,7 +12288,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749113082886</v>
       </c>
       <c r="H411" t="n">
         <v>12503</v>
@@ -12317,7 +12317,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G412" t="n">
-        <v>12.2456226348877</v>
+        <v>12.2456245422363</v>
       </c>
       <c r="H412" t="n">
         <v>20658</v>
@@ -12404,7 +12404,7 @@
         <v>13.25</v>
       </c>
       <c r="G415" t="n">
-        <v>12.2363872528076</v>
+        <v>12.2363882064819</v>
       </c>
       <c r="H415" t="n">
         <v>7126</v>
@@ -12491,7 +12491,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>11.9039287567139</v>
+        <v>11.9039278030396</v>
       </c>
       <c r="H418" t="n">
         <v>14336</v>
@@ -12520,7 +12520,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2640914916992</v>
+        <v>12.2640933990479</v>
       </c>
       <c r="H419" t="n">
         <v>18396</v>
@@ -12549,7 +12549,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2179174423218</v>
+        <v>12.2179183959961</v>
       </c>
       <c r="H420" t="n">
         <v>7911</v>
@@ -12607,7 +12607,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>11.9131622314453</v>
+        <v>11.913161277771</v>
       </c>
       <c r="H422" t="n">
         <v>19946</v>
@@ -12636,7 +12636,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G423" t="n">
-        <v>12.2733268737793</v>
+        <v>12.2733287811279</v>
       </c>
       <c r="H423" t="n">
         <v>13089</v>
@@ -12665,7 +12665,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G424" t="n">
-        <v>11.9039287567139</v>
+        <v>11.9039278030396</v>
       </c>
       <c r="H424" t="n">
         <v>24343</v>
@@ -12752,7 +12752,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749113082886</v>
       </c>
       <c r="H427" t="n">
         <v>25492</v>
@@ -12781,7 +12781,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749113082886</v>
       </c>
       <c r="H428" t="n">
         <v>12922</v>
@@ -12810,7 +12810,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.2825632095337</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H429" t="n">
         <v>7261</v>
@@ -12839,7 +12839,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G430" t="n">
-        <v>12.393383026123</v>
+        <v>12.3933839797974</v>
       </c>
       <c r="H430" t="n">
         <v>20268</v>
@@ -12868,7 +12868,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G431" t="n">
-        <v>12.3010330200195</v>
+        <v>12.3010339736938</v>
       </c>
       <c r="H431" t="n">
         <v>22331</v>
@@ -12897,7 +12897,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3287391662598</v>
+        <v>12.3287382125854</v>
       </c>
       <c r="H432" t="n">
         <v>7635</v>
@@ -12926,7 +12926,7 @@
         <v>13.25</v>
       </c>
       <c r="G433" t="n">
-        <v>12.2363872528076</v>
+        <v>12.2363882064819</v>
       </c>
       <c r="H433" t="n">
         <v>7413</v>
@@ -12955,7 +12955,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G434" t="n">
-        <v>12.1070985794067</v>
+        <v>12.1070976257324</v>
       </c>
       <c r="H434" t="n">
         <v>11138</v>
@@ -12984,7 +12984,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>12.2179174423218</v>
+        <v>12.2179183959961</v>
       </c>
       <c r="H435" t="n">
         <v>18844</v>
@@ -13042,7 +13042,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G437" t="n">
-        <v>12.1070985794067</v>
+        <v>12.1070976257324</v>
       </c>
       <c r="H437" t="n">
         <v>8285</v>
@@ -13100,7 +13100,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G439" t="n">
-        <v>12.1994495391846</v>
+        <v>12.1994476318359</v>
       </c>
       <c r="H439" t="n">
         <v>14352</v>
@@ -13129,7 +13129,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G440" t="n">
-        <v>12.2917976379395</v>
+        <v>12.2917995452881</v>
       </c>
       <c r="H440" t="n">
         <v>48259</v>
@@ -13187,7 +13187,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G442" t="n">
-        <v>12.1532735824585</v>
+        <v>12.1532745361328</v>
       </c>
       <c r="H442" t="n">
         <v>16556</v>
@@ -13216,7 +13216,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G443" t="n">
-        <v>12.3841495513916</v>
+        <v>12.384147644043</v>
       </c>
       <c r="H443" t="n">
         <v>9664</v>
@@ -13245,7 +13245,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G444" t="n">
-        <v>12.2825632095337</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H444" t="n">
         <v>13699</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.2733268737793</v>
+        <v>12.2733287811279</v>
       </c>
       <c r="H445" t="n">
         <v>5307</v>
@@ -13332,7 +13332,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G447" t="n">
-        <v>12.2086839675903</v>
+        <v>12.208683013916</v>
       </c>
       <c r="H447" t="n">
         <v>16520</v>
@@ -13390,7 +13390,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>12.3287391662598</v>
+        <v>12.3287382125854</v>
       </c>
       <c r="H449" t="n">
         <v>13397</v>
@@ -13419,7 +13419,7 @@
         <v>13.25</v>
       </c>
       <c r="G450" t="n">
-        <v>12.2363872528076</v>
+        <v>12.2363882064819</v>
       </c>
       <c r="H450" t="n">
         <v>8935</v>
@@ -13477,7 +13477,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G452" t="n">
-        <v>11.9778070449829</v>
+        <v>11.9778089523315</v>
       </c>
       <c r="H452" t="n">
         <v>39521</v>
@@ -13506,7 +13506,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G453" t="n">
-        <v>11.3960018157959</v>
+        <v>11.3960027694702</v>
       </c>
       <c r="H453" t="n">
         <v>44685</v>
@@ -13535,7 +13535,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>11.5899391174316</v>
+        <v>11.5899381637573</v>
       </c>
       <c r="H454" t="n">
         <v>36511</v>
@@ -13593,7 +13593,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G456" t="n">
-        <v>11.5899391174316</v>
+        <v>11.5899381637573</v>
       </c>
       <c r="H456" t="n">
         <v>15466</v>
@@ -13622,7 +13622,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G457" t="n">
-        <v>11.6176443099976</v>
+        <v>11.6176424026489</v>
       </c>
       <c r="H457" t="n">
         <v>48293</v>
@@ -13738,7 +13738,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G461" t="n">
-        <v>11.5899391174316</v>
+        <v>11.5899381637573</v>
       </c>
       <c r="H461" t="n">
         <v>27618</v>
@@ -13767,7 +13767,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>11.6638164520264</v>
+        <v>11.6638174057007</v>
       </c>
       <c r="H462" t="n">
         <v>23893</v>
@@ -13796,7 +13796,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G463" t="n">
-        <v>11.7284631729126</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H463" t="n">
         <v>5575</v>
@@ -13825,7 +13825,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9131622314453</v>
+        <v>11.913161277771</v>
       </c>
       <c r="H464" t="n">
         <v>21916</v>
@@ -13854,7 +13854,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>11.7284631729126</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H465" t="n">
         <v>16388</v>
@@ -14115,7 +14115,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>11.7284631729126</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H474" t="n">
         <v>5286</v>
@@ -14260,7 +14260,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G479" t="n">
-        <v>11.6730518341064</v>
+        <v>11.6730527877808</v>
       </c>
       <c r="H479" t="n">
         <v>28724</v>
@@ -14289,7 +14289,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>11.5899391174316</v>
+        <v>11.5899381637573</v>
       </c>
       <c r="H480" t="n">
         <v>20398</v>
@@ -14347,7 +14347,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G482" t="n">
-        <v>11.2482423782349</v>
+        <v>11.2482414245605</v>
       </c>
       <c r="H482" t="n">
         <v>15513</v>
@@ -14405,7 +14405,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G484" t="n">
-        <v>11.1189498901367</v>
+        <v>11.1189517974854</v>
       </c>
       <c r="H484" t="n">
         <v>21219</v>
@@ -14463,7 +14463,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>11.5437631607056</v>
+        <v>11.5437622070312</v>
       </c>
       <c r="H486" t="n">
         <v>16792</v>
@@ -14492,7 +14492,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G487" t="n">
-        <v>11.4237070083618</v>
+        <v>11.4237089157104</v>
       </c>
       <c r="H487" t="n">
         <v>10474</v>
@@ -14521,7 +14521,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G488" t="n">
-        <v>11.55299949646</v>
+        <v>11.5529975891113</v>
       </c>
       <c r="H488" t="n">
         <v>9432</v>
@@ -14550,7 +14550,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>11.4052381515503</v>
+        <v>11.405237197876</v>
       </c>
       <c r="H489" t="n">
         <v>17083</v>
@@ -14579,7 +14579,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>11.442177772522</v>
+        <v>11.4421787261963</v>
       </c>
       <c r="H490" t="n">
         <v>40207</v>
@@ -14608,7 +14608,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>11.4052381515503</v>
+        <v>11.405237197876</v>
       </c>
       <c r="H491" t="n">
         <v>13738</v>
@@ -14753,7 +14753,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.626877784729</v>
+        <v>11.6268768310547</v>
       </c>
       <c r="H496" t="n">
         <v>27293</v>
@@ -14782,7 +14782,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G497" t="n">
-        <v>11.811577796936</v>
+        <v>11.8115768432617</v>
       </c>
       <c r="H497" t="n">
         <v>49655</v>
@@ -14869,7 +14869,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.0978651046753</v>
+        <v>12.0978631973267</v>
       </c>
       <c r="H500" t="n">
         <v>48615</v>
@@ -14898,7 +14898,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.9593381881714</v>
+        <v>11.9593391418457</v>
       </c>
       <c r="H501" t="n">
         <v>18010</v>
@@ -14927,7 +14927,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>11.8669900894165</v>
+        <v>11.8669881820679</v>
       </c>
       <c r="H502" t="n">
         <v>9279</v>
@@ -14956,7 +14956,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G503" t="n">
-        <v>11.6730518341064</v>
+        <v>11.6730527877808</v>
       </c>
       <c r="H503" t="n">
         <v>39087</v>
@@ -15014,7 +15014,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>12.0978651046753</v>
+        <v>12.0978631973267</v>
       </c>
       <c r="H505" t="n">
         <v>24572</v>
@@ -15101,7 +15101,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G508" t="n">
-        <v>12.2086839675903</v>
+        <v>12.208683013916</v>
       </c>
       <c r="H508" t="n">
         <v>32115</v>
@@ -15130,7 +15130,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749113082886</v>
       </c>
       <c r="H509" t="n">
         <v>18412</v>
@@ -15159,7 +15159,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G510" t="n">
-        <v>12.393383026123</v>
+        <v>12.3933839797974</v>
       </c>
       <c r="H510" t="n">
         <v>18903</v>
@@ -15188,7 +15188,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G511" t="n">
-        <v>12.2456226348877</v>
+        <v>12.2456245422363</v>
       </c>
       <c r="H511" t="n">
         <v>14988</v>
@@ -15246,7 +15246,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G513" t="n">
-        <v>12.393383026123</v>
+        <v>12.3933839797974</v>
       </c>
       <c r="H513" t="n">
         <v>12459</v>
@@ -15275,7 +15275,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749113082886</v>
       </c>
       <c r="H514" t="n">
         <v>80026</v>
@@ -15304,7 +15304,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G515" t="n">
-        <v>12.393383026123</v>
+        <v>12.3933839797974</v>
       </c>
       <c r="H515" t="n">
         <v>29210</v>
@@ -15333,7 +15333,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G516" t="n">
-        <v>12.4487934112549</v>
+        <v>12.4487924575806</v>
       </c>
       <c r="H516" t="n">
         <v>69930</v>
@@ -15362,7 +15362,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G517" t="n">
-        <v>12.8736047744751</v>
+        <v>12.8736038208008</v>
       </c>
       <c r="H517" t="n">
         <v>87834</v>
@@ -15420,7 +15420,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G519" t="n">
-        <v>14.055685043335</v>
+        <v>14.0556859970093</v>
       </c>
       <c r="H519" t="n">
         <v>45100</v>
@@ -15449,7 +15449,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>14.0372152328491</v>
+        <v>14.0372161865234</v>
       </c>
       <c r="H520" t="n">
         <v>46142</v>
@@ -15478,7 +15478,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G521" t="n">
-        <v>13.8894567489624</v>
+        <v>13.8894548416138</v>
       </c>
       <c r="H521" t="n">
         <v>13307</v>
@@ -15536,7 +15536,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G523" t="n">
-        <v>14.5728464126587</v>
+        <v>14.5728454589844</v>
       </c>
       <c r="H523" t="n">
         <v>124863</v>
@@ -15594,7 +15594,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>13.5754652023315</v>
+        <v>13.5754642486572</v>
       </c>
       <c r="H525" t="n">
         <v>37038</v>
@@ -15623,7 +15623,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G526" t="n">
-        <v>14.1480340957642</v>
+        <v>14.1480360031128</v>
       </c>
       <c r="H526" t="n">
         <v>29950</v>
@@ -15681,7 +15681,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G528" t="n">
-        <v>13.6493444442749</v>
+        <v>13.6493463516235</v>
       </c>
       <c r="H528" t="n">
         <v>10284</v>
@@ -15739,7 +15739,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G530" t="n">
-        <v>14.3327350616455</v>
+        <v>14.3327379226685</v>
       </c>
       <c r="H530" t="n">
         <v>29090</v>
@@ -15768,7 +15768,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G531" t="n">
-        <v>14.462025642395</v>
+        <v>14.4620246887207</v>
       </c>
       <c r="H531" t="n">
         <v>18780</v>
@@ -15826,7 +15826,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G533" t="n">
-        <v>14.4250860214233</v>
+        <v>14.425085067749</v>
       </c>
       <c r="H533" t="n">
         <v>69309</v>
@@ -15855,7 +15855,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G534" t="n">
-        <v>14.129566192627</v>
+        <v>14.1295652389526</v>
       </c>
       <c r="H534" t="n">
         <v>14128</v>
@@ -15884,7 +15884,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G535" t="n">
-        <v>13.7786359786987</v>
+        <v>13.7786350250244</v>
       </c>
       <c r="H535" t="n">
         <v>23026</v>
@@ -15913,7 +15913,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G536" t="n">
-        <v>12.9474840164185</v>
+        <v>12.9474849700928</v>
       </c>
       <c r="H536" t="n">
         <v>21186</v>
@@ -15942,7 +15942,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G537" t="n">
-        <v>12.7258434295654</v>
+        <v>12.7258443832397</v>
       </c>
       <c r="H537" t="n">
         <v>27066</v>
@@ -15971,7 +15971,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G538" t="n">
-        <v>13.5754652023315</v>
+        <v>13.5754642486572</v>
       </c>
       <c r="H538" t="n">
         <v>21793</v>
@@ -16000,7 +16000,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G539" t="n">
-        <v>13.3168849945068</v>
+        <v>13.3168840408325</v>
       </c>
       <c r="H539" t="n">
         <v>11506</v>
@@ -16058,7 +16058,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>12.6889047622681</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H541" t="n">
         <v>21971</v>
@@ -16087,7 +16087,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G542" t="n">
-        <v>12.2456226348877</v>
+        <v>12.2456245422363</v>
       </c>
       <c r="H542" t="n">
         <v>30379</v>
@@ -16145,7 +16145,7 @@
         <v>14</v>
       </c>
       <c r="G544" t="n">
-        <v>12.9290132522583</v>
+        <v>12.9290142059326</v>
       </c>
       <c r="H544" t="n">
         <v>18798</v>
@@ -16232,7 +16232,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G547" t="n">
-        <v>12.6889047622681</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H547" t="n">
         <v>11775</v>
@@ -16261,7 +16261,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>12.6889047622681</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H548" t="n">
         <v>8538</v>
@@ -16319,7 +16319,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G550" t="n">
-        <v>12.060923576355</v>
+        <v>12.0609245300293</v>
       </c>
       <c r="H550" t="n">
         <v>36726</v>
@@ -16348,7 +16348,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749113082886</v>
       </c>
       <c r="H551" t="n">
         <v>17368</v>
@@ -16377,7 +16377,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G552" t="n">
-        <v>12.060923576355</v>
+        <v>12.0609245300293</v>
       </c>
       <c r="H552" t="n">
         <v>18740</v>
@@ -16406,7 +16406,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>11.9685726165771</v>
+        <v>11.9685735702515</v>
       </c>
       <c r="H553" t="n">
         <v>21116</v>
@@ -16435,7 +16435,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>11.7284631729126</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H554" t="n">
         <v>19343</v>
@@ -16464,7 +16464,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G555" t="n">
-        <v>11.7838716506958</v>
+        <v>11.7838735580444</v>
       </c>
       <c r="H555" t="n">
         <v>14724</v>
@@ -16493,7 +16493,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>12.060923576355</v>
+        <v>12.0609245300293</v>
       </c>
       <c r="H556" t="n">
         <v>15042</v>
@@ -16522,7 +16522,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749113082886</v>
       </c>
       <c r="H557" t="n">
         <v>13670</v>
@@ -16580,7 +16580,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>12.5411424636841</v>
+        <v>12.5411434173584</v>
       </c>
       <c r="H559" t="n">
         <v>11719</v>
@@ -16638,7 +16638,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>12.5596151351929</v>
+        <v>12.5596132278442</v>
       </c>
       <c r="H561" t="n">
         <v>12666</v>
@@ -16667,7 +16667,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G562" t="n">
-        <v>12.1163330078125</v>
+        <v>12.1163349151611</v>
       </c>
       <c r="H562" t="n">
         <v>18462</v>
@@ -16696,7 +16696,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>12.0978651046753</v>
+        <v>12.0978631973267</v>
       </c>
       <c r="H563" t="n">
         <v>13377</v>
@@ -16725,7 +16725,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>12.1163330078125</v>
+        <v>12.1163349151611</v>
       </c>
       <c r="H564" t="n">
         <v>6338</v>
@@ -16754,7 +16754,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>11.9870433807373</v>
+        <v>11.987042427063</v>
       </c>
       <c r="H565" t="n">
         <v>22210</v>
@@ -16783,7 +16783,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>12.2825632095337</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H566" t="n">
         <v>6247</v>
@@ -16812,7 +16812,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G567" t="n">
-        <v>12.1532735824585</v>
+        <v>12.1532745361328</v>
       </c>
       <c r="H567" t="n">
         <v>12123</v>
@@ -16841,7 +16841,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G568" t="n">
-        <v>12.023983001709</v>
+        <v>12.0239820480347</v>
       </c>
       <c r="H568" t="n">
         <v>6599</v>
@@ -16928,7 +16928,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G571" t="n">
-        <v>11.9685726165771</v>
+        <v>11.9685735702515</v>
       </c>
       <c r="H571" t="n">
         <v>25351</v>
@@ -16957,7 +16957,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>12.7443141937256</v>
+        <v>12.7443132400513</v>
       </c>
       <c r="H572" t="n">
         <v>37029</v>
@@ -16986,7 +16986,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>12.4118528366089</v>
+        <v>12.4118537902832</v>
       </c>
       <c r="H573" t="n">
         <v>8440</v>
@@ -17073,7 +17073,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G576" t="n">
-        <v>11.9685726165771</v>
+        <v>11.9685735702515</v>
       </c>
       <c r="H576" t="n">
         <v>20913</v>
@@ -17102,7 +17102,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>11.7654008865356</v>
+        <v>11.7654027938843</v>
       </c>
       <c r="H577" t="n">
         <v>20787</v>
@@ -17131,7 +17131,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G578" t="n">
-        <v>11.9685726165771</v>
+        <v>11.9685735702515</v>
       </c>
       <c r="H578" t="n">
         <v>19393</v>
@@ -17160,7 +17160,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G579" t="n">
-        <v>11.8023414611816</v>
+        <v>11.802342414856</v>
       </c>
       <c r="H579" t="n">
         <v>14168</v>
@@ -17189,7 +17189,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G580" t="n">
-        <v>12.2825632095337</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H580" t="n">
         <v>57823</v>
@@ -17247,7 +17247,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G582" t="n">
-        <v>12.2086839675903</v>
+        <v>12.208683013916</v>
       </c>
       <c r="H582" t="n">
         <v>7756</v>
@@ -17305,7 +17305,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G584" t="n">
-        <v>12.2086839675903</v>
+        <v>12.208683013916</v>
       </c>
       <c r="H584" t="n">
         <v>25244</v>
@@ -17334,7 +17334,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>12.3379745483398</v>
+        <v>12.3379735946655</v>
       </c>
       <c r="H585" t="n">
         <v>19013</v>
@@ -17363,7 +17363,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>13.298415184021</v>
+        <v>13.2984142303467</v>
       </c>
       <c r="H586" t="n">
         <v>55430</v>
@@ -17392,7 +17392,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>13.4831142425537</v>
+        <v>13.4831161499023</v>
       </c>
       <c r="H587" t="n">
         <v>33546</v>
@@ -17450,7 +17450,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G589" t="n">
-        <v>14.2034454345703</v>
+        <v>14.2034463882446</v>
       </c>
       <c r="H589" t="n">
         <v>26324</v>
@@ -17479,7 +17479,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G590" t="n">
-        <v>14.8498964309692</v>
+        <v>14.8498954772949</v>
       </c>
       <c r="H590" t="n">
         <v>123574</v>
@@ -17508,7 +17508,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G591" t="n">
-        <v>14.7206058502197</v>
+        <v>14.720606803894</v>
       </c>
       <c r="H591" t="n">
         <v>36292</v>
@@ -17537,7 +17537,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>14.6836671829224</v>
+        <v>14.683666229248</v>
       </c>
       <c r="H592" t="n">
         <v>20294</v>
@@ -17566,7 +17566,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G593" t="n">
-        <v>14.7390756607056</v>
+        <v>14.7390766143799</v>
       </c>
       <c r="H593" t="n">
         <v>62053</v>
@@ -17624,7 +17624,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>15.623797416687</v>
+        <v>15.6237993240356</v>
       </c>
       <c r="H595" t="n">
         <v>102934</v>
@@ -17682,7 +17682,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G597" t="n">
-        <v>15.1720247268677</v>
+        <v>15.172025680542</v>
       </c>
       <c r="H597" t="n">
         <v>26908</v>
@@ -17711,7 +17711,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G598" t="n">
-        <v>15.0214347839355</v>
+        <v>15.0214338302612</v>
       </c>
       <c r="H598" t="n">
         <v>33239</v>
@@ -17740,7 +17740,7 @@
         <v>16</v>
       </c>
       <c r="G599" t="n">
-        <v>15.05908203125</v>
+        <v>15.0590810775757</v>
       </c>
       <c r="H599" t="n">
         <v>46326</v>
@@ -17769,7 +17769,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G600" t="n">
-        <v>15.115550994873</v>
+        <v>15.1155519485474</v>
       </c>
       <c r="H600" t="n">
         <v>24400</v>
@@ -17798,7 +17798,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>15.2473211288452</v>
+        <v>15.2473201751709</v>
       </c>
       <c r="H601" t="n">
         <v>40267</v>
@@ -17827,7 +17827,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G602" t="n">
-        <v>15.0214347839355</v>
+        <v>15.0214338302612</v>
       </c>
       <c r="H602" t="n">
         <v>42765</v>
@@ -17856,7 +17856,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G603" t="n">
-        <v>14.0802402496338</v>
+        <v>14.0802412033081</v>
       </c>
       <c r="H603" t="n">
         <v>175945</v>
@@ -17885,7 +17885,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G604" t="n">
-        <v>13.7602367401123</v>
+        <v>13.760235786438</v>
       </c>
       <c r="H604" t="n">
         <v>57883</v>
@@ -17914,7 +17914,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G605" t="n">
-        <v>13.2143440246582</v>
+        <v>13.2143459320068</v>
       </c>
       <c r="H605" t="n">
         <v>62638</v>
@@ -17943,7 +17943,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>13.5531740188599</v>
+        <v>13.5531730651855</v>
       </c>
       <c r="H606" t="n">
         <v>42396</v>
@@ -17972,7 +17972,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G607" t="n">
-        <v>13.6284675598145</v>
+        <v>13.6284685134888</v>
       </c>
       <c r="H607" t="n">
         <v>45154</v>
@@ -18001,7 +18001,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>13.0261039733887</v>
+        <v>13.0261058807373</v>
       </c>
       <c r="H608" t="n">
         <v>41804</v>
@@ -18030,7 +18030,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>13.2143440246582</v>
+        <v>13.2143459320068</v>
       </c>
       <c r="H609" t="n">
         <v>27949</v>
@@ -18059,7 +18059,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>12.8943376541138</v>
+        <v>12.8943386077881</v>
       </c>
       <c r="H610" t="n">
         <v>22747</v>
@@ -18088,7 +18088,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.0637540817261</v>
+        <v>13.0637531280518</v>
       </c>
       <c r="H611" t="n">
         <v>44606</v>
@@ -18117,7 +18117,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>13.0261039733887</v>
+        <v>13.0261058807373</v>
       </c>
       <c r="H612" t="n">
         <v>45688</v>
@@ -18146,7 +18146,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G613" t="n">
-        <v>12.8378658294678</v>
+        <v>12.8378667831421</v>
       </c>
       <c r="H613" t="n">
         <v>32558</v>
@@ -18204,7 +18204,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G615" t="n">
-        <v>12.4990358352661</v>
+        <v>12.4990377426147</v>
       </c>
       <c r="H615" t="n">
         <v>47762</v>
@@ -18233,7 +18233,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G616" t="n">
-        <v>12.4990358352661</v>
+        <v>12.4990377426147</v>
       </c>
       <c r="H616" t="n">
         <v>50496</v>
@@ -18262,7 +18262,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G617" t="n">
-        <v>12.9508094787598</v>
+        <v>12.9508104324341</v>
       </c>
       <c r="H617" t="n">
         <v>38860</v>
@@ -18291,7 +18291,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G618" t="n">
-        <v>12.5743322372437</v>
+        <v>12.574333190918</v>
       </c>
       <c r="H618" t="n">
         <v>31911</v>
@@ -18320,7 +18320,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G619" t="n">
-        <v>12.6496276855469</v>
+        <v>12.6496286392212</v>
       </c>
       <c r="H619" t="n">
         <v>73351</v>
@@ -18349,7 +18349,7 @@
         <v>13.5</v>
       </c>
       <c r="G620" t="n">
-        <v>12.7061014175415</v>
+        <v>12.7061004638672</v>
       </c>
       <c r="H620" t="n">
         <v>85525</v>
@@ -18378,7 +18378,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G621" t="n">
-        <v>12.8190431594849</v>
+        <v>12.8190412521362</v>
       </c>
       <c r="H621" t="n">
         <v>49263</v>
@@ -18407,7 +18407,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G622" t="n">
-        <v>12.2919750213623</v>
+        <v>12.2919759750366</v>
       </c>
       <c r="H622" t="n">
         <v>38090</v>
@@ -18465,7 +18465,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G624" t="n">
-        <v>12.6684532165527</v>
+        <v>12.6684513092041</v>
       </c>
       <c r="H624" t="n">
         <v>29434</v>
@@ -18494,7 +18494,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6496276855469</v>
+        <v>12.6496286392212</v>
       </c>
       <c r="H625" t="n">
         <v>23975</v>
@@ -18523,7 +18523,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>12.7249250411987</v>
+        <v>12.7249240875244</v>
       </c>
       <c r="H626" t="n">
         <v>28431</v>
@@ -18552,7 +18552,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G627" t="n">
-        <v>12.2166795730591</v>
+        <v>12.2166786193848</v>
       </c>
       <c r="H627" t="n">
         <v>311770</v>
@@ -18581,7 +18581,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G628" t="n">
-        <v>13.6849384307861</v>
+        <v>13.6849393844604</v>
       </c>
       <c r="H628" t="n">
         <v>80331</v>
@@ -18610,7 +18610,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G629" t="n">
-        <v>13.7225875854492</v>
+        <v>13.7225885391235</v>
       </c>
       <c r="H629" t="n">
         <v>75182</v>
@@ -18639,7 +18639,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G630" t="n">
-        <v>13.9108266830444</v>
+        <v>13.9108257293701</v>
       </c>
       <c r="H630" t="n">
         <v>15587</v>
@@ -18668,7 +18668,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G631" t="n">
-        <v>13.8167085647583</v>
+        <v>13.816707611084</v>
       </c>
       <c r="H631" t="n">
         <v>29243</v>
@@ -18697,7 +18697,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>14.0237693786621</v>
+        <v>14.0237684249878</v>
       </c>
       <c r="H632" t="n">
         <v>219805</v>
@@ -18726,7 +18726,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G633" t="n">
-        <v>13.6849384307861</v>
+        <v>13.6849393844604</v>
       </c>
       <c r="H633" t="n">
         <v>9099</v>
@@ -18842,7 +18842,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G637" t="n">
-        <v>13.4025831222534</v>
+        <v>13.4025821685791</v>
       </c>
       <c r="H637" t="n">
         <v>19688</v>
@@ -18871,7 +18871,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G638" t="n">
-        <v>13.3837585449219</v>
+        <v>13.3837594985962</v>
       </c>
       <c r="H638" t="n">
         <v>2400</v>
@@ -18958,7 +18958,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>13.2708158493042</v>
+        <v>13.2708148956299</v>
       </c>
       <c r="H641" t="n">
         <v>8690</v>
@@ -18987,7 +18987,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G642" t="n">
-        <v>13.421404838562</v>
+        <v>13.4214057922363</v>
       </c>
       <c r="H642" t="n">
         <v>4111</v>
@@ -19016,7 +19016,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G643" t="n">
-        <v>13.4025831222534</v>
+        <v>13.4025821685791</v>
       </c>
       <c r="H643" t="n">
         <v>8538</v>
@@ -19045,7 +19045,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>13.2708158493042</v>
+        <v>13.2708148956299</v>
       </c>
       <c r="H644" t="n">
         <v>8275</v>
@@ -19074,7 +19074,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G645" t="n">
-        <v>12.6684532165527</v>
+        <v>12.6684513092041</v>
       </c>
       <c r="H645" t="n">
         <v>27011</v>
@@ -19103,7 +19103,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8378658294678</v>
+        <v>12.8378667831421</v>
       </c>
       <c r="H646" t="n">
         <v>34559</v>
@@ -19161,7 +19161,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>13.308464050293</v>
+        <v>13.3084630966187</v>
       </c>
       <c r="H648" t="n">
         <v>1656</v>
@@ -19219,7 +19219,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>12.8190431594849</v>
+        <v>12.8190412521362</v>
       </c>
       <c r="H650" t="n">
         <v>28895</v>
@@ -19248,7 +19248,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G651" t="n">
-        <v>12.6684532165527</v>
+        <v>12.6684513092041</v>
       </c>
       <c r="H651" t="n">
         <v>7188</v>
@@ -19277,7 +19277,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G652" t="n">
-        <v>13.0261039733887</v>
+        <v>13.0261058807373</v>
       </c>
       <c r="H652" t="n">
         <v>7630</v>
@@ -19306,7 +19306,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G653" t="n">
-        <v>12.517861366272</v>
+        <v>12.5178623199463</v>
       </c>
       <c r="H653" t="n">
         <v>15710</v>
@@ -19335,7 +19335,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G654" t="n">
-        <v>12.4613904953003</v>
+        <v>12.4613885879517</v>
       </c>
       <c r="H654" t="n">
         <v>31224</v>
@@ -19393,7 +19393,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G656" t="n">
-        <v>12.6496276855469</v>
+        <v>12.6496286392212</v>
       </c>
       <c r="H656" t="n">
         <v>25434</v>
@@ -19422,7 +19422,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G657" t="n">
-        <v>12.6308031082153</v>
+        <v>12.630805015564</v>
       </c>
       <c r="H657" t="n">
         <v>16488</v>
@@ -19480,7 +19480,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9319858551025</v>
+        <v>12.9319849014282</v>
       </c>
       <c r="H659" t="n">
         <v>5202</v>
@@ -19538,7 +19538,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>12.8943376541138</v>
+        <v>12.8943386077881</v>
       </c>
       <c r="H661" t="n">
         <v>39317</v>
@@ -19567,7 +19567,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G662" t="n">
-        <v>12.7625713348389</v>
+        <v>12.7625722885132</v>
       </c>
       <c r="H662" t="n">
         <v>24223</v>
@@ -19596,7 +19596,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G663" t="n">
-        <v>12.9508094787598</v>
+        <v>12.9508104324341</v>
       </c>
       <c r="H663" t="n">
         <v>14666</v>
@@ -19625,7 +19625,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8190431594849</v>
+        <v>12.8190412521362</v>
       </c>
       <c r="H664" t="n">
         <v>9694</v>
@@ -19654,7 +19654,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G665" t="n">
-        <v>12.9131631851196</v>
+        <v>12.9131622314453</v>
       </c>
       <c r="H665" t="n">
         <v>17681</v>
@@ -19683,7 +19683,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>12.8943376541138</v>
+        <v>12.8943386077881</v>
       </c>
       <c r="H666" t="n">
         <v>7320</v>
@@ -19712,7 +19712,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>12.8943376541138</v>
+        <v>12.8943386077881</v>
       </c>
       <c r="H667" t="n">
         <v>41367</v>
@@ -19741,7 +19741,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G668" t="n">
-        <v>12.8943376541138</v>
+        <v>12.8943386077881</v>
       </c>
       <c r="H668" t="n">
         <v>16289</v>
@@ -19770,7 +19770,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>12.8943376541138</v>
+        <v>12.8943386077881</v>
       </c>
       <c r="H669" t="n">
         <v>16801</v>
@@ -19799,7 +19799,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G670" t="n">
-        <v>12.7249250411987</v>
+        <v>12.7249240875244</v>
       </c>
       <c r="H670" t="n">
         <v>33982</v>
@@ -19828,7 +19828,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>12.8943376541138</v>
+        <v>12.8943386077881</v>
       </c>
       <c r="H671" t="n">
         <v>26938</v>
@@ -19857,7 +19857,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G672" t="n">
-        <v>12.9319858551025</v>
+        <v>12.9319849014282</v>
       </c>
       <c r="H672" t="n">
         <v>10426</v>
@@ -19915,7 +19915,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>13.7414112091064</v>
+        <v>13.7414121627808</v>
       </c>
       <c r="H674" t="n">
         <v>12363</v>
@@ -19944,7 +19944,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G675" t="n">
-        <v>14.0614175796509</v>
+        <v>14.0614166259766</v>
       </c>
       <c r="H675" t="n">
         <v>9586</v>
@@ -20002,7 +20002,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G677" t="n">
-        <v>14.2496566772461</v>
+        <v>14.2496557235718</v>
       </c>
       <c r="H677" t="n">
         <v>8698</v>
@@ -20031,7 +20031,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G678" t="n">
-        <v>14.0049467086792</v>
+        <v>14.0049448013306</v>
       </c>
       <c r="H678" t="n">
         <v>21151</v>
@@ -20060,7 +20060,7 @@
         <v>14.5</v>
       </c>
       <c r="G679" t="n">
-        <v>13.647292137146</v>
+        <v>13.6472930908203</v>
       </c>
       <c r="H679" t="n">
         <v>14249</v>
@@ -20089,7 +20089,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G680" t="n">
-        <v>13.6284675598145</v>
+        <v>13.6284685134888</v>
       </c>
       <c r="H680" t="n">
         <v>10072</v>
@@ -20118,7 +20118,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G681" t="n">
-        <v>13.4402284622192</v>
+        <v>13.4402303695679</v>
       </c>
       <c r="H681" t="n">
         <v>17611</v>
@@ -20176,7 +20176,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G683" t="n">
-        <v>13.4967021942139</v>
+        <v>13.4967012405396</v>
       </c>
       <c r="H683" t="n">
         <v>11768</v>
@@ -20408,7 +20408,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G691" t="n">
-        <v>15.2096738815308</v>
+        <v>15.2096719741821</v>
       </c>
       <c r="H691" t="n">
         <v>16469</v>
@@ -20437,7 +20437,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G692" t="n">
-        <v>15.0967292785645</v>
+        <v>15.0967311859131</v>
       </c>
       <c r="H692" t="n">
         <v>13953</v>
@@ -20495,7 +20495,7 @@
         <v>17.5</v>
       </c>
       <c r="G694" t="n">
-        <v>16.4708671569824</v>
+        <v>16.4708690643311</v>
       </c>
       <c r="H694" t="n">
         <v>116774</v>
@@ -20524,7 +20524,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G695" t="n">
-        <v>16.6402854919434</v>
+        <v>16.640287399292</v>
       </c>
       <c r="H695" t="n">
         <v>37330</v>
@@ -20553,7 +20553,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>16.8473491668701</v>
+        <v>16.8473453521729</v>
       </c>
       <c r="H696" t="n">
         <v>39967</v>
@@ -20582,7 +20582,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>16.5649909973145</v>
+        <v>16.5649871826172</v>
       </c>
       <c r="H697" t="n">
         <v>14328</v>
@@ -20611,7 +20611,7 @@
         <v>17.5</v>
       </c>
       <c r="G698" t="n">
-        <v>16.4708671569824</v>
+        <v>16.4708690643311</v>
       </c>
       <c r="H698" t="n">
         <v>15387</v>
@@ -20640,7 +20640,7 @@
         <v>17.5</v>
       </c>
       <c r="G699" t="n">
-        <v>16.4708671569824</v>
+        <v>16.4708690643311</v>
       </c>
       <c r="H699" t="n">
         <v>15872</v>
@@ -20669,7 +20669,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G700" t="n">
-        <v>16.1696910858154</v>
+        <v>16.1696891784668</v>
       </c>
       <c r="H700" t="n">
         <v>27678</v>
@@ -20698,7 +20698,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G701" t="n">
-        <v>15.8496809005737</v>
+        <v>15.8496837615967</v>
       </c>
       <c r="H701" t="n">
         <v>40628</v>
@@ -20756,7 +20756,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G703" t="n">
-        <v>15.2096738815308</v>
+        <v>15.2096719741821</v>
       </c>
       <c r="H703" t="n">
         <v>38409</v>
@@ -20785,7 +20785,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G704" t="n">
-        <v>15.1720247268677</v>
+        <v>15.172025680542</v>
       </c>
       <c r="H704" t="n">
         <v>22796</v>
@@ -20843,7 +20843,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G706" t="n">
-        <v>15.454381942749</v>
+        <v>15.4543828964233</v>
       </c>
       <c r="H706" t="n">
         <v>12028</v>
@@ -20901,7 +20901,7 @@
         <v>16</v>
       </c>
       <c r="G708" t="n">
-        <v>15.05908203125</v>
+        <v>15.0590810775757</v>
       </c>
       <c r="H708" t="n">
         <v>69525</v>
@@ -20930,7 +20930,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G709" t="n">
-        <v>15.1531991958618</v>
+        <v>15.1532011032104</v>
       </c>
       <c r="H709" t="n">
         <v>222278</v>
@@ -21017,7 +21017,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G712" t="n">
-        <v>14.3814220428467</v>
+        <v>14.3814210891724</v>
       </c>
       <c r="H712" t="n">
         <v>33810</v>
@@ -21046,7 +21046,7 @@
         <v>15.5</v>
       </c>
       <c r="G713" t="n">
-        <v>14.5884857177734</v>
+        <v>14.5884847640991</v>
       </c>
       <c r="H713" t="n">
         <v>18411</v>
@@ -21075,7 +21075,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>14.2496566772461</v>
+        <v>14.2496557235718</v>
       </c>
       <c r="H714" t="n">
         <v>11216</v>
@@ -21133,7 +21133,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G716" t="n">
-        <v>14.1367139816284</v>
+        <v>14.1367120742798</v>
       </c>
       <c r="H716" t="n">
         <v>38539</v>
@@ -21162,7 +21162,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G717" t="n">
-        <v>14.1367139816284</v>
+        <v>14.1367120742798</v>
       </c>
       <c r="H717" t="n">
         <v>19320</v>
@@ -21191,7 +21191,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G718" t="n">
-        <v>13.8355302810669</v>
+        <v>13.8355312347412</v>
       </c>
       <c r="H718" t="n">
         <v>22202</v>
@@ -21220,7 +21220,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G719" t="n">
-        <v>13.477876663208</v>
+        <v>13.4778776168823</v>
       </c>
       <c r="H719" t="n">
         <v>15534</v>
@@ -21249,7 +21249,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G720" t="n">
-        <v>13.4402284622192</v>
+        <v>13.4402303695679</v>
       </c>
       <c r="H720" t="n">
         <v>34866</v>
@@ -21278,7 +21278,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G721" t="n">
-        <v>13.4025831222534</v>
+        <v>13.4025821685791</v>
       </c>
       <c r="H721" t="n">
         <v>12930</v>
@@ -21307,7 +21307,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G722" t="n">
-        <v>13.7978839874268</v>
+        <v>13.7978820800781</v>
       </c>
       <c r="H722" t="n">
         <v>8577</v>
@@ -21336,7 +21336,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>13.9672975540161</v>
+        <v>13.9672994613647</v>
       </c>
       <c r="H723" t="n">
         <v>9349</v>
@@ -21394,7 +21394,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G725" t="n">
-        <v>14.4190702438354</v>
+        <v>14.4190711975098</v>
       </c>
       <c r="H725" t="n">
         <v>35787</v>
@@ -21423,7 +21423,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>14.3625993728638</v>
+        <v>14.3625974655151</v>
       </c>
       <c r="H726" t="n">
         <v>40002</v>
@@ -21568,7 +21568,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G731" t="n">
-        <v>15.4920291900635</v>
+        <v>15.4920301437378</v>
       </c>
       <c r="H731" t="n">
         <v>7238</v>
@@ -21597,7 +21597,7 @@
         <v>16</v>
       </c>
       <c r="G732" t="n">
-        <v>15.05908203125</v>
+        <v>15.0590810775757</v>
       </c>
       <c r="H732" t="n">
         <v>26438</v>
@@ -21626,7 +21626,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>14.9084911346436</v>
+        <v>14.9084901809692</v>
       </c>
       <c r="H733" t="n">
         <v>25096</v>
@@ -21655,7 +21655,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G734" t="n">
-        <v>16.0190982818604</v>
+        <v>16.019100189209</v>
       </c>
       <c r="H734" t="n">
         <v>84149</v>
@@ -21684,7 +21684,7 @@
         <v>17</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0002746582031</v>
+        <v>16.0002727508545</v>
       </c>
       <c r="H735" t="n">
         <v>51687</v>
@@ -21771,7 +21771,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>15.8120346069336</v>
+        <v>15.8120355606079</v>
       </c>
       <c r="H738" t="n">
         <v>239917</v>
@@ -21829,7 +21829,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>15.623797416687</v>
+        <v>15.6237993240356</v>
       </c>
       <c r="H740" t="n">
         <v>36284</v>
@@ -21887,7 +21887,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G742" t="n">
-        <v>16.2826328277588</v>
+        <v>16.2826309204102</v>
       </c>
       <c r="H742" t="n">
         <v>50666</v>
@@ -21945,7 +21945,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G744" t="n">
-        <v>16.2638092041016</v>
+        <v>16.2638072967529</v>
       </c>
       <c r="H744" t="n">
         <v>39499</v>
@@ -21974,7 +21974,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G745" t="n">
-        <v>15.5861482620239</v>
+        <v>15.5861492156982</v>
       </c>
       <c r="H745" t="n">
         <v>32663</v>
@@ -22003,7 +22003,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G746" t="n">
-        <v>15.7367401123047</v>
+        <v>15.7367391586304</v>
       </c>
       <c r="H746" t="n">
         <v>376457</v>
@@ -22090,7 +22090,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G749" t="n">
-        <v>15.8685064315796</v>
+        <v>15.8685083389282</v>
       </c>
       <c r="H749" t="n">
         <v>17333</v>
@@ -22177,7 +22177,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G752" t="n">
-        <v>15.0214347839355</v>
+        <v>15.0214338302612</v>
       </c>
       <c r="H752" t="n">
         <v>61475</v>
@@ -22351,7 +22351,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>14.6826038360596</v>
+        <v>14.6826047897339</v>
       </c>
       <c r="H758" t="n">
         <v>29036</v>
@@ -22409,7 +22409,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>14.4943647384644</v>
+        <v>14.4943656921387</v>
       </c>
       <c r="H760" t="n">
         <v>28613</v>
@@ -22554,7 +22554,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>15.1531991958618</v>
+        <v>15.1532011032104</v>
       </c>
       <c r="H765" t="n">
         <v>33018</v>
@@ -22583,7 +22583,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G766" t="n">
-        <v>15.8496809005737</v>
+        <v>15.8496837615967</v>
       </c>
       <c r="H766" t="n">
         <v>31229</v>
@@ -22728,7 +22728,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G771" t="n">
-        <v>15.5861482620239</v>
+        <v>15.5861492156982</v>
       </c>
       <c r="H771" t="n">
         <v>21817</v>
@@ -22757,7 +22757,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G772" t="n">
-        <v>15.2096738815308</v>
+        <v>15.2096719741821</v>
       </c>
       <c r="H772" t="n">
         <v>17228</v>
@@ -22786,7 +22786,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G773" t="n">
-        <v>14.9837865829468</v>
+        <v>14.9837856292725</v>
       </c>
       <c r="H773" t="n">
         <v>20915</v>
@@ -22815,7 +22815,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G774" t="n">
-        <v>15.3602628707886</v>
+        <v>15.3602647781372</v>
       </c>
       <c r="H774" t="n">
         <v>3951</v>
@@ -22844,7 +22844,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G775" t="n">
-        <v>15.6990947723389</v>
+        <v>15.6990919113159</v>
       </c>
       <c r="H775" t="n">
         <v>9940</v>
@@ -22873,7 +22873,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G776" t="n">
-        <v>15.5673274993896</v>
+        <v>15.5673265457153</v>
       </c>
       <c r="H776" t="n">
         <v>9528</v>
@@ -22902,7 +22902,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G777" t="n">
-        <v>15.5673274993896</v>
+        <v>15.5673265457153</v>
       </c>
       <c r="H777" t="n">
         <v>19550</v>
@@ -22960,7 +22960,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G779" t="n">
-        <v>15.8308582305908</v>
+        <v>15.8308591842651</v>
       </c>
       <c r="H779" t="n">
         <v>28378</v>
@@ -22989,7 +22989,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>15.906153678894</v>
+        <v>15.9061546325684</v>
       </c>
       <c r="H780" t="n">
         <v>6328</v>
@@ -23018,7 +23018,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>15.906153678894</v>
+        <v>15.9061546325684</v>
       </c>
       <c r="H781" t="n">
         <v>9105</v>
@@ -23047,7 +23047,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="n">
-        <v>16.0002746582031</v>
+        <v>16.0002727508545</v>
       </c>
       <c r="H782" t="n">
         <v>268855</v>
@@ -23076,7 +23076,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9438028335571</v>
+        <v>15.9438037872314</v>
       </c>
       <c r="H783" t="n">
         <v>107573</v>
@@ -23105,7 +23105,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>15.906153678894</v>
+        <v>15.9061546325684</v>
       </c>
       <c r="H784" t="n">
         <v>110670</v>
@@ -23134,7 +23134,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>15.906153678894</v>
+        <v>15.9061546325684</v>
       </c>
       <c r="H785" t="n">
         <v>12846</v>
@@ -23192,7 +23192,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G787" t="n">
-        <v>15.9249753952026</v>
+        <v>15.9249773025513</v>
       </c>
       <c r="H787" t="n">
         <v>20420</v>
@@ -23221,7 +23221,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G788" t="n">
-        <v>15.9438028335571</v>
+        <v>15.9438037872314</v>
       </c>
       <c r="H788" t="n">
         <v>276706</v>
@@ -23250,7 +23250,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>15.5485038757324</v>
+        <v>15.5485019683838</v>
       </c>
       <c r="H789" t="n">
         <v>34268</v>
@@ -23308,7 +23308,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G791" t="n">
-        <v>14.6261320114136</v>
+        <v>14.6261329650879</v>
       </c>
       <c r="H791" t="n">
         <v>43793</v>
@@ -23366,7 +23366,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>14.5696611404419</v>
+        <v>14.5696620941162</v>
       </c>
       <c r="H793" t="n">
         <v>63431</v>
@@ -23453,7 +23453,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G796" t="n">
-        <v>15.1343755722046</v>
+        <v>15.1343774795532</v>
       </c>
       <c r="H796" t="n">
         <v>31362</v>
@@ -23511,7 +23511,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G798" t="n">
-        <v>15.0402574539185</v>
+        <v>15.0402565002441</v>
       </c>
       <c r="H798" t="n">
         <v>8502</v>
@@ -23540,7 +23540,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G799" t="n">
-        <v>15.115550994873</v>
+        <v>15.1155519485474</v>
       </c>
       <c r="H799" t="n">
         <v>22101</v>
@@ -23598,7 +23598,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G801" t="n">
-        <v>15.115550994873</v>
+        <v>15.1155519485474</v>
       </c>
       <c r="H801" t="n">
         <v>11655</v>
@@ -23627,7 +23627,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>15.1531991958618</v>
+        <v>15.1532011032104</v>
       </c>
       <c r="H802" t="n">
         <v>13646</v>
@@ -23656,7 +23656,7 @@
         <v>16</v>
       </c>
       <c r="G803" t="n">
-        <v>15.05908203125</v>
+        <v>15.0590810775757</v>
       </c>
       <c r="H803" t="n">
         <v>24511</v>
@@ -23714,7 +23714,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G805" t="n">
-        <v>15.228497505188</v>
+        <v>15.2284955978394</v>
       </c>
       <c r="H805" t="n">
         <v>28018</v>
@@ -23830,7 +23830,7 @@
         <v>18</v>
       </c>
       <c r="G809" t="n">
-        <v>16.9414653778076</v>
+        <v>16.9414672851562</v>
       </c>
       <c r="H809" t="n">
         <v>47550</v>
@@ -23859,7 +23859,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G810" t="n">
-        <v>17.1673526763916</v>
+        <v>17.1673564910889</v>
       </c>
       <c r="H810" t="n">
         <v>86184</v>
@@ -23888,7 +23888,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G811" t="n">
-        <v>17.1861763000488</v>
+        <v>17.1861743927002</v>
       </c>
       <c r="H811" t="n">
         <v>29826</v>
@@ -24033,7 +24033,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>17.9767799377441</v>
+        <v>17.9767780303955</v>
       </c>
       <c r="H816" t="n">
         <v>80666</v>
@@ -24120,7 +24120,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2991180419922</v>
+        <v>17.2991199493408</v>
       </c>
       <c r="H819" t="n">
         <v>10687</v>
@@ -24149,7 +24149,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G820" t="n">
-        <v>17.43088722229</v>
+        <v>17.4308891296387</v>
       </c>
       <c r="H820" t="n">
         <v>12088</v>
@@ -24207,7 +24207,7 @@
         <v>18</v>
       </c>
       <c r="G822" t="n">
-        <v>16.9414653778076</v>
+        <v>16.9414672851562</v>
       </c>
       <c r="H822" t="n">
         <v>16704</v>
@@ -24236,7 +24236,7 @@
         <v>18</v>
       </c>
       <c r="G823" t="n">
-        <v>16.9414653778076</v>
+        <v>16.9414672851562</v>
       </c>
       <c r="H823" t="n">
         <v>13632</v>
@@ -24265,7 +24265,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G824" t="n">
-        <v>17.2991180419922</v>
+        <v>17.2991199493408</v>
       </c>
       <c r="H824" t="n">
         <v>29002</v>
@@ -24294,7 +24294,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>17.317943572998</v>
+        <v>17.3179416656494</v>
       </c>
       <c r="H825" t="n">
         <v>48078</v>
@@ -24323,7 +24323,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G826" t="n">
-        <v>17.3744144439697</v>
+        <v>17.3744125366211</v>
       </c>
       <c r="H826" t="n">
         <v>41675</v>
@@ -24352,7 +24352,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>17.317943572998</v>
+        <v>17.3179416656494</v>
       </c>
       <c r="H827" t="n">
         <v>5703</v>
@@ -24439,7 +24439,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G830" t="n">
-        <v>17.7508926391602</v>
+        <v>17.7508945465088</v>
       </c>
       <c r="H830" t="n">
         <v>43980</v>
@@ -24526,7 +24526,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G833" t="n">
-        <v>17.3744144439697</v>
+        <v>17.3744125366211</v>
       </c>
       <c r="H833" t="n">
         <v>22267</v>
@@ -24584,7 +24584,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G835" t="n">
-        <v>17.0732326507568</v>
+        <v>17.0732307434082</v>
       </c>
       <c r="H835" t="n">
         <v>8772</v>
@@ -24642,7 +24642,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="n">
-        <v>16.9414653778076</v>
+        <v>16.9414672851562</v>
       </c>
       <c r="H837" t="n">
         <v>10208</v>
@@ -24671,7 +24671,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>16.8473491668701</v>
+        <v>16.8473453521729</v>
       </c>
       <c r="H838" t="n">
         <v>13843</v>
@@ -24700,7 +24700,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.5649909973145</v>
+        <v>16.5649871826172</v>
       </c>
       <c r="H839" t="n">
         <v>6273</v>
@@ -24758,7 +24758,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G841" t="n">
-        <v>16.5649909973145</v>
+        <v>16.5649871826172</v>
       </c>
       <c r="H841" t="n">
         <v>3505</v>
@@ -24787,7 +24787,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G842" t="n">
-        <v>16.52734375</v>
+        <v>16.5273418426514</v>
       </c>
       <c r="H842" t="n">
         <v>14306</v>
@@ -24816,7 +24816,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>16.2826328277588</v>
+        <v>16.2826309204102</v>
       </c>
       <c r="H843" t="n">
         <v>1811</v>
@@ -24845,7 +24845,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G844" t="n">
-        <v>16.2261600494385</v>
+        <v>16.2261619567871</v>
       </c>
       <c r="H844" t="n">
         <v>32076</v>
@@ -24874,7 +24874,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>16.7908782958984</v>
+        <v>16.7908744812012</v>
       </c>
       <c r="H845" t="n">
         <v>21229</v>
@@ -24903,7 +24903,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G846" t="n">
-        <v>16.2261600494385</v>
+        <v>16.2261619567871</v>
       </c>
       <c r="H846" t="n">
         <v>11012</v>
@@ -24961,7 +24961,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G848" t="n">
-        <v>16.5159111022949</v>
+        <v>16.5159130096436</v>
       </c>
       <c r="H848" t="n">
         <v>12178</v>
@@ -24990,7 +24990,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>16.4775943756104</v>
+        <v>16.4775924682617</v>
       </c>
       <c r="H849" t="n">
         <v>12423</v>
@@ -25048,7 +25048,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>16.3817958831787</v>
+        <v>16.3817939758301</v>
       </c>
       <c r="H851" t="n">
         <v>16507</v>
@@ -25077,7 +25077,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G852" t="n">
-        <v>16.1710319519043</v>
+        <v>16.1710300445557</v>
       </c>
       <c r="H852" t="n">
         <v>14661</v>
@@ -25106,7 +25106,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G853" t="n">
-        <v>15.9411134719849</v>
+        <v>15.9411125183105</v>
       </c>
       <c r="H853" t="n">
         <v>4033</v>
@@ -25135,7 +25135,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G854" t="n">
-        <v>15.9219570159912</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H854" t="n">
         <v>21839</v>
@@ -25164,7 +25164,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G855" t="n">
-        <v>16.6117153167725</v>
+        <v>16.6117134094238</v>
       </c>
       <c r="H855" t="n">
         <v>18793</v>
@@ -25193,7 +25193,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G856" t="n">
-        <v>16.7458324432373</v>
+        <v>16.7458343505859</v>
       </c>
       <c r="H856" t="n">
         <v>25822</v>
@@ -25222,7 +25222,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G857" t="n">
-        <v>16.6117153167725</v>
+        <v>16.6117134094238</v>
       </c>
       <c r="H857" t="n">
         <v>7408</v>
@@ -25280,7 +25280,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G859" t="n">
-        <v>16.6883525848389</v>
+        <v>16.6883506774902</v>
       </c>
       <c r="H859" t="n">
         <v>31290</v>
@@ -25483,7 +25483,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>15.8836336135864</v>
+        <v>15.8836345672607</v>
       </c>
       <c r="H866" t="n">
         <v>47994</v>
@@ -25512,7 +25512,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>16.3817958831787</v>
+        <v>16.3817939758301</v>
       </c>
       <c r="H867" t="n">
         <v>14325</v>
@@ -25541,7 +25541,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G868" t="n">
-        <v>16.400951385498</v>
+        <v>16.4009532928467</v>
       </c>
       <c r="H868" t="n">
         <v>109228</v>
@@ -25570,7 +25570,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>15.902792930603</v>
+        <v>15.9027948379517</v>
       </c>
       <c r="H869" t="n">
         <v>13629</v>
@@ -25599,7 +25599,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G870" t="n">
-        <v>15.9602718353271</v>
+        <v>15.9602737426758</v>
       </c>
       <c r="H870" t="n">
         <v>4390</v>
@@ -25628,7 +25628,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>15.902792930603</v>
+        <v>15.9027948379517</v>
       </c>
       <c r="H871" t="n">
         <v>18739</v>
@@ -25657,7 +25657,7 @@
         <v>16.5</v>
       </c>
       <c r="G872" t="n">
-        <v>15.8069915771484</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H872" t="n">
         <v>14035</v>
@@ -25715,7 +25715,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G874" t="n">
-        <v>15.5962343215942</v>
+        <v>15.5962352752686</v>
       </c>
       <c r="H874" t="n">
         <v>3918</v>
@@ -25744,7 +25744,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G875" t="n">
-        <v>15.9219570159912</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H875" t="n">
         <v>7316</v>
@@ -25773,7 +25773,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G876" t="n">
-        <v>15.3663148880005</v>
+        <v>15.3663139343262</v>
       </c>
       <c r="H876" t="n">
         <v>10656</v>
@@ -25802,7 +25802,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G877" t="n">
-        <v>15.3088331222534</v>
+        <v>15.3088321685791</v>
       </c>
       <c r="H877" t="n">
         <v>21204</v>
@@ -25831,7 +25831,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G878" t="n">
-        <v>15.251353263855</v>
+        <v>15.2513542175293</v>
       </c>
       <c r="H878" t="n">
         <v>7496</v>
@@ -25860,7 +25860,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G879" t="n">
-        <v>14.925633430481</v>
+        <v>14.9256343841553</v>
       </c>
       <c r="H879" t="n">
         <v>15630</v>
@@ -25889,7 +25889,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>15.1363935470581</v>
+        <v>15.1363925933838</v>
       </c>
       <c r="H880" t="n">
         <v>24706</v>
@@ -25976,7 +25976,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>15.0405941009521</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H883" t="n">
         <v>69164</v>
@@ -26005,7 +26005,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>14.9447946548462</v>
+        <v>14.9447956085205</v>
       </c>
       <c r="H884" t="n">
         <v>22721</v>
@@ -26034,7 +26034,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G885" t="n">
-        <v>14.9447946548462</v>
+        <v>14.9447956085205</v>
       </c>
       <c r="H885" t="n">
         <v>12650</v>
@@ -26063,7 +26063,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G886" t="n">
-        <v>15.0597543716431</v>
+        <v>15.0597534179688</v>
       </c>
       <c r="H886" t="n">
         <v>25274</v>
@@ -26092,7 +26092,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G887" t="n">
-        <v>15.1938714981079</v>
+        <v>15.1938705444336</v>
       </c>
       <c r="H887" t="n">
         <v>17880</v>
@@ -26121,7 +26121,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>15.0022735595703</v>
+        <v>15.0022745132446</v>
       </c>
       <c r="H888" t="n">
         <v>16584</v>
@@ -26179,7 +26179,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.7915124893188</v>
+        <v>14.7915143966675</v>
       </c>
       <c r="H890" t="n">
         <v>23668</v>
@@ -26208,7 +26208,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G891" t="n">
-        <v>14.6573925018311</v>
+        <v>14.6573944091797</v>
       </c>
       <c r="H891" t="n">
         <v>34461</v>
@@ -26237,7 +26237,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G892" t="n">
-        <v>15.3854713439941</v>
+        <v>15.3854732513428</v>
       </c>
       <c r="H892" t="n">
         <v>28733</v>
@@ -26266,7 +26266,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G893" t="n">
-        <v>15.1172313690186</v>
+        <v>15.1172323226929</v>
       </c>
       <c r="H893" t="n">
         <v>23512</v>
@@ -26324,7 +26324,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G895" t="n">
-        <v>14.7723550796509</v>
+        <v>14.7723541259766</v>
       </c>
       <c r="H895" t="n">
         <v>15385</v>
@@ -26382,7 +26382,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>15.0405941009521</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H897" t="n">
         <v>10778</v>
@@ -26498,7 +26498,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G901" t="n">
-        <v>14.7723550796509</v>
+        <v>14.7723541259766</v>
       </c>
       <c r="H901" t="n">
         <v>18767</v>
@@ -26556,7 +26556,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G903" t="n">
-        <v>14.6573925018311</v>
+        <v>14.6573944091797</v>
       </c>
       <c r="H903" t="n">
         <v>23428</v>
@@ -26614,7 +26614,7 @@
         <v>15.5</v>
       </c>
       <c r="G905" t="n">
-        <v>14.8489942550659</v>
+        <v>14.8489933013916</v>
       </c>
       <c r="H905" t="n">
         <v>25182</v>
@@ -26643,7 +26643,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G906" t="n">
-        <v>14.9639539718628</v>
+        <v>14.9639520645142</v>
       </c>
       <c r="H906" t="n">
         <v>8263</v>
@@ -26672,7 +26672,7 @@
         <v>15.5</v>
       </c>
       <c r="G907" t="n">
-        <v>14.8489942550659</v>
+        <v>14.8489933013916</v>
       </c>
       <c r="H907" t="n">
         <v>23792</v>
@@ -26701,7 +26701,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>15.1363935470581</v>
+        <v>15.1363925933838</v>
       </c>
       <c r="H908" t="n">
         <v>18432</v>
@@ -26730,7 +26730,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G909" t="n">
-        <v>15.1938714981079</v>
+        <v>15.1938705444336</v>
       </c>
       <c r="H909" t="n">
         <v>132253</v>
@@ -26759,7 +26759,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>14.753191947937</v>
+        <v>14.7531929016113</v>
       </c>
       <c r="H910" t="n">
         <v>92952</v>
@@ -26817,7 +26817,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G912" t="n">
-        <v>15.0597543716431</v>
+        <v>15.0597534179688</v>
       </c>
       <c r="H912" t="n">
         <v>15340</v>
@@ -26846,7 +26846,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>14.9639539718628</v>
+        <v>14.9639520645142</v>
       </c>
       <c r="H913" t="n">
         <v>39651</v>
@@ -26875,7 +26875,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G914" t="n">
-        <v>14.7723550796509</v>
+        <v>14.7723541259766</v>
       </c>
       <c r="H914" t="n">
         <v>12216</v>
@@ -26933,7 +26933,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G916" t="n">
-        <v>14.4849538803101</v>
+        <v>14.4849548339844</v>
       </c>
       <c r="H916" t="n">
         <v>18837</v>
@@ -26991,7 +26991,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G918" t="n">
-        <v>14.5424346923828</v>
+        <v>14.5424337387085</v>
       </c>
       <c r="H918" t="n">
         <v>36150</v>
@@ -27136,7 +27136,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>14.5615930557251</v>
+        <v>14.5615949630737</v>
       </c>
       <c r="H923" t="n">
         <v>8466</v>
@@ -27194,7 +27194,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G925" t="n">
-        <v>14.4849538803101</v>
+        <v>14.4849548339844</v>
       </c>
       <c r="H925" t="n">
         <v>12803</v>
@@ -27252,7 +27252,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G927" t="n">
-        <v>14.3891544342041</v>
+        <v>14.3891534805298</v>
       </c>
       <c r="H927" t="n">
         <v>11124</v>
@@ -27281,7 +27281,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G928" t="n">
-        <v>14.5999126434326</v>
+        <v>14.5999135971069</v>
       </c>
       <c r="H928" t="n">
         <v>14866</v>
@@ -27310,7 +27310,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G929" t="n">
-        <v>15.1938714981079</v>
+        <v>15.1938705444336</v>
       </c>
       <c r="H929" t="n">
         <v>14936</v>
@@ -27339,7 +27339,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G930" t="n">
-        <v>14.8681545257568</v>
+        <v>14.8681554794312</v>
       </c>
       <c r="H930" t="n">
         <v>16059</v>
@@ -27397,7 +27397,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G932" t="n">
-        <v>14.504114151001</v>
+        <v>14.5041131973267</v>
       </c>
       <c r="H932" t="n">
         <v>19652</v>
@@ -27455,7 +27455,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G934" t="n">
-        <v>14.5424346923828</v>
+        <v>14.5424337387085</v>
       </c>
       <c r="H934" t="n">
         <v>10946</v>
@@ -27542,7 +27542,7 @@
         <v>16</v>
       </c>
       <c r="G937" t="n">
-        <v>15.3279933929443</v>
+        <v>15.3279943466187</v>
       </c>
       <c r="H937" t="n">
         <v>17828</v>
@@ -27571,7 +27571,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G938" t="n">
-        <v>15.6153936386108</v>
+        <v>15.6153926849365</v>
       </c>
       <c r="H938" t="n">
         <v>28450</v>
@@ -27600,7 +27600,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G939" t="n">
-        <v>15.4621124267578</v>
+        <v>15.4621133804321</v>
       </c>
       <c r="H939" t="n">
         <v>17098</v>
@@ -27629,7 +27629,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G940" t="n">
-        <v>15.6537141799927</v>
+        <v>15.653712272644</v>
       </c>
       <c r="H940" t="n">
         <v>49689</v>
@@ -27658,7 +27658,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G941" t="n">
-        <v>15.7303524017334</v>
+        <v>15.730354309082</v>
       </c>
       <c r="H941" t="n">
         <v>18615</v>
@@ -27716,7 +27716,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>15.7111921310425</v>
+        <v>15.7111930847168</v>
       </c>
       <c r="H943" t="n">
         <v>16463</v>
@@ -27745,7 +27745,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G944" t="n">
-        <v>15.5962343215942</v>
+        <v>15.5962352752686</v>
       </c>
       <c r="H944" t="n">
         <v>173872</v>
@@ -27774,7 +27774,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G945" t="n">
-        <v>15.7495155334473</v>
+        <v>15.7495126724243</v>
       </c>
       <c r="H945" t="n">
         <v>9355</v>
@@ -27803,7 +27803,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G946" t="n">
-        <v>15.9411134719849</v>
+        <v>15.9411125183105</v>
       </c>
       <c r="H946" t="n">
         <v>16911</v>
@@ -27832,7 +27832,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G947" t="n">
-        <v>15.8453159332275</v>
+        <v>15.8453149795532</v>
       </c>
       <c r="H947" t="n">
         <v>9454</v>
@@ -27890,7 +27890,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G949" t="n">
-        <v>15.5579147338867</v>
+        <v>15.5579137802124</v>
       </c>
       <c r="H949" t="n">
         <v>13664</v>
@@ -27919,7 +27919,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>15.902792930603</v>
+        <v>15.9027948379517</v>
       </c>
       <c r="H950" t="n">
         <v>15416</v>
@@ -27948,7 +27948,7 @@
         <v>16.5</v>
       </c>
       <c r="G951" t="n">
-        <v>15.8069915771484</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H951" t="n">
         <v>11208</v>
@@ -28006,7 +28006,7 @@
         <v>16.5</v>
       </c>
       <c r="G953" t="n">
-        <v>15.8069915771484</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H953" t="n">
         <v>27357</v>
@@ -28035,7 +28035,7 @@
         <v>16.5</v>
       </c>
       <c r="G954" t="n">
-        <v>15.8069915771484</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H954" t="n">
         <v>30809</v>
@@ -28064,7 +28064,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G955" t="n">
-        <v>15.5195922851562</v>
+        <v>15.5195932388306</v>
       </c>
       <c r="H955" t="n">
         <v>10063</v>
@@ -28122,7 +28122,7 @@
         <v>16</v>
       </c>
       <c r="G957" t="n">
-        <v>15.3279933929443</v>
+        <v>15.3279943466187</v>
       </c>
       <c r="H957" t="n">
         <v>2780</v>
@@ -28151,7 +28151,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G958" t="n">
-        <v>15.5962343215942</v>
+        <v>15.5962352752686</v>
       </c>
       <c r="H958" t="n">
         <v>4998</v>
@@ -28180,7 +28180,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G959" t="n">
-        <v>15.7686748504639</v>
+        <v>15.7686719894409</v>
       </c>
       <c r="H959" t="n">
         <v>16273</v>
@@ -28209,7 +28209,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>15.902792930603</v>
+        <v>15.9027948379517</v>
       </c>
       <c r="H960" t="n">
         <v>9306</v>
@@ -28238,7 +28238,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>15.7111921310425</v>
+        <v>15.7111930847168</v>
       </c>
       <c r="H961" t="n">
         <v>14436</v>
@@ -28267,7 +28267,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G962" t="n">
-        <v>15.6537141799927</v>
+        <v>15.653712272644</v>
       </c>
       <c r="H962" t="n">
         <v>19798</v>
@@ -28325,7 +28325,7 @@
         <v>16.5</v>
       </c>
       <c r="G964" t="n">
-        <v>15.8069915771484</v>
+        <v>15.8069934844971</v>
       </c>
       <c r="H964" t="n">
         <v>13857</v>
@@ -28354,7 +28354,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G965" t="n">
-        <v>15.9219570159912</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H965" t="n">
         <v>14484</v>
@@ -28383,7 +28383,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G966" t="n">
-        <v>16.0560722351074</v>
+        <v>16.0560741424561</v>
       </c>
       <c r="H966" t="n">
         <v>20089</v>
@@ -28441,7 +28441,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>16.3817958831787</v>
+        <v>16.3817939758301</v>
       </c>
       <c r="H968" t="n">
         <v>17165</v>
@@ -28470,7 +28470,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G969" t="n">
-        <v>17.0907154083252</v>
+        <v>17.0907115936279</v>
       </c>
       <c r="H969" t="n">
         <v>22005</v>
@@ -28528,7 +28528,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G971" t="n">
-        <v>16.8799495697021</v>
+        <v>16.8799533843994</v>
       </c>
       <c r="H971" t="n">
         <v>13007</v>
@@ -28644,7 +28644,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G975" t="n">
-        <v>16.9182739257812</v>
+        <v>16.9182720184326</v>
       </c>
       <c r="H975" t="n">
         <v>21250</v>
@@ -28673,7 +28673,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>17.0523891448975</v>
+        <v>17.0523929595947</v>
       </c>
       <c r="H976" t="n">
         <v>19467</v>
@@ -28702,7 +28702,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G977" t="n">
-        <v>16.7458324432373</v>
+        <v>16.7458343505859</v>
       </c>
       <c r="H977" t="n">
         <v>9950</v>
@@ -28818,7 +28818,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G981" t="n">
-        <v>18.1061916351318</v>
+        <v>18.1061935424805</v>
       </c>
       <c r="H981" t="n">
         <v>33750</v>
@@ -28876,7 +28876,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>17.5888748168945</v>
+        <v>17.5888729095459</v>
       </c>
       <c r="H983" t="n">
         <v>26009</v>
@@ -28963,7 +28963,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>18.048713684082</v>
+        <v>18.0487098693848</v>
       </c>
       <c r="H986" t="n">
         <v>28343</v>
@@ -28992,7 +28992,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G987" t="n">
-        <v>17.8954334259033</v>
+        <v>17.8954315185547</v>
       </c>
       <c r="H987" t="n">
         <v>20532</v>
@@ -29021,7 +29021,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G988" t="n">
-        <v>17.8762722015381</v>
+        <v>17.8762702941895</v>
       </c>
       <c r="H988" t="n">
         <v>13457</v>
@@ -29050,7 +29050,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="n">
-        <v>17.9912357330322</v>
+        <v>17.991231918335</v>
       </c>
       <c r="H989" t="n">
         <v>1479</v>
@@ -29079,7 +29079,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G990" t="n">
-        <v>17.8954334259033</v>
+        <v>17.8954315185547</v>
       </c>
       <c r="H990" t="n">
         <v>4792</v>
@@ -29195,7 +29195,7 @@
         <v>19.5</v>
       </c>
       <c r="G994" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809940338135</v>
       </c>
       <c r="H994" t="n">
         <v>48325</v>
@@ -29224,7 +29224,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G995" t="n">
-        <v>19.0258712768555</v>
+        <v>19.0258731842041</v>
       </c>
       <c r="H995" t="n">
         <v>45560</v>
@@ -29253,7 +29253,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G996" t="n">
-        <v>18.9492301940918</v>
+        <v>18.9492321014404</v>
       </c>
       <c r="H996" t="n">
         <v>20868</v>
@@ -29282,7 +29282,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G997" t="n">
-        <v>18.4702339172363</v>
+        <v>18.4702301025391</v>
       </c>
       <c r="H997" t="n">
         <v>51855</v>
@@ -29311,7 +29311,7 @@
         <v>19.5</v>
       </c>
       <c r="G998" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809940338135</v>
       </c>
       <c r="H998" t="n">
         <v>31925</v>
@@ -29340,7 +29340,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G999" t="n">
-        <v>18.8917503356934</v>
+        <v>18.891752243042</v>
       </c>
       <c r="H999" t="n">
         <v>27498</v>
@@ -29369,7 +29369,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>18.8342723846436</v>
+        <v>18.8342704772949</v>
       </c>
       <c r="H1000" t="n">
         <v>11571</v>
@@ -29427,7 +29427,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>19.7347946166992</v>
+        <v>19.7347927093506</v>
       </c>
       <c r="H1002" t="n">
         <v>52209</v>
@@ -29456,7 +29456,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.4473934173584</v>
+        <v>19.4473896026611</v>
       </c>
       <c r="H1003" t="n">
         <v>15031</v>
@@ -29485,7 +29485,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>19.5910930633545</v>
+        <v>19.5910911560059</v>
       </c>
       <c r="H1004" t="n">
         <v>17354</v>
@@ -29514,7 +29514,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.207893371582</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1005" t="n">
         <v>16818</v>
@@ -29543,7 +29543,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.207893371582</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1006" t="n">
         <v>11391</v>
@@ -29572,7 +29572,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>18.7767906188965</v>
+        <v>18.7767925262451</v>
       </c>
       <c r="H1007" t="n">
         <v>26511</v>
@@ -29601,7 +29601,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>19.54319190979</v>
+        <v>19.5431938171387</v>
       </c>
       <c r="H1008" t="n">
         <v>20730</v>
@@ -29659,7 +29659,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1010" t="n">
         <v>17102</v>
@@ -29688,7 +29688,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1011" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1011" t="n">
         <v>30838</v>
@@ -29717,7 +29717,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>19.2557926177979</v>
+        <v>19.2557907104492</v>
       </c>
       <c r="H1012" t="n">
         <v>34855</v>
@@ -29746,7 +29746,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>19.2557926177979</v>
+        <v>19.2557907104492</v>
       </c>
       <c r="H1013" t="n">
         <v>10024</v>
@@ -29775,7 +29775,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>19.4473934173584</v>
+        <v>19.4473896026611</v>
       </c>
       <c r="H1014" t="n">
         <v>12748</v>
@@ -29804,7 +29804,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>19.207893371582</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1015" t="n">
         <v>16605</v>
@@ -29833,7 +29833,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>19.54319190979</v>
+        <v>19.5431938171387</v>
       </c>
       <c r="H1016" t="n">
         <v>7685</v>
@@ -29862,7 +29862,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1017" t="n">
-        <v>19.5910930633545</v>
+        <v>19.5910911560059</v>
       </c>
       <c r="H1017" t="n">
         <v>32247</v>
@@ -29891,7 +29891,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1018" t="n">
-        <v>19.4952945709229</v>
+        <v>19.4952926635742</v>
       </c>
       <c r="H1018" t="n">
         <v>6892</v>
@@ -29949,7 +29949,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1020" t="n">
-        <v>20.1658897399902</v>
+        <v>20.1658916473389</v>
       </c>
       <c r="H1020" t="n">
         <v>34427</v>
@@ -30007,7 +30007,7 @@
         <v>22</v>
       </c>
       <c r="G1022" t="n">
-        <v>21.0759906768799</v>
+        <v>21.0759925842285</v>
       </c>
       <c r="H1022" t="n">
         <v>28445</v>
@@ -30036,7 +30036,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>21.0280914306641</v>
+        <v>21.0280933380127</v>
       </c>
       <c r="H1023" t="n">
         <v>19149</v>
@@ -30065,7 +30065,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>20.7406940460205</v>
+        <v>20.7406902313232</v>
       </c>
       <c r="H1024" t="n">
         <v>12238</v>
@@ -30094,7 +30094,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>20.5490913391113</v>
+        <v>20.5490894317627</v>
       </c>
       <c r="H1025" t="n">
         <v>9752</v>
@@ -30123,7 +30123,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322929382324</v>
       </c>
       <c r="H1026" t="n">
         <v>4444</v>
@@ -30152,7 +30152,7 @@
         <v>22</v>
       </c>
       <c r="G1027" t="n">
-        <v>21.0759906768799</v>
+        <v>21.0759925842285</v>
       </c>
       <c r="H1027" t="n">
         <v>17582</v>
@@ -30181,7 +30181,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322929382324</v>
       </c>
       <c r="H1028" t="n">
         <v>6993</v>
@@ -30384,7 +30384,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>19.9263877868652</v>
+        <v>19.9263896942139</v>
       </c>
       <c r="H1035" t="n">
         <v>8404</v>
@@ -30413,7 +30413,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1036" t="n">
-        <v>19.7826919555664</v>
+        <v>19.7826900482178</v>
       </c>
       <c r="H1036" t="n">
         <v>207787</v>
@@ -30442,7 +30442,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1037" t="n">
-        <v>19.2557926177979</v>
+        <v>19.2557907104492</v>
       </c>
       <c r="H1037" t="n">
         <v>26401</v>
@@ -30529,7 +30529,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>20.6927890777588</v>
+        <v>20.6927909851074</v>
       </c>
       <c r="H1040" t="n">
         <v>21385</v>
@@ -30558,7 +30558,7 @@
         <v>21.75</v>
       </c>
       <c r="G1041" t="n">
-        <v>20.8364925384521</v>
+        <v>20.8364906311035</v>
       </c>
       <c r="H1041" t="n">
         <v>11383</v>
@@ -30645,7 +30645,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322929382324</v>
       </c>
       <c r="H1044" t="n">
         <v>10768</v>
@@ -30674,7 +30674,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>21.1717891693115</v>
+        <v>21.1717929840088</v>
       </c>
       <c r="H1045" t="n">
         <v>34815</v>
@@ -30703,7 +30703,7 @@
         <v>22.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>21.3154907226562</v>
+        <v>21.3154926300049</v>
       </c>
       <c r="H1046" t="n">
         <v>27422</v>
@@ -30732,7 +30732,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1047" t="n">
-        <v>21.1238918304443</v>
+        <v>21.1238899230957</v>
       </c>
       <c r="H1047" t="n">
         <v>13111</v>
@@ -30790,7 +30790,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>21.3633880615234</v>
+        <v>21.3633899688721</v>
       </c>
       <c r="H1049" t="n">
         <v>10816</v>
@@ -30848,7 +30848,7 @@
         <v>22.25</v>
       </c>
       <c r="G1051" t="n">
-        <v>21.3154907226562</v>
+        <v>21.3154926300049</v>
       </c>
       <c r="H1051" t="n">
         <v>7933</v>
@@ -30877,7 +30877,7 @@
         <v>22</v>
       </c>
       <c r="G1052" t="n">
-        <v>21.0759906768799</v>
+        <v>21.0759925842285</v>
       </c>
       <c r="H1052" t="n">
         <v>16862</v>
@@ -30935,7 +30935,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1054" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1054" t="n">
         <v>26069</v>
@@ -30993,7 +30993,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>19.54319190979</v>
+        <v>19.5431938171387</v>
       </c>
       <c r="H1056" t="n">
         <v>18241</v>
@@ -31080,7 +31080,7 @@
         <v>19.5</v>
       </c>
       <c r="G1059" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809940338135</v>
       </c>
       <c r="H1059" t="n">
         <v>52887</v>
@@ -31109,7 +31109,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>18.7767906188965</v>
+        <v>18.7767925262451</v>
       </c>
       <c r="H1060" t="n">
         <v>21530</v>
@@ -31138,7 +31138,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1061" t="n">
-        <v>18.1253509521484</v>
+        <v>18.1253528594971</v>
       </c>
       <c r="H1061" t="n">
         <v>16465</v>
@@ -31167,7 +31167,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1062" t="n">
-        <v>17.5505542755127</v>
+        <v>17.5505504608154</v>
       </c>
       <c r="H1062" t="n">
         <v>14163</v>
@@ -31196,7 +31196,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1063" t="n">
-        <v>16.7458324432373</v>
+        <v>16.7458343505859</v>
       </c>
       <c r="H1063" t="n">
         <v>13732</v>
@@ -31225,7 +31225,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1064" t="n">
-        <v>16.247673034668</v>
+        <v>16.2476711273193</v>
       </c>
       <c r="H1064" t="n">
         <v>45443</v>
@@ -31254,7 +31254,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1065" t="n">
-        <v>16.1327114105225</v>
+        <v>16.1327133178711</v>
       </c>
       <c r="H1065" t="n">
         <v>56427</v>
@@ -31283,7 +31283,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1066" t="n">
-        <v>14.4274730682373</v>
+        <v>14.4274740219116</v>
       </c>
       <c r="H1066" t="n">
         <v>27594</v>
@@ -31370,7 +31370,7 @@
         <v>12.5</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9749946594238</v>
+        <v>11.9749937057495</v>
       </c>
       <c r="H1069" t="n">
         <v>35916</v>
@@ -31428,7 +31428,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1071" t="n">
-        <v>12.6455945968628</v>
+        <v>12.6455955505371</v>
       </c>
       <c r="H1071" t="n">
         <v>30195</v>
@@ -31515,7 +31515,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.2587146759033</v>
+        <v>13.258713722229</v>
       </c>
       <c r="H1074" t="n">
         <v>23012</v>
@@ -31544,7 +31544,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>13.507794380188</v>
+        <v>13.5077934265137</v>
       </c>
       <c r="H1075" t="n">
         <v>106622</v>
@@ -31573,7 +31573,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1076" t="n">
-        <v>13.9676342010498</v>
+        <v>13.9676351547241</v>
       </c>
       <c r="H1076" t="n">
         <v>20303</v>
@@ -31602,7 +31602,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1077" t="n">
-        <v>14.1400728225708</v>
+        <v>14.1400737762451</v>
       </c>
       <c r="H1077" t="n">
         <v>60704</v>
@@ -31660,7 +31660,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5999126434326</v>
+        <v>14.5999135971069</v>
       </c>
       <c r="H1079" t="n">
         <v>17157</v>
@@ -31689,7 +31689,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>14.6573925018311</v>
+        <v>14.6573944091797</v>
       </c>
       <c r="H1080" t="n">
         <v>12366</v>
@@ -31747,7 +31747,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1082" t="n">
-        <v>13.9676342010498</v>
+        <v>13.9676351547241</v>
       </c>
       <c r="H1082" t="n">
         <v>23628</v>
@@ -31776,7 +31776,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.0634336471558</v>
+        <v>14.0634326934814</v>
       </c>
       <c r="H1083" t="n">
         <v>12652</v>
@@ -31834,7 +31834,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1085" t="n">
-        <v>14.4274730682373</v>
+        <v>14.4274740219116</v>
       </c>
       <c r="H1085" t="n">
         <v>16830</v>
@@ -31863,7 +31863,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1086" t="n">
-        <v>14.6765537261963</v>
+        <v>14.676552772522</v>
       </c>
       <c r="H1086" t="n">
         <v>16117</v>
@@ -31892,7 +31892,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1087" t="n">
-        <v>14.7915124893188</v>
+        <v>14.7915143966675</v>
       </c>
       <c r="H1087" t="n">
         <v>22064</v>
@@ -32066,7 +32066,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.9219570159912</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H1093" t="n">
         <v>32303</v>
@@ -32095,7 +32095,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1094" t="n">
-        <v>16.8033142089844</v>
+        <v>16.8033123016357</v>
       </c>
       <c r="H1094" t="n">
         <v>9069</v>
@@ -32153,7 +32153,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1096" t="n">
-        <v>16.151876449585</v>
+        <v>16.1518745422363</v>
       </c>
       <c r="H1096" t="n">
         <v>24520</v>
@@ -32182,7 +32182,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.9219570159912</v>
+        <v>15.9219532012939</v>
       </c>
       <c r="H1097" t="n">
         <v>16332</v>
@@ -32211,7 +32211,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.6537141799927</v>
+        <v>15.653712272644</v>
       </c>
       <c r="H1098" t="n">
         <v>11694</v>
@@ -32240,7 +32240,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.8453159332275</v>
+        <v>15.8453149795532</v>
       </c>
       <c r="H1099" t="n">
         <v>11700</v>
@@ -32269,7 +32269,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1100" t="n">
-        <v>15.404634475708</v>
+        <v>15.4046335220337</v>
       </c>
       <c r="H1100" t="n">
         <v>12134</v>
@@ -32298,7 +32298,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.8681545257568</v>
+        <v>14.8681554794312</v>
       </c>
       <c r="H1101" t="n">
         <v>17167</v>
@@ -32356,7 +32356,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.0405941009521</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H1103" t="n">
         <v>8857</v>
@@ -32385,7 +32385,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.7111921310425</v>
+        <v>15.7111930847168</v>
       </c>
       <c r="H1104" t="n">
         <v>18855</v>
@@ -32472,7 +32472,7 @@
         <v>16</v>
       </c>
       <c r="G1107" t="n">
-        <v>15.3279933929443</v>
+        <v>15.3279943466187</v>
       </c>
       <c r="H1107" t="n">
         <v>1900</v>
@@ -32501,7 +32501,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.753191947937</v>
+        <v>14.7531929016113</v>
       </c>
       <c r="H1108" t="n">
         <v>12607</v>
@@ -32530,7 +32530,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1109" t="n">
-        <v>15.404634475708</v>
+        <v>15.4046335220337</v>
       </c>
       <c r="H1109" t="n">
         <v>4876</v>
@@ -32559,7 +32559,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.6153936386108</v>
+        <v>15.6153926849365</v>
       </c>
       <c r="H1110" t="n">
         <v>9207</v>
@@ -32588,7 +32588,7 @@
         <v>16</v>
       </c>
       <c r="G1111" t="n">
-        <v>15.3279933929443</v>
+        <v>15.3279943466187</v>
       </c>
       <c r="H1111" t="n">
         <v>24188</v>
@@ -32646,7 +32646,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1113" t="n">
-        <v>16.0752353668213</v>
+        <v>16.0752334594727</v>
       </c>
       <c r="H1113" t="n">
         <v>11905</v>
@@ -32675,7 +32675,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1114" t="n">
-        <v>15.9794340133667</v>
+        <v>15.9794321060181</v>
       </c>
       <c r="H1114" t="n">
         <v>6467</v>
@@ -32704,7 +32704,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1115" t="n">
-        <v>15.4621124267578</v>
+        <v>15.4621133804321</v>
       </c>
       <c r="H1115" t="n">
         <v>14639</v>
@@ -32733,7 +32733,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1116" t="n">
-        <v>16.1710319519043</v>
+        <v>16.1710300445557</v>
       </c>
       <c r="H1116" t="n">
         <v>20055</v>
@@ -32762,7 +32762,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1117" t="n">
-        <v>15.9602718353271</v>
+        <v>15.9602737426758</v>
       </c>
       <c r="H1117" t="n">
         <v>60107</v>
@@ -32791,7 +32791,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1118" t="n">
-        <v>16.5350761413574</v>
+        <v>16.5350723266602</v>
       </c>
       <c r="H1118" t="n">
         <v>18549</v>
@@ -32907,7 +32907,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1122" t="n">
-        <v>16.9949131011963</v>
+        <v>16.9949111938477</v>
       </c>
       <c r="H1122" t="n">
         <v>43243</v>
@@ -32965,7 +32965,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1124" t="n">
-        <v>18.5660305023193</v>
+        <v>18.566032409668</v>
       </c>
       <c r="H1124" t="n">
         <v>28971</v>
@@ -33023,7 +33023,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1126" t="n">
-        <v>17.6984634399414</v>
+        <v>17.6984615325928</v>
       </c>
       <c r="H1126" t="n">
         <v>20458</v>
@@ -33052,7 +33052,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3899955749512</v>
+        <v>17.3899936676025</v>
       </c>
       <c r="H1127" t="n">
         <v>26195</v>
@@ -33226,7 +33226,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1133" t="n">
-        <v>17.1008014678955</v>
+        <v>17.1007995605469</v>
       </c>
       <c r="H1133" t="n">
         <v>34044</v>
@@ -33255,7 +33255,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1134" t="n">
-        <v>17.58278465271</v>
+        <v>17.5827865600586</v>
       </c>
       <c r="H1134" t="n">
         <v>33739</v>
@@ -33284,7 +33284,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1135" t="n">
-        <v>17.4285488128662</v>
+        <v>17.4285507202148</v>
       </c>
       <c r="H1135" t="n">
         <v>18791</v>
@@ -33313,7 +33313,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1136" t="n">
-        <v>17.6599025726318</v>
+        <v>17.6599006652832</v>
       </c>
       <c r="H1136" t="n">
         <v>31243</v>
@@ -33516,7 +33516,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1143" t="n">
-        <v>18.161169052124</v>
+        <v>18.1611671447754</v>
       </c>
       <c r="H1143" t="n">
         <v>14962</v>
@@ -33574,7 +33574,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>18.5081939697266</v>
+        <v>18.5081958770752</v>
       </c>
       <c r="H1145" t="n">
         <v>18879</v>
@@ -33690,7 +33690,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1149" t="n">
-        <v>18.0454883575439</v>
+        <v>18.0454902648926</v>
       </c>
       <c r="H1149" t="n">
         <v>9891</v>
@@ -33893,7 +33893,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1156" t="n">
-        <v>18.9708995819092</v>
+        <v>18.9709014892578</v>
       </c>
       <c r="H1156" t="n">
         <v>20771</v>
@@ -33951,7 +33951,7 @@
         <v>20</v>
       </c>
       <c r="G1158" t="n">
-        <v>19.2793655395508</v>
+        <v>19.2793674468994</v>
       </c>
       <c r="H1158" t="n">
         <v>9642</v>
@@ -34038,7 +34038,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1161" t="n">
-        <v>18.3925189971924</v>
+        <v>18.3925170898438</v>
       </c>
       <c r="H1161" t="n">
         <v>22377</v>
@@ -34067,7 +34067,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1162" t="n">
-        <v>18.5853137969971</v>
+        <v>18.5853118896484</v>
       </c>
       <c r="H1162" t="n">
         <v>5703</v>
@@ -34125,7 +34125,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1164" t="n">
-        <v>19.4239654541016</v>
+        <v>19.4239635467529</v>
       </c>
       <c r="H1164" t="n">
         <v>14036</v>
@@ -34154,7 +34154,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1165" t="n">
-        <v>19.5685615539551</v>
+        <v>19.5685596466064</v>
       </c>
       <c r="H1165" t="n">
         <v>7027</v>
@@ -34183,7 +34183,7 @@
         <v>20.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>20.0023460388184</v>
+        <v>20.002347946167</v>
       </c>
       <c r="H1166" t="n">
         <v>13961</v>
@@ -34241,7 +34241,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1168" t="n">
-        <v>20.5325260162354</v>
+        <v>20.5325241088867</v>
       </c>
       <c r="H1168" t="n">
         <v>4535</v>
@@ -34299,7 +34299,7 @@
         <v>21.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>20.9663162231445</v>
+        <v>20.9663143157959</v>
       </c>
       <c r="H1170" t="n">
         <v>6965</v>
@@ -34473,7 +34473,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>21.1109104156494</v>
+        <v>21.1109085083008</v>
       </c>
       <c r="H1176" t="n">
         <v>21292</v>
@@ -34531,7 +34531,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>21.1109104156494</v>
+        <v>21.1109085083008</v>
       </c>
       <c r="H1178" t="n">
         <v>4147</v>
@@ -34560,7 +34560,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.4964942932129</v>
+        <v>21.4964962005615</v>
       </c>
       <c r="H1179" t="n">
         <v>12861</v>
@@ -34589,7 +34589,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.7856864929199</v>
+        <v>21.7856884002686</v>
       </c>
       <c r="H1180" t="n">
         <v>6893</v>
@@ -34618,7 +34618,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.7856864929199</v>
+        <v>21.7856884002686</v>
       </c>
       <c r="H1181" t="n">
         <v>6535</v>
@@ -34647,7 +34647,7 @@
         <v>22.25</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.4482975006104</v>
+        <v>21.448299407959</v>
       </c>
       <c r="H1182" t="n">
         <v>21926</v>
@@ -34676,7 +34676,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.2555046081543</v>
+        <v>21.2555027008057</v>
       </c>
       <c r="H1183" t="n">
         <v>1914</v>
@@ -34821,7 +34821,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1188" t="n">
-        <v>22.7014579772949</v>
+        <v>22.7014560699463</v>
       </c>
       <c r="H1188" t="n">
         <v>7650</v>
@@ -34908,7 +34908,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>22.7014579772949</v>
+        <v>22.7014560699463</v>
       </c>
       <c r="H1191" t="n">
         <v>16565</v>
@@ -35111,7 +35111,7 @@
         <v>24.75</v>
       </c>
       <c r="G1198" t="n">
-        <v>23.8582191467285</v>
+        <v>23.8582210540771</v>
       </c>
       <c r="H1198" t="n">
         <v>18951</v>
@@ -35198,7 +35198,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1201" t="n">
-        <v>22.9424476623535</v>
+        <v>22.9424495697021</v>
       </c>
       <c r="H1201" t="n">
         <v>13583</v>
@@ -35256,7 +35256,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1203" t="n">
-        <v>22.9906482696533</v>
+        <v>22.990650177002</v>
       </c>
       <c r="H1203" t="n">
         <v>17095</v>
@@ -35430,7 +35430,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>22.4604663848877</v>
+        <v>22.4604644775391</v>
       </c>
       <c r="H1209" t="n">
         <v>11525</v>
@@ -35459,7 +35459,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1210" t="n">
-        <v>21.7374877929688</v>
+        <v>21.7374897003174</v>
       </c>
       <c r="H1210" t="n">
         <v>41963</v>
@@ -35488,7 +35488,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1211" t="n">
-        <v>21.9784812927246</v>
+        <v>21.978479385376</v>
       </c>
       <c r="H1211" t="n">
         <v>20448</v>
@@ -35575,7 +35575,7 @@
         <v>22.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>21.4482975006104</v>
+        <v>21.448299407959</v>
       </c>
       <c r="H1214" t="n">
         <v>14540</v>
@@ -35604,7 +35604,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>21.4964942932129</v>
+        <v>21.4964962005615</v>
       </c>
       <c r="H1215" t="n">
         <v>12781</v>
@@ -35662,7 +35662,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>21.5446949005127</v>
+        <v>21.5446968078613</v>
       </c>
       <c r="H1217" t="n">
         <v>22396</v>
@@ -35807,7 +35807,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1222" t="n">
-        <v>21.4964942932129</v>
+        <v>21.4964962005615</v>
       </c>
       <c r="H1222" t="n">
         <v>16791</v>
@@ -35836,7 +35836,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1223" t="n">
-        <v>22.1230773925781</v>
+        <v>22.1230754852295</v>
       </c>
       <c r="H1223" t="n">
         <v>10829</v>
@@ -35865,7 +35865,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>21.7374877929688</v>
+        <v>21.7374897003174</v>
       </c>
       <c r="H1224" t="n">
         <v>24952</v>
@@ -35952,7 +35952,7 @@
         <v>21.75</v>
       </c>
       <c r="G1227" t="n">
-        <v>20.9663162231445</v>
+        <v>20.9663143157959</v>
       </c>
       <c r="H1227" t="n">
         <v>30164</v>
@@ -35981,7 +35981,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>21.1109104156494</v>
+        <v>21.1109085083008</v>
       </c>
       <c r="H1228" t="n">
         <v>17762</v>
@@ -36010,7 +36010,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>20.8699207305908</v>
+        <v>20.8699188232422</v>
       </c>
       <c r="H1229" t="n">
         <v>7853</v>
@@ -36039,7 +36039,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1230" t="n">
-        <v>21.4964942932129</v>
+        <v>21.4964962005615</v>
       </c>
       <c r="H1230" t="n">
         <v>11300</v>
@@ -36097,7 +36097,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>22.2676696777344</v>
+        <v>22.267671585083</v>
       </c>
       <c r="H1232" t="n">
         <v>22698</v>
@@ -36184,7 +36184,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1235" t="n">
-        <v>22.7496566772461</v>
+        <v>22.7496547698975</v>
       </c>
       <c r="H1235" t="n">
         <v>46203</v>
@@ -36213,7 +36213,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1236" t="n">
-        <v>21.9784812927246</v>
+        <v>21.978479385376</v>
       </c>
       <c r="H1236" t="n">
         <v>10509</v>
@@ -36271,7 +36271,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>22.9424476623535</v>
+        <v>22.9424495697021</v>
       </c>
       <c r="H1238" t="n">
         <v>43009</v>
@@ -36358,7 +36358,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1241" t="n">
-        <v>24.2438087463379</v>
+        <v>24.2438068389893</v>
       </c>
       <c r="H1241" t="n">
         <v>25874</v>
@@ -36416,7 +36416,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1243" t="n">
-        <v>25.6415596008301</v>
+        <v>25.6415615081787</v>
       </c>
       <c r="H1243" t="n">
         <v>73513</v>
@@ -36474,7 +36474,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>26.894718170166</v>
+        <v>26.8947200775146</v>
       </c>
       <c r="H1245" t="n">
         <v>30372</v>
@@ -36590,7 +36590,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>27.5694980621338</v>
+        <v>27.5694961547852</v>
       </c>
       <c r="H1249" t="n">
         <v>33067</v>
@@ -36648,7 +36648,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1251" t="n">
-        <v>29.7866249084473</v>
+        <v>29.7866230010986</v>
       </c>
       <c r="H1251" t="n">
         <v>72327</v>
@@ -36677,7 +36677,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>29.7866249084473</v>
+        <v>29.7866230010986</v>
       </c>
       <c r="H1252" t="n">
         <v>49221</v>
@@ -36706,7 +36706,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.8226566314697</v>
+        <v>28.8226547241211</v>
       </c>
       <c r="H1253" t="n">
         <v>18389</v>
@@ -36735,7 +36735,7 @@
         <v>30.75</v>
       </c>
       <c r="G1254" t="n">
-        <v>29.6420307159424</v>
+        <v>29.642032623291</v>
       </c>
       <c r="H1254" t="n">
         <v>19943</v>
@@ -36793,7 +36793,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>30.7987937927246</v>
+        <v>30.7987957000732</v>
       </c>
       <c r="H1256" t="n">
         <v>18704</v>
@@ -36851,7 +36851,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1258" t="n">
-        <v>31.9073524475098</v>
+        <v>31.9073600769043</v>
       </c>
       <c r="H1258" t="n">
         <v>35388</v>
@@ -36880,7 +36880,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1259" t="n">
-        <v>31.4253730773926</v>
+        <v>31.4253692626953</v>
       </c>
       <c r="H1259" t="n">
         <v>20414</v>
@@ -36938,7 +36938,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>31.4253730773926</v>
+        <v>31.4253692626953</v>
       </c>
       <c r="H1261" t="n">
         <v>15477</v>
@@ -37025,7 +37025,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1264" t="n">
-        <v>32.1965484619141</v>
+        <v>32.1965522766113</v>
       </c>
       <c r="H1264" t="n">
         <v>51922</v>
@@ -37054,7 +37054,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1265" t="n">
-        <v>31.9073524475098</v>
+        <v>31.9073600769043</v>
       </c>
       <c r="H1265" t="n">
         <v>38913</v>
@@ -37083,7 +37083,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>33.1605186462402</v>
+        <v>33.160514831543</v>
       </c>
       <c r="H1266" t="n">
         <v>32379</v>
@@ -37112,7 +37112,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>33.0641212463379</v>
+        <v>33.0641136169434</v>
       </c>
       <c r="H1267" t="n">
         <v>28183</v>
@@ -37170,7 +37170,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1269" t="n">
-        <v>33.3533058166504</v>
+        <v>33.3533020019531</v>
       </c>
       <c r="H1269" t="n">
         <v>15100</v>
@@ -37199,7 +37199,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G1270" t="n">
-        <v>33.5943031311035</v>
+        <v>33.5942993164062</v>
       </c>
       <c r="H1270" t="n">
         <v>10186</v>
@@ -37402,7 +37402,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1277" t="n">
-        <v>37.0163879394531</v>
+        <v>37.0163917541504</v>
       </c>
       <c r="H1277" t="n">
         <v>46240</v>
@@ -37431,7 +37431,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>36.0524253845215</v>
+        <v>36.0524215698242</v>
       </c>
       <c r="H1278" t="n">
         <v>107154</v>
@@ -37518,7 +37518,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1281" t="n">
-        <v>32.4375381469727</v>
+        <v>32.4375343322754</v>
       </c>
       <c r="H1281" t="n">
         <v>72316</v>
@@ -37547,7 +37547,7 @@
         <v>33.75</v>
       </c>
       <c r="G1282" t="n">
-        <v>32.533935546875</v>
+        <v>32.5339317321777</v>
       </c>
       <c r="H1282" t="n">
         <v>23671</v>
@@ -37576,7 +37576,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1283" t="n">
-        <v>32.6303329467773</v>
+        <v>32.6303291320801</v>
       </c>
       <c r="H1283" t="n">
         <v>15355</v>
@@ -37721,7 +37721,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1288" t="n">
-        <v>30.4614028930664</v>
+        <v>30.4614009857178</v>
       </c>
       <c r="H1288" t="n">
         <v>36519</v>
@@ -37779,7 +37779,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G1290" t="n">
-        <v>30.9915866851807</v>
+        <v>30.9915885925293</v>
       </c>
       <c r="H1290" t="n">
         <v>41352</v>
@@ -37837,7 +37837,7 @@
         <v>33.75</v>
       </c>
       <c r="G1292" t="n">
-        <v>32.533935546875</v>
+        <v>32.5339317321777</v>
       </c>
       <c r="H1292" t="n">
         <v>74097</v>
@@ -37953,7 +37953,7 @@
         <v>36.4500007629395</v>
       </c>
       <c r="G1296" t="n">
-        <v>35.1366500854492</v>
+        <v>35.136646270752</v>
       </c>
       <c r="H1296" t="n">
         <v>111817</v>
@@ -37982,7 +37982,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1297" t="n">
-        <v>35.5222358703613</v>
+        <v>35.5222320556641</v>
       </c>
       <c r="H1297" t="n">
         <v>66413</v>
@@ -38185,7 +38185,7 @@
         <v>36.25</v>
       </c>
       <c r="G1304" t="n">
-        <v>34.9438514709473</v>
+        <v>34.9438552856445</v>
       </c>
       <c r="H1304" t="n">
         <v>86269</v>
@@ -38243,7 +38243,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1306" t="n">
-        <v>36.5344085693359</v>
+        <v>36.5344047546387</v>
       </c>
       <c r="H1306" t="n">
         <v>61223</v>
@@ -38359,7 +38359,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1310" t="n">
-        <v>37.883960723877</v>
+        <v>37.8839645385742</v>
       </c>
       <c r="H1310" t="n">
         <v>85804</v>
@@ -38388,7 +38388,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G1311" t="n">
-        <v>38.4623413085938</v>
+        <v>38.462345123291</v>
       </c>
       <c r="H1311" t="n">
         <v>50654</v>
@@ -38417,7 +38417,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1312" t="n">
-        <v>38.60693359375</v>
+        <v>38.6069297790527</v>
       </c>
       <c r="H1312" t="n">
         <v>66065</v>
@@ -38446,7 +38446,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1313" t="n">
-        <v>39.667308807373</v>
+        <v>39.6673049926758</v>
       </c>
       <c r="H1313" t="n">
         <v>59423</v>
@@ -38475,7 +38475,7 @@
         <v>41</v>
       </c>
       <c r="G1314" t="n">
-        <v>39.522705078125</v>
+        <v>39.5227012634277</v>
       </c>
       <c r="H1314" t="n">
         <v>57551</v>
@@ -38504,7 +38504,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G1315" t="n">
-        <v>38.4141387939453</v>
+        <v>38.4141426086426</v>
       </c>
       <c r="H1315" t="n">
         <v>53283</v>
@@ -38533,7 +38533,7 @@
         <v>40</v>
       </c>
       <c r="G1316" t="n">
-        <v>38.5587310791016</v>
+        <v>38.5587348937988</v>
       </c>
       <c r="H1316" t="n">
         <v>67922</v>
@@ -38562,7 +38562,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1317" t="n">
-        <v>39.667308807373</v>
+        <v>39.6673049926758</v>
       </c>
       <c r="H1317" t="n">
         <v>89209</v>
@@ -38591,7 +38591,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1318" t="n">
-        <v>39.4745063781738</v>
+        <v>39.4745101928711</v>
       </c>
       <c r="H1318" t="n">
         <v>37364</v>
@@ -38649,7 +38649,7 @@
         <v>41.5</v>
       </c>
       <c r="G1320" t="n">
-        <v>40.0046920776367</v>
+        <v>40.004695892334</v>
       </c>
       <c r="H1320" t="n">
         <v>55839</v>
@@ -38707,7 +38707,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1322" t="n">
-        <v>40.1010818481445</v>
+        <v>40.1010856628418</v>
       </c>
       <c r="H1322" t="n">
         <v>112558</v>
@@ -38765,7 +38765,7 @@
         <v>43.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>41.7398414611816</v>
+        <v>41.7398376464844</v>
       </c>
       <c r="H1324" t="n">
         <v>124785</v>
@@ -38794,7 +38794,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1325" t="n">
-        <v>39.9082946777344</v>
+        <v>39.9082984924316</v>
       </c>
       <c r="H1325" t="n">
         <v>603584</v>
@@ -38910,7 +38910,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G1329" t="n">
-        <v>41.8844299316406</v>
+        <v>41.8844261169434</v>
       </c>
       <c r="H1329" t="n">
         <v>51912</v>
@@ -38939,7 +38939,7 @@
         <v>44.0499992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>42.4628105163574</v>
+        <v>42.4628067016602</v>
       </c>
       <c r="H1330" t="n">
         <v>33082</v>
@@ -38968,7 +38968,7 @@
         <v>43</v>
       </c>
       <c r="G1331" t="n">
-        <v>41.4506416320801</v>
+        <v>41.4506454467773</v>
       </c>
       <c r="H1331" t="n">
         <v>41166</v>
@@ -38997,7 +38997,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>42.2218208312988</v>
+        <v>42.2218170166016</v>
       </c>
       <c r="H1332" t="n">
         <v>46759</v>
@@ -39026,7 +39026,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>43.3303833007812</v>
+        <v>43.330379486084</v>
       </c>
       <c r="H1333" t="n">
         <v>107887</v>
@@ -39055,7 +39055,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G1334" t="n">
-        <v>43.9569625854492</v>
+        <v>43.956958770752</v>
       </c>
       <c r="H1334" t="n">
         <v>40852</v>
@@ -39084,7 +39084,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>44.5353393554688</v>
+        <v>44.535343170166</v>
       </c>
       <c r="H1335" t="n">
         <v>27530</v>
@@ -39113,7 +39113,7 @@
         <v>46.25</v>
       </c>
       <c r="G1336" t="n">
-        <v>44.5835342407227</v>
+        <v>44.5835380554199</v>
       </c>
       <c r="H1336" t="n">
         <v>34471</v>
@@ -39142,7 +39142,7 @@
         <v>47.2000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>45.4993133544922</v>
+        <v>45.4993095397949</v>
       </c>
       <c r="H1337" t="n">
         <v>49349</v>
@@ -39171,7 +39171,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1338" t="n">
-        <v>44.2461547851562</v>
+        <v>44.246150970459</v>
       </c>
       <c r="H1338" t="n">
         <v>80310</v>
@@ -39200,7 +39200,7 @@
         <v>46.5</v>
       </c>
       <c r="G1339" t="n">
-        <v>44.8245391845703</v>
+        <v>44.824535369873</v>
       </c>
       <c r="H1339" t="n">
         <v>47700</v>
@@ -39287,7 +39287,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G1342" t="n">
-        <v>44.7763366699219</v>
+        <v>44.7763328552246</v>
       </c>
       <c r="H1342" t="n">
         <v>54058</v>
@@ -39316,7 +39316,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G1343" t="n">
-        <v>46.0776863098145</v>
+        <v>46.0776901245117</v>
       </c>
       <c r="H1343" t="n">
         <v>40986</v>
@@ -39345,7 +39345,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G1344" t="n">
-        <v>44.9691314697266</v>
+        <v>44.9691276550293</v>
       </c>
       <c r="H1344" t="n">
         <v>41720</v>
@@ -39374,7 +39374,7 @@
         <v>46.25</v>
       </c>
       <c r="G1345" t="n">
-        <v>44.5835342407227</v>
+        <v>44.5835380554199</v>
       </c>
       <c r="H1345" t="n">
         <v>46730</v>
@@ -39403,7 +39403,7 @@
         <v>46.0999984741211</v>
       </c>
       <c r="G1346" t="n">
-        <v>44.4389457702637</v>
+        <v>44.4389495849609</v>
       </c>
       <c r="H1346" t="n">
         <v>35822</v>
@@ -39432,7 +39432,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1347" t="n">
-        <v>44.2461547851562</v>
+        <v>44.246150970459</v>
       </c>
       <c r="H1347" t="n">
         <v>65693</v>
@@ -39461,7 +39461,7 @@
         <v>46</v>
       </c>
       <c r="G1348" t="n">
-        <v>44.3425445556641</v>
+        <v>44.3425483703613</v>
       </c>
       <c r="H1348" t="n">
         <v>45543</v>
@@ -39490,7 +39490,7 @@
         <v>46</v>
       </c>
       <c r="G1349" t="n">
-        <v>44.3425445556641</v>
+        <v>44.3425483703613</v>
       </c>
       <c r="H1349" t="n">
         <v>25766</v>
@@ -39519,7 +39519,7 @@
         <v>45.75</v>
       </c>
       <c r="G1350" t="n">
-        <v>44.1015548706055</v>
+        <v>44.1015586853027</v>
       </c>
       <c r="H1350" t="n">
         <v>26538</v>
@@ -39577,7 +39577,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G1352" t="n">
-        <v>42.9929885864258</v>
+        <v>42.992992401123</v>
       </c>
       <c r="H1352" t="n">
         <v>52488</v>
@@ -39635,7 +39635,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>43.0893898010254</v>
+        <v>43.0893936157227</v>
       </c>
       <c r="H1354" t="n">
         <v>14472</v>
@@ -39664,7 +39664,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>42.7038078308105</v>
+        <v>42.7038040161133</v>
       </c>
       <c r="H1355" t="n">
         <v>43736</v>
@@ -39693,7 +39693,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>42.7038078308105</v>
+        <v>42.7038040161133</v>
       </c>
       <c r="H1356" t="n">
         <v>19545</v>
@@ -39722,7 +39722,7 @@
         <v>44.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>42.8965950012207</v>
+        <v>42.896598815918</v>
       </c>
       <c r="H1357" t="n">
         <v>36274</v>
@@ -39780,7 +39780,7 @@
         <v>44.8499984741211</v>
       </c>
       <c r="G1359" t="n">
-        <v>43.2339859008789</v>
+        <v>43.2339820861816</v>
       </c>
       <c r="H1359" t="n">
         <v>34206</v>
@@ -39809,7 +39809,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G1360" t="n">
-        <v>42.2700157165527</v>
+        <v>42.27001953125</v>
       </c>
       <c r="H1360" t="n">
         <v>32244</v>
@@ -39838,7 +39838,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G1361" t="n">
-        <v>41.8844299316406</v>
+        <v>41.8844261169434</v>
       </c>
       <c r="H1361" t="n">
         <v>12965</v>
@@ -39867,7 +39867,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1362" t="n">
-        <v>42.2218208312988</v>
+        <v>42.2218170166016</v>
       </c>
       <c r="H1362" t="n">
         <v>19208</v>
@@ -80006,9 +80006,38 @@
         <v>32.9500007629395</v>
       </c>
       <c r="H2746" t="n">
-        <v>79016</v>
+        <v>79269</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>32.4500007629395</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>33.5999984741211</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>32.4500007629395</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>32.8499984741211</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>32.8499984741211</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>49015</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G3" t="n">
-        <v>6.73136377334595</v>
+        <v>6.73136281967163</v>
       </c>
       <c r="H3" t="n">
         <v>30952</v>
@@ -485,7 +485,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6343822479248</v>
+        <v>6.63438272476196</v>
       </c>
       <c r="H4" t="n">
         <v>6498</v>
@@ -514,7 +514,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>6.74458694458008</v>
+        <v>6.74458742141724</v>
       </c>
       <c r="H5" t="n">
         <v>87223</v>
@@ -543,7 +543,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>6.74458694458008</v>
+        <v>6.74458742141724</v>
       </c>
       <c r="H6" t="n">
         <v>33933</v>
@@ -572,7 +572,7 @@
         <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.61234092712402</v>
+        <v>6.61234140396118</v>
       </c>
       <c r="H7" t="n">
         <v>14765</v>
@@ -659,7 +659,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>6.52417707443237</v>
+        <v>6.52417659759521</v>
       </c>
       <c r="H10" t="n">
         <v>35744</v>
@@ -688,7 +688,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>6.29494857788086</v>
+        <v>6.29494905471802</v>
       </c>
       <c r="H11" t="n">
         <v>36818</v>
@@ -717,7 +717,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>6.07453775405884</v>
+        <v>6.07453680038452</v>
       </c>
       <c r="H12" t="n">
         <v>100254</v>
@@ -746,7 +746,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>6.32580614089966</v>
+        <v>6.32580661773682</v>
       </c>
       <c r="H13" t="n">
         <v>18590</v>
@@ -804,7 +804,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>6.53299283981323</v>
+        <v>6.53299331665039</v>
       </c>
       <c r="H15" t="n">
         <v>54538</v>
@@ -862,7 +862,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G17" t="n">
-        <v>5.87175846099854</v>
+        <v>5.87175941467285</v>
       </c>
       <c r="H17" t="n">
         <v>43671</v>
@@ -891,7 +891,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>6.497727394104</v>
+        <v>6.49772787094116</v>
       </c>
       <c r="H18" t="n">
         <v>45693</v>
@@ -920,7 +920,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>6.62997436523438</v>
+        <v>6.62997341156006</v>
       </c>
       <c r="H19" t="n">
         <v>19134</v>
@@ -949,7 +949,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G20" t="n">
-        <v>6.73577117919922</v>
+        <v>6.73577260971069</v>
       </c>
       <c r="H20" t="n">
         <v>8655</v>
@@ -1007,7 +1007,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G22" t="n">
-        <v>6.63879060745239</v>
+        <v>6.63879108428955</v>
       </c>
       <c r="H22" t="n">
         <v>4038</v>
@@ -1036,7 +1036,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6652398109436</v>
+        <v>6.66523933410645</v>
       </c>
       <c r="H23" t="n">
         <v>8355</v>
@@ -1123,7 +1123,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G26" t="n">
-        <v>5.87175846099854</v>
+        <v>5.87175941467285</v>
       </c>
       <c r="H26" t="n">
         <v>57381</v>
@@ -1152,7 +1152,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G27" t="n">
-        <v>5.99518918991089</v>
+        <v>5.99518871307373</v>
       </c>
       <c r="H27" t="n">
         <v>26561</v>
@@ -1181,7 +1181,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87616682052612</v>
+        <v>5.87616777420044</v>
       </c>
       <c r="H28" t="n">
         <v>32757</v>
@@ -1210,7 +1210,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>6.25968217849731</v>
+        <v>6.25968313217163</v>
       </c>
       <c r="H29" t="n">
         <v>30386</v>
@@ -1268,7 +1268,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>6.22882509231567</v>
+        <v>6.22882556915283</v>
       </c>
       <c r="H31" t="n">
         <v>13397</v>
@@ -1297,7 +1297,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>6.37429666519165</v>
+        <v>6.37429761886597</v>
       </c>
       <c r="H32" t="n">
         <v>6426</v>
@@ -1326,7 +1326,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G33" t="n">
-        <v>6.31698942184448</v>
+        <v>6.31698989868164</v>
       </c>
       <c r="H33" t="n">
         <v>2348</v>
@@ -1355,7 +1355,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>6.48450231552124</v>
+        <v>6.48450326919556</v>
       </c>
       <c r="H34" t="n">
         <v>9218</v>
@@ -1384,7 +1384,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>6.52417707443237</v>
+        <v>6.52417659759521</v>
       </c>
       <c r="H35" t="n">
         <v>11539</v>
@@ -1413,7 +1413,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>6.30817317962646</v>
+        <v>6.30817461013794</v>
       </c>
       <c r="H36" t="n">
         <v>4275</v>
@@ -1471,7 +1471,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>6.36548042297363</v>
+        <v>6.36547994613647</v>
       </c>
       <c r="H38" t="n">
         <v>930</v>
@@ -1500,7 +1500,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>6.37429666519165</v>
+        <v>6.37429761886597</v>
       </c>
       <c r="H39" t="n">
         <v>2421</v>
@@ -1529,7 +1529,7 @@
         <v>7.125</v>
       </c>
       <c r="G40" t="n">
-        <v>6.2817234992981</v>
+        <v>6.28172302246094</v>
       </c>
       <c r="H40" t="n">
         <v>1780</v>
@@ -1558,7 +1558,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>6.38311243057251</v>
+        <v>6.38311386108398</v>
       </c>
       <c r="H41" t="n">
         <v>8021</v>
@@ -1587,7 +1587,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>6.3302149772644</v>
+        <v>6.33021450042725</v>
       </c>
       <c r="H42" t="n">
         <v>5727</v>
@@ -1645,7 +1645,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>6.60793209075928</v>
+        <v>6.60793256759644</v>
       </c>
       <c r="H44" t="n">
         <v>16548</v>
@@ -1674,7 +1674,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>6.40956211090088</v>
+        <v>6.40956258773804</v>
       </c>
       <c r="H45" t="n">
         <v>25241</v>
@@ -1703,7 +1703,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>6.40956211090088</v>
+        <v>6.40956258773804</v>
       </c>
       <c r="H46" t="n">
         <v>1765</v>
@@ -1732,7 +1732,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G47" t="n">
-        <v>6.20237588882446</v>
+        <v>6.2023754119873</v>
       </c>
       <c r="H47" t="n">
         <v>9433</v>
@@ -1790,7 +1790,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>6.25086736679077</v>
+        <v>6.2508659362793</v>
       </c>
       <c r="H49" t="n">
         <v>44447</v>
@@ -1819,7 +1819,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>6.25968217849731</v>
+        <v>6.25968313217163</v>
       </c>
       <c r="H50" t="n">
         <v>5680</v>
@@ -1877,7 +1877,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G52" t="n">
-        <v>6.60352468490601</v>
+        <v>6.60352420806885</v>
       </c>
       <c r="H52" t="n">
         <v>32408</v>
@@ -1935,7 +1935,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>6.41397142410278</v>
+        <v>6.41397094726562</v>
       </c>
       <c r="H54" t="n">
         <v>22911</v>
@@ -1993,7 +1993,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G56" t="n">
-        <v>6.38752222061157</v>
+        <v>6.38752174377441</v>
       </c>
       <c r="H56" t="n">
         <v>35518</v>
@@ -2022,7 +2022,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G57" t="n">
-        <v>6.42719554901123</v>
+        <v>6.42719507217407</v>
       </c>
       <c r="H57" t="n">
         <v>56192</v>
@@ -2051,7 +2051,7 @@
         <v>7.5</v>
       </c>
       <c r="G58" t="n">
-        <v>6.61234092712402</v>
+        <v>6.61234140396118</v>
       </c>
       <c r="H58" t="n">
         <v>51559</v>
@@ -2109,7 +2109,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G60" t="n">
-        <v>6.34343862533569</v>
+        <v>6.34343910217285</v>
       </c>
       <c r="H60" t="n">
         <v>8385</v>
@@ -2138,7 +2138,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="n">
-        <v>6.17151832580566</v>
+        <v>6.17151784896851</v>
       </c>
       <c r="H61" t="n">
         <v>13993</v>
@@ -2167,7 +2167,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>6.04368019104004</v>
+        <v>6.04367971420288</v>
       </c>
       <c r="H62" t="n">
         <v>142264</v>
@@ -2196,7 +2196,7 @@
         <v>7</v>
       </c>
       <c r="G63" t="n">
-        <v>6.17151832580566</v>
+        <v>6.17151784896851</v>
       </c>
       <c r="H63" t="n">
         <v>22234</v>
@@ -2225,7 +2225,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>6.2640905380249</v>
+        <v>6.26409101486206</v>
       </c>
       <c r="H64" t="n">
         <v>26313</v>
@@ -2254,7 +2254,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G65" t="n">
-        <v>6.38752222061157</v>
+        <v>6.38752174377441</v>
       </c>
       <c r="H65" t="n">
         <v>24365</v>
@@ -2312,7 +2312,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>6.26849889755249</v>
+        <v>6.26849937438965</v>
       </c>
       <c r="H67" t="n">
         <v>68623</v>
@@ -2341,7 +2341,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G68" t="n">
-        <v>6.22441673278809</v>
+        <v>6.22441720962524</v>
       </c>
       <c r="H68" t="n">
         <v>16070</v>
@@ -2370,7 +2370,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G69" t="n">
-        <v>6.19796705245972</v>
+        <v>6.19796800613403</v>
       </c>
       <c r="H69" t="n">
         <v>64201</v>
@@ -2428,7 +2428,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>6.13184499740601</v>
+        <v>6.13184452056885</v>
       </c>
       <c r="H71" t="n">
         <v>17623</v>
@@ -2457,7 +2457,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>6.16710996627808</v>
+        <v>6.16711044311523</v>
       </c>
       <c r="H72" t="n">
         <v>104245</v>
@@ -2486,7 +2486,7 @@
         <v>7.125</v>
       </c>
       <c r="G73" t="n">
-        <v>6.2817234992981</v>
+        <v>6.28172302246094</v>
       </c>
       <c r="H73" t="n">
         <v>34698</v>
@@ -2515,7 +2515,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>6.25968217849731</v>
+        <v>6.25968313217163</v>
       </c>
       <c r="H74" t="n">
         <v>2836</v>
@@ -2573,7 +2573,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G76" t="n">
-        <v>6.30817317962646</v>
+        <v>6.30817461013794</v>
       </c>
       <c r="H76" t="n">
         <v>2944</v>
@@ -2602,7 +2602,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42719554901123</v>
+        <v>6.42719507217407</v>
       </c>
       <c r="H77" t="n">
         <v>4802</v>
@@ -2631,7 +2631,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>6.60352468490601</v>
+        <v>6.60352420806885</v>
       </c>
       <c r="H78" t="n">
         <v>55158</v>
@@ -2660,7 +2660,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>6.56385040283203</v>
+        <v>6.56385087966919</v>
       </c>
       <c r="H79" t="n">
         <v>13140</v>
@@ -2689,7 +2689,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G80" t="n">
-        <v>6.56385040283203</v>
+        <v>6.56385087966919</v>
       </c>
       <c r="H80" t="n">
         <v>12413</v>
@@ -2747,7 +2747,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>6.47127819061279</v>
+        <v>6.47127676010132</v>
       </c>
       <c r="H82" t="n">
         <v>74460</v>
@@ -2776,7 +2776,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>6.39633846282959</v>
+        <v>6.39633798599243</v>
       </c>
       <c r="H83" t="n">
         <v>1073</v>
@@ -2805,7 +2805,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>6.40956211090088</v>
+        <v>6.40956258773804</v>
       </c>
       <c r="H84" t="n">
         <v>1248</v>
@@ -2834,7 +2834,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>6.60761213302612</v>
+        <v>6.60761022567749</v>
       </c>
       <c r="H85" t="n">
         <v>14179</v>
@@ -2892,7 +2892,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G87" t="n">
-        <v>6.51758861541748</v>
+        <v>6.51758909225464</v>
       </c>
       <c r="H87" t="n">
         <v>892</v>
@@ -2921,7 +2921,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>6.41856479644775</v>
+        <v>6.41856527328491</v>
       </c>
       <c r="H88" t="n">
         <v>8092</v>
@@ -2979,7 +2979,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>6.53109216690063</v>
+        <v>6.53109264373779</v>
       </c>
       <c r="H90" t="n">
         <v>12379</v>
@@ -3037,7 +3037,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>6.59410715103149</v>
+        <v>6.59410762786865</v>
       </c>
       <c r="H92" t="n">
         <v>5057</v>
@@ -3066,7 +3066,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>6.66612529754639</v>
+        <v>6.66612577438354</v>
       </c>
       <c r="H93" t="n">
         <v>11596</v>
@@ -3095,7 +3095,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G94" t="n">
-        <v>6.57160234451294</v>
+        <v>6.5716028213501</v>
       </c>
       <c r="H94" t="n">
         <v>45313</v>
@@ -3124,7 +3124,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>6.65712356567383</v>
+        <v>6.65712308883667</v>
       </c>
       <c r="H95" t="n">
         <v>34946</v>
@@ -3182,7 +3182,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>6.59410715103149</v>
+        <v>6.59410762786865</v>
       </c>
       <c r="H97" t="n">
         <v>83067</v>
@@ -3240,7 +3240,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G99" t="n">
-        <v>6.72463989257812</v>
+        <v>6.72463846206665</v>
       </c>
       <c r="H99" t="n">
         <v>18269</v>
@@ -3327,7 +3327,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>6.95869541168213</v>
+        <v>6.95869636535645</v>
       </c>
       <c r="H102" t="n">
         <v>12849</v>
@@ -3356,7 +3356,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G103" t="n">
-        <v>7.07572460174561</v>
+        <v>7.07572507858276</v>
       </c>
       <c r="H103" t="n">
         <v>33454</v>
@@ -3385,7 +3385,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G104" t="n">
-        <v>7.22426128387451</v>
+        <v>7.2242603302002</v>
       </c>
       <c r="H104" t="n">
         <v>63841</v>
@@ -3443,7 +3443,7 @@
         <v>8.25</v>
       </c>
       <c r="G106" t="n">
-        <v>7.4268102645874</v>
+        <v>7.42681074142456</v>
       </c>
       <c r="H106" t="n">
         <v>20708</v>
@@ -3501,7 +3501,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>7.35029220581055</v>
+        <v>7.35029125213623</v>
       </c>
       <c r="H108" t="n">
         <v>3935</v>
@@ -3530,7 +3530,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G109" t="n">
-        <v>7.22876214981079</v>
+        <v>7.22876167297363</v>
       </c>
       <c r="H109" t="n">
         <v>17502</v>
@@ -3617,7 +3617,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.1972541809082</v>
+        <v>7.19725513458252</v>
       </c>
       <c r="H112" t="n">
         <v>4314</v>
@@ -3646,7 +3646,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G113" t="n">
-        <v>7.17024803161621</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H113" t="n">
         <v>15482</v>
@@ -3675,7 +3675,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>7.06672286987305</v>
+        <v>7.06672239303589</v>
       </c>
       <c r="H114" t="n">
         <v>22711</v>
@@ -3733,7 +3733,7 @@
         <v>7.75</v>
       </c>
       <c r="G116" t="n">
-        <v>6.97670030593872</v>
+        <v>6.97670078277588</v>
       </c>
       <c r="H116" t="n">
         <v>36916</v>
@@ -3762,7 +3762,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>7.05321979522705</v>
+        <v>7.05321931838989</v>
       </c>
       <c r="H117" t="n">
         <v>13746</v>
@@ -3849,7 +3849,7 @@
         <v>7.875</v>
       </c>
       <c r="G120" t="n">
-        <v>7.08922910690308</v>
+        <v>7.0892276763916</v>
       </c>
       <c r="H120" t="n">
         <v>11937</v>
@@ -3878,7 +3878,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G121" t="n">
-        <v>7.13874053955078</v>
+        <v>7.13874006271362</v>
       </c>
       <c r="H121" t="n">
         <v>15972</v>
@@ -3907,7 +3907,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>7.28277587890625</v>
+        <v>7.28277635574341</v>
       </c>
       <c r="H122" t="n">
         <v>34317</v>
@@ -3936,7 +3936,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G123" t="n">
-        <v>7.29627799987793</v>
+        <v>7.29627847671509</v>
       </c>
       <c r="H123" t="n">
         <v>7525</v>
@@ -3965,7 +3965,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>6.9721999168396</v>
+        <v>6.97219896316528</v>
       </c>
       <c r="H124" t="n">
         <v>18527</v>
@@ -3994,7 +3994,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>6.70663499832153</v>
+        <v>6.70663452148438</v>
       </c>
       <c r="H125" t="n">
         <v>18043</v>
@@ -4023,7 +4023,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.95869541168213</v>
+        <v>6.95869636535645</v>
       </c>
       <c r="H126" t="n">
         <v>13479</v>
@@ -4110,7 +4110,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H129" t="n">
         <v>30647</v>
@@ -4168,7 +4168,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>6.65262222290039</v>
+        <v>6.65262126922607</v>
       </c>
       <c r="H131" t="n">
         <v>10765</v>
@@ -4255,7 +4255,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>6.60761213302612</v>
+        <v>6.60761022567749</v>
       </c>
       <c r="H134" t="n">
         <v>11755</v>
@@ -4284,7 +4284,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G135" t="n">
-        <v>6.55359745025635</v>
+        <v>6.55359792709351</v>
       </c>
       <c r="H135" t="n">
         <v>8542</v>
@@ -4313,7 +4313,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.57160234451294</v>
+        <v>6.5716028213501</v>
       </c>
       <c r="H136" t="n">
         <v>11466</v>
@@ -4371,7 +4371,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>6.41856479644775</v>
+        <v>6.41856527328491</v>
       </c>
       <c r="H138" t="n">
         <v>7018</v>
@@ -4400,7 +4400,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>6.39155864715576</v>
+        <v>6.3915581703186</v>
       </c>
       <c r="H139" t="n">
         <v>14786</v>
@@ -4458,7 +4458,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G141" t="n">
-        <v>6.62561559677124</v>
+        <v>6.62561511993408</v>
       </c>
       <c r="H141" t="n">
         <v>7918</v>
@@ -4545,7 +4545,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>6.40956211090088</v>
+        <v>6.40956258773804</v>
       </c>
       <c r="H144" t="n">
         <v>14425</v>
@@ -4574,7 +4574,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>6.72913980484009</v>
+        <v>6.72914028167725</v>
       </c>
       <c r="H145" t="n">
         <v>40578</v>
@@ -4603,7 +4603,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>6.54009485244751</v>
+        <v>6.54009437561035</v>
       </c>
       <c r="H146" t="n">
         <v>3693</v>
@@ -4661,7 +4661,7 @@
         <v>7.5</v>
       </c>
       <c r="G148" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H148" t="n">
         <v>13911</v>
@@ -4690,7 +4690,7 @@
         <v>7.5</v>
       </c>
       <c r="G149" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H149" t="n">
         <v>16812</v>
@@ -4719,7 +4719,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G150" t="n">
-        <v>6.68413066864014</v>
+        <v>6.68413019180298</v>
       </c>
       <c r="H150" t="n">
         <v>1322</v>
@@ -4748,7 +4748,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G151" t="n">
-        <v>6.54009485244751</v>
+        <v>6.54009437561035</v>
       </c>
       <c r="H151" t="n">
         <v>2590</v>
@@ -4777,7 +4777,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G152" t="n">
-        <v>6.46357488632202</v>
+        <v>6.46357583999634</v>
       </c>
       <c r="H152" t="n">
         <v>32309</v>
@@ -4806,7 +4806,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G153" t="n">
-        <v>6.51308822631836</v>
+        <v>6.51308727264404</v>
       </c>
       <c r="H153" t="n">
         <v>3696</v>
@@ -4835,7 +4835,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>6.6346173286438</v>
+        <v>6.63461780548096</v>
       </c>
       <c r="H154" t="n">
         <v>3535</v>
@@ -4864,7 +4864,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H155" t="n">
         <v>38855</v>
@@ -4922,7 +4922,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>6.70663499832153</v>
+        <v>6.70663452148438</v>
       </c>
       <c r="H157" t="n">
         <v>25297</v>
@@ -4951,7 +4951,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>6.66162395477295</v>
+        <v>6.66162443161011</v>
       </c>
       <c r="H158" t="n">
         <v>40928</v>
@@ -4980,7 +4980,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>6.73364162445068</v>
+        <v>6.73364210128784</v>
       </c>
       <c r="H159" t="n">
         <v>45305</v>
@@ -5038,7 +5038,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>6.67512702941895</v>
+        <v>6.67512655258179</v>
       </c>
       <c r="H161" t="n">
         <v>7546</v>
@@ -5096,7 +5096,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66162395477295</v>
+        <v>6.66162443161011</v>
       </c>
       <c r="H163" t="n">
         <v>6528</v>
@@ -5125,7 +5125,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G164" t="n">
-        <v>6.76064825057983</v>
+        <v>6.76064920425415</v>
       </c>
       <c r="H164" t="n">
         <v>44354</v>
@@ -5154,7 +5154,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>6.70663499832153</v>
+        <v>6.70663452148438</v>
       </c>
       <c r="H165" t="n">
         <v>14807</v>
@@ -5183,7 +5183,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>6.76965045928955</v>
+        <v>6.76964998245239</v>
       </c>
       <c r="H166" t="n">
         <v>24039</v>
@@ -5270,7 +5270,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>6.79665756225586</v>
+        <v>6.7966570854187</v>
       </c>
       <c r="H169" t="n">
         <v>14815</v>
@@ -5357,7 +5357,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>6.87767648696899</v>
+        <v>6.87767696380615</v>
       </c>
       <c r="H172" t="n">
         <v>8643</v>
@@ -5415,7 +5415,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>6.95419549942017</v>
+        <v>6.95419502258301</v>
       </c>
       <c r="H174" t="n">
         <v>289197</v>
@@ -5444,7 +5444,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G175" t="n">
-        <v>7.07572460174561</v>
+        <v>7.07572507858276</v>
       </c>
       <c r="H175" t="n">
         <v>50017</v>
@@ -5473,7 +5473,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G176" t="n">
-        <v>7.14774227142334</v>
+        <v>7.1477427482605</v>
       </c>
       <c r="H176" t="n">
         <v>78414</v>
@@ -5502,7 +5502,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G177" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H177" t="n">
         <v>109990</v>
@@ -5560,7 +5560,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H179" t="n">
         <v>14514</v>
@@ -5589,7 +5589,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G180" t="n">
-        <v>7.17024803161621</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H180" t="n">
         <v>5632</v>
@@ -5618,7 +5618,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.05321979522705</v>
+        <v>7.05321931838989</v>
       </c>
       <c r="H181" t="n">
         <v>17322</v>
@@ -5647,7 +5647,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>7.05321979522705</v>
+        <v>7.05321931838989</v>
       </c>
       <c r="H182" t="n">
         <v>12460</v>
@@ -5676,7 +5676,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G183" t="n">
-        <v>6.9857029914856</v>
+        <v>6.98570346832275</v>
       </c>
       <c r="H183" t="n">
         <v>20651</v>
@@ -5821,7 +5821,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G188" t="n">
-        <v>6.87767648696899</v>
+        <v>6.87767696380615</v>
       </c>
       <c r="H188" t="n">
         <v>2677</v>
@@ -5850,7 +5850,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.79665756225586</v>
+        <v>6.7966570854187</v>
       </c>
       <c r="H189" t="n">
         <v>17762</v>
@@ -5879,7 +5879,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G190" t="n">
-        <v>6.60761213302612</v>
+        <v>6.60761022567749</v>
       </c>
       <c r="H190" t="n">
         <v>16505</v>
@@ -5937,7 +5937,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>6.62561559677124</v>
+        <v>6.62561511993408</v>
       </c>
       <c r="H192" t="n">
         <v>6508</v>
@@ -5966,7 +5966,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G193" t="n">
-        <v>6.67062568664551</v>
+        <v>6.67062664031982</v>
       </c>
       <c r="H193" t="n">
         <v>23088</v>
@@ -5995,7 +5995,7 @@
         <v>7.5</v>
       </c>
       <c r="G194" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H194" t="n">
         <v>25240</v>
@@ -6024,7 +6024,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G195" t="n">
-        <v>6.85967254638672</v>
+        <v>6.85967206954956</v>
       </c>
       <c r="H195" t="n">
         <v>15028</v>
@@ -6111,7 +6111,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G198" t="n">
-        <v>6.96319818496704</v>
+        <v>6.9631986618042</v>
       </c>
       <c r="H198" t="n">
         <v>16556</v>
@@ -6140,7 +6140,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G199" t="n">
-        <v>7.16574764251709</v>
+        <v>7.16574668884277</v>
       </c>
       <c r="H199" t="n">
         <v>15275</v>
@@ -6198,7 +6198,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G201" t="n">
-        <v>7.14774227142334</v>
+        <v>7.1477427482605</v>
       </c>
       <c r="H201" t="n">
         <v>15443</v>
@@ -6256,7 +6256,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G203" t="n">
-        <v>7.03071403503418</v>
+        <v>7.03071355819702</v>
       </c>
       <c r="H203" t="n">
         <v>1632</v>
@@ -6285,7 +6285,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G204" t="n">
-        <v>7.07572460174561</v>
+        <v>7.07572507858276</v>
       </c>
       <c r="H204" t="n">
         <v>10951</v>
@@ -6314,7 +6314,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G205" t="n">
-        <v>7.02171182632446</v>
+        <v>7.0217113494873</v>
       </c>
       <c r="H205" t="n">
         <v>3253</v>
@@ -6401,7 +6401,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="n">
-        <v>7.12073564529419</v>
+        <v>7.12073612213135</v>
       </c>
       <c r="H208" t="n">
         <v>8822</v>
@@ -6430,7 +6430,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G209" t="n">
-        <v>7.05772113800049</v>
+        <v>7.05772161483765</v>
       </c>
       <c r="H209" t="n">
         <v>37159</v>
@@ -6488,7 +6488,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>7.12973737716675</v>
+        <v>7.12973833084106</v>
       </c>
       <c r="H211" t="n">
         <v>6629</v>
@@ -6604,7 +6604,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>7.35479259490967</v>
+        <v>7.35479211807251</v>
       </c>
       <c r="H215" t="n">
         <v>10432</v>
@@ -6633,7 +6633,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G216" t="n">
-        <v>7.19275283813477</v>
+        <v>7.19275379180908</v>
       </c>
       <c r="H216" t="n">
         <v>12650</v>
@@ -6662,7 +6662,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G217" t="n">
-        <v>7.21976041793823</v>
+        <v>7.21976137161255</v>
       </c>
       <c r="H217" t="n">
         <v>14711</v>
@@ -6691,7 +6691,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G218" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H218" t="n">
         <v>5931</v>
@@ -6720,7 +6720,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>7.16124486923218</v>
+        <v>7.16124534606934</v>
       </c>
       <c r="H219" t="n">
         <v>3644</v>
@@ -6749,7 +6749,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G220" t="n">
-        <v>7.17024803161621</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H220" t="n">
         <v>11070</v>
@@ -6807,7 +6807,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G222" t="n">
-        <v>7.34128952026367</v>
+        <v>7.34129047393799</v>
       </c>
       <c r="H222" t="n">
         <v>11097</v>
@@ -6836,7 +6836,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>7.06672286987305</v>
+        <v>7.06672239303589</v>
       </c>
       <c r="H223" t="n">
         <v>44997</v>
@@ -6923,7 +6923,7 @@
         <v>7.5</v>
       </c>
       <c r="G226" t="n">
-        <v>6.75164556503296</v>
+        <v>6.75164604187012</v>
       </c>
       <c r="H226" t="n">
         <v>30587</v>
@@ -6952,7 +6952,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G227" t="n">
-        <v>7.00820827484131</v>
+        <v>7.00820875167847</v>
       </c>
       <c r="H227" t="n">
         <v>43110</v>
@@ -6981,7 +6981,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G228" t="n">
-        <v>7.15224313735962</v>
+        <v>7.15224409103394</v>
       </c>
       <c r="H228" t="n">
         <v>13253</v>
@@ -7010,7 +7010,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>6.88667964935303</v>
+        <v>6.88667869567871</v>
       </c>
       <c r="H229" t="n">
         <v>32778</v>
@@ -7039,7 +7039,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>6.87767648696899</v>
+        <v>6.87767696380615</v>
       </c>
       <c r="H230" t="n">
         <v>16359</v>
@@ -7184,7 +7184,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G235" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H235" t="n">
         <v>6049</v>
@@ -7242,7 +7242,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G237" t="n">
-        <v>7.21976041793823</v>
+        <v>7.21976137161255</v>
       </c>
       <c r="H237" t="n">
         <v>36844</v>
@@ -7300,7 +7300,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G239" t="n">
-        <v>7.15224313735962</v>
+        <v>7.15224409103394</v>
       </c>
       <c r="H239" t="n">
         <v>103907</v>
@@ -7329,7 +7329,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G240" t="n">
-        <v>7.15674448013306</v>
+        <v>7.15674495697021</v>
       </c>
       <c r="H240" t="n">
         <v>9254</v>
@@ -7358,7 +7358,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G241" t="n">
-        <v>7.48982715606689</v>
+        <v>7.48982620239258</v>
       </c>
       <c r="H241" t="n">
         <v>99151</v>
@@ -7387,7 +7387,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G242" t="n">
-        <v>7.44931507110596</v>
+        <v>7.44931602478027</v>
       </c>
       <c r="H242" t="n">
         <v>12622</v>
@@ -7416,7 +7416,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>7.4718222618103</v>
+        <v>7.47182035446167</v>
       </c>
       <c r="H243" t="n">
         <v>2167</v>
@@ -7445,7 +7445,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>7.17024803161621</v>
+        <v>7.17024850845337</v>
       </c>
       <c r="H244" t="n">
         <v>14353</v>
@@ -7474,7 +7474,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76064825057983</v>
+        <v>6.76064920425415</v>
       </c>
       <c r="H245" t="n">
         <v>205811</v>
@@ -7503,7 +7503,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G246" t="n">
-        <v>7.15224313735962</v>
+        <v>7.15224409103394</v>
       </c>
       <c r="H246" t="n">
         <v>60307</v>
@@ -7590,7 +7590,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>7.24676704406738</v>
+        <v>7.24676752090454</v>
       </c>
       <c r="H249" t="n">
         <v>5962</v>
@@ -7648,7 +7648,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>7.57984685897827</v>
+        <v>7.57984828948975</v>
       </c>
       <c r="H251" t="n">
         <v>10255</v>
@@ -7677,7 +7677,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G252" t="n">
-        <v>7.63386011123657</v>
+        <v>7.63386058807373</v>
       </c>
       <c r="H252" t="n">
         <v>12877</v>
@@ -7706,7 +7706,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>7.69687604904175</v>
+        <v>7.69687652587891</v>
       </c>
       <c r="H253" t="n">
         <v>15824</v>
@@ -7735,7 +7735,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>7.69687604904175</v>
+        <v>7.69687652587891</v>
       </c>
       <c r="H254" t="n">
         <v>4269</v>
@@ -7764,7 +7764,7 @@
         <v>8.5</v>
       </c>
       <c r="G255" t="n">
-        <v>7.65186595916748</v>
+        <v>7.65186500549316</v>
       </c>
       <c r="H255" t="n">
         <v>9504</v>
@@ -7793,7 +7793,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>7.64736366271973</v>
+        <v>7.64736413955688</v>
       </c>
       <c r="H256" t="n">
         <v>6072</v>
@@ -7880,7 +7880,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G259" t="n">
-        <v>7.93993520736694</v>
+        <v>7.9399356842041</v>
       </c>
       <c r="H259" t="n">
         <v>22787</v>
@@ -7938,7 +7938,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G261" t="n">
-        <v>8.38104343414307</v>
+        <v>8.38104438781738</v>
       </c>
       <c r="H261" t="n">
         <v>17570</v>
@@ -7967,7 +7967,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G262" t="n">
-        <v>8.41705131530762</v>
+        <v>8.41705226898193</v>
       </c>
       <c r="H262" t="n">
         <v>14117</v>
@@ -7996,7 +7996,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G263" t="n">
-        <v>8.54308414459229</v>
+        <v>8.54308223724365</v>
       </c>
       <c r="H263" t="n">
         <v>63169</v>
@@ -8025,7 +8025,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G264" t="n">
-        <v>8.34503555297852</v>
+        <v>8.34503364562988</v>
       </c>
       <c r="H264" t="n">
         <v>15973</v>
@@ -8112,7 +8112,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G267" t="n">
-        <v>8.19199657440186</v>
+        <v>8.19199848175049</v>
       </c>
       <c r="H267" t="n">
         <v>22967</v>
@@ -8141,7 +8141,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>8.21000194549561</v>
+        <v>8.21000099182129</v>
       </c>
       <c r="H268" t="n">
         <v>19678</v>
@@ -8170,7 +8170,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.19199657440186</v>
+        <v>8.19199848175049</v>
       </c>
       <c r="H269" t="n">
         <v>14531</v>
@@ -8199,7 +8199,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G270" t="n">
-        <v>8.30452632904053</v>
+        <v>8.30452537536621</v>
       </c>
       <c r="H270" t="n">
         <v>20634</v>
@@ -8257,7 +8257,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G272" t="n">
-        <v>8.29552364349365</v>
+        <v>8.29552268981934</v>
       </c>
       <c r="H272" t="n">
         <v>5173</v>
@@ -8286,7 +8286,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>8.29102230072021</v>
+        <v>8.2910213470459</v>
       </c>
       <c r="H273" t="n">
         <v>8840</v>
@@ -8344,7 +8344,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.34053516387939</v>
+        <v>8.34053421020508</v>
       </c>
       <c r="H275" t="n">
         <v>9669</v>
@@ -8402,7 +8402,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27301597595215</v>
+        <v>8.27301692962646</v>
       </c>
       <c r="H277" t="n">
         <v>8784</v>
@@ -8431,7 +8431,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>8.26851654052734</v>
+        <v>8.26851558685303</v>
       </c>
       <c r="H278" t="n">
         <v>7392</v>
@@ -8460,7 +8460,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>8.06596660614014</v>
+        <v>8.0659646987915</v>
       </c>
       <c r="H279" t="n">
         <v>8370</v>
@@ -8489,7 +8489,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.30452632904053</v>
+        <v>8.30452537536621</v>
       </c>
       <c r="H280" t="n">
         <v>12394</v>
@@ -8518,7 +8518,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G281" t="n">
-        <v>8.27301597595215</v>
+        <v>8.27301692962646</v>
       </c>
       <c r="H281" t="n">
         <v>2669</v>
@@ -8605,7 +8605,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>8.17399406433105</v>
+        <v>8.17399311065674</v>
       </c>
       <c r="H284" t="n">
         <v>11189</v>
@@ -8634,7 +8634,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G285" t="n">
-        <v>8.04346084594727</v>
+        <v>8.04345989227295</v>
       </c>
       <c r="H285" t="n">
         <v>7927</v>
@@ -8692,7 +8692,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>8.25051116943359</v>
+        <v>8.25051212310791</v>
       </c>
       <c r="H287" t="n">
         <v>7786</v>
@@ -8779,7 +8779,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G290" t="n">
-        <v>8.44855976104736</v>
+        <v>8.44856071472168</v>
       </c>
       <c r="H290" t="n">
         <v>15210</v>
@@ -8837,7 +8837,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G292" t="n">
-        <v>8.39004421234131</v>
+        <v>8.39004516601562</v>
       </c>
       <c r="H292" t="n">
         <v>8874</v>
@@ -8895,7 +8895,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>8.29102230072021</v>
+        <v>8.2910213470459</v>
       </c>
       <c r="H294" t="n">
         <v>1198</v>
@@ -8924,7 +8924,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G295" t="n">
-        <v>8.19649791717529</v>
+        <v>8.19649887084961</v>
       </c>
       <c r="H295" t="n">
         <v>6432</v>
@@ -9011,7 +9011,7 @@
         <v>9</v>
       </c>
       <c r="G298" t="n">
-        <v>8.101975440979</v>
+        <v>8.10197639465332</v>
       </c>
       <c r="H298" t="n">
         <v>13178</v>
@@ -9040,7 +9040,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>8.17399406433105</v>
+        <v>8.17399311065674</v>
       </c>
       <c r="H299" t="n">
         <v>8253</v>
@@ -9069,7 +9069,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G300" t="n">
-        <v>8.19199657440186</v>
+        <v>8.19199848175049</v>
       </c>
       <c r="H300" t="n">
         <v>4018</v>
@@ -9098,7 +9098,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G301" t="n">
-        <v>8.24601173400879</v>
+        <v>8.24600982666016</v>
       </c>
       <c r="H301" t="n">
         <v>3221</v>
@@ -9185,7 +9185,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.38104343414307</v>
+        <v>8.38104438781738</v>
       </c>
       <c r="H304" t="n">
         <v>8463</v>
@@ -9330,7 +9330,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>9.54232788085938</v>
+        <v>9.54232597351074</v>
       </c>
       <c r="H309" t="n">
         <v>74268</v>
@@ -9359,7 +9359,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G310" t="n">
-        <v>9.21824645996094</v>
+        <v>9.21824550628662</v>
       </c>
       <c r="H310" t="n">
         <v>329180</v>
@@ -9388,7 +9388,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>9.18223762512207</v>
+        <v>9.18223857879639</v>
       </c>
       <c r="H311" t="n">
         <v>148251</v>
@@ -9417,7 +9417,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G312" t="n">
-        <v>8.98419094085693</v>
+        <v>8.9841890335083</v>
       </c>
       <c r="H312" t="n">
         <v>187205</v>
@@ -9446,7 +9446,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G313" t="n">
-        <v>9.1282262802124</v>
+        <v>9.12822437286377</v>
       </c>
       <c r="H313" t="n">
         <v>92730</v>
@@ -9504,7 +9504,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>9.17323589324951</v>
+        <v>9.1732349395752</v>
       </c>
       <c r="H315" t="n">
         <v>33999</v>
@@ -9562,7 +9562,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G317" t="n">
-        <v>9.19124031066895</v>
+        <v>9.19124221801758</v>
       </c>
       <c r="H317" t="n">
         <v>89765</v>
@@ -9649,7 +9649,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>8.91217231750488</v>
+        <v>8.91217422485352</v>
       </c>
       <c r="H320" t="n">
         <v>33661</v>
@@ -9736,7 +9736,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G323" t="n">
-        <v>9.18223762512207</v>
+        <v>9.18223857879639</v>
       </c>
       <c r="H323" t="n">
         <v>28608</v>
@@ -9765,7 +9765,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>9.09221744537354</v>
+        <v>9.09221649169922</v>
       </c>
       <c r="H324" t="n">
         <v>60826</v>
@@ -9794,7 +9794,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>9.18223762512207</v>
+        <v>9.18223857879639</v>
       </c>
       <c r="H325" t="n">
         <v>31199</v>
@@ -9823,7 +9823,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>9.18223762512207</v>
+        <v>9.18223857879639</v>
       </c>
       <c r="H326" t="n">
         <v>9038</v>
@@ -9852,7 +9852,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G327" t="n">
-        <v>9.19124031066895</v>
+        <v>9.19124221801758</v>
       </c>
       <c r="H327" t="n">
         <v>18130</v>
@@ -9881,7 +9881,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G328" t="n">
-        <v>9.21824645996094</v>
+        <v>9.21824550628662</v>
       </c>
       <c r="H328" t="n">
         <v>33831</v>
@@ -9939,7 +9939,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G330" t="n">
-        <v>9.51532077789307</v>
+        <v>9.51531982421875</v>
       </c>
       <c r="H330" t="n">
         <v>28246</v>
@@ -9968,7 +9968,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>9.43430042266846</v>
+        <v>9.43429851531982</v>
       </c>
       <c r="H331" t="n">
         <v>20952</v>
@@ -9997,7 +9997,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>9.7673807144165</v>
+        <v>9.76738166809082</v>
       </c>
       <c r="H332" t="n">
         <v>47651</v>
@@ -10026,7 +10026,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>9.85740184783936</v>
+        <v>9.85740280151367</v>
       </c>
       <c r="H333" t="n">
         <v>33063</v>
@@ -10055,7 +10055,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G334" t="n">
-        <v>10.1724796295166</v>
+        <v>10.1724805831909</v>
       </c>
       <c r="H334" t="n">
         <v>69722</v>
@@ -10084,7 +10084,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>10.1724796295166</v>
+        <v>10.1724805831909</v>
       </c>
       <c r="H335" t="n">
         <v>42397</v>
@@ -10113,7 +10113,7 @@
         <v>11</v>
       </c>
       <c r="G336" t="n">
-        <v>9.90241622924805</v>
+        <v>9.90241432189941</v>
       </c>
       <c r="H336" t="n">
         <v>76445</v>
@@ -10142,7 +10142,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>10.4065389633179</v>
+        <v>10.4065361022949</v>
       </c>
       <c r="H337" t="n">
         <v>40167</v>
@@ -10171,7 +10171,7 @@
         <v>12</v>
       </c>
       <c r="G338" t="n">
-        <v>10.8026342391968</v>
+        <v>10.8026332855225</v>
       </c>
       <c r="H338" t="n">
         <v>30759</v>
@@ -10200,7 +10200,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G339" t="n">
-        <v>10.7666244506836</v>
+        <v>10.7666254043579</v>
       </c>
       <c r="H339" t="n">
         <v>28305</v>
@@ -10229,7 +10229,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G340" t="n">
-        <v>10.8656482696533</v>
+        <v>10.8656492233276</v>
       </c>
       <c r="H340" t="n">
         <v>22947</v>
@@ -10258,7 +10258,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>10.8926563262939</v>
+        <v>10.8926553726196</v>
       </c>
       <c r="H341" t="n">
         <v>28178</v>
@@ -10287,7 +10287,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G342" t="n">
-        <v>10.6946058273315</v>
+        <v>10.6946077346802</v>
       </c>
       <c r="H342" t="n">
         <v>25809</v>
@@ -10345,7 +10345,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>10.7126121520996</v>
+        <v>10.712610244751</v>
       </c>
       <c r="H344" t="n">
         <v>24005</v>
@@ -10374,7 +10374,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G345" t="n">
-        <v>10.4355611801147</v>
+        <v>10.4355621337891</v>
       </c>
       <c r="H345" t="n">
         <v>32972</v>
@@ -10403,7 +10403,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G346" t="n">
-        <v>10.1862163543701</v>
+        <v>10.1862154006958</v>
       </c>
       <c r="H346" t="n">
         <v>47367</v>
@@ -10432,7 +10432,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>9.97381019592285</v>
+        <v>9.97381114959717</v>
       </c>
       <c r="H347" t="n">
         <v>68068</v>
@@ -10490,7 +10490,7 @@
         <v>11.25</v>
       </c>
       <c r="G349" t="n">
-        <v>10.3893852233887</v>
+        <v>10.389386177063</v>
       </c>
       <c r="H349" t="n">
         <v>56227</v>
@@ -10519,7 +10519,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>10.4355611801147</v>
+        <v>10.4355621337891</v>
       </c>
       <c r="H350" t="n">
         <v>30035</v>
@@ -10548,7 +10548,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>10.4355611801147</v>
+        <v>10.4355621337891</v>
       </c>
       <c r="H351" t="n">
         <v>40215</v>
@@ -10577,7 +10577,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G352" t="n">
-        <v>10.2416276931763</v>
+        <v>10.241626739502</v>
       </c>
       <c r="H352" t="n">
         <v>127658</v>
@@ -10606,7 +10606,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G353" t="n">
-        <v>10.1862163543701</v>
+        <v>10.1862154006958</v>
       </c>
       <c r="H353" t="n">
         <v>59986</v>
@@ -10635,7 +10635,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G354" t="n">
-        <v>10.3616819381714</v>
+        <v>10.3616809844971</v>
       </c>
       <c r="H354" t="n">
         <v>31434</v>
@@ -10693,7 +10693,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G356" t="n">
-        <v>10.4725017547607</v>
+        <v>10.4725027084351</v>
       </c>
       <c r="H356" t="n">
         <v>48558</v>
@@ -10722,7 +10722,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G357" t="n">
-        <v>10.4725017547607</v>
+        <v>10.4725027084351</v>
       </c>
       <c r="H357" t="n">
         <v>24284</v>
@@ -10780,7 +10780,7 @@
         <v>11.25</v>
       </c>
       <c r="G359" t="n">
-        <v>10.3893852233887</v>
+        <v>10.389386177063</v>
       </c>
       <c r="H359" t="n">
         <v>34591</v>
@@ -10838,7 +10838,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G361" t="n">
-        <v>10.4355611801147</v>
+        <v>10.4355621337891</v>
       </c>
       <c r="H361" t="n">
         <v>51186</v>
@@ -10867,7 +10867,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G362" t="n">
-        <v>10.500205039978</v>
+        <v>10.5002059936523</v>
       </c>
       <c r="H362" t="n">
         <v>218070</v>
@@ -10896,7 +10896,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G363" t="n">
-        <v>10.7033758163452</v>
+        <v>10.7033777236938</v>
       </c>
       <c r="H363" t="n">
         <v>16441</v>
@@ -10954,7 +10954,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>11.728461265564</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H365" t="n">
         <v>70727</v>
@@ -11012,7 +11012,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>11.1743631362915</v>
+        <v>11.1743621826172</v>
       </c>
       <c r="H367" t="n">
         <v>25812</v>
@@ -11041,7 +11041,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>11.2574768066406</v>
+        <v>11.2574777603149</v>
       </c>
       <c r="H368" t="n">
         <v>10908</v>
@@ -11070,7 +11070,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G369" t="n">
-        <v>11.0543069839478</v>
+        <v>11.0543060302734</v>
       </c>
       <c r="H369" t="n">
         <v>23293</v>
@@ -11128,7 +11128,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G371" t="n">
-        <v>10.9896621704102</v>
+        <v>10.9896612167358</v>
       </c>
       <c r="H371" t="n">
         <v>8663</v>
@@ -11157,7 +11157,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G372" t="n">
-        <v>10.7864933013916</v>
+        <v>10.786491394043</v>
       </c>
       <c r="H372" t="n">
         <v>5170</v>
@@ -11186,7 +11186,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>10.7126121520996</v>
+        <v>10.7126131057739</v>
       </c>
       <c r="H373" t="n">
         <v>10682</v>
@@ -11215,7 +11215,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G374" t="n">
-        <v>10.6941423416138</v>
+        <v>10.6941413879395</v>
       </c>
       <c r="H374" t="n">
         <v>15214</v>
@@ -11244,7 +11244,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434871673584</v>
       </c>
       <c r="H375" t="n">
         <v>7306</v>
@@ -11273,7 +11273,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434871673584</v>
       </c>
       <c r="H376" t="n">
         <v>16228</v>
@@ -11302,7 +11302,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G377" t="n">
-        <v>10.823431968689</v>
+        <v>10.8234310150146</v>
       </c>
       <c r="H377" t="n">
         <v>6649</v>
@@ -11331,7 +11331,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434871673584</v>
       </c>
       <c r="H378" t="n">
         <v>19573</v>
@@ -11389,7 +11389,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G380" t="n">
-        <v>10.6941423416138</v>
+        <v>10.6941413879395</v>
       </c>
       <c r="H380" t="n">
         <v>9143</v>
@@ -11418,7 +11418,7 @@
         <v>12</v>
       </c>
       <c r="G381" t="n">
-        <v>11.0820140838623</v>
+        <v>11.0820121765137</v>
       </c>
       <c r="H381" t="n">
         <v>23532</v>
@@ -11505,7 +11505,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G384" t="n">
-        <v>11.0266017913818</v>
+        <v>11.0266008377075</v>
       </c>
       <c r="H384" t="n">
         <v>32520</v>
@@ -11563,7 +11563,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G386" t="n">
-        <v>11.4052381515503</v>
+        <v>11.405237197876</v>
       </c>
       <c r="H386" t="n">
         <v>24629</v>
@@ -11592,7 +11592,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>11.3590631484985</v>
+        <v>11.3590621948242</v>
       </c>
       <c r="H387" t="n">
         <v>23382</v>
@@ -11621,7 +11621,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G388" t="n">
-        <v>11.663818359375</v>
+        <v>11.6638174057007</v>
       </c>
       <c r="H388" t="n">
         <v>26892</v>
@@ -11650,7 +11650,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>12.0516881942749</v>
+        <v>12.0516872406006</v>
       </c>
       <c r="H389" t="n">
         <v>23206</v>
@@ -11737,7 +11737,7 @@
         <v>13.5</v>
       </c>
       <c r="G392" t="n">
-        <v>12.467264175415</v>
+        <v>12.4672632217407</v>
       </c>
       <c r="H392" t="n">
         <v>55837</v>
@@ -11766,7 +11766,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G393" t="n">
-        <v>12.4764966964722</v>
+        <v>12.4764986038208</v>
       </c>
       <c r="H393" t="n">
         <v>15976</v>
@@ -11824,7 +11824,7 @@
         <v>13.75</v>
       </c>
       <c r="G395" t="n">
-        <v>12.6981401443481</v>
+        <v>12.6981382369995</v>
       </c>
       <c r="H395" t="n">
         <v>26338</v>
@@ -11853,7 +11853,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G396" t="n">
-        <v>12.4857339859009</v>
+        <v>12.4857330322266</v>
       </c>
       <c r="H396" t="n">
         <v>20735</v>
@@ -11882,7 +11882,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G397" t="n">
-        <v>12.7443141937256</v>
+        <v>12.7443132400513</v>
       </c>
       <c r="H397" t="n">
         <v>74045</v>
@@ -11911,7 +11911,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G398" t="n">
-        <v>12.679669380188</v>
+        <v>12.6796674728394</v>
       </c>
       <c r="H398" t="n">
         <v>50702</v>
@@ -11940,7 +11940,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>12.494969367981</v>
+        <v>12.4949684143066</v>
       </c>
       <c r="H399" t="n">
         <v>185144</v>
@@ -11969,7 +11969,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G400" t="n">
-        <v>12.5319089889526</v>
+        <v>12.531907081604</v>
       </c>
       <c r="H400" t="n">
         <v>70356</v>
@@ -11998,7 +11998,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>12.5134382247925</v>
+        <v>12.5134372711182</v>
       </c>
       <c r="H401" t="n">
         <v>7478</v>
@@ -12056,7 +12056,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G403" t="n">
-        <v>12.4487943649292</v>
+        <v>12.4487934112549</v>
       </c>
       <c r="H403" t="n">
         <v>14247</v>
@@ -12114,7 +12114,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G405" t="n">
-        <v>12.494969367981</v>
+        <v>12.4949684143066</v>
       </c>
       <c r="H405" t="n">
         <v>56576</v>
@@ -12143,7 +12143,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G406" t="n">
-        <v>12.6334953308105</v>
+        <v>12.6334934234619</v>
       </c>
       <c r="H406" t="n">
         <v>44462</v>
@@ -12172,7 +12172,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G407" t="n">
-        <v>12.5780839920044</v>
+        <v>12.5780830383301</v>
       </c>
       <c r="H407" t="n">
         <v>4498</v>
@@ -12201,7 +12201,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G408" t="n">
-        <v>12.5042037963867</v>
+        <v>12.5042028427124</v>
       </c>
       <c r="H408" t="n">
         <v>9196</v>
@@ -12230,7 +12230,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G409" t="n">
-        <v>12.1348028182983</v>
+        <v>12.1348037719727</v>
       </c>
       <c r="H409" t="n">
         <v>22568</v>
@@ -12259,7 +12259,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G410" t="n">
-        <v>12.3472089767456</v>
+        <v>12.3472080230713</v>
       </c>
       <c r="H410" t="n">
         <v>16035</v>
@@ -12288,7 +12288,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749122619629</v>
       </c>
       <c r="H411" t="n">
         <v>12503</v>
@@ -12346,7 +12346,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G413" t="n">
-        <v>12.3195018768311</v>
+        <v>12.3195028305054</v>
       </c>
       <c r="H413" t="n">
         <v>44925</v>
@@ -12375,7 +12375,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>11.8392820358276</v>
+        <v>11.839282989502</v>
       </c>
       <c r="H414" t="n">
         <v>42777</v>
@@ -12462,7 +12462,7 @@
         <v>13</v>
       </c>
       <c r="G417" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055122375488</v>
       </c>
       <c r="H417" t="n">
         <v>13465</v>
@@ -12491,7 +12491,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>11.9039287567139</v>
+        <v>11.9039278030396</v>
       </c>
       <c r="H418" t="n">
         <v>14336</v>
@@ -12520,7 +12520,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2640933990479</v>
+        <v>12.2640924453735</v>
       </c>
       <c r="H419" t="n">
         <v>18396</v>
@@ -12549,7 +12549,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2179193496704</v>
+        <v>12.2179183959961</v>
       </c>
       <c r="H420" t="n">
         <v>7911</v>
@@ -12607,7 +12607,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>11.9131641387939</v>
+        <v>11.9131622314453</v>
       </c>
       <c r="H422" t="n">
         <v>19946</v>
@@ -12665,7 +12665,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G424" t="n">
-        <v>11.9039287567139</v>
+        <v>11.9039278030396</v>
       </c>
       <c r="H424" t="n">
         <v>24343</v>
@@ -12694,7 +12694,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="n">
-        <v>11.8392820358276</v>
+        <v>11.839282989502</v>
       </c>
       <c r="H425" t="n">
         <v>14551</v>
@@ -12723,7 +12723,7 @@
         <v>13</v>
       </c>
       <c r="G426" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055122375488</v>
       </c>
       <c r="H426" t="n">
         <v>22961</v>
@@ -12752,7 +12752,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749122619629</v>
       </c>
       <c r="H427" t="n">
         <v>25492</v>
@@ -12781,7 +12781,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749122619629</v>
       </c>
       <c r="H428" t="n">
         <v>12922</v>
@@ -12810,7 +12810,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>12.2825632095337</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H429" t="n">
         <v>7261</v>
@@ -12839,7 +12839,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G430" t="n">
-        <v>12.3933839797974</v>
+        <v>12.393383026123</v>
       </c>
       <c r="H430" t="n">
         <v>20268</v>
@@ -12868,7 +12868,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G431" t="n">
-        <v>12.3010330200195</v>
+        <v>12.3010339736938</v>
       </c>
       <c r="H431" t="n">
         <v>22331</v>
@@ -12955,7 +12955,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G434" t="n">
-        <v>12.1070966720581</v>
+        <v>12.1070976257324</v>
       </c>
       <c r="H434" t="n">
         <v>11138</v>
@@ -12984,7 +12984,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>12.2179193496704</v>
+        <v>12.2179183959961</v>
       </c>
       <c r="H435" t="n">
         <v>18844</v>
@@ -13042,7 +13042,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G437" t="n">
-        <v>12.1070966720581</v>
+        <v>12.1070976257324</v>
       </c>
       <c r="H437" t="n">
         <v>8285</v>
@@ -13071,7 +13071,7 @@
         <v>13</v>
       </c>
       <c r="G438" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055122375488</v>
       </c>
       <c r="H438" t="n">
         <v>9997</v>
@@ -13100,7 +13100,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G439" t="n">
-        <v>12.1994485855103</v>
+        <v>12.1994476318359</v>
       </c>
       <c r="H439" t="n">
         <v>14352</v>
@@ -13245,7 +13245,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G444" t="n">
-        <v>12.2825632095337</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H444" t="n">
         <v>13699</v>
@@ -13332,7 +13332,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G447" t="n">
-        <v>12.208683013916</v>
+        <v>12.2086839675903</v>
       </c>
       <c r="H447" t="n">
         <v>16520</v>
@@ -13477,7 +13477,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G452" t="n">
-        <v>11.9778079986572</v>
+        <v>11.9778089523315</v>
       </c>
       <c r="H452" t="n">
         <v>39521</v>
@@ -13622,7 +13622,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G457" t="n">
-        <v>11.6176433563232</v>
+        <v>11.6176414489746</v>
       </c>
       <c r="H457" t="n">
         <v>48293</v>
@@ -13651,7 +13651,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>11.6361122131348</v>
+        <v>11.6361131668091</v>
       </c>
       <c r="H458" t="n">
         <v>17232</v>
@@ -13680,7 +13680,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G459" t="n">
-        <v>11.7007579803467</v>
+        <v>11.7007570266724</v>
       </c>
       <c r="H459" t="n">
         <v>11056</v>
@@ -13709,7 +13709,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G460" t="n">
-        <v>11.8762216567993</v>
+        <v>11.8762226104736</v>
       </c>
       <c r="H460" t="n">
         <v>21524</v>
@@ -13767,7 +13767,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>11.663818359375</v>
+        <v>11.6638174057007</v>
       </c>
       <c r="H462" t="n">
         <v>23893</v>
@@ -13796,7 +13796,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G463" t="n">
-        <v>11.728461265564</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H463" t="n">
         <v>5575</v>
@@ -13825,7 +13825,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9131641387939</v>
+        <v>11.9131622314453</v>
       </c>
       <c r="H464" t="n">
         <v>21916</v>
@@ -13854,7 +13854,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>11.728461265564</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H465" t="n">
         <v>16388</v>
@@ -13883,7 +13883,7 @@
         <v>12.75</v>
       </c>
       <c r="G466" t="n">
-        <v>11.7746381759644</v>
+        <v>11.77463722229</v>
       </c>
       <c r="H466" t="n">
         <v>31358</v>
@@ -13912,7 +13912,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>11.8208141326904</v>
+        <v>11.8208122253418</v>
       </c>
       <c r="H467" t="n">
         <v>16468</v>
@@ -13970,7 +13970,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G469" t="n">
-        <v>11.8392820358276</v>
+        <v>11.839282989502</v>
       </c>
       <c r="H469" t="n">
         <v>27147</v>
@@ -13999,7 +13999,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G470" t="n">
-        <v>12.1809787750244</v>
+        <v>12.1809768676758</v>
       </c>
       <c r="H470" t="n">
         <v>16276</v>
@@ -14057,7 +14057,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G472" t="n">
-        <v>12.1809787750244</v>
+        <v>12.1809768676758</v>
       </c>
       <c r="H472" t="n">
         <v>16441</v>
@@ -14086,7 +14086,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>11.8208141326904</v>
+        <v>11.8208122253418</v>
       </c>
       <c r="H473" t="n">
         <v>43189</v>
@@ -14115,7 +14115,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>11.728461265564</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H474" t="n">
         <v>5286</v>
@@ -14260,7 +14260,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G479" t="n">
-        <v>11.6730527877808</v>
+        <v>11.6730537414551</v>
       </c>
       <c r="H479" t="n">
         <v>28724</v>
@@ -14318,7 +14318,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G481" t="n">
-        <v>11.146656036377</v>
+        <v>11.1466569900513</v>
       </c>
       <c r="H481" t="n">
         <v>60312</v>
@@ -14347,7 +14347,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G482" t="n">
-        <v>11.2482433319092</v>
+        <v>11.2482423782349</v>
       </c>
       <c r="H482" t="n">
         <v>15513</v>
@@ -14376,7 +14376,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G483" t="n">
-        <v>11.146656036377</v>
+        <v>11.1466569900513</v>
       </c>
       <c r="H483" t="n">
         <v>11357</v>
@@ -14434,7 +14434,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>11.4975891113281</v>
+        <v>11.4975872039795</v>
       </c>
       <c r="H485" t="n">
         <v>26166</v>
@@ -14492,7 +14492,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G487" t="n">
-        <v>11.4237070083618</v>
+        <v>11.4237079620361</v>
       </c>
       <c r="H487" t="n">
         <v>10474</v>
@@ -14550,7 +14550,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G489" t="n">
-        <v>11.4052381515503</v>
+        <v>11.405237197876</v>
       </c>
       <c r="H489" t="n">
         <v>17083</v>
@@ -14608,7 +14608,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>11.4052381515503</v>
+        <v>11.405237197876</v>
       </c>
       <c r="H491" t="n">
         <v>13738</v>
@@ -14637,7 +14637,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G492" t="n">
-        <v>11.5345258712769</v>
+        <v>11.5345277786255</v>
       </c>
       <c r="H492" t="n">
         <v>4712</v>
@@ -14695,7 +14695,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>11.4514102935791</v>
+        <v>11.4514122009277</v>
       </c>
       <c r="H494" t="n">
         <v>21701</v>
@@ -14724,7 +14724,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>11.4514102935791</v>
+        <v>11.4514122009277</v>
       </c>
       <c r="H495" t="n">
         <v>33685</v>
@@ -14753,7 +14753,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.626877784729</v>
+        <v>11.6268768310547</v>
       </c>
       <c r="H496" t="n">
         <v>27293</v>
@@ -14811,7 +14811,7 @@
         <v>12.75</v>
       </c>
       <c r="G498" t="n">
-        <v>11.7746381759644</v>
+        <v>11.77463722229</v>
       </c>
       <c r="H498" t="n">
         <v>24024</v>
@@ -14840,7 +14840,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.8208141326904</v>
+        <v>11.8208122253418</v>
       </c>
       <c r="H499" t="n">
         <v>27307</v>
@@ -14869,7 +14869,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.0978651046753</v>
+        <v>12.0978622436523</v>
       </c>
       <c r="H500" t="n">
         <v>48615</v>
@@ -14898,7 +14898,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.9593381881714</v>
+        <v>11.9593362808228</v>
       </c>
       <c r="H501" t="n">
         <v>18010</v>
@@ -14927,7 +14927,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>11.8669891357422</v>
+        <v>11.8669881820679</v>
       </c>
       <c r="H502" t="n">
         <v>9279</v>
@@ -14956,7 +14956,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G503" t="n">
-        <v>11.6730527877808</v>
+        <v>11.6730537414551</v>
       </c>
       <c r="H503" t="n">
         <v>39087</v>
@@ -14985,7 +14985,7 @@
         <v>13</v>
       </c>
       <c r="G504" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055122375488</v>
       </c>
       <c r="H504" t="n">
         <v>38999</v>
@@ -15014,7 +15014,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>12.0978651046753</v>
+        <v>12.0978622436523</v>
       </c>
       <c r="H505" t="n">
         <v>24572</v>
@@ -15072,7 +15072,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G507" t="n">
-        <v>12.3195018768311</v>
+        <v>12.3195028305054</v>
       </c>
       <c r="H507" t="n">
         <v>28342</v>
@@ -15101,7 +15101,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G508" t="n">
-        <v>12.208683013916</v>
+        <v>12.2086839675903</v>
       </c>
       <c r="H508" t="n">
         <v>32115</v>
@@ -15130,7 +15130,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749122619629</v>
       </c>
       <c r="H509" t="n">
         <v>18412</v>
@@ -15159,7 +15159,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G510" t="n">
-        <v>12.3933839797974</v>
+        <v>12.393383026123</v>
       </c>
       <c r="H510" t="n">
         <v>18903</v>
@@ -15246,7 +15246,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G513" t="n">
-        <v>12.3933839797974</v>
+        <v>12.393383026123</v>
       </c>
       <c r="H513" t="n">
         <v>12459</v>
@@ -15275,7 +15275,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749122619629</v>
       </c>
       <c r="H514" t="n">
         <v>80026</v>
@@ -15304,7 +15304,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G515" t="n">
-        <v>12.3933839797974</v>
+        <v>12.393383026123</v>
       </c>
       <c r="H515" t="n">
         <v>29210</v>
@@ -15333,7 +15333,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G516" t="n">
-        <v>12.4487943649292</v>
+        <v>12.4487934112549</v>
       </c>
       <c r="H516" t="n">
         <v>69930</v>
@@ -15362,7 +15362,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G517" t="n">
-        <v>12.8736028671265</v>
+        <v>12.8736047744751</v>
       </c>
       <c r="H517" t="n">
         <v>87834</v>
@@ -15420,7 +15420,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G519" t="n">
-        <v>14.0556840896606</v>
+        <v>14.0556859970093</v>
       </c>
       <c r="H519" t="n">
         <v>45100</v>
@@ -15565,7 +15565,7 @@
         <v>15</v>
       </c>
       <c r="G524" t="n">
-        <v>13.8525152206421</v>
+        <v>13.8525161743164</v>
       </c>
       <c r="H524" t="n">
         <v>75282</v>
@@ -15594,7 +15594,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>13.5754642486572</v>
+        <v>13.5754652023315</v>
       </c>
       <c r="H525" t="n">
         <v>37038</v>
@@ -15652,7 +15652,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G527" t="n">
-        <v>13.9633350372314</v>
+        <v>13.9633359909058</v>
       </c>
       <c r="H527" t="n">
         <v>14884</v>
@@ -15681,7 +15681,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G528" t="n">
-        <v>13.6493453979492</v>
+        <v>13.6493444442749</v>
       </c>
       <c r="H528" t="n">
         <v>10284</v>
@@ -15739,7 +15739,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G530" t="n">
-        <v>14.3327360153198</v>
+        <v>14.3327369689941</v>
       </c>
       <c r="H530" t="n">
         <v>29090</v>
@@ -15797,7 +15797,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G532" t="n">
-        <v>14.5174360275269</v>
+        <v>14.5174369812012</v>
       </c>
       <c r="H532" t="n">
         <v>46991</v>
@@ -15855,7 +15855,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G534" t="n">
-        <v>14.129566192627</v>
+        <v>14.1295652389526</v>
       </c>
       <c r="H534" t="n">
         <v>14128</v>
@@ -15884,7 +15884,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G535" t="n">
-        <v>13.7786340713501</v>
+        <v>13.7786350250244</v>
       </c>
       <c r="H535" t="n">
         <v>23026</v>
@@ -15942,7 +15942,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G537" t="n">
-        <v>12.7258443832397</v>
+        <v>12.7258424758911</v>
       </c>
       <c r="H537" t="n">
         <v>27066</v>
@@ -15971,7 +15971,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G538" t="n">
-        <v>13.5754642486572</v>
+        <v>13.5754652023315</v>
       </c>
       <c r="H538" t="n">
         <v>21793</v>
@@ -16000,7 +16000,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G539" t="n">
-        <v>13.3168859481812</v>
+        <v>13.3168840408325</v>
       </c>
       <c r="H539" t="n">
         <v>11506</v>
@@ -16058,7 +16058,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>12.6889028549194</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H541" t="n">
         <v>21971</v>
@@ -16116,7 +16116,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G543" t="n">
-        <v>12.5042037963867</v>
+        <v>12.5042028427124</v>
       </c>
       <c r="H543" t="n">
         <v>10554</v>
@@ -16145,7 +16145,7 @@
         <v>14</v>
       </c>
       <c r="G544" t="n">
-        <v>12.9290151596069</v>
+        <v>12.9290142059326</v>
       </c>
       <c r="H544" t="n">
         <v>18798</v>
@@ -16174,7 +16174,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G545" t="n">
-        <v>13.4646444320679</v>
+        <v>13.4646434783936</v>
       </c>
       <c r="H545" t="n">
         <v>14684</v>
@@ -16203,7 +16203,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G546" t="n">
-        <v>13.2614736557007</v>
+        <v>13.2614755630493</v>
       </c>
       <c r="H546" t="n">
         <v>24512</v>
@@ -16232,7 +16232,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G547" t="n">
-        <v>12.6889028549194</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H547" t="n">
         <v>11775</v>
@@ -16261,7 +16261,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>12.6889028549194</v>
+        <v>12.6889038085938</v>
       </c>
       <c r="H548" t="n">
         <v>8538</v>
@@ -16348,7 +16348,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749122619629</v>
       </c>
       <c r="H551" t="n">
         <v>17368</v>
@@ -16406,7 +16406,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>11.9685716629028</v>
+        <v>11.9685735702515</v>
       </c>
       <c r="H553" t="n">
         <v>21116</v>
@@ -16435,7 +16435,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>11.728461265564</v>
+        <v>11.7284622192383</v>
       </c>
       <c r="H554" t="n">
         <v>19343</v>
@@ -16464,7 +16464,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G555" t="n">
-        <v>11.7838726043701</v>
+        <v>11.7838735580444</v>
       </c>
       <c r="H555" t="n">
         <v>14724</v>
@@ -16522,7 +16522,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>12.3749132156372</v>
+        <v>12.3749122619629</v>
       </c>
       <c r="H557" t="n">
         <v>13670</v>
@@ -16551,7 +16551,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G558" t="n">
-        <v>12.5042037963867</v>
+        <v>12.5042028427124</v>
       </c>
       <c r="H558" t="n">
         <v>25228</v>
@@ -16609,7 +16609,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G560" t="n">
-        <v>12.6704339981079</v>
+        <v>12.6704330444336</v>
       </c>
       <c r="H560" t="n">
         <v>5777</v>
@@ -16638,7 +16638,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>12.5596132278442</v>
+        <v>12.5596122741699</v>
       </c>
       <c r="H561" t="n">
         <v>12666</v>
@@ -16667,7 +16667,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G562" t="n">
-        <v>12.1163330078125</v>
+        <v>12.1163339614868</v>
       </c>
       <c r="H562" t="n">
         <v>18462</v>
@@ -16696,7 +16696,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>12.0978651046753</v>
+        <v>12.0978622436523</v>
       </c>
       <c r="H563" t="n">
         <v>13377</v>
@@ -16725,7 +16725,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>12.1163330078125</v>
+        <v>12.1163339614868</v>
       </c>
       <c r="H564" t="n">
         <v>6338</v>
@@ -16754,7 +16754,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>11.9870433807373</v>
+        <v>11.9870405197144</v>
       </c>
       <c r="H565" t="n">
         <v>22210</v>
@@ -16783,7 +16783,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>12.2825632095337</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H566" t="n">
         <v>6247</v>
@@ -16841,7 +16841,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G568" t="n">
-        <v>12.023983001709</v>
+        <v>12.0239839553833</v>
       </c>
       <c r="H568" t="n">
         <v>6599</v>
@@ -16870,7 +16870,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G569" t="n">
-        <v>11.8762216567993</v>
+        <v>11.8762226104736</v>
       </c>
       <c r="H569" t="n">
         <v>17683</v>
@@ -16899,7 +16899,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G570" t="n">
-        <v>11.5622329711914</v>
+        <v>11.5622339248657</v>
       </c>
       <c r="H570" t="n">
         <v>22685</v>
@@ -16928,7 +16928,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G571" t="n">
-        <v>11.9685716629028</v>
+        <v>11.9685735702515</v>
       </c>
       <c r="H571" t="n">
         <v>25351</v>
@@ -16957,7 +16957,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>12.7443141937256</v>
+        <v>12.7443132400513</v>
       </c>
       <c r="H572" t="n">
         <v>37029</v>
@@ -17044,7 +17044,7 @@
         <v>13</v>
       </c>
       <c r="G575" t="n">
-        <v>12.0055131912231</v>
+        <v>12.0055122375488</v>
       </c>
       <c r="H575" t="n">
         <v>21274</v>
@@ -17073,7 +17073,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G576" t="n">
-        <v>11.9685716629028</v>
+        <v>11.9685735702515</v>
       </c>
       <c r="H576" t="n">
         <v>20913</v>
@@ -17102,7 +17102,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>11.7654027938843</v>
+        <v>11.76540184021</v>
       </c>
       <c r="H577" t="n">
         <v>20787</v>
@@ -17131,7 +17131,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G578" t="n">
-        <v>11.9685716629028</v>
+        <v>11.9685735702515</v>
       </c>
       <c r="H578" t="n">
         <v>19393</v>
@@ -17160,7 +17160,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G579" t="n">
-        <v>11.8023414611816</v>
+        <v>11.8023433685303</v>
       </c>
       <c r="H579" t="n">
         <v>14168</v>
@@ -17189,7 +17189,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G580" t="n">
-        <v>12.2825632095337</v>
+        <v>12.282564163208</v>
       </c>
       <c r="H580" t="n">
         <v>57823</v>
@@ -17247,7 +17247,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G582" t="n">
-        <v>12.208683013916</v>
+        <v>12.2086839675903</v>
       </c>
       <c r="H582" t="n">
         <v>7756</v>
@@ -17305,7 +17305,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G584" t="n">
-        <v>12.208683013916</v>
+        <v>12.2086839675903</v>
       </c>
       <c r="H584" t="n">
         <v>25244</v>
@@ -17334,7 +17334,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>12.3379726409912</v>
+        <v>12.3379735946655</v>
       </c>
       <c r="H585" t="n">
         <v>19013</v>
@@ -17363,7 +17363,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>13.298415184021</v>
+        <v>13.2984142303467</v>
       </c>
       <c r="H586" t="n">
         <v>55430</v>
@@ -17392,7 +17392,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>13.483115196228</v>
+        <v>13.4831161499023</v>
       </c>
       <c r="H587" t="n">
         <v>33546</v>
@@ -17421,7 +17421,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>13.6678171157837</v>
+        <v>13.6678152084351</v>
       </c>
       <c r="H588" t="n">
         <v>31315</v>
@@ -17450,7 +17450,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G589" t="n">
-        <v>14.2034463882446</v>
+        <v>14.2034473419189</v>
       </c>
       <c r="H589" t="n">
         <v>26324</v>
@@ -17508,7 +17508,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G591" t="n">
-        <v>14.7206058502197</v>
+        <v>14.720606803894</v>
       </c>
       <c r="H591" t="n">
         <v>36292</v>
@@ -17595,7 +17595,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649620056152</v>
       </c>
       <c r="H594" t="n">
         <v>15207</v>
@@ -17624,7 +17624,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>15.623797416687</v>
+        <v>15.6237964630127</v>
       </c>
       <c r="H595" t="n">
         <v>102934</v>
@@ -17653,7 +17653,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>15.3414373397827</v>
+        <v>15.3414392471313</v>
       </c>
       <c r="H596" t="n">
         <v>47839</v>
@@ -17682,7 +17682,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G597" t="n">
-        <v>15.172025680542</v>
+        <v>15.1720237731934</v>
       </c>
       <c r="H597" t="n">
         <v>26908</v>
@@ -17740,7 +17740,7 @@
         <v>16</v>
       </c>
       <c r="G599" t="n">
-        <v>15.0590810775757</v>
+        <v>15.0590801239014</v>
       </c>
       <c r="H599" t="n">
         <v>46326</v>
@@ -17798,7 +17798,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>15.2473211288452</v>
+        <v>15.2473201751709</v>
       </c>
       <c r="H601" t="n">
         <v>40267</v>
@@ -17856,7 +17856,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G603" t="n">
-        <v>14.0802402496338</v>
+        <v>14.0802412033081</v>
       </c>
       <c r="H603" t="n">
         <v>175945</v>
@@ -17885,7 +17885,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G604" t="n">
-        <v>13.7602338790894</v>
+        <v>13.7602348327637</v>
       </c>
       <c r="H604" t="n">
         <v>57883</v>
@@ -17914,7 +17914,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G605" t="n">
-        <v>13.2143430709839</v>
+        <v>13.2143440246582</v>
       </c>
       <c r="H605" t="n">
         <v>62638</v>
@@ -17943,7 +17943,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>13.5531740188599</v>
+        <v>13.5531721115112</v>
       </c>
       <c r="H606" t="n">
         <v>42396</v>
@@ -17972,7 +17972,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G607" t="n">
-        <v>13.6284685134888</v>
+        <v>13.6284675598145</v>
       </c>
       <c r="H607" t="n">
         <v>45154</v>
@@ -18001,7 +18001,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>13.0261058807373</v>
+        <v>13.0261068344116</v>
       </c>
       <c r="H608" t="n">
         <v>41804</v>
@@ -18030,7 +18030,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G609" t="n">
-        <v>13.2143430709839</v>
+        <v>13.2143440246582</v>
       </c>
       <c r="H609" t="n">
         <v>27949</v>
@@ -18088,7 +18088,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.0637540817261</v>
+        <v>13.0637531280518</v>
       </c>
       <c r="H611" t="n">
         <v>44606</v>
@@ -18117,7 +18117,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G612" t="n">
-        <v>13.0261058807373</v>
+        <v>13.0261068344116</v>
       </c>
       <c r="H612" t="n">
         <v>45688</v>
@@ -18175,7 +18175,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>12.0472660064697</v>
+        <v>12.0472650527954</v>
       </c>
       <c r="H614" t="n">
         <v>91627</v>
@@ -18262,7 +18262,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G617" t="n">
-        <v>12.9508085250854</v>
+        <v>12.9508113861084</v>
       </c>
       <c r="H617" t="n">
         <v>38860</v>
@@ -18291,7 +18291,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G618" t="n">
-        <v>12.5743341445923</v>
+        <v>12.5743322372437</v>
       </c>
       <c r="H618" t="n">
         <v>31911</v>
@@ -18320,7 +18320,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G619" t="n">
-        <v>12.6496267318726</v>
+        <v>12.6496276855469</v>
       </c>
       <c r="H619" t="n">
         <v>73351</v>
@@ -18349,7 +18349,7 @@
         <v>13.5</v>
       </c>
       <c r="G620" t="n">
-        <v>12.7061014175415</v>
+        <v>12.7060985565186</v>
       </c>
       <c r="H620" t="n">
         <v>85525</v>
@@ -18378,7 +18378,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G621" t="n">
-        <v>12.8190422058105</v>
+        <v>12.8190431594849</v>
       </c>
       <c r="H621" t="n">
         <v>49263</v>
@@ -18436,7 +18436,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G623" t="n">
-        <v>12.6872749328613</v>
+        <v>12.6872758865356</v>
       </c>
       <c r="H623" t="n">
         <v>41237</v>
@@ -18465,7 +18465,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G624" t="n">
-        <v>12.6684513092041</v>
+        <v>12.6684522628784</v>
       </c>
       <c r="H624" t="n">
         <v>29434</v>
@@ -18494,7 +18494,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6496267318726</v>
+        <v>12.6496276855469</v>
       </c>
       <c r="H625" t="n">
         <v>23975</v>
@@ -18523,7 +18523,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>12.7249250411987</v>
+        <v>12.7249240875244</v>
       </c>
       <c r="H626" t="n">
         <v>28431</v>
@@ -18552,7 +18552,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G627" t="n">
-        <v>12.2166805267334</v>
+        <v>12.2166786193848</v>
       </c>
       <c r="H627" t="n">
         <v>311770</v>
@@ -18610,7 +18610,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G629" t="n">
-        <v>13.7225894927979</v>
+        <v>13.7225866317749</v>
       </c>
       <c r="H629" t="n">
         <v>75182</v>
@@ -18639,7 +18639,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G630" t="n">
-        <v>13.9108266830444</v>
+        <v>13.9108257293701</v>
       </c>
       <c r="H630" t="n">
         <v>15587</v>
@@ -18668,7 +18668,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G631" t="n">
-        <v>13.8167085647583</v>
+        <v>13.8167057037354</v>
       </c>
       <c r="H631" t="n">
         <v>29243</v>
@@ -18784,7 +18784,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G635" t="n">
-        <v>13.5343494415283</v>
+        <v>13.534348487854</v>
       </c>
       <c r="H635" t="n">
         <v>66702</v>
@@ -18813,7 +18813,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>13.364935874939</v>
+        <v>13.3649349212646</v>
       </c>
       <c r="H636" t="n">
         <v>25417</v>
@@ -18871,7 +18871,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G638" t="n">
-        <v>13.3837594985962</v>
+        <v>13.3837585449219</v>
       </c>
       <c r="H638" t="n">
         <v>2400</v>
@@ -18958,7 +18958,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>13.2708148956299</v>
+        <v>13.2708158493042</v>
       </c>
       <c r="H641" t="n">
         <v>8690</v>
@@ -19045,7 +19045,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>13.2708148956299</v>
+        <v>13.2708158493042</v>
       </c>
       <c r="H644" t="n">
         <v>8275</v>
@@ -19074,7 +19074,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G645" t="n">
-        <v>12.6684513092041</v>
+        <v>12.6684522628784</v>
       </c>
       <c r="H645" t="n">
         <v>27011</v>
@@ -19219,7 +19219,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>12.8190422058105</v>
+        <v>12.8190431594849</v>
       </c>
       <c r="H650" t="n">
         <v>28895</v>
@@ -19248,7 +19248,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G651" t="n">
-        <v>12.6684513092041</v>
+        <v>12.6684522628784</v>
       </c>
       <c r="H651" t="n">
         <v>7188</v>
@@ -19277,7 +19277,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G652" t="n">
-        <v>13.0261058807373</v>
+        <v>13.0261068344116</v>
       </c>
       <c r="H652" t="n">
         <v>7630</v>
@@ -19393,7 +19393,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G656" t="n">
-        <v>12.6496267318726</v>
+        <v>12.6496276855469</v>
       </c>
       <c r="H656" t="n">
         <v>25434</v>
@@ -19451,7 +19451,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>12.9884576797485</v>
+        <v>12.9884586334229</v>
       </c>
       <c r="H658" t="n">
         <v>15739</v>
@@ -19480,7 +19480,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9319849014282</v>
+        <v>12.9319868087769</v>
       </c>
       <c r="H659" t="n">
         <v>5202</v>
@@ -19567,7 +19567,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G662" t="n">
-        <v>12.7625713348389</v>
+        <v>12.7625722885132</v>
       </c>
       <c r="H662" t="n">
         <v>24223</v>
@@ -19596,7 +19596,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G663" t="n">
-        <v>12.9508085250854</v>
+        <v>12.9508113861084</v>
       </c>
       <c r="H663" t="n">
         <v>14666</v>
@@ -19625,7 +19625,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8190422058105</v>
+        <v>12.8190431594849</v>
       </c>
       <c r="H664" t="n">
         <v>9694</v>
@@ -19799,7 +19799,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G670" t="n">
-        <v>12.7249250411987</v>
+        <v>12.7249240875244</v>
       </c>
       <c r="H670" t="n">
         <v>33982</v>
@@ -19857,7 +19857,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G672" t="n">
-        <v>12.9319849014282</v>
+        <v>12.9319868087769</v>
       </c>
       <c r="H672" t="n">
         <v>10426</v>
@@ -19886,7 +19886,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G673" t="n">
-        <v>13.5343494415283</v>
+        <v>13.534348487854</v>
       </c>
       <c r="H673" t="n">
         <v>25749</v>
@@ -19915,7 +19915,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>13.7414112091064</v>
+        <v>13.7414131164551</v>
       </c>
       <c r="H674" t="n">
         <v>12363</v>
@@ -19973,7 +19973,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>14.2120084762573</v>
+        <v>14.212007522583</v>
       </c>
       <c r="H676" t="n">
         <v>32860</v>
@@ -20002,7 +20002,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G677" t="n">
-        <v>14.2496566772461</v>
+        <v>14.2496557235718</v>
       </c>
       <c r="H677" t="n">
         <v>8698</v>
@@ -20031,7 +20031,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G678" t="n">
-        <v>14.0049467086792</v>
+        <v>14.0049457550049</v>
       </c>
       <c r="H678" t="n">
         <v>21151</v>
@@ -20060,7 +20060,7 @@
         <v>14.5</v>
       </c>
       <c r="G679" t="n">
-        <v>13.6472940444946</v>
+        <v>13.6472911834717</v>
       </c>
       <c r="H679" t="n">
         <v>14249</v>
@@ -20089,7 +20089,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G680" t="n">
-        <v>13.6284685134888</v>
+        <v>13.6284675598145</v>
       </c>
       <c r="H680" t="n">
         <v>10072</v>
@@ -20118,7 +20118,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G681" t="n">
-        <v>13.4402294158936</v>
+        <v>13.4402303695679</v>
       </c>
       <c r="H681" t="n">
         <v>17611</v>
@@ -20147,7 +20147,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G682" t="n">
-        <v>13.703763961792</v>
+        <v>13.7037658691406</v>
       </c>
       <c r="H682" t="n">
         <v>1334</v>
@@ -20292,7 +20292,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G687" t="n">
-        <v>14.2120084762573</v>
+        <v>14.212007522583</v>
       </c>
       <c r="H687" t="n">
         <v>55840</v>
@@ -20321,7 +20321,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>14.2120084762573</v>
+        <v>14.212007522583</v>
       </c>
       <c r="H688" t="n">
         <v>27758</v>
@@ -20350,7 +20350,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>14.8708448410034</v>
+        <v>14.8708429336548</v>
       </c>
       <c r="H689" t="n">
         <v>112456</v>
@@ -20408,7 +20408,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G691" t="n">
-        <v>15.2096710205078</v>
+        <v>15.2096729278564</v>
       </c>
       <c r="H691" t="n">
         <v>16469</v>
@@ -20466,7 +20466,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>15.3414373397827</v>
+        <v>15.3414392471313</v>
       </c>
       <c r="H693" t="n">
         <v>19626</v>
@@ -20495,7 +20495,7 @@
         <v>17.5</v>
       </c>
       <c r="G694" t="n">
-        <v>16.4708671569824</v>
+        <v>16.4708690643311</v>
       </c>
       <c r="H694" t="n">
         <v>116774</v>
@@ -20524,7 +20524,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G695" t="n">
-        <v>16.6402835845947</v>
+        <v>16.6402854919434</v>
       </c>
       <c r="H695" t="n">
         <v>37330</v>
@@ -20582,7 +20582,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>16.5649890899658</v>
+        <v>16.5649929046631</v>
       </c>
       <c r="H697" t="n">
         <v>14328</v>
@@ -20611,7 +20611,7 @@
         <v>17.5</v>
       </c>
       <c r="G698" t="n">
-        <v>16.4708671569824</v>
+        <v>16.4708690643311</v>
       </c>
       <c r="H698" t="n">
         <v>15387</v>
@@ -20640,7 +20640,7 @@
         <v>17.5</v>
       </c>
       <c r="G699" t="n">
-        <v>16.4708671569824</v>
+        <v>16.4708690643311</v>
       </c>
       <c r="H699" t="n">
         <v>15872</v>
@@ -20727,7 +20727,7 @@
         <v>16.5</v>
       </c>
       <c r="G702" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296783447266</v>
       </c>
       <c r="H702" t="n">
         <v>24760</v>
@@ -20756,7 +20756,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G703" t="n">
-        <v>15.2096710205078</v>
+        <v>15.2096729278564</v>
       </c>
       <c r="H703" t="n">
         <v>38409</v>
@@ -20785,7 +20785,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G704" t="n">
-        <v>15.172025680542</v>
+        <v>15.1720237731934</v>
       </c>
       <c r="H704" t="n">
         <v>22796</v>
@@ -20814,7 +20814,7 @@
         <v>16.5</v>
       </c>
       <c r="G705" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296783447266</v>
       </c>
       <c r="H705" t="n">
         <v>33314</v>
@@ -20843,7 +20843,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G706" t="n">
-        <v>15.4543828964233</v>
+        <v>15.4543800354004</v>
       </c>
       <c r="H706" t="n">
         <v>12028</v>
@@ -20872,7 +20872,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9461374282837</v>
+        <v>14.946138381958</v>
       </c>
       <c r="H707" t="n">
         <v>35782</v>
@@ -20901,7 +20901,7 @@
         <v>16</v>
       </c>
       <c r="G708" t="n">
-        <v>15.0590810775757</v>
+        <v>15.0590801239014</v>
       </c>
       <c r="H708" t="n">
         <v>69525</v>
@@ -20930,7 +20930,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G709" t="n">
-        <v>15.1532020568848</v>
+        <v>15.1532011032104</v>
       </c>
       <c r="H709" t="n">
         <v>222278</v>
@@ -20988,7 +20988,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G711" t="n">
-        <v>14.5508365631104</v>
+        <v>14.5508375167847</v>
       </c>
       <c r="H711" t="n">
         <v>35122</v>
@@ -21017,7 +21017,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G712" t="n">
-        <v>14.3814220428467</v>
+        <v>14.381422996521</v>
       </c>
       <c r="H712" t="n">
         <v>33810</v>
@@ -21046,7 +21046,7 @@
         <v>15.5</v>
       </c>
       <c r="G713" t="n">
-        <v>14.5884866714478</v>
+        <v>14.5884838104248</v>
       </c>
       <c r="H713" t="n">
         <v>18411</v>
@@ -21075,7 +21075,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>14.2496566772461</v>
+        <v>14.2496557235718</v>
       </c>
       <c r="H714" t="n">
         <v>11216</v>
@@ -21133,7 +21133,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G716" t="n">
-        <v>14.1367120742798</v>
+        <v>14.1367139816284</v>
       </c>
       <c r="H716" t="n">
         <v>38539</v>
@@ -21162,7 +21162,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G717" t="n">
-        <v>14.1367120742798</v>
+        <v>14.1367139816284</v>
       </c>
       <c r="H717" t="n">
         <v>19320</v>
@@ -21220,7 +21220,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G719" t="n">
-        <v>13.4778776168823</v>
+        <v>13.4778757095337</v>
       </c>
       <c r="H719" t="n">
         <v>15534</v>
@@ -21249,7 +21249,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G720" t="n">
-        <v>13.4402294158936</v>
+        <v>13.4402303695679</v>
       </c>
       <c r="H720" t="n">
         <v>34866</v>
@@ -21307,7 +21307,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G722" t="n">
-        <v>13.7978820800781</v>
+        <v>13.7978849411011</v>
       </c>
       <c r="H722" t="n">
         <v>8577</v>
@@ -21336,7 +21336,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>13.9672975540161</v>
+        <v>13.9672985076904</v>
       </c>
       <c r="H723" t="n">
         <v>9349</v>
@@ -21365,7 +21365,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G724" t="n">
-        <v>14.8143711090088</v>
+        <v>14.8143720626831</v>
       </c>
       <c r="H724" t="n">
         <v>44298</v>
@@ -21394,7 +21394,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G725" t="n">
-        <v>14.4190692901611</v>
+        <v>14.4190702438354</v>
       </c>
       <c r="H725" t="n">
         <v>35787</v>
@@ -21423,7 +21423,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>14.3625974655151</v>
+        <v>14.3625993728638</v>
       </c>
       <c r="H726" t="n">
         <v>40002</v>
@@ -21452,7 +21452,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649620056152</v>
       </c>
       <c r="H727" t="n">
         <v>129841</v>
@@ -21481,7 +21481,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649620056152</v>
       </c>
       <c r="H728" t="n">
         <v>20384</v>
@@ -21510,7 +21510,7 @@
         <v>16.5</v>
       </c>
       <c r="G729" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296783447266</v>
       </c>
       <c r="H729" t="n">
         <v>18316</v>
@@ -21539,7 +21539,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>15.3414373397827</v>
+        <v>15.3414392471313</v>
       </c>
       <c r="H730" t="n">
         <v>15618</v>
@@ -21568,7 +21568,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G731" t="n">
-        <v>15.4920291900635</v>
+        <v>15.4920282363892</v>
       </c>
       <c r="H731" t="n">
         <v>7238</v>
@@ -21597,7 +21597,7 @@
         <v>16</v>
       </c>
       <c r="G732" t="n">
-        <v>15.0590810775757</v>
+        <v>15.0590801239014</v>
       </c>
       <c r="H732" t="n">
         <v>26438</v>
@@ -21626,7 +21626,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G733" t="n">
-        <v>14.9084901809692</v>
+        <v>14.9084911346436</v>
       </c>
       <c r="H733" t="n">
         <v>25096</v>
@@ -21655,7 +21655,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G734" t="n">
-        <v>16.0190963745117</v>
+        <v>16.0190982818604</v>
       </c>
       <c r="H734" t="n">
         <v>84149</v>
@@ -21684,7 +21684,7 @@
         <v>17</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0002765655518</v>
+        <v>16.0002727508545</v>
       </c>
       <c r="H735" t="n">
         <v>51687</v>
@@ -21742,7 +21742,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G737" t="n">
-        <v>15.9814510345459</v>
+        <v>15.9814491271973</v>
       </c>
       <c r="H737" t="n">
         <v>120061</v>
@@ -21771,7 +21771,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>15.8120346069336</v>
+        <v>15.8120336532593</v>
       </c>
       <c r="H738" t="n">
         <v>239917</v>
@@ -21800,7 +21800,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G739" t="n">
-        <v>15.397910118103</v>
+        <v>15.3979120254517</v>
       </c>
       <c r="H739" t="n">
         <v>47654</v>
@@ -21829,7 +21829,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>15.623797416687</v>
+        <v>15.6237964630127</v>
       </c>
       <c r="H740" t="n">
         <v>36284</v>
@@ -21858,7 +21858,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G741" t="n">
-        <v>15.9626235961914</v>
+        <v>15.9626245498657</v>
       </c>
       <c r="H741" t="n">
         <v>34956</v>
@@ -22003,7 +22003,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G746" t="n">
-        <v>15.7367391586304</v>
+        <v>15.7367401123047</v>
       </c>
       <c r="H746" t="n">
         <v>376457</v>
@@ -22061,7 +22061,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G748" t="n">
-        <v>15.9814510345459</v>
+        <v>15.9814491271973</v>
       </c>
       <c r="H748" t="n">
         <v>133164</v>
@@ -22119,7 +22119,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649620056152</v>
       </c>
       <c r="H750" t="n">
         <v>66185</v>
@@ -22206,7 +22206,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649620056152</v>
       </c>
       <c r="H753" t="n">
         <v>20532</v>
@@ -22235,7 +22235,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>15.3414373397827</v>
+        <v>15.3414392471313</v>
       </c>
       <c r="H754" t="n">
         <v>53120</v>
@@ -22293,7 +22293,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G756" t="n">
-        <v>15.4167356491089</v>
+        <v>15.4167337417603</v>
       </c>
       <c r="H756" t="n">
         <v>16829</v>
@@ -22351,7 +22351,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>14.6826038360596</v>
+        <v>14.6826047897339</v>
       </c>
       <c r="H758" t="n">
         <v>29036</v>
@@ -22380,7 +22380,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G759" t="n">
-        <v>14.8520193099976</v>
+        <v>14.8520202636719</v>
       </c>
       <c r="H759" t="n">
         <v>38103</v>
@@ -22409,7 +22409,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>14.4943656921387</v>
+        <v>14.4943647384644</v>
       </c>
       <c r="H760" t="n">
         <v>28613</v>
@@ -22467,7 +22467,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G762" t="n">
-        <v>14.8143711090088</v>
+        <v>14.8143720626831</v>
       </c>
       <c r="H762" t="n">
         <v>39225</v>
@@ -22554,7 +22554,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>15.1532020568848</v>
+        <v>15.1532011032104</v>
       </c>
       <c r="H765" t="n">
         <v>33018</v>
@@ -22612,7 +22612,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G767" t="n">
-        <v>15.9814510345459</v>
+        <v>15.9814491271973</v>
       </c>
       <c r="H767" t="n">
         <v>33646</v>
@@ -22641,7 +22641,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G768" t="n">
-        <v>15.9814510345459</v>
+        <v>15.9814491271973</v>
       </c>
       <c r="H768" t="n">
         <v>18071</v>
@@ -22670,7 +22670,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G769" t="n">
-        <v>15.6802682876587</v>
+        <v>15.680269241333</v>
       </c>
       <c r="H769" t="n">
         <v>18660</v>
@@ -22699,7 +22699,7 @@
         <v>16.5</v>
       </c>
       <c r="G770" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296783447266</v>
       </c>
       <c r="H770" t="n">
         <v>11383</v>
@@ -22757,7 +22757,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G772" t="n">
-        <v>15.2096710205078</v>
+        <v>15.2096729278564</v>
       </c>
       <c r="H772" t="n">
         <v>17228</v>
@@ -22815,7 +22815,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G774" t="n">
-        <v>15.3602628707886</v>
+        <v>15.3602619171143</v>
       </c>
       <c r="H774" t="n">
         <v>3951</v>
@@ -22844,7 +22844,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G775" t="n">
-        <v>15.6990928649902</v>
+        <v>15.6990938186646</v>
       </c>
       <c r="H775" t="n">
         <v>9940</v>
@@ -23047,7 +23047,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="n">
-        <v>16.0002765655518</v>
+        <v>16.0002727508545</v>
       </c>
       <c r="H782" t="n">
         <v>268855</v>
@@ -23076,7 +23076,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9438018798828</v>
+        <v>15.9438037872314</v>
       </c>
       <c r="H783" t="n">
         <v>107573</v>
@@ -23163,7 +23163,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G786" t="n">
-        <v>15.9814510345459</v>
+        <v>15.9814491271973</v>
       </c>
       <c r="H786" t="n">
         <v>18675</v>
@@ -23192,7 +23192,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G787" t="n">
-        <v>15.924976348877</v>
+        <v>15.9249792098999</v>
       </c>
       <c r="H787" t="n">
         <v>20420</v>
@@ -23221,7 +23221,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G788" t="n">
-        <v>15.9438018798828</v>
+        <v>15.9438037872314</v>
       </c>
       <c r="H788" t="n">
         <v>276706</v>
@@ -23279,7 +23279,7 @@
         <v>16.5</v>
       </c>
       <c r="G790" t="n">
-        <v>15.5296773910522</v>
+        <v>15.5296783447266</v>
       </c>
       <c r="H790" t="n">
         <v>11262</v>
@@ -23308,7 +23308,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G791" t="n">
-        <v>14.6261320114136</v>
+        <v>14.6261329650879</v>
       </c>
       <c r="H791" t="n">
         <v>43793</v>
@@ -23337,7 +23337,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G792" t="n">
-        <v>14.8520193099976</v>
+        <v>14.8520202636719</v>
       </c>
       <c r="H792" t="n">
         <v>26400</v>
@@ -23366,7 +23366,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>14.5696620941162</v>
+        <v>14.5696601867676</v>
       </c>
       <c r="H793" t="n">
         <v>63431</v>
@@ -23395,7 +23395,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G794" t="n">
-        <v>14.7955474853516</v>
+        <v>14.7955484390259</v>
       </c>
       <c r="H794" t="n">
         <v>15500</v>
@@ -23424,7 +23424,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G795" t="n">
-        <v>14.9461374282837</v>
+        <v>14.946138381958</v>
       </c>
       <c r="H795" t="n">
         <v>11544</v>
@@ -23453,7 +23453,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G796" t="n">
-        <v>15.1343765258789</v>
+        <v>15.1343774795532</v>
       </c>
       <c r="H796" t="n">
         <v>31362</v>
@@ -23511,7 +23511,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G798" t="n">
-        <v>15.0402574539185</v>
+        <v>15.0402584075928</v>
       </c>
       <c r="H798" t="n">
         <v>8502</v>
@@ -23569,7 +23569,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>14.9649610519409</v>
+        <v>14.9649620056152</v>
       </c>
       <c r="H800" t="n">
         <v>29640</v>
@@ -23627,7 +23627,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>15.1532020568848</v>
+        <v>15.1532011032104</v>
       </c>
       <c r="H802" t="n">
         <v>13646</v>
@@ -23656,7 +23656,7 @@
         <v>16</v>
       </c>
       <c r="G803" t="n">
-        <v>15.0590810775757</v>
+        <v>15.0590801239014</v>
       </c>
       <c r="H803" t="n">
         <v>24511</v>
@@ -23714,7 +23714,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G805" t="n">
-        <v>15.2284955978394</v>
+        <v>15.228497505188</v>
       </c>
       <c r="H805" t="n">
         <v>28018</v>
@@ -23743,7 +23743,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6802682876587</v>
+        <v>15.680269241333</v>
       </c>
       <c r="H806" t="n">
         <v>76749</v>
@@ -23772,7 +23772,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G807" t="n">
-        <v>15.9626235961914</v>
+        <v>15.9626245498657</v>
       </c>
       <c r="H807" t="n">
         <v>21659</v>
@@ -23801,7 +23801,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G808" t="n">
-        <v>16.1320381164551</v>
+        <v>16.1320400238037</v>
       </c>
       <c r="H808" t="n">
         <v>49127</v>
@@ -23946,7 +23946,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>17.0355854034424</v>
+        <v>17.0355892181396</v>
       </c>
       <c r="H813" t="n">
         <v>23814</v>
@@ -23975,7 +23975,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G814" t="n">
-        <v>16.9979362487793</v>
+        <v>16.9979400634766</v>
       </c>
       <c r="H814" t="n">
         <v>8415</v>
@@ -24004,7 +24004,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G815" t="n">
-        <v>16.9979362487793</v>
+        <v>16.9979400634766</v>
       </c>
       <c r="H815" t="n">
         <v>7309</v>
@@ -24033,7 +24033,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>17.9767761230469</v>
+        <v>17.9767780303955</v>
       </c>
       <c r="H816" t="n">
         <v>80666</v>
@@ -24120,7 +24120,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2991180419922</v>
+        <v>17.2991199493408</v>
       </c>
       <c r="H819" t="n">
         <v>10687</v>
@@ -24149,7 +24149,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G820" t="n">
-        <v>17.4308891296387</v>
+        <v>17.43088722229</v>
       </c>
       <c r="H820" t="n">
         <v>12088</v>
@@ -24178,7 +24178,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G821" t="n">
-        <v>16.9791164398193</v>
+        <v>16.9791145324707</v>
       </c>
       <c r="H821" t="n">
         <v>11574</v>
@@ -24265,7 +24265,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G824" t="n">
-        <v>17.2991180419922</v>
+        <v>17.2991199493408</v>
       </c>
       <c r="H824" t="n">
         <v>29002</v>
@@ -24381,7 +24381,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>17.0355854034424</v>
+        <v>17.0355892181396</v>
       </c>
       <c r="H828" t="n">
         <v>17978</v>
@@ -24439,7 +24439,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G830" t="n">
-        <v>17.7508945465088</v>
+        <v>17.7508926391602</v>
       </c>
       <c r="H830" t="n">
         <v>43980</v>
@@ -24613,7 +24613,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>17.0355854034424</v>
+        <v>17.0355892181396</v>
       </c>
       <c r="H836" t="n">
         <v>11528</v>
@@ -24700,7 +24700,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.5649890899658</v>
+        <v>16.5649929046631</v>
       </c>
       <c r="H839" t="n">
         <v>6273</v>
@@ -24729,7 +24729,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G840" t="n">
-        <v>16.5085201263428</v>
+        <v>16.5085220336914</v>
       </c>
       <c r="H840" t="n">
         <v>12297</v>
@@ -24758,7 +24758,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G841" t="n">
-        <v>16.5649890899658</v>
+        <v>16.5649929046631</v>
       </c>
       <c r="H841" t="n">
         <v>3505</v>
@@ -24845,7 +24845,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G844" t="n">
-        <v>16.2261581420898</v>
+        <v>16.2261619567871</v>
       </c>
       <c r="H844" t="n">
         <v>32076</v>
@@ -24874,7 +24874,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>16.7908763885498</v>
+        <v>16.7908782958984</v>
       </c>
       <c r="H845" t="n">
         <v>21229</v>
@@ -24903,7 +24903,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G846" t="n">
-        <v>16.2261581420898</v>
+        <v>16.2261619567871</v>
       </c>
       <c r="H846" t="n">
         <v>11012</v>
@@ -24932,7 +24932,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>16.0943946838379</v>
+        <v>16.0943927764893</v>
       </c>
       <c r="H847" t="n">
         <v>12324</v>
@@ -24961,7 +24961,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G848" t="n">
-        <v>16.5159111022949</v>
+        <v>16.5159130096436</v>
       </c>
       <c r="H848" t="n">
         <v>12178</v>
@@ -25019,7 +25019,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G850" t="n">
-        <v>16.324312210083</v>
+        <v>16.3243160247803</v>
       </c>
       <c r="H850" t="n">
         <v>3053</v>
@@ -25048,7 +25048,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>16.3817939758301</v>
+        <v>16.3817920684814</v>
       </c>
       <c r="H851" t="n">
         <v>16507</v>
@@ -25077,7 +25077,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G852" t="n">
-        <v>16.1710300445557</v>
+        <v>16.1710338592529</v>
       </c>
       <c r="H852" t="n">
         <v>14661</v>
@@ -25106,7 +25106,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G853" t="n">
-        <v>15.9411144256592</v>
+        <v>15.9411134719849</v>
       </c>
       <c r="H853" t="n">
         <v>4033</v>
@@ -25135,7 +25135,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G854" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219541549683</v>
       </c>
       <c r="H854" t="n">
         <v>21839</v>
@@ -25309,7 +25309,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>16.5733947753906</v>
+        <v>16.5733909606934</v>
       </c>
       <c r="H860" t="n">
         <v>62737</v>
@@ -25338,7 +25338,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G861" t="n">
-        <v>16.3626308441162</v>
+        <v>16.3626327514648</v>
       </c>
       <c r="H861" t="n">
         <v>153682</v>
@@ -25367,7 +25367,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>16.3626308441162</v>
+        <v>16.3626327514648</v>
       </c>
       <c r="H862" t="n">
         <v>39468</v>
@@ -25396,7 +25396,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G863" t="n">
-        <v>16.4584331512451</v>
+        <v>16.4584350585938</v>
       </c>
       <c r="H863" t="n">
         <v>9877</v>
@@ -25425,7 +25425,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G864" t="n">
-        <v>16.5733947753906</v>
+        <v>16.5733909606934</v>
       </c>
       <c r="H864" t="n">
         <v>5442</v>
@@ -25454,7 +25454,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>16.5733947753906</v>
+        <v>16.5733909606934</v>
       </c>
       <c r="H865" t="n">
         <v>59065</v>
@@ -25483,7 +25483,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>15.8836326599121</v>
+        <v>15.8836336135864</v>
       </c>
       <c r="H866" t="n">
         <v>47994</v>
@@ -25512,7 +25512,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>16.3817939758301</v>
+        <v>16.3817920684814</v>
       </c>
       <c r="H867" t="n">
         <v>14325</v>
@@ -25541,7 +25541,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G868" t="n">
-        <v>16.4009532928467</v>
+        <v>16.4009552001953</v>
       </c>
       <c r="H868" t="n">
         <v>109228</v>
@@ -25570,7 +25570,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>15.902792930603</v>
+        <v>15.9027919769287</v>
       </c>
       <c r="H869" t="n">
         <v>13629</v>
@@ -25599,7 +25599,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G870" t="n">
-        <v>15.9602718353271</v>
+        <v>15.9602737426758</v>
       </c>
       <c r="H870" t="n">
         <v>4390</v>
@@ -25628,7 +25628,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>15.902792930603</v>
+        <v>15.9027919769287</v>
       </c>
       <c r="H871" t="n">
         <v>18739</v>
@@ -25657,7 +25657,7 @@
         <v>16.5</v>
       </c>
       <c r="G872" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069944381714</v>
       </c>
       <c r="H872" t="n">
         <v>14035</v>
@@ -25686,7 +25686,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G873" t="n">
-        <v>15.672872543335</v>
+        <v>15.6728754043579</v>
       </c>
       <c r="H873" t="n">
         <v>2435</v>
@@ -25715,7 +25715,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G874" t="n">
-        <v>15.5962352752686</v>
+        <v>15.5962333679199</v>
       </c>
       <c r="H874" t="n">
         <v>3918</v>
@@ -25744,7 +25744,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G875" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219541549683</v>
       </c>
       <c r="H875" t="n">
         <v>7316</v>
@@ -25773,7 +25773,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G876" t="n">
-        <v>15.3663129806519</v>
+        <v>15.3663148880005</v>
       </c>
       <c r="H876" t="n">
         <v>10656</v>
@@ -25802,7 +25802,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G877" t="n">
-        <v>15.3088331222534</v>
+        <v>15.3088340759277</v>
       </c>
       <c r="H877" t="n">
         <v>21204</v>
@@ -25831,7 +25831,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G878" t="n">
-        <v>15.251353263855</v>
+        <v>15.2513542175293</v>
       </c>
       <c r="H878" t="n">
         <v>7496</v>
@@ -25860,7 +25860,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G879" t="n">
-        <v>14.925633430481</v>
+        <v>14.9256343841553</v>
       </c>
       <c r="H879" t="n">
         <v>15630</v>
@@ -25918,7 +25918,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G881" t="n">
-        <v>15.1747121810913</v>
+        <v>15.1747140884399</v>
       </c>
       <c r="H881" t="n">
         <v>8496</v>
@@ -25947,7 +25947,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>15.078914642334</v>
+        <v>15.0789136886597</v>
       </c>
       <c r="H882" t="n">
         <v>6649</v>
@@ -25976,7 +25976,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>15.0405941009521</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H883" t="n">
         <v>69164</v>
@@ -26121,7 +26121,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>15.0022745132446</v>
+        <v>15.002272605896</v>
       </c>
       <c r="H888" t="n">
         <v>16584</v>
@@ -26179,7 +26179,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.7915143966675</v>
+        <v>14.7915124893188</v>
       </c>
       <c r="H890" t="n">
         <v>23668</v>
@@ -26237,7 +26237,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G892" t="n">
-        <v>15.3854722976685</v>
+        <v>15.3854732513428</v>
       </c>
       <c r="H892" t="n">
         <v>28733</v>
@@ -26266,7 +26266,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G893" t="n">
-        <v>15.1172323226929</v>
+        <v>15.1172342300415</v>
       </c>
       <c r="H893" t="n">
         <v>23512</v>
@@ -26295,7 +26295,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G894" t="n">
-        <v>15.078914642334</v>
+        <v>15.0789136886597</v>
       </c>
       <c r="H894" t="n">
         <v>11452</v>
@@ -26353,7 +26353,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G896" t="n">
-        <v>15.078914642334</v>
+        <v>15.0789136886597</v>
       </c>
       <c r="H896" t="n">
         <v>33514</v>
@@ -26382,7 +26382,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>15.0405941009521</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H897" t="n">
         <v>10778</v>
@@ -26411,7 +26411,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G898" t="n">
-        <v>15.0214338302612</v>
+        <v>15.0214347839355</v>
       </c>
       <c r="H898" t="n">
         <v>10003</v>
@@ -26440,7 +26440,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G899" t="n">
-        <v>14.9064741134644</v>
+        <v>14.9064750671387</v>
       </c>
       <c r="H899" t="n">
         <v>23480</v>
@@ -26527,7 +26527,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G902" t="n">
-        <v>14.734034538269</v>
+        <v>14.7340354919434</v>
       </c>
       <c r="H902" t="n">
         <v>12786</v>
@@ -26585,7 +26585,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G904" t="n">
-        <v>14.6957139968872</v>
+        <v>14.6957130432129</v>
       </c>
       <c r="H904" t="n">
         <v>20029</v>
@@ -26643,7 +26643,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G906" t="n">
-        <v>14.9639549255371</v>
+        <v>14.9639520645142</v>
       </c>
       <c r="H906" t="n">
         <v>8263</v>
@@ -26759,7 +26759,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>14.7531938552856</v>
+        <v>14.7531929016113</v>
       </c>
       <c r="H910" t="n">
         <v>92952</v>
@@ -26846,7 +26846,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>14.9639549255371</v>
+        <v>14.9639520645142</v>
       </c>
       <c r="H913" t="n">
         <v>39651</v>
@@ -26904,7 +26904,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G915" t="n">
-        <v>14.829833984375</v>
+        <v>14.8298330307007</v>
       </c>
       <c r="H915" t="n">
         <v>5731</v>
@@ -26933,7 +26933,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G916" t="n">
-        <v>14.4849529266357</v>
+        <v>14.4849538803101</v>
       </c>
       <c r="H916" t="n">
         <v>18837</v>
@@ -27020,7 +27020,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G919" t="n">
-        <v>14.6957139968872</v>
+        <v>14.6957130432129</v>
       </c>
       <c r="H919" t="n">
         <v>6752</v>
@@ -27078,7 +27078,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G921" t="n">
-        <v>14.580753326416</v>
+        <v>14.5807542800903</v>
       </c>
       <c r="H921" t="n">
         <v>6470</v>
@@ -27136,7 +27136,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>14.5615949630737</v>
+        <v>14.5615930557251</v>
       </c>
       <c r="H923" t="n">
         <v>8466</v>
@@ -27165,7 +27165,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G924" t="n">
-        <v>14.4083137512207</v>
+        <v>14.408314704895</v>
       </c>
       <c r="H924" t="n">
         <v>9269</v>
@@ -27194,7 +27194,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G925" t="n">
-        <v>14.4849529266357</v>
+        <v>14.4849538803101</v>
       </c>
       <c r="H925" t="n">
         <v>12803</v>
@@ -27223,7 +27223,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G926" t="n">
-        <v>14.580753326416</v>
+        <v>14.5807542800903</v>
       </c>
       <c r="H926" t="n">
         <v>92</v>
@@ -27252,7 +27252,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G927" t="n">
-        <v>14.3891534805298</v>
+        <v>14.3891553878784</v>
       </c>
       <c r="H927" t="n">
         <v>11124</v>
@@ -27281,7 +27281,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G928" t="n">
-        <v>14.5999145507812</v>
+        <v>14.5999126434326</v>
       </c>
       <c r="H928" t="n">
         <v>14866</v>
@@ -27339,7 +27339,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G930" t="n">
-        <v>14.8681545257568</v>
+        <v>14.8681535720825</v>
       </c>
       <c r="H930" t="n">
         <v>16059</v>
@@ -27397,7 +27397,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G932" t="n">
-        <v>14.5041131973267</v>
+        <v>14.504114151001</v>
       </c>
       <c r="H932" t="n">
         <v>19652</v>
@@ -27484,7 +27484,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G935" t="n">
-        <v>14.829833984375</v>
+        <v>14.8298330307007</v>
       </c>
       <c r="H935" t="n">
         <v>35345</v>
@@ -27542,7 +27542,7 @@
         <v>16</v>
       </c>
       <c r="G937" t="n">
-        <v>15.3279933929443</v>
+        <v>15.32799243927</v>
       </c>
       <c r="H937" t="n">
         <v>17828</v>
@@ -27571,7 +27571,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G938" t="n">
-        <v>15.6153917312622</v>
+        <v>15.6153936386108</v>
       </c>
       <c r="H938" t="n">
         <v>28450</v>
@@ -27658,7 +27658,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G941" t="n">
-        <v>15.730354309082</v>
+        <v>15.7303514480591</v>
       </c>
       <c r="H941" t="n">
         <v>18615</v>
@@ -27687,7 +27687,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>16.0943927764893</v>
+        <v>16.0943908691406</v>
       </c>
       <c r="H942" t="n">
         <v>46123</v>
@@ -27716,7 +27716,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>15.7111930847168</v>
+        <v>15.7111940383911</v>
       </c>
       <c r="H943" t="n">
         <v>16463</v>
@@ -27745,7 +27745,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G944" t="n">
-        <v>15.5962352752686</v>
+        <v>15.5962333679199</v>
       </c>
       <c r="H944" t="n">
         <v>173872</v>
@@ -27803,7 +27803,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G946" t="n">
-        <v>15.9411144256592</v>
+        <v>15.9411134719849</v>
       </c>
       <c r="H946" t="n">
         <v>16911</v>
@@ -27832,7 +27832,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G947" t="n">
-        <v>15.8453140258789</v>
+        <v>15.8453149795532</v>
       </c>
       <c r="H947" t="n">
         <v>9454</v>
@@ -27861,7 +27861,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G948" t="n">
-        <v>15.577073097229</v>
+        <v>15.5770740509033</v>
       </c>
       <c r="H948" t="n">
         <v>12265</v>
@@ -27890,7 +27890,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G949" t="n">
-        <v>15.5579147338867</v>
+        <v>15.5579128265381</v>
       </c>
       <c r="H949" t="n">
         <v>13664</v>
@@ -27919,7 +27919,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>15.902792930603</v>
+        <v>15.9027919769287</v>
       </c>
       <c r="H950" t="n">
         <v>15416</v>
@@ -27948,7 +27948,7 @@
         <v>16.5</v>
       </c>
       <c r="G951" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069944381714</v>
       </c>
       <c r="H951" t="n">
         <v>11208</v>
@@ -27977,7 +27977,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>15.7878332138062</v>
+        <v>15.7878322601318</v>
       </c>
       <c r="H952" t="n">
         <v>10445</v>
@@ -28006,7 +28006,7 @@
         <v>16.5</v>
       </c>
       <c r="G953" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069944381714</v>
       </c>
       <c r="H953" t="n">
         <v>27357</v>
@@ -28035,7 +28035,7 @@
         <v>16.5</v>
       </c>
       <c r="G954" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069944381714</v>
       </c>
       <c r="H954" t="n">
         <v>30809</v>
@@ -28064,7 +28064,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G955" t="n">
-        <v>15.5195941925049</v>
+        <v>15.5195932388306</v>
       </c>
       <c r="H955" t="n">
         <v>10063</v>
@@ -28093,7 +28093,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G956" t="n">
-        <v>15.4429540634155</v>
+        <v>15.4429531097412</v>
       </c>
       <c r="H956" t="n">
         <v>4139</v>
@@ -28122,7 +28122,7 @@
         <v>16</v>
       </c>
       <c r="G957" t="n">
-        <v>15.3279933929443</v>
+        <v>15.32799243927</v>
       </c>
       <c r="H957" t="n">
         <v>2780</v>
@@ -28151,7 +28151,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G958" t="n">
-        <v>15.5962352752686</v>
+        <v>15.5962333679199</v>
       </c>
       <c r="H958" t="n">
         <v>4998</v>
@@ -28180,7 +28180,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G959" t="n">
-        <v>15.7686729431152</v>
+        <v>15.7686719894409</v>
       </c>
       <c r="H959" t="n">
         <v>16273</v>
@@ -28209,7 +28209,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>15.902792930603</v>
+        <v>15.9027919769287</v>
       </c>
       <c r="H960" t="n">
         <v>9306</v>
@@ -28238,7 +28238,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>15.7111930847168</v>
+        <v>15.7111940383911</v>
       </c>
       <c r="H961" t="n">
         <v>14436</v>
@@ -28296,7 +28296,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G963" t="n">
-        <v>15.8644752502441</v>
+        <v>15.8644723892212</v>
       </c>
       <c r="H963" t="n">
         <v>11265</v>
@@ -28325,7 +28325,7 @@
         <v>16.5</v>
       </c>
       <c r="G964" t="n">
-        <v>15.8069925308228</v>
+        <v>15.8069944381714</v>
       </c>
       <c r="H964" t="n">
         <v>13857</v>
@@ -28354,7 +28354,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G965" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219541549683</v>
       </c>
       <c r="H965" t="n">
         <v>14484</v>
@@ -28383,7 +28383,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G966" t="n">
-        <v>16.0560722351074</v>
+        <v>16.0560760498047</v>
       </c>
       <c r="H966" t="n">
         <v>20089</v>
@@ -28412,7 +28412,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>16.0943927764893</v>
+        <v>16.0943908691406</v>
       </c>
       <c r="H967" t="n">
         <v>5416</v>
@@ -28441,7 +28441,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>16.3817939758301</v>
+        <v>16.3817920684814</v>
       </c>
       <c r="H968" t="n">
         <v>17165</v>
@@ -28470,7 +28470,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G969" t="n">
-        <v>17.0907115936279</v>
+        <v>17.0907135009766</v>
       </c>
       <c r="H969" t="n">
         <v>22005</v>
@@ -28528,7 +28528,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G971" t="n">
-        <v>16.8799514770508</v>
+        <v>16.8799533843994</v>
       </c>
       <c r="H971" t="n">
         <v>13007</v>
@@ -28586,7 +28586,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G973" t="n">
-        <v>16.822473526001</v>
+        <v>16.8224716186523</v>
       </c>
       <c r="H973" t="n">
         <v>36106</v>
@@ -28644,7 +28644,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G975" t="n">
-        <v>16.918270111084</v>
+        <v>16.9182739257812</v>
       </c>
       <c r="H975" t="n">
         <v>21250</v>
@@ -28673,7 +28673,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>17.0523910522461</v>
+        <v>17.0523948669434</v>
       </c>
       <c r="H976" t="n">
         <v>19467</v>
@@ -28731,7 +28731,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G978" t="n">
-        <v>16.822473526001</v>
+        <v>16.8224716186523</v>
       </c>
       <c r="H978" t="n">
         <v>21158</v>
@@ -28789,7 +28789,7 @@
         <v>19</v>
       </c>
       <c r="G980" t="n">
-        <v>18.2019901275635</v>
+        <v>18.2019939422607</v>
       </c>
       <c r="H980" t="n">
         <v>66764</v>
@@ -28818,7 +28818,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G981" t="n">
-        <v>18.1061935424805</v>
+        <v>18.1061916351318</v>
       </c>
       <c r="H981" t="n">
         <v>33750</v>
@@ -28847,7 +28847,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>17.5313911437988</v>
+        <v>17.5313930511475</v>
       </c>
       <c r="H982" t="n">
         <v>10102</v>
@@ -28934,7 +28934,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>17.9145927429199</v>
+        <v>17.9145946502686</v>
       </c>
       <c r="H985" t="n">
         <v>23558</v>
@@ -28963,7 +28963,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>18.0487117767334</v>
+        <v>18.048713684082</v>
       </c>
       <c r="H986" t="n">
         <v>28343</v>
@@ -29021,7 +29021,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G988" t="n">
-        <v>17.8762741088867</v>
+        <v>17.8762702941895</v>
       </c>
       <c r="H988" t="n">
         <v>13457</v>
@@ -29050,7 +29050,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="n">
-        <v>17.991231918335</v>
+        <v>17.9912338256836</v>
       </c>
       <c r="H989" t="n">
         <v>1479</v>
@@ -29108,7 +29108,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G991" t="n">
-        <v>17.9145927429199</v>
+        <v>17.9145946502686</v>
       </c>
       <c r="H991" t="n">
         <v>2191</v>
@@ -29137,7 +29137,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G992" t="n">
-        <v>17.8571109771729</v>
+        <v>17.8571128845215</v>
       </c>
       <c r="H992" t="n">
         <v>10094</v>
@@ -29195,7 +29195,7 @@
         <v>19.5</v>
       </c>
       <c r="G994" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809940338135</v>
       </c>
       <c r="H994" t="n">
         <v>48325</v>
@@ -29253,7 +29253,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G996" t="n">
-        <v>18.9492321014404</v>
+        <v>18.9492301940918</v>
       </c>
       <c r="H996" t="n">
         <v>20868</v>
@@ -29282,7 +29282,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G997" t="n">
-        <v>18.4702320098877</v>
+        <v>18.4702339172363</v>
       </c>
       <c r="H997" t="n">
         <v>51855</v>
@@ -29311,7 +29311,7 @@
         <v>19.5</v>
       </c>
       <c r="G998" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809940338135</v>
       </c>
       <c r="H998" t="n">
         <v>31925</v>
@@ -29369,7 +29369,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>18.8342723846436</v>
+        <v>18.8342704772949</v>
       </c>
       <c r="H1000" t="n">
         <v>11571</v>
@@ -29398,7 +29398,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>19.3515949249268</v>
+        <v>19.3515911102295</v>
       </c>
       <c r="H1001" t="n">
         <v>70746</v>
@@ -29514,7 +29514,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.2078952789307</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1005" t="n">
         <v>16818</v>
@@ -29543,7 +29543,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.2078952789307</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1006" t="n">
         <v>11391</v>
@@ -29572,7 +29572,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>18.7767906188965</v>
+        <v>18.7767925262451</v>
       </c>
       <c r="H1007" t="n">
         <v>26511</v>
@@ -29601,7 +29601,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>19.54319190979</v>
+        <v>19.5431900024414</v>
       </c>
       <c r="H1008" t="n">
         <v>20730</v>
@@ -29659,7 +29659,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1010" t="n">
         <v>17102</v>
@@ -29688,7 +29688,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1011" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1011" t="n">
         <v>30838</v>
@@ -29804,7 +29804,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>19.2078952789307</v>
+        <v>19.2078895568848</v>
       </c>
       <c r="H1015" t="n">
         <v>16605</v>
@@ -29833,7 +29833,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>19.54319190979</v>
+        <v>19.5431900024414</v>
       </c>
       <c r="H1016" t="n">
         <v>7685</v>
@@ -29891,7 +29891,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1018" t="n">
-        <v>19.4952907562256</v>
+        <v>19.4952926635742</v>
       </c>
       <c r="H1018" t="n">
         <v>6892</v>
@@ -29920,7 +29920,7 @@
         <v>21</v>
       </c>
       <c r="G1019" t="n">
-        <v>20.1179904937744</v>
+        <v>20.117992401123</v>
       </c>
       <c r="H1019" t="n">
         <v>36720</v>
@@ -29978,7 +29978,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>22.1297912597656</v>
+        <v>22.1297931671143</v>
       </c>
       <c r="H1021" t="n">
         <v>42813</v>
@@ -30007,7 +30007,7 @@
         <v>22</v>
       </c>
       <c r="G1022" t="n">
-        <v>21.0759944915771</v>
+        <v>21.0759887695312</v>
       </c>
       <c r="H1022" t="n">
         <v>28445</v>
@@ -30036,7 +30036,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>21.0280895233154</v>
+        <v>21.0280914306641</v>
       </c>
       <c r="H1023" t="n">
         <v>19149</v>
@@ -30065,7 +30065,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>20.7406921386719</v>
+        <v>20.7406902313232</v>
       </c>
       <c r="H1024" t="n">
         <v>12238</v>
@@ -30123,7 +30123,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322891235352</v>
       </c>
       <c r="H1026" t="n">
         <v>4444</v>
@@ -30152,7 +30152,7 @@
         <v>22</v>
       </c>
       <c r="G1027" t="n">
-        <v>21.0759944915771</v>
+        <v>21.0759887695312</v>
       </c>
       <c r="H1027" t="n">
         <v>17582</v>
@@ -30181,7 +30181,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322891235352</v>
       </c>
       <c r="H1028" t="n">
         <v>6993</v>
@@ -30210,7 +30210,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1029" t="n">
-        <v>20.6448879241943</v>
+        <v>20.644889831543</v>
       </c>
       <c r="H1029" t="n">
         <v>6458</v>
@@ -30239,7 +30239,7 @@
         <v>21.5</v>
       </c>
       <c r="G1030" t="n">
-        <v>20.5969944000244</v>
+        <v>20.5969924926758</v>
       </c>
       <c r="H1030" t="n">
         <v>6027</v>
@@ -30268,7 +30268,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>20.6448879241943</v>
+        <v>20.644889831543</v>
       </c>
       <c r="H1031" t="n">
         <v>3174</v>
@@ -30297,7 +30297,7 @@
         <v>21.5</v>
       </c>
       <c r="G1032" t="n">
-        <v>20.5969944000244</v>
+        <v>20.5969924926758</v>
       </c>
       <c r="H1032" t="n">
         <v>9135</v>
@@ -30384,7 +30384,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>19.9263916015625</v>
+        <v>19.9263896942139</v>
       </c>
       <c r="H1035" t="n">
         <v>8404</v>
@@ -30413,7 +30413,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1036" t="n">
-        <v>19.7826900482178</v>
+        <v>19.7826919555664</v>
       </c>
       <c r="H1036" t="n">
         <v>207787</v>
@@ -30471,7 +30471,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1038" t="n">
-        <v>19.0067119598389</v>
+        <v>19.0067138671875</v>
       </c>
       <c r="H1038" t="n">
         <v>22140</v>
@@ -30529,7 +30529,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>20.6927909851074</v>
+        <v>20.6927928924561</v>
       </c>
       <c r="H1040" t="n">
         <v>21385</v>
@@ -30558,7 +30558,7 @@
         <v>21.75</v>
       </c>
       <c r="G1041" t="n">
-        <v>20.8364925384521</v>
+        <v>20.8364906311035</v>
       </c>
       <c r="H1041" t="n">
         <v>11383</v>
@@ -30587,7 +30587,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>20.6448879241943</v>
+        <v>20.644889831543</v>
       </c>
       <c r="H1042" t="n">
         <v>21457</v>
@@ -30645,7 +30645,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>20.9322910308838</v>
+        <v>20.9322891235352</v>
       </c>
       <c r="H1044" t="n">
         <v>10768</v>
@@ -30674,7 +30674,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>21.1717891693115</v>
+        <v>21.1717910766602</v>
       </c>
       <c r="H1045" t="n">
         <v>34815</v>
@@ -30703,7 +30703,7 @@
         <v>22.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>21.3154945373535</v>
+        <v>21.3154907226562</v>
       </c>
       <c r="H1046" t="n">
         <v>27422</v>
@@ -30732,7 +30732,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1047" t="n">
-        <v>21.1238899230957</v>
+        <v>21.1238880157471</v>
       </c>
       <c r="H1047" t="n">
         <v>13111</v>
@@ -30761,7 +30761,7 @@
         <v>22.5</v>
       </c>
       <c r="G1048" t="n">
-        <v>21.5549907684326</v>
+        <v>21.554988861084</v>
       </c>
       <c r="H1048" t="n">
         <v>13026</v>
@@ -30819,7 +30819,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1050" t="n">
-        <v>21.7465877532959</v>
+        <v>21.7465915679932</v>
       </c>
       <c r="H1050" t="n">
         <v>12109</v>
@@ -30848,7 +30848,7 @@
         <v>22.25</v>
       </c>
       <c r="G1051" t="n">
-        <v>21.3154945373535</v>
+        <v>21.3154907226562</v>
       </c>
       <c r="H1051" t="n">
         <v>7933</v>
@@ -30877,7 +30877,7 @@
         <v>22</v>
       </c>
       <c r="G1052" t="n">
-        <v>21.0759944915771</v>
+        <v>21.0759887695312</v>
       </c>
       <c r="H1052" t="n">
         <v>16862</v>
@@ -30935,7 +30935,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1054" t="n">
-        <v>19.6868934631348</v>
+        <v>19.6868915557861</v>
       </c>
       <c r="H1054" t="n">
         <v>26069</v>
@@ -30964,7 +30964,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>20.0221920013428</v>
+        <v>20.0221881866455</v>
       </c>
       <c r="H1055" t="n">
         <v>41841</v>
@@ -30993,7 +30993,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>19.54319190979</v>
+        <v>19.5431900024414</v>
       </c>
       <c r="H1056" t="n">
         <v>18241</v>
@@ -31051,7 +31051,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1058" t="n">
-        <v>18.6618328094482</v>
+        <v>18.661828994751</v>
       </c>
       <c r="H1058" t="n">
         <v>54563</v>
@@ -31080,7 +31080,7 @@
         <v>19.5</v>
       </c>
       <c r="G1059" t="n">
-        <v>18.6809921264648</v>
+        <v>18.6809940338135</v>
       </c>
       <c r="H1059" t="n">
         <v>52887</v>
@@ -31109,7 +31109,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>18.7767906188965</v>
+        <v>18.7767925262451</v>
       </c>
       <c r="H1060" t="n">
         <v>21530</v>
@@ -31138,7 +31138,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1061" t="n">
-        <v>18.1253509521484</v>
+        <v>18.1253547668457</v>
       </c>
       <c r="H1061" t="n">
         <v>16465</v>
@@ -31167,7 +31167,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1062" t="n">
-        <v>17.5505542755127</v>
+        <v>17.5505504608154</v>
       </c>
       <c r="H1062" t="n">
         <v>14163</v>
@@ -31225,7 +31225,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1064" t="n">
-        <v>16.2476749420166</v>
+        <v>16.2476711273193</v>
       </c>
       <c r="H1064" t="n">
         <v>45443</v>
@@ -31254,7 +31254,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1065" t="n">
-        <v>16.1327114105225</v>
+        <v>16.1327133178711</v>
       </c>
       <c r="H1065" t="n">
         <v>56427</v>
@@ -31283,7 +31283,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1066" t="n">
-        <v>14.4274749755859</v>
+        <v>14.4274740219116</v>
       </c>
       <c r="H1066" t="n">
         <v>27594</v>
@@ -31312,7 +31312,7 @@
         <v>15</v>
       </c>
       <c r="G1067" t="n">
-        <v>14.3699932098389</v>
+        <v>14.3699941635132</v>
       </c>
       <c r="H1067" t="n">
         <v>37376</v>
@@ -31341,7 +31341,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.4156742095947</v>
+        <v>12.4156761169434</v>
       </c>
       <c r="H1068" t="n">
         <v>42840</v>
@@ -31370,7 +31370,7 @@
         <v>12.5</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9749937057495</v>
+        <v>11.9749956130981</v>
       </c>
       <c r="H1069" t="n">
         <v>35916</v>
@@ -31428,7 +31428,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1071" t="n">
-        <v>12.6455945968628</v>
+        <v>12.6455936431885</v>
       </c>
       <c r="H1071" t="n">
         <v>30195</v>
@@ -31457,7 +31457,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1072" t="n">
-        <v>12.8563537597656</v>
+        <v>12.8563547134399</v>
       </c>
       <c r="H1072" t="n">
         <v>49016</v>
@@ -31486,7 +31486,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1073" t="n">
-        <v>11.9366750717163</v>
+        <v>11.936674118042</v>
       </c>
       <c r="H1073" t="n">
         <v>36917</v>
@@ -31515,7 +31515,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1074" t="n">
-        <v>13.258713722229</v>
+        <v>13.2587156295776</v>
       </c>
       <c r="H1074" t="n">
         <v>23012</v>
@@ -31544,7 +31544,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>13.5077953338623</v>
+        <v>13.507794380188</v>
       </c>
       <c r="H1075" t="n">
         <v>106622</v>
@@ -31573,7 +31573,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1076" t="n">
-        <v>13.9676342010498</v>
+        <v>13.9676322937012</v>
       </c>
       <c r="H1076" t="n">
         <v>20303</v>
@@ -31631,7 +31631,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.2358741760254</v>
+        <v>14.2358732223511</v>
       </c>
       <c r="H1078" t="n">
         <v>13798</v>
@@ -31660,7 +31660,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5999145507812</v>
+        <v>14.5999126434326</v>
       </c>
       <c r="H1079" t="n">
         <v>17157</v>
@@ -31747,7 +31747,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1082" t="n">
-        <v>13.9676342010498</v>
+        <v>13.9676322937012</v>
       </c>
       <c r="H1082" t="n">
         <v>23628</v>
@@ -31805,7 +31805,7 @@
         <v>15</v>
       </c>
       <c r="G1084" t="n">
-        <v>14.3699932098389</v>
+        <v>14.3699941635132</v>
       </c>
       <c r="H1084" t="n">
         <v>32335</v>
@@ -31834,7 +31834,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1085" t="n">
-        <v>14.4274749755859</v>
+        <v>14.4274740219116</v>
       </c>
       <c r="H1085" t="n">
         <v>16830</v>
@@ -31892,7 +31892,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1087" t="n">
-        <v>14.7915143966675</v>
+        <v>14.7915124893188</v>
       </c>
       <c r="H1087" t="n">
         <v>22064</v>
@@ -31921,7 +31921,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1088" t="n">
-        <v>14.2358741760254</v>
+        <v>14.2358732223511</v>
       </c>
       <c r="H1088" t="n">
         <v>26022</v>
@@ -31950,7 +31950,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1089" t="n">
-        <v>14.0442733764648</v>
+        <v>14.0442752838135</v>
       </c>
       <c r="H1089" t="n">
         <v>19202</v>
@@ -31979,7 +31979,7 @@
         <v>15</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.3699932098389</v>
+        <v>14.3699941635132</v>
       </c>
       <c r="H1090" t="n">
         <v>19170</v>
@@ -32008,7 +32008,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.3471536636353</v>
+        <v>15.3471527099609</v>
       </c>
       <c r="H1091" t="n">
         <v>18167</v>
@@ -32066,7 +32066,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219541549683</v>
       </c>
       <c r="H1093" t="n">
         <v>32303</v>
@@ -32095,7 +32095,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1094" t="n">
-        <v>16.8033142089844</v>
+        <v>16.803316116333</v>
       </c>
       <c r="H1094" t="n">
         <v>9069</v>
@@ -32182,7 +32182,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.9219532012939</v>
+        <v>15.9219541549683</v>
       </c>
       <c r="H1097" t="n">
         <v>16332</v>
@@ -32240,7 +32240,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.8453140258789</v>
+        <v>15.8453149795532</v>
       </c>
       <c r="H1099" t="n">
         <v>11700</v>
@@ -32298,7 +32298,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.8681545257568</v>
+        <v>14.8681535720825</v>
       </c>
       <c r="H1101" t="n">
         <v>17167</v>
@@ -32327,7 +32327,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>15.078914642334</v>
+        <v>15.0789136886597</v>
       </c>
       <c r="H1102" t="n">
         <v>15088</v>
@@ -32356,7 +32356,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.0405941009521</v>
+        <v>15.0405931472778</v>
       </c>
       <c r="H1103" t="n">
         <v>8857</v>
@@ -32385,7 +32385,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.7111930847168</v>
+        <v>15.7111940383911</v>
       </c>
       <c r="H1104" t="n">
         <v>18855</v>
@@ -32414,7 +32414,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.672872543335</v>
+        <v>15.6728754043579</v>
       </c>
       <c r="H1105" t="n">
         <v>4569</v>
@@ -32443,7 +32443,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.3471536636353</v>
+        <v>15.3471527099609</v>
       </c>
       <c r="H1106" t="n">
         <v>18764</v>
@@ -32472,7 +32472,7 @@
         <v>16</v>
       </c>
       <c r="G1107" t="n">
-        <v>15.3279933929443</v>
+        <v>15.32799243927</v>
       </c>
       <c r="H1107" t="n">
         <v>1900</v>
@@ -32501,7 +32501,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1108" t="n">
-        <v>14.7531938552856</v>
+        <v>14.7531929016113</v>
       </c>
       <c r="H1108" t="n">
         <v>12607</v>
@@ -32559,7 +32559,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>15.6153917312622</v>
+        <v>15.6153936386108</v>
       </c>
       <c r="H1110" t="n">
         <v>9207</v>
@@ -32588,7 +32588,7 @@
         <v>16</v>
       </c>
       <c r="G1111" t="n">
-        <v>15.3279933929443</v>
+        <v>15.32799243927</v>
       </c>
       <c r="H1111" t="n">
         <v>24188</v>
@@ -32733,7 +32733,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1116" t="n">
-        <v>16.1710300445557</v>
+        <v>16.1710338592529</v>
       </c>
       <c r="H1116" t="n">
         <v>20055</v>
@@ -32762,7 +32762,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1117" t="n">
-        <v>15.9602718353271</v>
+        <v>15.9602737426758</v>
       </c>
       <c r="H1117" t="n">
         <v>60107</v>
@@ -32820,7 +32820,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>17.148193359375</v>
+        <v>17.1481952667236</v>
       </c>
       <c r="H1119" t="n">
         <v>33288</v>
@@ -32878,7 +32878,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1121" t="n">
-        <v>16.8607921600342</v>
+        <v>16.8607940673828</v>
       </c>
       <c r="H1121" t="n">
         <v>6992</v>
@@ -32907,7 +32907,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1122" t="n">
-        <v>16.994909286499</v>
+        <v>16.9949131011963</v>
       </c>
       <c r="H1122" t="n">
         <v>43243</v>
@@ -32965,7 +32965,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1124" t="n">
-        <v>18.5660305023193</v>
+        <v>18.5660285949707</v>
       </c>
       <c r="H1124" t="n">
         <v>28971</v>
@@ -33052,7 +33052,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3899936676025</v>
+        <v>17.3899917602539</v>
       </c>
       <c r="H1127" t="n">
         <v>26195</v>
@@ -33081,7 +33081,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.3707122802734</v>
+        <v>17.3707103729248</v>
       </c>
       <c r="H1128" t="n">
         <v>29290</v>
@@ -33110,7 +33110,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1129" t="n">
-        <v>17.1393585205078</v>
+        <v>17.1393566131592</v>
       </c>
       <c r="H1129" t="n">
         <v>12350</v>
@@ -33197,7 +33197,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1132" t="n">
-        <v>17.5442276000977</v>
+        <v>17.5442295074463</v>
       </c>
       <c r="H1132" t="n">
         <v>37987</v>
@@ -33226,7 +33226,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1133" t="n">
-        <v>17.1007995605469</v>
+        <v>17.1008014678955</v>
       </c>
       <c r="H1133" t="n">
         <v>34044</v>
@@ -33255,7 +33255,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1134" t="n">
-        <v>17.5827865600586</v>
+        <v>17.58278465271</v>
       </c>
       <c r="H1134" t="n">
         <v>33739</v>
@@ -33313,7 +33313,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1136" t="n">
-        <v>17.6599025726318</v>
+        <v>17.6599006652832</v>
       </c>
       <c r="H1136" t="n">
         <v>31243</v>
@@ -33371,7 +33371,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1138" t="n">
-        <v>17.871976852417</v>
+        <v>17.8719749450684</v>
       </c>
       <c r="H1138" t="n">
         <v>21883</v>
@@ -33400,7 +33400,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1139" t="n">
-        <v>17.9876518249512</v>
+        <v>17.9876499176025</v>
       </c>
       <c r="H1139" t="n">
         <v>12742</v>
@@ -33429,7 +33429,7 @@
         <v>19</v>
       </c>
       <c r="G1140" t="n">
-        <v>18.3153991699219</v>
+        <v>18.3154029846191</v>
       </c>
       <c r="H1140" t="n">
         <v>10722</v>
@@ -33487,7 +33487,7 @@
         <v>18.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>17.8334178924561</v>
+        <v>17.8334159851074</v>
       </c>
       <c r="H1142" t="n">
         <v>21361</v>
@@ -33545,7 +33545,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1144" t="n">
-        <v>18.1804466247559</v>
+        <v>18.1804447174072</v>
       </c>
       <c r="H1144" t="n">
         <v>40063</v>
@@ -33632,7 +33632,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1147" t="n">
-        <v>18.1804466247559</v>
+        <v>18.1804447174072</v>
       </c>
       <c r="H1147" t="n">
         <v>11344</v>
@@ -33661,7 +33661,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1148" t="n">
-        <v>17.9876518249512</v>
+        <v>17.9876499176025</v>
       </c>
       <c r="H1148" t="n">
         <v>17868</v>
@@ -33690,7 +33690,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1149" t="n">
-        <v>18.0454883575439</v>
+        <v>18.0454902648926</v>
       </c>
       <c r="H1149" t="n">
         <v>9891</v>
@@ -33777,7 +33777,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1152" t="n">
-        <v>18.758825302124</v>
+        <v>18.7588233947754</v>
       </c>
       <c r="H1152" t="n">
         <v>11136</v>
@@ -33835,7 +33835,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>18.6045913696289</v>
+        <v>18.6045894622803</v>
       </c>
       <c r="H1154" t="n">
         <v>10853</v>
@@ -33864,7 +33864,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1155" t="n">
-        <v>18.8359451293945</v>
+        <v>18.8359470367432</v>
       </c>
       <c r="H1155" t="n">
         <v>8163</v>
@@ -33922,7 +33922,7 @@
         <v>20.25</v>
       </c>
       <c r="G1157" t="n">
-        <v>19.5203609466553</v>
+        <v>19.5203590393066</v>
       </c>
       <c r="H1157" t="n">
         <v>40676</v>
@@ -33980,7 +33980,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1159" t="n">
-        <v>18.8745021820068</v>
+        <v>18.8745002746582</v>
       </c>
       <c r="H1159" t="n">
         <v>43267</v>
@@ -34009,7 +34009,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1160" t="n">
-        <v>19.0287380218506</v>
+        <v>19.028736114502</v>
       </c>
       <c r="H1160" t="n">
         <v>13172</v>
@@ -34038,7 +34038,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1161" t="n">
-        <v>18.3925151824951</v>
+        <v>18.3925170898438</v>
       </c>
       <c r="H1161" t="n">
         <v>22377</v>
@@ -34067,7 +34067,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1162" t="n">
-        <v>18.5853118896484</v>
+        <v>18.5853137969971</v>
       </c>
       <c r="H1162" t="n">
         <v>5703</v>
@@ -34096,7 +34096,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1163" t="n">
-        <v>18.8359451293945</v>
+        <v>18.8359470367432</v>
       </c>
       <c r="H1163" t="n">
         <v>10885</v>
@@ -34183,7 +34183,7 @@
         <v>20.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>20.002347946167</v>
+        <v>20.0023460388184</v>
       </c>
       <c r="H1166" t="n">
         <v>13961</v>
@@ -34212,7 +34212,7 @@
         <v>21</v>
       </c>
       <c r="G1167" t="n">
-        <v>20.2433395385742</v>
+        <v>20.2433376312256</v>
       </c>
       <c r="H1167" t="n">
         <v>11434</v>
@@ -34328,7 +34328,7 @@
         <v>22</v>
       </c>
       <c r="G1171" t="n">
-        <v>21.2073078155518</v>
+        <v>21.2073040008545</v>
       </c>
       <c r="H1171" t="n">
         <v>5314</v>
@@ -34357,7 +34357,7 @@
         <v>22</v>
       </c>
       <c r="G1172" t="n">
-        <v>21.2073078155518</v>
+        <v>21.2073040008545</v>
       </c>
       <c r="H1172" t="n">
         <v>3910</v>
@@ -34386,7 +34386,7 @@
         <v>22</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.2073078155518</v>
+        <v>21.2073040008545</v>
       </c>
       <c r="H1173" t="n">
         <v>2585</v>
@@ -34415,7 +34415,7 @@
         <v>22</v>
       </c>
       <c r="G1174" t="n">
-        <v>21.2073078155518</v>
+        <v>21.2073040008545</v>
       </c>
       <c r="H1174" t="n">
         <v>644</v>
@@ -34444,7 +34444,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1175" t="n">
-        <v>21.6410903930664</v>
+        <v>21.641092300415</v>
       </c>
       <c r="H1175" t="n">
         <v>11127</v>
@@ -34502,7 +34502,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1177" t="n">
-        <v>21.6410903930664</v>
+        <v>21.641092300415</v>
       </c>
       <c r="H1177" t="n">
         <v>2456</v>
@@ -34589,7 +34589,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>21.7856903076172</v>
+        <v>21.7856884002686</v>
       </c>
       <c r="H1180" t="n">
         <v>6893</v>
@@ -34618,7 +34618,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.7856903076172</v>
+        <v>21.7856884002686</v>
       </c>
       <c r="H1181" t="n">
         <v>6535</v>
@@ -34647,7 +34647,7 @@
         <v>22.25</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.448299407959</v>
+        <v>21.4482975006104</v>
       </c>
       <c r="H1182" t="n">
         <v>21926</v>
@@ -34676,7 +34676,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.2555027008057</v>
+        <v>21.255500793457</v>
       </c>
       <c r="H1183" t="n">
         <v>1914</v>
@@ -34734,7 +34734,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>22.3640670776367</v>
+        <v>22.364070892334</v>
       </c>
       <c r="H1185" t="n">
         <v>39937</v>
@@ -34792,7 +34792,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1187" t="n">
         <v>78393</v>
@@ -34879,7 +34879,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1190" t="n">
         <v>7828</v>
@@ -35053,7 +35053,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>23.9546165466309</v>
+        <v>23.9546184539795</v>
       </c>
       <c r="H1196" t="n">
         <v>25747</v>
@@ -35169,7 +35169,7 @@
         <v>23.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>22.6532611846924</v>
+        <v>22.6532592773438</v>
       </c>
       <c r="H1200" t="n">
         <v>19479</v>
@@ -35198,7 +35198,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1201" t="n">
-        <v>22.9424495697021</v>
+        <v>22.9424476623535</v>
       </c>
       <c r="H1201" t="n">
         <v>13583</v>
@@ -35285,7 +35285,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>22.7978534698486</v>
+        <v>22.7978515625</v>
       </c>
       <c r="H1204" t="n">
         <v>5860</v>
@@ -35314,7 +35314,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1205" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1205" t="n">
         <v>12389</v>
@@ -35343,7 +35343,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1206" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1206" t="n">
         <v>6582</v>
@@ -35372,7 +35372,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1207" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1207" t="n">
         <v>5521</v>
@@ -35401,7 +35401,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>22.8460521697998</v>
+        <v>22.8460540771484</v>
       </c>
       <c r="H1208" t="n">
         <v>5027</v>
@@ -35430,7 +35430,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>22.4604644775391</v>
+        <v>22.4604663848877</v>
       </c>
       <c r="H1209" t="n">
         <v>11525</v>
@@ -35488,7 +35488,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1211" t="n">
-        <v>21.978479385376</v>
+        <v>21.9784812927246</v>
       </c>
       <c r="H1211" t="n">
         <v>20448</v>
@@ -35517,7 +35517,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1212" t="n">
-        <v>21.6410903930664</v>
+        <v>21.641092300415</v>
       </c>
       <c r="H1212" t="n">
         <v>18037</v>
@@ -35575,7 +35575,7 @@
         <v>22.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>21.448299407959</v>
+        <v>21.4482975006104</v>
       </c>
       <c r="H1214" t="n">
         <v>14540</v>
@@ -35662,7 +35662,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>21.54469871521</v>
+        <v>21.5446949005127</v>
       </c>
       <c r="H1217" t="n">
         <v>22396</v>
@@ -35749,7 +35749,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1220" t="n">
-        <v>21.0145111083984</v>
+        <v>21.0145092010498</v>
       </c>
       <c r="H1220" t="n">
         <v>10119</v>
@@ -35836,7 +35836,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1223" t="n">
-        <v>22.1230754852295</v>
+        <v>22.1230773925781</v>
       </c>
       <c r="H1223" t="n">
         <v>10829</v>
@@ -35923,7 +35923,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>21.8820819854736</v>
+        <v>21.8820838928223</v>
       </c>
       <c r="H1226" t="n">
         <v>12138</v>
@@ -36010,7 +36010,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>20.8699188232422</v>
+        <v>20.8699169158936</v>
       </c>
       <c r="H1229" t="n">
         <v>7853</v>
@@ -36068,7 +36068,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>22.0266819000244</v>
+        <v>22.0266799926758</v>
       </c>
       <c r="H1231" t="n">
         <v>7936</v>
@@ -36097,7 +36097,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>22.267671585083</v>
+        <v>22.2676734924316</v>
       </c>
       <c r="H1232" t="n">
         <v>22698</v>
@@ -36213,7 +36213,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1236" t="n">
-        <v>21.978479385376</v>
+        <v>21.9784812927246</v>
       </c>
       <c r="H1236" t="n">
         <v>10509</v>
@@ -36242,7 +36242,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>22.5568599700928</v>
+        <v>22.5568618774414</v>
       </c>
       <c r="H1237" t="n">
         <v>17962</v>
@@ -36271,7 +36271,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>22.9424495697021</v>
+        <v>22.9424476623535</v>
       </c>
       <c r="H1238" t="n">
         <v>43009</v>
@@ -36358,7 +36358,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1241" t="n">
-        <v>24.2438049316406</v>
+        <v>24.2438068389893</v>
       </c>
       <c r="H1241" t="n">
         <v>25874</v>
@@ -36445,7 +36445,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1244" t="n">
-        <v>26.0753440856934</v>
+        <v>26.0753421783447</v>
       </c>
       <c r="H1244" t="n">
         <v>23119</v>
@@ -36474,7 +36474,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>26.894718170166</v>
+        <v>26.8947200775146</v>
       </c>
       <c r="H1245" t="n">
         <v>30372</v>
@@ -36561,7 +36561,7 @@
         <v>27.25</v>
       </c>
       <c r="G1248" t="n">
-        <v>26.2681407928467</v>
+        <v>26.268138885498</v>
       </c>
       <c r="H1248" t="n">
         <v>13949</v>
@@ -36590,7 +36590,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>27.5694961547852</v>
+        <v>27.5694980621338</v>
       </c>
       <c r="H1249" t="n">
         <v>33067</v>
@@ -36706,7 +36706,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>28.8226547241211</v>
+        <v>28.8226566314697</v>
       </c>
       <c r="H1253" t="n">
         <v>18389</v>
@@ -36764,7 +36764,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>30.2686100006104</v>
+        <v>30.2686080932617</v>
       </c>
       <c r="H1255" t="n">
         <v>16774</v>
@@ -36793,7 +36793,7 @@
         <v>31.9500007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>30.7987937927246</v>
+        <v>30.798791885376</v>
       </c>
       <c r="H1256" t="n">
         <v>18704</v>
@@ -36822,7 +36822,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>31.6181640625</v>
+        <v>31.6181659698486</v>
       </c>
       <c r="H1257" t="n">
         <v>36265</v>
@@ -36851,7 +36851,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1258" t="n">
-        <v>31.9073524475098</v>
+        <v>31.907356262207</v>
       </c>
       <c r="H1258" t="n">
         <v>35388</v>
@@ -36880,7 +36880,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1259" t="n">
-        <v>31.4253673553467</v>
+        <v>31.4253730773926</v>
       </c>
       <c r="H1259" t="n">
         <v>20414</v>
@@ -36938,7 +36938,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>31.4253673553467</v>
+        <v>31.4253730773926</v>
       </c>
       <c r="H1261" t="n">
         <v>15477</v>
@@ -36967,7 +36967,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1262" t="n">
-        <v>31.1361808776855</v>
+        <v>31.1361789703369</v>
       </c>
       <c r="H1262" t="n">
         <v>15654</v>
@@ -37025,7 +37025,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1264" t="n">
-        <v>32.1965484619141</v>
+        <v>32.1965446472168</v>
       </c>
       <c r="H1264" t="n">
         <v>51922</v>
@@ -37054,7 +37054,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1265" t="n">
-        <v>31.9073524475098</v>
+        <v>31.907356262207</v>
       </c>
       <c r="H1265" t="n">
         <v>38913</v>
@@ -37112,7 +37112,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>33.0641212463379</v>
+        <v>33.0641174316406</v>
       </c>
       <c r="H1267" t="n">
         <v>28183</v>
@@ -37141,7 +37141,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1268" t="n">
-        <v>32.6785354614258</v>
+        <v>32.6785316467285</v>
       </c>
       <c r="H1268" t="n">
         <v>9658</v>
@@ -37170,7 +37170,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1269" t="n">
-        <v>33.3533096313477</v>
+        <v>33.3533058166504</v>
       </c>
       <c r="H1269" t="n">
         <v>15100</v>
@@ -37228,7 +37228,7 @@
         <v>35.25</v>
       </c>
       <c r="G1271" t="n">
-        <v>33.9798851013184</v>
+        <v>33.9798889160156</v>
       </c>
       <c r="H1271" t="n">
         <v>25245</v>
@@ -37257,7 +37257,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>34.6064682006836</v>
+        <v>34.6064720153809</v>
       </c>
       <c r="H1272" t="n">
         <v>62227</v>
@@ -37286,7 +37286,7 @@
         <v>35.75</v>
       </c>
       <c r="G1273" t="n">
-        <v>34.4618721008301</v>
+        <v>34.4618682861328</v>
       </c>
       <c r="H1273" t="n">
         <v>31684</v>
@@ -37315,7 +37315,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G1274" t="n">
-        <v>35.2330436706543</v>
+        <v>35.2330474853516</v>
       </c>
       <c r="H1274" t="n">
         <v>24175</v>
@@ -37344,7 +37344,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1275" t="n">
-        <v>35.3294410705566</v>
+        <v>35.3294448852539</v>
       </c>
       <c r="H1275" t="n">
         <v>20262</v>
@@ -37431,7 +37431,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>36.0524215698242</v>
+        <v>36.0524253845215</v>
       </c>
       <c r="H1278" t="n">
         <v>107154</v>
@@ -37460,7 +37460,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G1279" t="n">
-        <v>34.1726837158203</v>
+        <v>34.172679901123</v>
       </c>
       <c r="H1279" t="n">
         <v>36895</v>
@@ -37518,7 +37518,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1281" t="n">
-        <v>32.4375381469727</v>
+        <v>32.4375419616699</v>
       </c>
       <c r="H1281" t="n">
         <v>72316</v>
@@ -37547,7 +37547,7 @@
         <v>33.75</v>
       </c>
       <c r="G1282" t="n">
-        <v>32.5339317321777</v>
+        <v>32.533935546875</v>
       </c>
       <c r="H1282" t="n">
         <v>23671</v>
@@ -37605,7 +37605,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1284" t="n">
-        <v>32.5821304321289</v>
+        <v>32.5821342468262</v>
       </c>
       <c r="H1284" t="n">
         <v>18652</v>
@@ -37634,7 +37634,7 @@
         <v>33</v>
       </c>
       <c r="G1285" t="n">
-        <v>31.8109569549561</v>
+        <v>31.8109607696533</v>
       </c>
       <c r="H1285" t="n">
         <v>22631</v>
@@ -37692,7 +37692,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.7023963928223</v>
+        <v>30.7023944854736</v>
       </c>
       <c r="H1287" t="n">
         <v>57334</v>
@@ -37750,7 +37750,7 @@
         <v>31.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>30.3650035858154</v>
+        <v>30.3650054931641</v>
       </c>
       <c r="H1289" t="n">
         <v>48079</v>
@@ -37808,7 +37808,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1291" t="n">
-        <v>32.5821304321289</v>
+        <v>32.5821342468262</v>
       </c>
       <c r="H1291" t="n">
         <v>73551</v>
@@ -37837,7 +37837,7 @@
         <v>33.75</v>
       </c>
       <c r="G1292" t="n">
-        <v>32.5339317321777</v>
+        <v>32.533935546875</v>
       </c>
       <c r="H1292" t="n">
         <v>74097</v>
@@ -37924,7 +37924,7 @@
         <v>35.25</v>
       </c>
       <c r="G1295" t="n">
-        <v>33.9798851013184</v>
+        <v>33.9798889160156</v>
       </c>
       <c r="H1295" t="n">
         <v>54531</v>
@@ -37953,7 +37953,7 @@
         <v>36.4500007629395</v>
       </c>
       <c r="G1296" t="n">
-        <v>35.1366500854492</v>
+        <v>35.136646270752</v>
       </c>
       <c r="H1296" t="n">
         <v>111817</v>
@@ -37982,7 +37982,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G1297" t="n">
-        <v>35.5222320556641</v>
+        <v>35.5222358703613</v>
       </c>
       <c r="H1297" t="n">
         <v>66413</v>
@@ -38040,7 +38040,7 @@
         <v>38.5</v>
       </c>
       <c r="G1299" t="n">
-        <v>37.1127815246582</v>
+        <v>37.1127853393555</v>
       </c>
       <c r="H1299" t="n">
         <v>98764</v>
@@ -38127,7 +38127,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G1302" t="n">
-        <v>35.8114318847656</v>
+        <v>35.8114280700684</v>
       </c>
       <c r="H1302" t="n">
         <v>34863</v>
@@ -38156,7 +38156,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1303" t="n">
-        <v>36.2934150695801</v>
+        <v>36.2934112548828</v>
       </c>
       <c r="H1303" t="n">
         <v>107601</v>
@@ -38214,7 +38214,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1305" t="n">
-        <v>34.8474617004395</v>
+        <v>34.8474578857422</v>
       </c>
       <c r="H1305" t="n">
         <v>28063</v>
@@ -38272,7 +38272,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>36.919994354248</v>
+        <v>36.9199867248535</v>
       </c>
       <c r="H1307" t="n">
         <v>58934</v>
@@ -38301,7 +38301,7 @@
         <v>38.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>37.1127815246582</v>
+        <v>37.1127853393555</v>
       </c>
       <c r="H1308" t="n">
         <v>51626</v>
@@ -38330,7 +38330,7 @@
         <v>38.9000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>37.4983787536621</v>
+        <v>37.4983749389648</v>
       </c>
       <c r="H1309" t="n">
         <v>75548</v>
@@ -38591,7 +38591,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1318" t="n">
-        <v>39.4745025634766</v>
+        <v>39.4745063781738</v>
       </c>
       <c r="H1318" t="n">
         <v>37364</v>
@@ -38620,7 +38620,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>40.2938804626465</v>
+        <v>40.2938766479492</v>
       </c>
       <c r="H1319" t="n">
         <v>66695</v>
@@ -38649,7 +38649,7 @@
         <v>41.5</v>
       </c>
       <c r="G1320" t="n">
-        <v>40.004695892334</v>
+        <v>40.0046920776367</v>
       </c>
       <c r="H1320" t="n">
         <v>55839</v>
@@ -38707,7 +38707,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1322" t="n">
-        <v>40.1010894775391</v>
+        <v>40.1010856628418</v>
       </c>
       <c r="H1322" t="n">
         <v>112558</v>
@@ -38765,7 +38765,7 @@
         <v>43.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>41.7398376464844</v>
+        <v>41.7398338317871</v>
       </c>
       <c r="H1324" t="n">
         <v>124785</v>
@@ -38823,7 +38823,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>41.0168571472168</v>
+        <v>41.0168533325195</v>
       </c>
       <c r="H1326" t="n">
         <v>78966</v>
@@ -38881,7 +38881,7 @@
         <v>43.75</v>
       </c>
       <c r="G1328" t="n">
-        <v>42.1736183166504</v>
+        <v>42.1736221313477</v>
       </c>
       <c r="H1328" t="n">
         <v>56261</v>
@@ -38910,7 +38910,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G1329" t="n">
-        <v>41.8844261169434</v>
+        <v>41.8844299316406</v>
       </c>
       <c r="H1329" t="n">
         <v>51912</v>
@@ -38939,7 +38939,7 @@
         <v>44.0499992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>42.4628067016602</v>
+        <v>42.4628105163574</v>
       </c>
       <c r="H1330" t="n">
         <v>33082</v>
@@ -39026,7 +39026,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>43.330379486084</v>
+        <v>43.3303833007812</v>
       </c>
       <c r="H1333" t="n">
         <v>107887</v>
@@ -39055,7 +39055,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G1334" t="n">
-        <v>43.956958770752</v>
+        <v>43.9569625854492</v>
       </c>
       <c r="H1334" t="n">
         <v>40852</v>
@@ -39084,7 +39084,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>44.535343170166</v>
+        <v>44.5353469848633</v>
       </c>
       <c r="H1335" t="n">
         <v>27530</v>
@@ -39171,7 +39171,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1338" t="n">
-        <v>44.246150970459</v>
+        <v>44.2461547851562</v>
       </c>
       <c r="H1338" t="n">
         <v>80310</v>
@@ -39258,7 +39258,7 @@
         <v>47</v>
       </c>
       <c r="G1341" t="n">
-        <v>45.3065223693848</v>
+        <v>45.3065185546875</v>
       </c>
       <c r="H1341" t="n">
         <v>44501</v>
@@ -39345,7 +39345,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G1344" t="n">
-        <v>44.9691352844238</v>
+        <v>44.9691314697266</v>
       </c>
       <c r="H1344" t="n">
         <v>41720</v>
@@ -39403,7 +39403,7 @@
         <v>46.0999984741211</v>
       </c>
       <c r="G1346" t="n">
-        <v>44.4389419555664</v>
+        <v>44.4389495849609</v>
       </c>
       <c r="H1346" t="n">
         <v>35822</v>
@@ -39432,7 +39432,7 @@
         <v>45.9000015258789</v>
       </c>
       <c r="G1347" t="n">
-        <v>44.246150970459</v>
+        <v>44.2461547851562</v>
       </c>
       <c r="H1347" t="n">
         <v>65693</v>
@@ -39519,7 +39519,7 @@
         <v>45.75</v>
       </c>
       <c r="G1350" t="n">
-        <v>44.1015510559082</v>
+        <v>44.1015548706055</v>
       </c>
       <c r="H1350" t="n">
         <v>26538</v>
@@ -39635,7 +39635,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>43.0893974304199</v>
+        <v>43.0893898010254</v>
       </c>
       <c r="H1354" t="n">
         <v>14472</v>
@@ -39722,7 +39722,7 @@
         <v>44.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>42.896598815918</v>
+        <v>42.8965950012207</v>
       </c>
       <c r="H1357" t="n">
         <v>36274</v>
@@ -39780,7 +39780,7 @@
         <v>44.8499984741211</v>
       </c>
       <c r="G1359" t="n">
-        <v>43.2339859008789</v>
+        <v>43.2339820861816</v>
       </c>
       <c r="H1359" t="n">
         <v>34206</v>
@@ -39838,7 +39838,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G1361" t="n">
-        <v>41.8844261169434</v>
+        <v>41.8844299316406</v>
       </c>
       <c r="H1361" t="n">
         <v>12965</v>
@@ -39896,7 +39896,7 @@
         <v>43.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>42.1736183166504</v>
+        <v>42.1736221313477</v>
       </c>
       <c r="H1363" t="n">
         <v>26881</v>
@@ -39954,7 +39954,7 @@
         <v>41</v>
       </c>
       <c r="G1365" t="n">
-        <v>39.8873901367188</v>
+        <v>39.887393951416</v>
       </c>
       <c r="H1365" t="n">
         <v>77970</v>
@@ -39983,7 +39983,7 @@
         <v>40.75</v>
       </c>
       <c r="G1366" t="n">
-        <v>39.6441764831543</v>
+        <v>39.644172668457</v>
       </c>
       <c r="H1366" t="n">
         <v>41112</v>
@@ -40012,7 +40012,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1367" t="n">
-        <v>39.3036766052246</v>
+        <v>39.3036727905273</v>
       </c>
       <c r="H1367" t="n">
         <v>25479</v>
@@ -40041,7 +40041,7 @@
         <v>40.75</v>
       </c>
       <c r="G1368" t="n">
-        <v>39.6441764831543</v>
+        <v>39.644172668457</v>
       </c>
       <c r="H1368" t="n">
         <v>45883</v>
@@ -40070,7 +40070,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1369" t="n">
-        <v>39.9360313415527</v>
+        <v>39.93603515625</v>
       </c>
       <c r="H1369" t="n">
         <v>31140</v>
@@ -40099,7 +40099,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G1370" t="n">
-        <v>40.7143249511719</v>
+        <v>40.7143287658691</v>
       </c>
       <c r="H1370" t="n">
         <v>49708</v>
@@ -40128,7 +40128,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1371" t="n">
-        <v>39.8387451171875</v>
+        <v>39.8387489318848</v>
       </c>
       <c r="H1371" t="n">
         <v>27182</v>
@@ -40157,7 +40157,7 @@
         <v>41</v>
       </c>
       <c r="G1372" t="n">
-        <v>39.8873901367188</v>
+        <v>39.887393951416</v>
       </c>
       <c r="H1372" t="n">
         <v>57151</v>
@@ -40186,7 +40186,7 @@
         <v>41.75</v>
       </c>
       <c r="G1373" t="n">
-        <v>40.6170387268066</v>
+        <v>40.6170425415039</v>
       </c>
       <c r="H1373" t="n">
         <v>39695</v>
@@ -40273,7 +40273,7 @@
         <v>40.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>39.6441764831543</v>
+        <v>39.644172668457</v>
       </c>
       <c r="H1376" t="n">
         <v>18859</v>
@@ -40302,7 +40302,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1377" t="n">
-        <v>39.7414588928223</v>
+        <v>39.7414627075195</v>
       </c>
       <c r="H1377" t="n">
         <v>20903</v>
@@ -40447,7 +40447,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1382" t="n">
-        <v>39.3036766052246</v>
+        <v>39.3036727905273</v>
       </c>
       <c r="H1382" t="n">
         <v>31729</v>
@@ -40476,7 +40476,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1383" t="n">
-        <v>39.3036766052246</v>
+        <v>39.3036727905273</v>
       </c>
       <c r="H1383" t="n">
         <v>23120</v>
@@ -40534,7 +40534,7 @@
         <v>41</v>
       </c>
       <c r="G1385" t="n">
-        <v>39.8873901367188</v>
+        <v>39.887393951416</v>
       </c>
       <c r="H1385" t="n">
         <v>46942</v>
@@ -40563,7 +40563,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1386" t="n">
-        <v>39.7901077270508</v>
+        <v>39.790111541748</v>
       </c>
       <c r="H1386" t="n">
         <v>56852</v>
@@ -40592,7 +40592,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1387" t="n">
-        <v>39.9360313415527</v>
+        <v>39.93603515625</v>
       </c>
       <c r="H1387" t="n">
         <v>37409</v>
@@ -40621,7 +40621,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1388" t="n">
-        <v>37.7470932006836</v>
+        <v>37.7470893859863</v>
       </c>
       <c r="H1388" t="n">
         <v>324275</v>
@@ -40650,7 +40650,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1389" t="n">
-        <v>36.5796546936035</v>
+        <v>36.5796508789062</v>
       </c>
       <c r="H1389" t="n">
         <v>39179</v>
@@ -40679,7 +40679,7 @@
         <v>38.5</v>
       </c>
       <c r="G1390" t="n">
-        <v>37.4552268981934</v>
+        <v>37.4552307128906</v>
       </c>
       <c r="H1390" t="n">
         <v>47327</v>
@@ -40708,7 +40708,7 @@
         <v>38.5</v>
       </c>
       <c r="G1391" t="n">
-        <v>37.4552268981934</v>
+        <v>37.4552307128906</v>
       </c>
       <c r="H1391" t="n">
         <v>48561</v>
@@ -40737,7 +40737,7 @@
         <v>38.5</v>
       </c>
       <c r="G1392" t="n">
-        <v>37.4552268981934</v>
+        <v>37.4552307128906</v>
       </c>
       <c r="H1392" t="n">
         <v>25297</v>
@@ -40766,7 +40766,7 @@
         <v>39</v>
       </c>
       <c r="G1393" t="n">
-        <v>37.9416656494141</v>
+        <v>37.9416694641113</v>
       </c>
       <c r="H1393" t="n">
         <v>42924</v>
@@ -40795,7 +40795,7 @@
         <v>40.5</v>
       </c>
       <c r="G1394" t="n">
-        <v>39.4009628295898</v>
+        <v>39.4009590148926</v>
       </c>
       <c r="H1394" t="n">
         <v>66821</v>
@@ -40940,7 +40940,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1399" t="n">
-        <v>41.9304008483887</v>
+        <v>41.9304046630859</v>
       </c>
       <c r="H1399" t="n">
         <v>41415</v>
@@ -40969,7 +40969,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>41.2980422973633</v>
+        <v>41.2980461120605</v>
       </c>
       <c r="H1400" t="n">
         <v>19152</v>
@@ -40998,7 +40998,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>40.9088935852051</v>
+        <v>40.9088973999023</v>
       </c>
       <c r="H1401" t="n">
         <v>24304</v>
@@ -41027,7 +41027,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1402" t="n">
-        <v>40.2278900146484</v>
+        <v>40.2278938293457</v>
       </c>
       <c r="H1402" t="n">
         <v>21119</v>
@@ -41056,7 +41056,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1403" t="n">
-        <v>40.276538848877</v>
+        <v>40.2765426635742</v>
       </c>
       <c r="H1403" t="n">
         <v>15210</v>
@@ -41114,7 +41114,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1405" t="n">
-        <v>42.0276870727539</v>
+        <v>42.0276908874512</v>
       </c>
       <c r="H1405" t="n">
         <v>26569</v>
@@ -41143,7 +41143,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>41.8817596435547</v>
+        <v>41.881763458252</v>
       </c>
       <c r="H1406" t="n">
         <v>37750</v>
@@ -41172,7 +41172,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1407" t="n">
-        <v>42.0276870727539</v>
+        <v>42.0276908874512</v>
       </c>
       <c r="H1407" t="n">
         <v>55339</v>
@@ -41259,7 +41259,7 @@
         <v>43.75</v>
       </c>
       <c r="G1410" t="n">
-        <v>42.5627632141113</v>
+        <v>42.5627670288086</v>
       </c>
       <c r="H1410" t="n">
         <v>54135</v>
@@ -41317,7 +41317,7 @@
         <v>46.5</v>
       </c>
       <c r="G1412" t="n">
-        <v>45.2381439208984</v>
+        <v>45.2381401062012</v>
       </c>
       <c r="H1412" t="n">
         <v>68983</v>
@@ -41346,7 +41346,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>46.016429901123</v>
+        <v>46.0164260864258</v>
       </c>
       <c r="H1413" t="n">
         <v>59781</v>
@@ -41375,7 +41375,7 @@
         <v>49</v>
       </c>
       <c r="G1414" t="n">
-        <v>47.6702919006348</v>
+        <v>47.670295715332</v>
       </c>
       <c r="H1414" t="n">
         <v>61055</v>
@@ -41404,7 +41404,7 @@
         <v>48.4500007629395</v>
       </c>
       <c r="G1415" t="n">
-        <v>47.1352233886719</v>
+        <v>47.1352195739746</v>
       </c>
       <c r="H1415" t="n">
         <v>45439</v>
@@ -41491,7 +41491,7 @@
         <v>49.75</v>
       </c>
       <c r="G1418" t="n">
-        <v>48.3999443054199</v>
+        <v>48.3999404907227</v>
       </c>
       <c r="H1418" t="n">
         <v>24032</v>
@@ -41578,7 +41578,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1421" t="n">
-        <v>49.518741607666</v>
+        <v>49.5187339782715</v>
       </c>
       <c r="H1421" t="n">
         <v>34927</v>
@@ -41665,7 +41665,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>49.8106002807617</v>
+        <v>49.8105926513672</v>
       </c>
       <c r="H1424" t="n">
         <v>6244</v>
@@ -41723,7 +41723,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1426" t="n">
-        <v>51.1725997924805</v>
+        <v>51.172607421875</v>
       </c>
       <c r="H1426" t="n">
         <v>29748</v>
@@ -41839,7 +41839,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1430" t="n">
-        <v>49.518741607666</v>
+        <v>49.5187339782715</v>
       </c>
       <c r="H1430" t="n">
         <v>10686</v>
@@ -41897,7 +41897,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>50.2970314025879</v>
+        <v>50.2970275878906</v>
       </c>
       <c r="H1432" t="n">
         <v>17986</v>
@@ -41926,7 +41926,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1433" t="n">
-        <v>49.518741607666</v>
+        <v>49.5187339782715</v>
       </c>
       <c r="H1433" t="n">
         <v>3413</v>
@@ -42013,7 +42013,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1436" t="n">
-        <v>50.0051765441895</v>
+        <v>50.0051727294922</v>
       </c>
       <c r="H1436" t="n">
         <v>6946</v>
@@ -42100,7 +42100,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1439" t="n">
-        <v>50.7834587097168</v>
+        <v>50.7834548950195</v>
       </c>
       <c r="H1439" t="n">
         <v>7107</v>
@@ -42158,7 +42158,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1441" t="n">
-        <v>51.6590309143066</v>
+        <v>51.6590347290039</v>
       </c>
       <c r="H1441" t="n">
         <v>39982</v>
@@ -42187,7 +42187,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>51.7563247680664</v>
+        <v>51.7563285827637</v>
       </c>
       <c r="H1442" t="n">
         <v>11399</v>
@@ -42216,7 +42216,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1443" t="n">
-        <v>50.6861724853516</v>
+        <v>50.6861686706543</v>
       </c>
       <c r="H1443" t="n">
         <v>21751</v>
@@ -42245,7 +42245,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1444" t="n">
-        <v>50.6861724853516</v>
+        <v>50.6861686706543</v>
       </c>
       <c r="H1444" t="n">
         <v>10254</v>
@@ -42506,7 +42506,7 @@
         <v>46</v>
       </c>
       <c r="G1453" t="n">
-        <v>44.751708984375</v>
+        <v>44.7517051696777</v>
       </c>
       <c r="H1453" t="n">
         <v>39412</v>
@@ -42535,7 +42535,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G1454" t="n">
-        <v>43.8761291503906</v>
+        <v>43.8761329650879</v>
       </c>
       <c r="H1454" t="n">
         <v>33818</v>
@@ -42564,7 +42564,7 @@
         <v>44.8499984741211</v>
       </c>
       <c r="G1455" t="n">
-        <v>43.6329193115234</v>
+        <v>43.6329154968262</v>
       </c>
       <c r="H1455" t="n">
         <v>14985</v>
@@ -42709,7 +42709,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>41.0548286437988</v>
+        <v>41.0548324584961</v>
       </c>
       <c r="H1460" t="n">
         <v>78916</v>
@@ -42767,7 +42767,7 @@
         <v>42.75</v>
       </c>
       <c r="G1462" t="n">
-        <v>41.589900970459</v>
+        <v>41.5899047851562</v>
       </c>
       <c r="H1462" t="n">
         <v>18154</v>
@@ -42796,7 +42796,7 @@
         <v>43.75</v>
       </c>
       <c r="G1463" t="n">
-        <v>42.5627632141113</v>
+        <v>42.5627670288086</v>
       </c>
       <c r="H1463" t="n">
         <v>28158</v>
@@ -42825,7 +42825,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>41.8817596435547</v>
+        <v>41.881763458252</v>
       </c>
       <c r="H1464" t="n">
         <v>31910</v>
@@ -42970,7 +42970,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1469" t="n">
-        <v>41.9304008483887</v>
+        <v>41.9304046630859</v>
       </c>
       <c r="H1469" t="n">
         <v>38576</v>
@@ -42999,7 +42999,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1470" t="n">
-        <v>43.0978355407715</v>
+        <v>43.0978393554688</v>
       </c>
       <c r="H1470" t="n">
         <v>62485</v>
@@ -43057,7 +43057,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1472" t="n">
-        <v>44.1679878234863</v>
+        <v>44.1679916381836</v>
       </c>
       <c r="H1472" t="n">
         <v>20722</v>
@@ -43086,7 +43086,7 @@
         <v>46.5499992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>45.2867774963379</v>
+        <v>45.2867813110352</v>
       </c>
       <c r="H1473" t="n">
         <v>63603</v>
@@ -43231,7 +43231,7 @@
         <v>46.8499984741211</v>
       </c>
       <c r="G1478" t="n">
-        <v>45.5786437988281</v>
+        <v>45.5786399841309</v>
       </c>
       <c r="H1478" t="n">
         <v>14381</v>
@@ -43260,7 +43260,7 @@
         <v>46.8499984741211</v>
       </c>
       <c r="G1479" t="n">
-        <v>45.5786437988281</v>
+        <v>45.5786399841309</v>
       </c>
       <c r="H1479" t="n">
         <v>52522</v>
@@ -43289,7 +43289,7 @@
         <v>46.5</v>
       </c>
       <c r="G1480" t="n">
-        <v>45.2381439208984</v>
+        <v>45.2381401062012</v>
       </c>
       <c r="H1480" t="n">
         <v>55647</v>
@@ -43318,7 +43318,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>42.6114082336426</v>
+        <v>42.6114120483398</v>
       </c>
       <c r="H1481" t="n">
         <v>24016</v>
@@ -43434,7 +43434,7 @@
         <v>42.0499992370605</v>
       </c>
       <c r="G1485" t="n">
-        <v>40.9088935852051</v>
+        <v>40.9088973999023</v>
       </c>
       <c r="H1485" t="n">
         <v>22787</v>
@@ -43550,7 +43550,7 @@
         <v>43.4500007629395</v>
       </c>
       <c r="G1489" t="n">
-        <v>42.2709083557129</v>
+        <v>42.2709121704102</v>
       </c>
       <c r="H1489" t="n">
         <v>16907</v>
@@ -43724,7 +43724,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1495" t="n">
-        <v>39.7414588928223</v>
+        <v>39.7414627075195</v>
       </c>
       <c r="H1495" t="n">
         <v>37033</v>
@@ -43811,7 +43811,7 @@
         <v>40</v>
       </c>
       <c r="G1498" t="n">
-        <v>38.9145278930664</v>
+        <v>38.9145240783691</v>
       </c>
       <c r="H1498" t="n">
         <v>46418</v>
@@ -43840,7 +43840,7 @@
         <v>41</v>
       </c>
       <c r="G1499" t="n">
-        <v>39.8873901367188</v>
+        <v>39.887393951416</v>
       </c>
       <c r="H1499" t="n">
         <v>29821</v>
@@ -43898,7 +43898,7 @@
         <v>40.5</v>
       </c>
       <c r="G1501" t="n">
-        <v>39.4009628295898</v>
+        <v>39.4009590148926</v>
       </c>
       <c r="H1501" t="n">
         <v>21617</v>
@@ -43927,7 +43927,7 @@
         <v>41.75</v>
       </c>
       <c r="G1502" t="n">
-        <v>40.6170387268066</v>
+        <v>40.6170425415039</v>
       </c>
       <c r="H1502" t="n">
         <v>10130</v>
@@ -43956,7 +43956,7 @@
         <v>41</v>
       </c>
       <c r="G1503" t="n">
-        <v>39.8873901367188</v>
+        <v>39.887393951416</v>
       </c>
       <c r="H1503" t="n">
         <v>26477</v>
@@ -44014,7 +44014,7 @@
         <v>41.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>40.3738250732422</v>
+        <v>40.3738212585449</v>
       </c>
       <c r="H1505" t="n">
         <v>49113</v>
@@ -44043,7 +44043,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G1506" t="n">
-        <v>40.276538848877</v>
+        <v>40.2765426635742</v>
       </c>
       <c r="H1506" t="n">
         <v>30676</v>
@@ -44130,7 +44130,7 @@
         <v>41.5</v>
       </c>
       <c r="G1509" t="n">
-        <v>40.3738250732422</v>
+        <v>40.3738212585449</v>
       </c>
       <c r="H1509" t="n">
         <v>12765</v>
@@ -44246,7 +44246,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1513" t="n">
-        <v>40.9575347900391</v>
+        <v>40.9575386047363</v>
       </c>
       <c r="H1513" t="n">
         <v>51618</v>
@@ -44304,7 +44304,7 @@
         <v>41.75</v>
       </c>
       <c r="G1515" t="n">
-        <v>40.6170387268066</v>
+        <v>40.6170425415039</v>
       </c>
       <c r="H1515" t="n">
         <v>36647</v>
@@ -44420,7 +44420,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>39.8387451171875</v>
+        <v>39.8387489318848</v>
       </c>
       <c r="H1519" t="n">
         <v>22656</v>
@@ -44449,7 +44449,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1520" t="n">
-        <v>40.2278900146484</v>
+        <v>40.2278938293457</v>
       </c>
       <c r="H1520" t="n">
         <v>5882</v>
@@ -44478,7 +44478,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1521" t="n">
-        <v>41.4439735412598</v>
+        <v>41.443977355957</v>
       </c>
       <c r="H1521" t="n">
         <v>7723</v>
@@ -44507,7 +44507,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1522" t="n">
-        <v>41.9304008483887</v>
+        <v>41.9304046630859</v>
       </c>
       <c r="H1522" t="n">
         <v>10672</v>
@@ -44565,7 +44565,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1524" t="n">
-        <v>42.6114082336426</v>
+        <v>42.6114120483398</v>
       </c>
       <c r="H1524" t="n">
         <v>8134</v>
@@ -44594,7 +44594,7 @@
         <v>44</v>
       </c>
       <c r="G1525" t="n">
-        <v>42.8059844970703</v>
+        <v>42.805980682373</v>
       </c>
       <c r="H1525" t="n">
         <v>10586</v>
@@ -44623,7 +44623,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>43.0978355407715</v>
+        <v>43.0978393554688</v>
       </c>
       <c r="H1526" t="n">
         <v>10749</v>
@@ -44739,7 +44739,7 @@
         <v>41.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>40.3738250732422</v>
+        <v>40.3738212585449</v>
       </c>
       <c r="H1530" t="n">
         <v>14734</v>
@@ -44797,7 +44797,7 @@
         <v>41</v>
       </c>
       <c r="G1532" t="n">
-        <v>39.8873901367188</v>
+        <v>39.887393951416</v>
       </c>
       <c r="H1532" t="n">
         <v>28911</v>
@@ -44826,7 +44826,7 @@
         <v>41</v>
       </c>
       <c r="G1533" t="n">
-        <v>39.8873901367188</v>
+        <v>39.887393951416</v>
       </c>
       <c r="H1533" t="n">
         <v>23270</v>
@@ -44942,7 +44942,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1537" t="n">
-        <v>42.7086944580078</v>
+        <v>42.7087020874023</v>
       </c>
       <c r="H1537" t="n">
         <v>33304</v>
@@ -45029,7 +45029,7 @@
         <v>45.0499992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>43.8274841308594</v>
+        <v>43.8274879455566</v>
       </c>
       <c r="H1540" t="n">
         <v>27354</v>
@@ -45116,7 +45116,7 @@
         <v>40</v>
       </c>
       <c r="G1543" t="n">
-        <v>38.9145278930664</v>
+        <v>38.9145240783691</v>
       </c>
       <c r="H1543" t="n">
         <v>51335</v>
@@ -45145,7 +45145,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1544" t="n">
-        <v>39.7414588928223</v>
+        <v>39.7414627075195</v>
       </c>
       <c r="H1544" t="n">
         <v>32434</v>
@@ -45203,7 +45203,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G1546" t="n">
-        <v>38.9631729125977</v>
+        <v>38.9631690979004</v>
       </c>
       <c r="H1546" t="n">
         <v>41584</v>
@@ -45232,7 +45232,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1547" t="n">
-        <v>40.9575347900391</v>
+        <v>40.9575386047363</v>
       </c>
       <c r="H1547" t="n">
         <v>31413</v>
@@ -45319,7 +45319,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1550" t="n">
-        <v>41.9304008483887</v>
+        <v>41.9304046630859</v>
       </c>
       <c r="H1550" t="n">
         <v>18406</v>
@@ -45348,7 +45348,7 @@
         <v>41.75</v>
       </c>
       <c r="G1551" t="n">
-        <v>40.6170387268066</v>
+        <v>40.6170425415039</v>
       </c>
       <c r="H1551" t="n">
         <v>25686</v>
@@ -45377,7 +45377,7 @@
         <v>39.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>38.4280967712402</v>
+        <v>38.428092956543</v>
       </c>
       <c r="H1552" t="n">
         <v>54803</v>
@@ -45406,7 +45406,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1553" t="n">
-        <v>36.2877998352051</v>
+        <v>36.2877960205078</v>
       </c>
       <c r="H1553" t="n">
         <v>92254</v>
@@ -45464,7 +45464,7 @@
         <v>38</v>
       </c>
       <c r="G1555" t="n">
-        <v>36.9687995910645</v>
+        <v>36.9688034057617</v>
       </c>
       <c r="H1555" t="n">
         <v>44471</v>
@@ -45551,7 +45551,7 @@
         <v>36.4500007629395</v>
       </c>
       <c r="G1558" t="n">
-        <v>35.460865020752</v>
+        <v>35.4608612060547</v>
       </c>
       <c r="H1558" t="n">
         <v>56945</v>
@@ -45580,7 +45580,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>36.5796546936035</v>
+        <v>36.5796508789062</v>
       </c>
       <c r="H1559" t="n">
         <v>38770</v>
@@ -45609,7 +45609,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1560" t="n">
-        <v>36.385082244873</v>
+        <v>36.3850860595703</v>
       </c>
       <c r="H1560" t="n">
         <v>42191</v>
@@ -45725,7 +45725,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>35.3149337768555</v>
+        <v>35.3149299621582</v>
       </c>
       <c r="H1564" t="n">
         <v>19114</v>
@@ -45783,7 +45783,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>35.3149337768555</v>
+        <v>35.3149299621582</v>
       </c>
       <c r="H1566" t="n">
         <v>30539</v>
@@ -45841,7 +45841,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G1568" t="n">
-        <v>35.2176475524902</v>
+        <v>35.2176513671875</v>
       </c>
       <c r="H1568" t="n">
         <v>33386</v>
@@ -45957,7 +45957,7 @@
         <v>32.25</v>
       </c>
       <c r="G1572" t="n">
-        <v>31.3748378753662</v>
+        <v>31.3748397827148</v>
       </c>
       <c r="H1572" t="n">
         <v>36177</v>
@@ -46015,7 +46015,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1574" t="n">
-        <v>32.8827743530273</v>
+        <v>32.8827781677246</v>
       </c>
       <c r="H1574" t="n">
         <v>38290</v>
@@ -46073,7 +46073,7 @@
         <v>34.25</v>
       </c>
       <c r="G1576" t="n">
-        <v>33.3205642700195</v>
+        <v>33.3205604553223</v>
       </c>
       <c r="H1576" t="n">
         <v>15592</v>
@@ -46131,7 +46131,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1578" t="n">
-        <v>34.4393577575684</v>
+        <v>34.4393615722656</v>
       </c>
       <c r="H1578" t="n">
         <v>28640</v>
@@ -46276,7 +46276,7 @@
         <v>33.75</v>
       </c>
       <c r="G1583" t="n">
-        <v>32.8341331481934</v>
+        <v>32.8341369628906</v>
       </c>
       <c r="H1583" t="n">
         <v>27565</v>
@@ -46305,7 +46305,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1584" t="n">
-        <v>32.3963432312012</v>
+        <v>32.3963470458984</v>
       </c>
       <c r="H1584" t="n">
         <v>32763</v>
@@ -46392,7 +46392,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1587" t="n">
-        <v>31.3261966705322</v>
+        <v>31.3261985778809</v>
       </c>
       <c r="H1587" t="n">
         <v>59769</v>
@@ -46450,7 +46450,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1589" t="n">
-        <v>32.6395645141602</v>
+        <v>32.6395606994629</v>
       </c>
       <c r="H1589" t="n">
         <v>48764</v>
@@ -46595,7 +46595,7 @@
         <v>30.3600006103516</v>
       </c>
       <c r="G1594" t="n">
-        <v>29.5361270904541</v>
+        <v>29.5361289978027</v>
       </c>
       <c r="H1594" t="n">
         <v>31465</v>
@@ -46682,7 +46682,7 @@
         <v>32.8400001525879</v>
       </c>
       <c r="G1597" t="n">
-        <v>31.9488296508789</v>
+        <v>31.9488258361816</v>
       </c>
       <c r="H1597" t="n">
         <v>27447</v>
@@ -46740,7 +46740,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1599" t="n">
-        <v>31.209451675415</v>
+        <v>31.2094535827637</v>
       </c>
       <c r="H1599" t="n">
         <v>80880</v>
@@ -46798,7 +46798,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G1601" t="n">
-        <v>31.2678241729736</v>
+        <v>31.267822265625</v>
       </c>
       <c r="H1601" t="n">
         <v>57698</v>
@@ -46827,7 +46827,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1602" t="n">
-        <v>31.5402240753174</v>
+        <v>31.5402221679688</v>
       </c>
       <c r="H1602" t="n">
         <v>31293</v>
@@ -46943,7 +46943,7 @@
         <v>29.0599994659424</v>
       </c>
       <c r="G1606" t="n">
-        <v>28.2714042663574</v>
+        <v>28.2714061737061</v>
       </c>
       <c r="H1606" t="n">
         <v>28018</v>
@@ -47059,7 +47059,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1610" t="n">
-        <v>28.7578353881836</v>
+        <v>28.7578372955322</v>
       </c>
       <c r="H1610" t="n">
         <v>28739</v>
@@ -47088,7 +47088,7 @@
         <v>29.6200008392334</v>
       </c>
       <c r="G1611" t="n">
-        <v>28.8162117004395</v>
+        <v>28.8162097930908</v>
       </c>
       <c r="H1611" t="n">
         <v>12002</v>
@@ -47146,7 +47146,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1613" t="n">
-        <v>28.1935729980469</v>
+        <v>28.1935749053955</v>
       </c>
       <c r="H1613" t="n">
         <v>25386</v>
@@ -47262,7 +47262,7 @@
         <v>29.2800006866455</v>
       </c>
       <c r="G1617" t="n">
-        <v>28.4854354858398</v>
+        <v>28.4854373931885</v>
       </c>
       <c r="H1617" t="n">
         <v>31648</v>
@@ -80125,6 +80125,35 @@
         <v>19756</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>33.8499984741211</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>34.2000007629395</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>32.6500015258789</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>33.4000015258789</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>33.4000015258789</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>68526</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>
